--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="203">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260822--01</t>
-  </si>
-  <si>
-    <t>20260822--02</t>
-  </si>
-  <si>
-    <t>20260822--03</t>
-  </si>
-  <si>
     <t>20260823--01</t>
   </si>
   <si>
@@ -136,19 +127,19 @@
     <t>20260828--02</t>
   </si>
   <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>04:37</t>
+    <t>20260829--01</t>
+  </si>
+  <si>
+    <t>20260829--02</t>
+  </si>
+  <si>
+    <t>20260829--03</t>
   </si>
   <si>
     <t>04:18</t>
   </si>
   <si>
-    <t>06:34</t>
+    <t>06:33</t>
   </si>
   <si>
     <t>05:35</t>
@@ -160,7 +151,7 @@
     <t>02:17</t>
   </si>
   <si>
-    <t>06:39</t>
+    <t>06:38</t>
   </si>
   <si>
     <t>06:19</t>
@@ -172,7 +163,7 @@
     <t>06:35</t>
   </si>
   <si>
-    <t>02:30</t>
+    <t>02:29</t>
   </si>
   <si>
     <t>05:37</t>
@@ -181,10 +172,10 @@
     <t>05:47</t>
   </si>
   <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>04:29</t>
+    <t>04:23</t>
+  </si>
+  <si>
+    <t>04:28</t>
   </si>
   <si>
     <t>06:28</t>
@@ -199,39 +190,33 @@
     <t>06:37</t>
   </si>
   <si>
-    <t>02:55</t>
-  </si>
-  <si>
-    <t>01:09</t>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>03:48</t>
+  </si>
+  <si>
+    <t>02:08</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:01</t>
-  </si>
-  <si>
-    <t>04:35</t>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>04:34</t>
   </si>
   <si>
     <t>00:23</t>
   </si>
   <si>
-    <t>04:20</t>
+    <t>04:19</t>
   </si>
   <si>
     <t>00:54</t>
   </si>
   <si>
-    <t>04:30:36</t>
-  </si>
-  <si>
-    <t>21:08:04</t>
-  </si>
-  <si>
-    <t>22:45:54</t>
-  </si>
-  <si>
     <t>03:41:22</t>
   </si>
   <si>
@@ -274,7 +259,7 @@
     <t>21:05:09</t>
   </si>
   <si>
-    <t>02:00:30</t>
+    <t>02:00:31</t>
   </si>
   <si>
     <t>03:37:26</t>
@@ -289,13 +274,13 @@
     <t>02:47:44</t>
   </si>
   <si>
-    <t>04:32:58</t>
-  </si>
-  <si>
-    <t>21:10:11</t>
-  </si>
-  <si>
-    <t>22:48:28</t>
+    <t>01:58:03</t>
+  </si>
+  <si>
+    <t>03:35:42</t>
+  </si>
+  <si>
+    <t>20:13:46</t>
   </si>
   <si>
     <t>03:44:04</t>
@@ -337,13 +322,13 @@
     <t>04:29:27</t>
   </si>
   <si>
-    <t>21:07:47</t>
-  </si>
-  <si>
-    <t>02:03:08</t>
-  </si>
-  <si>
-    <t>03:39:33</t>
+    <t>21:07:48</t>
+  </si>
+  <si>
+    <t>02:03:09</t>
+  </si>
+  <si>
+    <t>03:39:34</t>
   </si>
   <si>
     <t>20:17:25</t>
@@ -355,19 +340,19 @@
     <t>02:49:50</t>
   </si>
   <si>
-    <t>04:35:43</t>
-  </si>
-  <si>
-    <t>21:13:22</t>
-  </si>
-  <si>
-    <t>22:50:46</t>
+    <t>02:00:13</t>
+  </si>
+  <si>
+    <t>03:38:28</t>
+  </si>
+  <si>
+    <t>20:17:10</t>
   </si>
   <si>
     <t>03:46:13</t>
   </si>
   <si>
-    <t>05:23:41</t>
+    <t>05:23:40</t>
   </si>
   <si>
     <t>20:24:02</t>
@@ -397,7 +382,7 @@
     <t>21:59:47</t>
   </si>
   <si>
-    <t>02:55:08</t>
+    <t>02:55:07</t>
   </si>
   <si>
     <t>04:32:20</t>
@@ -409,7 +394,7 @@
     <t>02:05:23</t>
   </si>
   <si>
-    <t>03:42:47</t>
+    <t>03:42:48</t>
   </si>
   <si>
     <t>20:20:11</t>
@@ -418,22 +403,22 @@
     <t>01:15:31</t>
   </si>
   <si>
-    <t>02:53:08</t>
-  </si>
-  <si>
-    <t>04:38:28</t>
-  </si>
-  <si>
-    <t>21:16:33</t>
-  </si>
-  <si>
-    <t>22:53:05</t>
+    <t>02:53:09</t>
+  </si>
+  <si>
+    <t>02:03:23</t>
+  </si>
+  <si>
+    <t>03:40:22</t>
+  </si>
+  <si>
+    <t>20:18:14</t>
   </si>
   <si>
     <t>03:48:22</t>
   </si>
   <si>
-    <t>05:26:58</t>
+    <t>05:26:57</t>
   </si>
   <si>
     <t>20:26:50</t>
@@ -445,166 +430,166 @@
     <t>02:57:44</t>
   </si>
   <si>
+    <t>04:37:35</t>
+  </si>
+  <si>
+    <t>21:14:51</t>
+  </si>
+  <si>
+    <t>03:47:55</t>
+  </si>
+  <si>
+    <t>05:23:52</t>
+  </si>
+  <si>
+    <t>20:25:26</t>
+  </si>
+  <si>
+    <t>22:01:01</t>
+  </si>
+  <si>
+    <t>02:57:56</t>
+  </si>
+  <si>
+    <t>04:35:14</t>
+  </si>
+  <si>
+    <t>21:12:11</t>
+  </si>
+  <si>
+    <t>02:07:37</t>
+  </si>
+  <si>
+    <t>03:46:02</t>
+  </si>
+  <si>
+    <t>20:22:58</t>
+  </si>
+  <si>
+    <t>01:16:49</t>
+  </si>
+  <si>
+    <t>02:56:27</t>
+  </si>
+  <si>
+    <t>02:06:33</t>
+  </si>
+  <si>
+    <t>03:42:16</t>
+  </si>
+  <si>
+    <t>20:19:18</t>
+  </si>
+  <si>
+    <t>03:51:03</t>
+  </si>
+  <si>
+    <t>05:29:04</t>
+  </si>
+  <si>
+    <t>20:29:08</t>
+  </si>
+  <si>
+    <t>22:06:23</t>
+  </si>
+  <si>
+    <t>03:01:06</t>
+  </si>
+  <si>
+    <t>04:39:42</t>
+  </si>
+  <si>
+    <t>21:17:01</t>
+  </si>
+  <si>
+    <t>03:50:05</t>
+  </si>
+  <si>
+    <t>05:26:33</t>
+  </si>
+  <si>
+    <t>20:27:32</t>
+  </si>
+  <si>
+    <t>22:04:18</t>
+  </si>
+  <si>
+    <t>03:00:16</t>
+  </si>
+  <si>
+    <t>04:37:30</t>
+  </si>
+  <si>
+    <t>21:14:50</t>
+  </si>
+  <si>
+    <t>02:10:15</t>
+  </si>
+  <si>
+    <t>03:48:09</t>
+  </si>
+  <si>
+    <t>20:25:19</t>
+  </si>
+  <si>
+    <t>01:20:03</t>
+  </si>
+  <si>
+    <t>02:58:33</t>
+  </si>
+  <si>
+    <t>02:08:43</t>
+  </si>
+  <si>
+    <t>03:45:03</t>
+  </si>
+  <si>
+    <t>20:22:42</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>45°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>03:49:59</t>
+  </si>
+  <si>
+    <t>05:22:57</t>
+  </si>
+  <si>
+    <t>20:25:49</t>
+  </si>
+  <si>
+    <t>21:58:47</t>
+  </si>
+  <si>
     <t>04:37:36</t>
   </si>
   <si>
-    <t>21:14:51</t>
-  </si>
-  <si>
-    <t>03:47:55</t>
-  </si>
-  <si>
-    <t>05:23:52</t>
-  </si>
-  <si>
-    <t>20:25:26</t>
-  </si>
-  <si>
-    <t>22:01:02</t>
-  </si>
-  <si>
-    <t>02:57:56</t>
-  </si>
-  <si>
-    <t>04:35:14</t>
-  </si>
-  <si>
-    <t>21:12:11</t>
-  </si>
-  <si>
-    <t>02:07:37</t>
-  </si>
-  <si>
-    <t>03:46:01</t>
-  </si>
-  <si>
-    <t>20:22:58</t>
-  </si>
-  <si>
-    <t>01:16:49</t>
-  </si>
-  <si>
-    <t>02:56:27</t>
-  </si>
-  <si>
-    <t>04:40:51</t>
-  </si>
-  <si>
-    <t>21:18:41</t>
-  </si>
-  <si>
-    <t>22:55:40</t>
-  </si>
-  <si>
-    <t>03:51:04</t>
-  </si>
-  <si>
-    <t>05:29:05</t>
-  </si>
-  <si>
-    <t>20:29:08</t>
-  </si>
-  <si>
-    <t>22:06:23</t>
-  </si>
-  <si>
-    <t>03:01:06</t>
-  </si>
-  <si>
-    <t>04:39:42</t>
-  </si>
-  <si>
-    <t>21:17:01</t>
-  </si>
-  <si>
-    <t>03:50:05</t>
-  </si>
-  <si>
-    <t>05:26:33</t>
-  </si>
-  <si>
-    <t>20:27:32</t>
-  </si>
-  <si>
-    <t>22:04:18</t>
-  </si>
-  <si>
-    <t>03:00:16</t>
-  </si>
-  <si>
-    <t>04:37:30</t>
-  </si>
-  <si>
-    <t>21:14:50</t>
-  </si>
-  <si>
-    <t>02:10:15</t>
-  </si>
-  <si>
-    <t>03:48:09</t>
-  </si>
-  <si>
-    <t>20:25:19</t>
-  </si>
-  <si>
-    <t>01:20:02</t>
-  </si>
-  <si>
-    <t>02:58:33</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>45°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>04:35:33</t>
-  </si>
-  <si>
-    <t>21:11:20</t>
-  </si>
-  <si>
-    <t>03:49:59</t>
-  </si>
-  <si>
-    <t>05:22:57</t>
-  </si>
-  <si>
-    <t>20:25:50</t>
-  </si>
-  <si>
-    <t>21:58:47</t>
-  </si>
-  <si>
-    <t>21:12:52</t>
+    <t>21:12:51</t>
   </si>
   <si>
     <t>05:25:16</t>
@@ -619,19 +604,19 @@
     <t>21:12:42</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -686,7 +671,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,31 +689,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,13 +713,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1316,7 +1301,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>40</v>
@@ -1325,45 +1310,45 @@
         <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L2" s="4">
-        <v>-26</v>
+        <v>-34.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1372,7 +1357,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>41</v>
@@ -1381,45 +1366,45 @@
         <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L3" s="4">
-        <v>-20.5</v>
+        <v>-16.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O3" s="8">
-        <v>23</v>
-      </c>
-      <c r="P3" s="9">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+        <v>200</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1428,7 +1413,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>42</v>
@@ -1437,45 +1422,45 @@
         <v>63</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="L4" s="4">
-        <v>-38</v>
+        <v>-10.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O4" s="8">
-        <v>25</v>
-      </c>
-      <c r="P4" s="10">
-        <v>20</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
+        <v>200</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1484,55 +1469,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L5" s="4">
-        <v>-34.9</v>
+        <v>-29.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="O5" s="9">
+        <v>4</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1540,54 +1525,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="L6" s="4">
-        <v>-16.8</v>
+        <v>-42.7</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1596,54 +1581,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L7" s="4">
-        <v>-10.8</v>
+        <v>-26.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O7" s="8">
-        <v>26</v>
-      </c>
-      <c r="P7" s="11">
-        <v>12</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+        <v>199</v>
+      </c>
+      <c r="O7" s="11">
+        <v>34</v>
+      </c>
+      <c r="P7" s="12">
+        <v>34</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1652,54 +1637,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L8" s="4">
-        <v>-29.9</v>
+        <v>-20.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
+        <v>200</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1708,54 +1693,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>181</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L9" s="4">
-        <v>-42.7</v>
+        <v>-35.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
+        <v>199</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1764,54 +1749,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="L10" s="4">
-        <v>-26.5</v>
+        <v>-17.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
+        <v>199</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1820,54 +1805,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="L11" s="4">
-        <v>-20.8</v>
+        <v>-11</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
+        <v>202</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1876,54 +1861,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="L12" s="4">
-        <v>-35.6</v>
+        <v>-30.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
+        <v>201</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1932,54 +1917,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="L13" s="4">
-        <v>-17.3</v>
+        <v>-43.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
+        <v>199</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1988,54 +1973,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="L14" s="4">
-        <v>-11</v>
+        <v>-27.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7">
+        <v>199</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2044,54 +2029,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L15" s="4">
-        <v>-30.2</v>
+        <v>-21</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7">
+        <v>34</v>
+      </c>
+      <c r="P15" s="12">
+        <v>34</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2100,54 +2085,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>181</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L16" s="4">
-        <v>-43.4</v>
+        <v>-49.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O16" s="8">
-        <v>18</v>
-      </c>
-      <c r="P16" s="10">
-        <v>18</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7">
+        <v>199</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2156,54 +2141,54 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>181</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L17" s="4">
-        <v>-27.3</v>
+        <v>-36.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O17" s="8">
-        <v>23</v>
-      </c>
-      <c r="P17" s="12">
-        <v>23</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7">
+        <v>199</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2212,54 +2197,54 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-10.9</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="L18" s="4">
-        <v>-21</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O18" s="8">
-        <v>15</v>
-      </c>
-      <c r="P18" s="9">
-        <v>15</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7">
+      <c r="O18" s="11">
+        <v>63</v>
+      </c>
+      <c r="P18" s="13">
+        <v>61</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2268,54 +2253,54 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>181</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L19" s="4">
-        <v>-49.1</v>
+        <v>-51.9</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O19" s="13">
-        <v>37</v>
+        <v>201</v>
+      </c>
+      <c r="O19" s="11">
+        <v>66</v>
       </c>
       <c r="P19" s="14">
-        <v>37</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7">
+        <v>66</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2324,54 +2309,54 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>181</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L20" s="4">
-        <v>-36.4</v>
+        <v>-44.2</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O20" s="13">
-        <v>42</v>
-      </c>
-      <c r="P20" s="15">
-        <v>42</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
+        <v>199</v>
+      </c>
+      <c r="O20" s="11">
+        <v>58</v>
+      </c>
+      <c r="P20" s="13">
+        <v>58</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2380,54 +2365,54 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="L21" s="4">
-        <v>-10.9</v>
+        <v>-49.9</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O21" s="13">
-        <v>73</v>
-      </c>
-      <c r="P21" s="16">
-        <v>59</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>0</v>
-      </c>
-      <c r="R21" s="7">
+        <v>199</v>
+      </c>
+      <c r="O21" s="11">
+        <v>49</v>
+      </c>
+      <c r="P21" s="15">
+        <v>49</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2436,54 +2421,54 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>181</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L22" s="4">
-        <v>-51.9</v>
+        <v>-37.2</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O22" s="8">
-        <v>38</v>
-      </c>
-      <c r="P22" s="15">
-        <v>38</v>
-      </c>
-      <c r="Q22" s="7">
-        <v>0</v>
-      </c>
-      <c r="R22" s="7">
+        <v>201</v>
+      </c>
+      <c r="O22" s="11">
+        <v>43</v>
+      </c>
+      <c r="P22" s="16">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2492,54 +2477,54 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="L23" s="4">
-        <v>-44.2</v>
+        <v>-11</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O23" s="13">
-        <v>41</v>
-      </c>
-      <c r="P23" s="15">
-        <v>41</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>0</v>
-      </c>
-      <c r="R23" s="7">
+        <v>201</v>
+      </c>
+      <c r="O23" s="9">
+        <v>3</v>
+      </c>
+      <c r="P23" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
         <v>0</v>
       </c>
     </row>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="180">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260823--01</t>
-  </si>
-  <si>
-    <t>20260823--02</t>
-  </si>
-  <si>
-    <t>20260823--03</t>
-  </si>
-  <si>
-    <t>20260823--04</t>
-  </si>
-  <si>
     <t>20260824--01</t>
   </si>
   <si>
@@ -136,16 +124,10 @@
     <t>20260829--03</t>
   </si>
   <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>06:33</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>05:40</t>
+    <t>20260830--01</t>
+  </si>
+  <si>
+    <t>20260830--02</t>
   </si>
   <si>
     <t>02:17</t>
@@ -157,13 +139,16 @@
     <t>06:19</t>
   </si>
   <si>
-    <t>04:10</t>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>04:11</t>
   </si>
   <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>02:29</t>
+    <t>02:30</t>
   </si>
   <si>
     <t>05:37</t>
@@ -172,7 +157,7 @@
     <t>05:47</t>
   </si>
   <si>
-    <t>04:23</t>
+    <t>04:24</t>
   </si>
   <si>
     <t>04:28</t>
@@ -181,10 +166,10 @@
     <t>06:28</t>
   </si>
   <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>02:36</t>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>02:35</t>
   </si>
   <si>
     <t>06:37</t>
@@ -199,36 +184,18 @@
     <t>02:08</t>
   </si>
   <si>
+    <t>05:41</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>00:23</t>
-  </si>
-  <si>
     <t>04:19</t>
   </si>
   <si>
     <t>00:54</t>
   </si>
   <si>
-    <t>03:41:22</t>
-  </si>
-  <si>
-    <t>05:18:17</t>
-  </si>
-  <si>
-    <t>20:18:58</t>
-  </si>
-  <si>
-    <t>21:56:06</t>
-  </si>
-  <si>
     <t>02:52:06</t>
   </si>
   <si>
@@ -244,55 +211,49 @@
     <t>05:17:01</t>
   </si>
   <si>
-    <t>20:16:46</t>
-  </si>
-  <si>
-    <t>21:55:17</t>
-  </si>
-  <si>
-    <t>02:49:59</t>
-  </si>
-  <si>
-    <t>04:27:11</t>
-  </si>
-  <si>
-    <t>21:05:09</t>
-  </si>
-  <si>
-    <t>02:00:31</t>
-  </si>
-  <si>
-    <t>03:37:26</t>
-  </si>
-  <si>
-    <t>20:15:05</t>
-  </si>
-  <si>
-    <t>01:10:59</t>
-  </si>
-  <si>
-    <t>02:47:44</t>
-  </si>
-  <si>
-    <t>01:58:03</t>
-  </si>
-  <si>
-    <t>03:35:42</t>
-  </si>
-  <si>
-    <t>20:13:46</t>
-  </si>
-  <si>
-    <t>03:44:04</t>
-  </si>
-  <si>
-    <t>05:20:24</t>
-  </si>
-  <si>
-    <t>20:21:15</t>
-  </si>
-  <si>
-    <t>21:58:24</t>
+    <t>20:16:45</t>
+  </si>
+  <si>
+    <t>21:55:16</t>
+  </si>
+  <si>
+    <t>02:49:58</t>
+  </si>
+  <si>
+    <t>04:27:10</t>
+  </si>
+  <si>
+    <t>21:05:08</t>
+  </si>
+  <si>
+    <t>02:00:29</t>
+  </si>
+  <si>
+    <t>03:37:25</t>
+  </si>
+  <si>
+    <t>20:15:03</t>
+  </si>
+  <si>
+    <t>01:10:57</t>
+  </si>
+  <si>
+    <t>02:47:42</t>
+  </si>
+  <si>
+    <t>01:58:00</t>
+  </si>
+  <si>
+    <t>03:35:39</t>
+  </si>
+  <si>
+    <t>20:13:42</t>
+  </si>
+  <si>
+    <t>01:08:17</t>
+  </si>
+  <si>
+    <t>02:45:30</t>
   </si>
   <si>
     <t>02:55:27</t>
@@ -307,61 +268,55 @@
     <t>03:41:36</t>
   </si>
   <si>
-    <t>05:19:42</t>
-  </si>
-  <si>
-    <t>20:18:51</t>
-  </si>
-  <si>
-    <t>21:58:32</t>
-  </si>
-  <si>
-    <t>02:52:19</t>
-  </si>
-  <si>
-    <t>04:29:27</t>
-  </si>
-  <si>
-    <t>21:07:48</t>
-  </si>
-  <si>
-    <t>02:03:09</t>
-  </si>
-  <si>
-    <t>03:39:34</t>
-  </si>
-  <si>
-    <t>20:17:25</t>
-  </si>
-  <si>
-    <t>01:14:13</t>
-  </si>
-  <si>
-    <t>02:49:50</t>
-  </si>
-  <si>
-    <t>02:00:13</t>
-  </si>
-  <si>
-    <t>03:38:28</t>
-  </si>
-  <si>
-    <t>20:17:10</t>
-  </si>
-  <si>
-    <t>03:46:13</t>
-  </si>
-  <si>
-    <t>05:23:40</t>
-  </si>
-  <si>
-    <t>20:24:02</t>
-  </si>
-  <si>
-    <t>22:01:14</t>
-  </si>
-  <si>
-    <t>02:56:36</t>
+    <t>05:19:41</t>
+  </si>
+  <si>
+    <t>20:18:50</t>
+  </si>
+  <si>
+    <t>21:58:31</t>
+  </si>
+  <si>
+    <t>02:52:18</t>
+  </si>
+  <si>
+    <t>04:29:26</t>
+  </si>
+  <si>
+    <t>21:07:46</t>
+  </si>
+  <si>
+    <t>02:03:07</t>
+  </si>
+  <si>
+    <t>03:39:32</t>
+  </si>
+  <si>
+    <t>20:17:24</t>
+  </si>
+  <si>
+    <t>01:14:11</t>
+  </si>
+  <si>
+    <t>02:49:48</t>
+  </si>
+  <si>
+    <t>02:00:10</t>
+  </si>
+  <si>
+    <t>03:38:25</t>
+  </si>
+  <si>
+    <t>20:17:06</t>
+  </si>
+  <si>
+    <t>01:10:36</t>
+  </si>
+  <si>
+    <t>02:47:48</t>
+  </si>
+  <si>
+    <t>02:56:35</t>
   </si>
   <si>
     <t>04:34:16</t>
@@ -373,58 +328,52 @@
     <t>03:44:45</t>
   </si>
   <si>
-    <t>05:21:47</t>
-  </si>
-  <si>
-    <t>20:22:08</t>
-  </si>
-  <si>
-    <t>21:59:47</t>
+    <t>05:21:46</t>
+  </si>
+  <si>
+    <t>20:22:07</t>
+  </si>
+  <si>
+    <t>21:59:46</t>
   </si>
   <si>
     <t>02:55:07</t>
   </si>
   <si>
-    <t>04:32:20</t>
-  </si>
-  <si>
-    <t>21:09:59</t>
-  </si>
-  <si>
-    <t>02:05:23</t>
-  </si>
-  <si>
-    <t>03:42:48</t>
-  </si>
-  <si>
-    <t>20:20:11</t>
-  </si>
-  <si>
-    <t>01:15:31</t>
-  </si>
-  <si>
-    <t>02:53:09</t>
-  </si>
-  <si>
-    <t>02:03:23</t>
-  </si>
-  <si>
-    <t>03:40:22</t>
-  </si>
-  <si>
-    <t>20:18:14</t>
-  </si>
-  <si>
-    <t>03:48:22</t>
-  </si>
-  <si>
-    <t>05:26:57</t>
-  </si>
-  <si>
-    <t>20:26:50</t>
-  </si>
-  <si>
-    <t>22:04:04</t>
+    <t>04:32:19</t>
+  </si>
+  <si>
+    <t>21:09:58</t>
+  </si>
+  <si>
+    <t>02:05:21</t>
+  </si>
+  <si>
+    <t>03:42:46</t>
+  </si>
+  <si>
+    <t>20:20:09</t>
+  </si>
+  <si>
+    <t>01:15:29</t>
+  </si>
+  <si>
+    <t>02:53:06</t>
+  </si>
+  <si>
+    <t>02:03:20</t>
+  </si>
+  <si>
+    <t>03:40:19</t>
+  </si>
+  <si>
+    <t>20:18:10</t>
+  </si>
+  <si>
+    <t>01:13:26</t>
+  </si>
+  <si>
+    <t>02:50:37</t>
   </si>
   <si>
     <t>02:57:44</t>
@@ -436,67 +385,61 @@
     <t>21:14:51</t>
   </si>
   <si>
-    <t>03:47:55</t>
+    <t>03:47:54</t>
   </si>
   <si>
     <t>05:23:52</t>
   </si>
   <si>
-    <t>20:25:26</t>
+    <t>20:25:25</t>
   </si>
   <si>
     <t>22:01:01</t>
   </si>
   <si>
-    <t>02:57:56</t>
-  </si>
-  <si>
-    <t>04:35:14</t>
-  </si>
-  <si>
-    <t>21:12:11</t>
-  </si>
-  <si>
-    <t>02:07:37</t>
-  </si>
-  <si>
-    <t>03:46:02</t>
-  </si>
-  <si>
-    <t>20:22:58</t>
-  </si>
-  <si>
-    <t>01:16:49</t>
-  </si>
-  <si>
-    <t>02:56:27</t>
-  </si>
-  <si>
-    <t>02:06:33</t>
-  </si>
-  <si>
-    <t>03:42:16</t>
-  </si>
-  <si>
-    <t>20:19:18</t>
-  </si>
-  <si>
-    <t>03:51:03</t>
-  </si>
-  <si>
-    <t>05:29:04</t>
-  </si>
-  <si>
-    <t>20:29:08</t>
-  </si>
-  <si>
-    <t>22:06:23</t>
-  </si>
-  <si>
-    <t>03:01:06</t>
-  </si>
-  <si>
-    <t>04:39:42</t>
+    <t>02:57:55</t>
+  </si>
+  <si>
+    <t>04:35:13</t>
+  </si>
+  <si>
+    <t>21:12:10</t>
+  </si>
+  <si>
+    <t>02:07:35</t>
+  </si>
+  <si>
+    <t>03:46:00</t>
+  </si>
+  <si>
+    <t>20:22:56</t>
+  </si>
+  <si>
+    <t>01:16:46</t>
+  </si>
+  <si>
+    <t>02:56:25</t>
+  </si>
+  <si>
+    <t>02:06:30</t>
+  </si>
+  <si>
+    <t>03:42:13</t>
+  </si>
+  <si>
+    <t>20:19:14</t>
+  </si>
+  <si>
+    <t>01:16:17</t>
+  </si>
+  <si>
+    <t>02:53:25</t>
+  </si>
+  <si>
+    <t>03:01:05</t>
+  </si>
+  <si>
+    <t>04:39:41</t>
   </si>
   <si>
     <t>21:17:01</t>
@@ -508,84 +451,72 @@
     <t>05:26:33</t>
   </si>
   <si>
-    <t>20:27:32</t>
-  </si>
-  <si>
-    <t>22:04:18</t>
-  </si>
-  <si>
-    <t>03:00:16</t>
-  </si>
-  <si>
-    <t>04:37:30</t>
-  </si>
-  <si>
-    <t>21:14:50</t>
-  </si>
-  <si>
-    <t>02:10:15</t>
-  </si>
-  <si>
-    <t>03:48:09</t>
-  </si>
-  <si>
-    <t>20:25:19</t>
-  </si>
-  <si>
-    <t>01:20:03</t>
-  </si>
-  <si>
-    <t>02:58:33</t>
-  </si>
-  <si>
-    <t>02:08:43</t>
-  </si>
-  <si>
-    <t>03:45:03</t>
-  </si>
-  <si>
-    <t>20:22:42</t>
+    <t>20:27:31</t>
+  </si>
+  <si>
+    <t>22:04:17</t>
+  </si>
+  <si>
+    <t>03:00:15</t>
+  </si>
+  <si>
+    <t>04:37:29</t>
+  </si>
+  <si>
+    <t>21:14:49</t>
+  </si>
+  <si>
+    <t>02:10:13</t>
+  </si>
+  <si>
+    <t>03:48:07</t>
+  </si>
+  <si>
+    <t>20:25:17</t>
+  </si>
+  <si>
+    <t>01:20:00</t>
+  </si>
+  <si>
+    <t>02:58:31</t>
+  </si>
+  <si>
+    <t>02:08:40</t>
+  </si>
+  <si>
+    <t>03:45:00</t>
+  </si>
+  <si>
+    <t>20:22:38</t>
+  </si>
+  <si>
+    <t>01:18:35</t>
+  </si>
+  <si>
+    <t>02:55:43</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>29°</t>
   </si>
   <si>
     <t>4°</t>
   </si>
   <si>
-    <t>45°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
     <t>8°</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>03:49:59</t>
-  </si>
-  <si>
-    <t>05:22:57</t>
-  </si>
-  <si>
-    <t>20:25:49</t>
-  </si>
-  <si>
-    <t>21:58:47</t>
-  </si>
-  <si>
     <t>04:37:36</t>
   </si>
   <si>
@@ -595,13 +526,13 @@
     <t>05:25:16</t>
   </si>
   <si>
-    <t>20:26:32</t>
-  </si>
-  <si>
-    <t>21:59:26</t>
-  </si>
-  <si>
-    <t>21:12:42</t>
+    <t>20:26:31</t>
+  </si>
+  <si>
+    <t>21:59:25</t>
+  </si>
+  <si>
+    <t>21:12:41</t>
   </si>
   <si>
     <t>B</t>
@@ -613,13 +544,13 @@
     <t>A</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>1</t>
@@ -656,7 +587,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,13 +602,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,13 +620,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,7 +650,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,7 +662,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -820,6 +763,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1223,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1301,49 +1250,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="L2" s="4">
-        <v>-34.9</v>
+        <v>-42.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="O2" s="6">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P2" s="7">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1357,45 +1306,45 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="L3" s="4">
-        <v>-16.8</v>
+        <v>-26.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O3" s="9">
+        <v>177</v>
+      </c>
+      <c r="O3" s="6">
         <v>0</v>
       </c>
       <c r="P3" s="8">
@@ -1413,49 +1362,49 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="L4" s="4">
-        <v>-10.8</v>
+        <v>-20.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>178</v>
+      </c>
+      <c r="O4" s="6">
+        <v>11</v>
+      </c>
+      <c r="P4" s="9">
+        <v>3</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1469,46 +1418,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>189</v>
+        <v>63</v>
       </c>
       <c r="L5" s="4">
-        <v>-29.9</v>
+        <v>-35.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O5" s="9">
-        <v>4</v>
+        <v>177</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1516,8 +1465,8 @@
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="10">
-        <v>3</v>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1525,52 +1474,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="L6" s="4">
-        <v>-42.7</v>
+        <v>-17.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O6" s="9">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
+        <v>177</v>
+      </c>
+      <c r="O6" s="10">
+        <v>33</v>
+      </c>
+      <c r="P6" s="11">
+        <v>33</v>
       </c>
       <c r="Q6" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" s="8">
         <v>0</v>
@@ -1581,49 +1530,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="L7" s="4">
-        <v>-26.5</v>
+        <v>-11</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O7" s="11">
-        <v>34</v>
-      </c>
-      <c r="P7" s="12">
-        <v>34</v>
+        <v>179</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
@@ -1637,45 +1586,45 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="L8" s="4">
-        <v>-20.8</v>
+        <v>-30.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O8" s="9">
+        <v>176</v>
+      </c>
+      <c r="O8" s="6">
         <v>0</v>
       </c>
       <c r="P8" s="8">
@@ -1693,45 +1642,45 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="L9" s="4">
-        <v>-35.6</v>
+        <v>-43.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O9" s="9">
+        <v>177</v>
+      </c>
+      <c r="O9" s="6">
         <v>0</v>
       </c>
       <c r="P9" s="8">
@@ -1749,45 +1698,45 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-27.3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-17.3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O10" s="9">
+      <c r="O10" s="6">
         <v>0</v>
       </c>
       <c r="P10" s="8">
@@ -1805,49 +1754,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="L11" s="4">
-        <v>-11</v>
+        <v>-21</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
+        <v>178</v>
+      </c>
+      <c r="O11" s="6">
+        <v>18</v>
+      </c>
+      <c r="P11" s="12">
+        <v>18</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1861,45 +1810,45 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>194</v>
+        <v>70</v>
       </c>
       <c r="L12" s="4">
-        <v>-30.2</v>
+        <v>-49.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O12" s="9">
+        <v>177</v>
+      </c>
+      <c r="O12" s="6">
         <v>0</v>
       </c>
       <c r="P12" s="8">
@@ -1917,45 +1866,45 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="L13" s="4">
-        <v>-43.4</v>
+        <v>-36.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O13" s="9">
+        <v>177</v>
+      </c>
+      <c r="O13" s="6">
         <v>0</v>
       </c>
       <c r="P13" s="8">
@@ -1973,49 +1922,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="L14" s="4">
-        <v>-27.3</v>
+        <v>-10.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
+        <v>178</v>
+      </c>
+      <c r="O14" s="13">
+        <v>66</v>
+      </c>
+      <c r="P14" s="14">
+        <v>64</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -2029,49 +1978,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>195</v>
+        <v>73</v>
       </c>
       <c r="L15" s="4">
-        <v>-21</v>
+        <v>-51.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O15" s="6">
-        <v>34</v>
-      </c>
-      <c r="P15" s="12">
-        <v>34</v>
+        <v>176</v>
+      </c>
+      <c r="O15" s="13">
+        <v>62</v>
+      </c>
+      <c r="P15" s="15">
+        <v>62</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -2085,49 +2034,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="L16" s="4">
-        <v>-49.1</v>
+        <v>-44.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
+        <v>177</v>
+      </c>
+      <c r="O16" s="13">
+        <v>55</v>
+      </c>
+      <c r="P16" s="16">
+        <v>55</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2141,49 +2090,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L17" s="4">
-        <v>-36.4</v>
+        <v>-49.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O17" s="9">
-        <v>0</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
+        <v>177</v>
+      </c>
+      <c r="O17" s="13">
+        <v>48</v>
+      </c>
+      <c r="P17" s="17">
+        <v>48</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2197,49 +2146,49 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="L18" s="4">
-        <v>-10.9</v>
+        <v>-37.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O18" s="11">
-        <v>63</v>
-      </c>
-      <c r="P18" s="13">
-        <v>61</v>
+        <v>177</v>
+      </c>
+      <c r="O18" s="13">
+        <v>47</v>
+      </c>
+      <c r="P18" s="18">
+        <v>47</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
@@ -2253,49 +2202,49 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="L19" s="4">
-        <v>-51.9</v>
+        <v>-11</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O19" s="11">
-        <v>66</v>
-      </c>
-      <c r="P19" s="14">
-        <v>66</v>
+        <v>176</v>
+      </c>
+      <c r="O19" s="10">
+        <v>20</v>
+      </c>
+      <c r="P19" s="9">
+        <v>7</v>
       </c>
       <c r="Q19" s="8">
         <v>0</v>
@@ -2309,49 +2258,49 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-52.6</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-44.2</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="N20" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O20" s="11">
-        <v>58</v>
-      </c>
-      <c r="P20" s="13">
-        <v>58</v>
+        <v>177</v>
+      </c>
+      <c r="O20" s="6">
+        <v>2</v>
+      </c>
+      <c r="P20" s="8">
+        <v>2</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
@@ -2365,226 +2314,114 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L21" s="4">
-        <v>-49.9</v>
+        <v>-45</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O21" s="11">
-        <v>49</v>
-      </c>
-      <c r="P21" s="15">
-        <v>49</v>
+        <v>177</v>
+      </c>
+      <c r="O21" s="6">
+        <v>3</v>
+      </c>
+      <c r="P21" s="9">
+        <v>3</v>
       </c>
       <c r="Q21" s="8">
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="2">
-        <v>14</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-37.2</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O22" s="11">
-        <v>43</v>
-      </c>
-      <c r="P22" s="16">
-        <v>43</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
-      </c>
-      <c r="R22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="2">
-        <v>11</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-11</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O23" s="9">
-        <v>3</v>
-      </c>
-      <c r="P23" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0</v>
-      </c>
-      <c r="R23" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2603,12 +2440,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2625,22 +2462,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="176">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260824--01</t>
-  </si>
-  <si>
-    <t>20260824--02</t>
-  </si>
-  <si>
-    <t>20260824--03</t>
-  </si>
-  <si>
     <t>20260825--01</t>
   </si>
   <si>
@@ -130,79 +121,79 @@
     <t>20260830--02</t>
   </si>
   <si>
-    <t>02:17</t>
-  </si>
-  <si>
-    <t>06:38</t>
+    <t>20260831--01</t>
+  </si>
+  <si>
+    <t>20260831--02</t>
+  </si>
+  <si>
+    <t>20260831--03</t>
   </si>
   <si>
     <t>06:19</t>
   </si>
   <si>
-    <t>06:18</t>
-  </si>
-  <si>
     <t>04:11</t>
   </si>
   <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>02:30</t>
+    <t>02:29</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>04:23</t>
+  </si>
+  <si>
+    <t>04:28</t>
+  </si>
+  <si>
+    <t>06:28</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>06:37</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>03:48</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>05:40</t>
   </si>
   <si>
     <t>05:37</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>04:28</t>
-  </si>
-  <si>
-    <t>06:28</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>06:37</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>03:48</t>
-  </si>
-  <si>
-    <t>02:08</t>
-  </si>
-  <si>
-    <t>05:41</t>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>02:46</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:19</t>
-  </si>
-  <si>
-    <t>00:54</t>
-  </si>
-  <si>
-    <t>02:52:06</t>
-  </si>
-  <si>
-    <t>04:28:51</t>
-  </si>
-  <si>
-    <t>21:06:23</t>
+    <t>00:53</t>
   </si>
   <si>
     <t>03:39:25</t>
@@ -223,49 +214,49 @@
     <t>04:27:10</t>
   </si>
   <si>
-    <t>21:05:08</t>
-  </si>
-  <si>
-    <t>02:00:29</t>
-  </si>
-  <si>
-    <t>03:37:25</t>
-  </si>
-  <si>
-    <t>20:15:03</t>
-  </si>
-  <si>
-    <t>01:10:57</t>
-  </si>
-  <si>
-    <t>02:47:42</t>
-  </si>
-  <si>
-    <t>01:58:00</t>
-  </si>
-  <si>
-    <t>03:35:39</t>
-  </si>
-  <si>
-    <t>20:13:42</t>
-  </si>
-  <si>
-    <t>01:08:17</t>
-  </si>
-  <si>
-    <t>02:45:30</t>
-  </si>
-  <si>
-    <t>02:55:27</t>
-  </si>
-  <si>
-    <t>04:30:57</t>
-  </si>
-  <si>
-    <t>21:08:32</t>
-  </si>
-  <si>
-    <t>03:41:36</t>
+    <t>21:05:07</t>
+  </si>
+  <si>
+    <t>02:00:28</t>
+  </si>
+  <si>
+    <t>03:37:24</t>
+  </si>
+  <si>
+    <t>20:15:02</t>
+  </si>
+  <si>
+    <t>01:10:55</t>
+  </si>
+  <si>
+    <t>02:47:41</t>
+  </si>
+  <si>
+    <t>01:57:58</t>
+  </si>
+  <si>
+    <t>03:35:36</t>
+  </si>
+  <si>
+    <t>20:13:39</t>
+  </si>
+  <si>
+    <t>01:08:14</t>
+  </si>
+  <si>
+    <t>02:45:27</t>
+  </si>
+  <si>
+    <t>00:18:28</t>
+  </si>
+  <si>
+    <t>01:55:24</t>
+  </si>
+  <si>
+    <t>23:28:39</t>
+  </si>
+  <si>
+    <t>03:41:35</t>
   </si>
   <si>
     <t>05:19:41</t>
@@ -286,43 +277,43 @@
     <t>21:07:46</t>
   </si>
   <si>
-    <t>02:03:07</t>
-  </si>
-  <si>
-    <t>03:39:32</t>
-  </si>
-  <si>
-    <t>20:17:24</t>
-  </si>
-  <si>
-    <t>01:14:11</t>
-  </si>
-  <si>
-    <t>02:49:48</t>
-  </si>
-  <si>
-    <t>02:00:10</t>
-  </si>
-  <si>
-    <t>03:38:25</t>
-  </si>
-  <si>
-    <t>20:17:06</t>
-  </si>
-  <si>
-    <t>01:10:36</t>
-  </si>
-  <si>
-    <t>02:47:48</t>
-  </si>
-  <si>
-    <t>02:56:35</t>
-  </si>
-  <si>
-    <t>04:34:16</t>
-  </si>
-  <si>
-    <t>21:11:41</t>
+    <t>02:03:06</t>
+  </si>
+  <si>
+    <t>03:39:31</t>
+  </si>
+  <si>
+    <t>20:17:22</t>
+  </si>
+  <si>
+    <t>01:14:10</t>
+  </si>
+  <si>
+    <t>02:49:46</t>
+  </si>
+  <si>
+    <t>02:00:07</t>
+  </si>
+  <si>
+    <t>03:38:23</t>
+  </si>
+  <si>
+    <t>20:17:02</t>
+  </si>
+  <si>
+    <t>01:10:33</t>
+  </si>
+  <si>
+    <t>02:47:45</t>
+  </si>
+  <si>
+    <t>00:21:04</t>
+  </si>
+  <si>
+    <t>01:57:32</t>
+  </si>
+  <si>
+    <t>23:31:49</t>
   </si>
   <si>
     <t>03:44:45</t>
@@ -337,52 +328,52 @@
     <t>21:59:46</t>
   </si>
   <si>
-    <t>02:55:07</t>
+    <t>02:55:06</t>
   </si>
   <si>
     <t>04:32:19</t>
   </si>
   <si>
-    <t>21:09:58</t>
-  </si>
-  <si>
-    <t>02:05:21</t>
-  </si>
-  <si>
-    <t>03:42:46</t>
-  </si>
-  <si>
-    <t>20:20:09</t>
-  </si>
-  <si>
-    <t>01:15:29</t>
-  </si>
-  <si>
-    <t>02:53:06</t>
-  </si>
-  <si>
-    <t>02:03:20</t>
-  </si>
-  <si>
-    <t>03:40:19</t>
-  </si>
-  <si>
-    <t>20:18:10</t>
-  </si>
-  <si>
-    <t>01:13:26</t>
-  </si>
-  <si>
-    <t>02:50:37</t>
-  </si>
-  <si>
-    <t>02:57:44</t>
-  </si>
-  <si>
-    <t>04:37:35</t>
-  </si>
-  <si>
-    <t>21:14:51</t>
+    <t>21:09:57</t>
+  </si>
+  <si>
+    <t>02:05:20</t>
+  </si>
+  <si>
+    <t>03:42:45</t>
+  </si>
+  <si>
+    <t>20:20:08</t>
+  </si>
+  <si>
+    <t>01:15:27</t>
+  </si>
+  <si>
+    <t>02:53:05</t>
+  </si>
+  <si>
+    <t>02:03:17</t>
+  </si>
+  <si>
+    <t>03:40:16</t>
+  </si>
+  <si>
+    <t>20:18:07</t>
+  </si>
+  <si>
+    <t>01:13:23</t>
+  </si>
+  <si>
+    <t>02:50:33</t>
+  </si>
+  <si>
+    <t>00:23:21</t>
+  </si>
+  <si>
+    <t>02:00:44</t>
+  </si>
+  <si>
+    <t>23:33:12</t>
   </si>
   <si>
     <t>03:47:54</t>
@@ -394,61 +385,61 @@
     <t>20:25:25</t>
   </si>
   <si>
-    <t>22:01:01</t>
-  </si>
-  <si>
-    <t>02:57:55</t>
-  </si>
-  <si>
-    <t>04:35:13</t>
-  </si>
-  <si>
-    <t>21:12:10</t>
-  </si>
-  <si>
-    <t>02:07:35</t>
-  </si>
-  <si>
-    <t>03:46:00</t>
-  </si>
-  <si>
-    <t>20:22:56</t>
-  </si>
-  <si>
-    <t>01:16:46</t>
-  </si>
-  <si>
-    <t>02:56:25</t>
-  </si>
-  <si>
-    <t>02:06:30</t>
-  </si>
-  <si>
-    <t>03:42:13</t>
-  </si>
-  <si>
-    <t>20:19:14</t>
-  </si>
-  <si>
-    <t>01:16:17</t>
-  </si>
-  <si>
-    <t>02:53:25</t>
-  </si>
-  <si>
-    <t>03:01:05</t>
-  </si>
-  <si>
-    <t>04:39:41</t>
-  </si>
-  <si>
-    <t>21:17:01</t>
-  </si>
-  <si>
-    <t>03:50:05</t>
-  </si>
-  <si>
-    <t>05:26:33</t>
+    <t>22:01:00</t>
+  </si>
+  <si>
+    <t>02:57:54</t>
+  </si>
+  <si>
+    <t>04:35:12</t>
+  </si>
+  <si>
+    <t>21:12:09</t>
+  </si>
+  <si>
+    <t>02:07:34</t>
+  </si>
+  <si>
+    <t>03:45:59</t>
+  </si>
+  <si>
+    <t>20:22:55</t>
+  </si>
+  <si>
+    <t>01:16:45</t>
+  </si>
+  <si>
+    <t>02:56:23</t>
+  </si>
+  <si>
+    <t>02:06:28</t>
+  </si>
+  <si>
+    <t>03:42:11</t>
+  </si>
+  <si>
+    <t>20:19:12</t>
+  </si>
+  <si>
+    <t>01:16:13</t>
+  </si>
+  <si>
+    <t>02:53:22</t>
+  </si>
+  <si>
+    <t>00:25:39</t>
+  </si>
+  <si>
+    <t>02:03:55</t>
+  </si>
+  <si>
+    <t>23:34:35</t>
+  </si>
+  <si>
+    <t>03:50:04</t>
+  </si>
+  <si>
+    <t>05:26:32</t>
   </si>
   <si>
     <t>20:27:31</t>
@@ -457,54 +448,57 @@
     <t>22:04:17</t>
   </si>
   <si>
-    <t>03:00:15</t>
-  </si>
-  <si>
-    <t>04:37:29</t>
-  </si>
-  <si>
-    <t>21:14:49</t>
-  </si>
-  <si>
-    <t>02:10:13</t>
-  </si>
-  <si>
-    <t>03:48:07</t>
-  </si>
-  <si>
-    <t>20:25:17</t>
-  </si>
-  <si>
-    <t>01:20:00</t>
-  </si>
-  <si>
-    <t>02:58:31</t>
-  </si>
-  <si>
-    <t>02:08:40</t>
-  </si>
-  <si>
-    <t>03:45:00</t>
-  </si>
-  <si>
-    <t>20:22:38</t>
-  </si>
-  <si>
-    <t>01:18:35</t>
-  </si>
-  <si>
-    <t>02:55:43</t>
+    <t>03:00:14</t>
+  </si>
+  <si>
+    <t>04:37:28</t>
+  </si>
+  <si>
+    <t>21:14:48</t>
+  </si>
+  <si>
+    <t>02:10:12</t>
+  </si>
+  <si>
+    <t>03:48:06</t>
+  </si>
+  <si>
+    <t>20:25:15</t>
+  </si>
+  <si>
+    <t>01:19:59</t>
+  </si>
+  <si>
+    <t>02:58:29</t>
+  </si>
+  <si>
+    <t>02:08:37</t>
+  </si>
+  <si>
+    <t>03:44:57</t>
+  </si>
+  <si>
+    <t>20:22:35</t>
+  </si>
+  <si>
+    <t>01:18:32</t>
+  </si>
+  <si>
+    <t>02:55:39</t>
+  </si>
+  <si>
+    <t>00:28:14</t>
+  </si>
+  <si>
+    <t>02:06:03</t>
+  </si>
+  <si>
+    <t>23:37:45</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
     <t>4°</t>
   </si>
   <si>
@@ -517,43 +511,37 @@
     <t>-</t>
   </si>
   <si>
-    <t>04:37:36</t>
-  </si>
-  <si>
-    <t>21:12:51</t>
-  </si>
-  <si>
-    <t>05:25:16</t>
+    <t>05:25:15</t>
   </si>
   <si>
     <t>20:26:31</t>
   </si>
   <si>
-    <t>21:59:25</t>
-  </si>
-  <si>
-    <t>21:12:41</t>
+    <t>21:59:24</t>
+  </si>
+  <si>
+    <t>21:12:40</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -587,7 +575,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -602,13 +590,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,25 +608,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -656,25 +626,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,7 +673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -754,21 +712,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1250,13 +1193,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>60</v>
@@ -1280,19 +1223,19 @@
         <v>60</v>
       </c>
       <c r="L2" s="4">
-        <v>-42.7</v>
+        <v>-35.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="O2" s="6">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="P2" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1306,13 +1249,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>61</v>
@@ -1333,25 +1276,25 @@
         <v>161</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L3" s="4">
-        <v>-26.5</v>
+        <v>-17.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="O3" s="9">
+        <v>3</v>
       </c>
       <c r="P3" s="8">
         <v>0</v>
       </c>
       <c r="Q3" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" s="8">
         <v>0</v>
@@ -1362,13 +1305,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>62</v>
@@ -1386,25 +1329,25 @@
         <v>142</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L4" s="4">
-        <v>-20.8</v>
+        <v>-11</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O4" s="6">
-        <v>11</v>
-      </c>
-      <c r="P4" s="9">
-        <v>3</v>
+        <v>173</v>
+      </c>
+      <c r="O4" s="9">
+        <v>1</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1418,13 +1361,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>63</v>
@@ -1442,21 +1385,21 @@
         <v>143</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="L5" s="4">
-        <v>-35.6</v>
+        <v>-30.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O5" s="6">
+        <v>174</v>
+      </c>
+      <c r="O5" s="9">
         <v>0</v>
       </c>
       <c r="P5" s="8">
@@ -1474,13 +1417,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>64</v>
@@ -1498,28 +1441,28 @@
         <v>144</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-43.4</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L6" s="4">
-        <v>-17.3</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O6" s="10">
-        <v>33</v>
-      </c>
-      <c r="P6" s="11">
-        <v>33</v>
+        <v>172</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
       </c>
       <c r="Q6" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" s="8">
         <v>0</v>
@@ -1530,13 +1473,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>65</v>
@@ -1554,21 +1497,21 @@
         <v>145</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="L7" s="4">
-        <v>-11</v>
+        <v>-27.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O7" s="6">
+        <v>172</v>
+      </c>
+      <c r="O7" s="9">
         <v>0</v>
       </c>
       <c r="P7" s="8">
@@ -1586,13 +1529,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>66</v>
@@ -1610,25 +1553,25 @@
         <v>146</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L8" s="4">
-        <v>-30.2</v>
+        <v>-21</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
+        <v>175</v>
+      </c>
+      <c r="O8" s="9">
+        <v>12</v>
       </c>
       <c r="P8" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1642,13 +1585,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>67</v>
@@ -1672,15 +1615,15 @@
         <v>67</v>
       </c>
       <c r="L9" s="4">
-        <v>-43.4</v>
+        <v>-49.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O9" s="6">
+        <v>172</v>
+      </c>
+      <c r="O9" s="9">
         <v>0</v>
       </c>
       <c r="P9" s="8">
@@ -1698,13 +1641,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>68</v>
@@ -1728,15 +1671,15 @@
         <v>68</v>
       </c>
       <c r="L10" s="4">
-        <v>-27.3</v>
+        <v>-36.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O10" s="6">
+        <v>172</v>
+      </c>
+      <c r="O10" s="9">
         <v>0</v>
       </c>
       <c r="P10" s="8">
@@ -1754,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>69</v>
@@ -1778,25 +1721,25 @@
         <v>149</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="L11" s="4">
-        <v>-21</v>
+        <v>-10.9</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O11" s="6">
-        <v>18</v>
-      </c>
-      <c r="P11" s="12">
-        <v>18</v>
+      <c r="O11" s="10">
+        <v>69</v>
+      </c>
+      <c r="P11" s="11">
+        <v>67</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1810,13 +1753,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>70</v>
@@ -1840,19 +1783,19 @@
         <v>70</v>
       </c>
       <c r="L12" s="4">
-        <v>-49.1</v>
+        <v>-51.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
+        <v>174</v>
+      </c>
+      <c r="O12" s="10">
+        <v>70</v>
+      </c>
+      <c r="P12" s="12">
+        <v>68</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1866,13 +1809,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>71</v>
@@ -1896,19 +1839,19 @@
         <v>71</v>
       </c>
       <c r="L13" s="4">
-        <v>-36.4</v>
+        <v>-44.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="O13" s="10">
+        <v>70</v>
+      </c>
+      <c r="P13" s="12">
+        <v>69</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1922,13 +1865,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>72</v>
@@ -1946,25 +1889,25 @@
         <v>152</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="L14" s="4">
-        <v>-10.9</v>
+        <v>-49.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O14" s="13">
-        <v>66</v>
-      </c>
-      <c r="P14" s="14">
-        <v>64</v>
+        <v>172</v>
+      </c>
+      <c r="O14" s="6">
+        <v>32</v>
+      </c>
+      <c r="P14" s="13">
+        <v>32</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1978,13 +1921,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>73</v>
@@ -2008,19 +1951,19 @@
         <v>73</v>
       </c>
       <c r="L15" s="4">
-        <v>-51.9</v>
+        <v>-37.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O15" s="13">
-        <v>62</v>
-      </c>
-      <c r="P15" s="15">
-        <v>62</v>
+        <v>172</v>
+      </c>
+      <c r="O15" s="6">
+        <v>29</v>
+      </c>
+      <c r="P15" s="13">
+        <v>29</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -2034,13 +1977,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>74</v>
@@ -2058,25 +2001,25 @@
         <v>154</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="L16" s="4">
-        <v>-44.2</v>
+        <v>-11</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O16" s="13">
-        <v>55</v>
-      </c>
-      <c r="P16" s="16">
-        <v>55</v>
+        <v>174</v>
+      </c>
+      <c r="O16" s="9">
+        <v>2</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2090,13 +2033,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>75</v>
@@ -2120,19 +2063,19 @@
         <v>75</v>
       </c>
       <c r="L17" s="4">
-        <v>-49.9</v>
+        <v>-52.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O17" s="13">
-        <v>48</v>
-      </c>
-      <c r="P17" s="17">
-        <v>48</v>
+        <v>172</v>
+      </c>
+      <c r="O17" s="9">
+        <v>2</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2146,13 +2089,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>76</v>
@@ -2176,19 +2119,19 @@
         <v>76</v>
       </c>
       <c r="L18" s="4">
-        <v>-37.2</v>
+        <v>-45</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O18" s="13">
-        <v>47</v>
-      </c>
-      <c r="P18" s="18">
-        <v>47</v>
+        <v>172</v>
+      </c>
+      <c r="O18" s="9">
+        <v>1</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
@@ -2202,13 +2145,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>77</v>
@@ -2226,31 +2169,19 @@
         <v>157</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="L19" s="4">
-        <v>-11</v>
+        <v>-51.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O19" s="10">
-        <v>20</v>
-      </c>
-      <c r="P19" s="9">
-        <v>7</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2258,13 +2189,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>78</v>
@@ -2288,25 +2219,13 @@
         <v>78</v>
       </c>
       <c r="L20" s="4">
-        <v>-52.6</v>
+        <v>-50.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O20" s="6">
-        <v>2</v>
-      </c>
-      <c r="P20" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="8">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2314,13 +2233,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>79</v>
@@ -2344,25 +2263,13 @@
         <v>79</v>
       </c>
       <c r="L21" s="4">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O21" s="6">
-        <v>3</v>
-      </c>
-      <c r="P21" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8">
-        <v>0</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260825--01</t>
-  </si>
-  <si>
-    <t>20260825--02</t>
-  </si>
-  <si>
-    <t>20260825--03</t>
-  </si>
-  <si>
-    <t>20260825--04</t>
-  </si>
-  <si>
     <t>20260826--01</t>
   </si>
   <si>
@@ -130,49 +118,40 @@
     <t>20260831--03</t>
   </si>
   <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>04:11</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>02:29</t>
+    <t>20260901--01</t>
   </si>
   <si>
     <t>05:36</t>
   </si>
   <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>04:23</t>
-  </si>
-  <si>
-    <t>04:28</t>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>04:27</t>
   </si>
   <si>
     <t>06:28</t>
   </si>
   <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>02:35</t>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>02:34</t>
   </si>
   <si>
     <t>06:37</t>
   </si>
   <si>
-    <t>06:21</t>
+    <t>06:20</t>
   </si>
   <si>
     <t>03:48</t>
   </si>
   <si>
-    <t>02:10</t>
+    <t>02:09</t>
   </si>
   <si>
     <t>05:40</t>
@@ -181,37 +160,25 @@
     <t>05:37</t>
   </si>
   <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>06:23</t>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>06:24</t>
   </si>
   <si>
     <t>02:46</t>
   </si>
   <si>
+    <t>06:36</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:53</t>
-  </si>
-  <si>
-    <t>03:39:25</t>
-  </si>
-  <si>
-    <t>05:17:01</t>
-  </si>
-  <si>
-    <t>20:16:45</t>
-  </si>
-  <si>
-    <t>21:55:16</t>
-  </si>
-  <si>
     <t>02:49:58</t>
   </si>
   <si>
-    <t>04:27:10</t>
+    <t>04:27:09</t>
   </si>
   <si>
     <t>21:05:07</t>
@@ -220,118 +187,100 @@
     <t>02:00:28</t>
   </si>
   <si>
-    <t>03:37:24</t>
-  </si>
-  <si>
-    <t>20:15:02</t>
-  </si>
-  <si>
-    <t>01:10:55</t>
+    <t>03:37:23</t>
+  </si>
+  <si>
+    <t>20:15:01</t>
+  </si>
+  <si>
+    <t>01:10:54</t>
+  </si>
+  <si>
+    <t>02:47:39</t>
+  </si>
+  <si>
+    <t>01:57:55</t>
+  </si>
+  <si>
+    <t>03:35:34</t>
+  </si>
+  <si>
+    <t>20:13:36</t>
+  </si>
+  <si>
+    <t>01:08:10</t>
+  </si>
+  <si>
+    <t>02:45:23</t>
+  </si>
+  <si>
+    <t>00:18:23</t>
+  </si>
+  <si>
+    <t>01:55:18</t>
+  </si>
+  <si>
+    <t>23:28:32</t>
+  </si>
+  <si>
+    <t>01:05:16</t>
+  </si>
+  <si>
+    <t>02:52:18</t>
+  </si>
+  <si>
+    <t>04:29:25</t>
+  </si>
+  <si>
+    <t>21:07:45</t>
+  </si>
+  <si>
+    <t>02:03:06</t>
+  </si>
+  <si>
+    <t>03:39:30</t>
+  </si>
+  <si>
+    <t>20:17:21</t>
+  </si>
+  <si>
+    <t>01:14:09</t>
+  </si>
+  <si>
+    <t>02:49:45</t>
+  </si>
+  <si>
+    <t>02:00:05</t>
+  </si>
+  <si>
+    <t>03:38:20</t>
+  </si>
+  <si>
+    <t>20:16:59</t>
+  </si>
+  <si>
+    <t>01:10:29</t>
   </si>
   <si>
     <t>02:47:41</t>
   </si>
   <si>
-    <t>01:57:58</t>
-  </si>
-  <si>
-    <t>03:35:36</t>
-  </si>
-  <si>
-    <t>20:13:39</t>
-  </si>
-  <si>
-    <t>01:08:14</t>
-  </si>
-  <si>
-    <t>02:45:27</t>
-  </si>
-  <si>
-    <t>00:18:28</t>
-  </si>
-  <si>
-    <t>01:55:24</t>
-  </si>
-  <si>
-    <t>23:28:39</t>
-  </si>
-  <si>
-    <t>03:41:35</t>
-  </si>
-  <si>
-    <t>05:19:41</t>
-  </si>
-  <si>
-    <t>20:18:50</t>
-  </si>
-  <si>
-    <t>21:58:31</t>
-  </si>
-  <si>
-    <t>02:52:18</t>
-  </si>
-  <si>
-    <t>04:29:26</t>
-  </si>
-  <si>
-    <t>21:07:46</t>
-  </si>
-  <si>
-    <t>02:03:06</t>
-  </si>
-  <si>
-    <t>03:39:31</t>
-  </si>
-  <si>
-    <t>20:17:22</t>
-  </si>
-  <si>
-    <t>01:14:10</t>
-  </si>
-  <si>
-    <t>02:49:46</t>
-  </si>
-  <si>
-    <t>02:00:07</t>
-  </si>
-  <si>
-    <t>03:38:23</t>
-  </si>
-  <si>
-    <t>20:17:02</t>
-  </si>
-  <si>
-    <t>01:10:33</t>
-  </si>
-  <si>
-    <t>02:47:45</t>
-  </si>
-  <si>
-    <t>00:21:04</t>
-  </si>
-  <si>
-    <t>01:57:32</t>
-  </si>
-  <si>
-    <t>23:31:49</t>
-  </si>
-  <si>
-    <t>03:44:45</t>
-  </si>
-  <si>
-    <t>05:21:46</t>
-  </si>
-  <si>
-    <t>20:22:07</t>
-  </si>
-  <si>
-    <t>21:59:46</t>
+    <t>00:20:59</t>
+  </si>
+  <si>
+    <t>01:57:26</t>
+  </si>
+  <si>
+    <t>23:31:42</t>
+  </si>
+  <si>
+    <t>01:07:22</t>
   </si>
   <si>
     <t>02:55:06</t>
   </si>
   <si>
-    <t>04:32:19</t>
+    <t>04:32:18</t>
   </si>
   <si>
     <t>21:09:57</t>
@@ -340,52 +289,43 @@
     <t>02:05:20</t>
   </si>
   <si>
-    <t>03:42:45</t>
-  </si>
-  <si>
-    <t>20:20:08</t>
-  </si>
-  <si>
-    <t>01:15:27</t>
-  </si>
-  <si>
-    <t>02:53:05</t>
-  </si>
-  <si>
-    <t>02:03:17</t>
-  </si>
-  <si>
-    <t>03:40:16</t>
-  </si>
-  <si>
-    <t>20:18:07</t>
-  </si>
-  <si>
-    <t>01:13:23</t>
-  </si>
-  <si>
-    <t>02:50:33</t>
-  </si>
-  <si>
-    <t>00:23:21</t>
-  </si>
-  <si>
-    <t>02:00:44</t>
-  </si>
-  <si>
-    <t>23:33:12</t>
-  </si>
-  <si>
-    <t>03:47:54</t>
-  </si>
-  <si>
-    <t>05:23:52</t>
-  </si>
-  <si>
-    <t>20:25:25</t>
-  </si>
-  <si>
-    <t>22:01:00</t>
+    <t>03:42:44</t>
+  </si>
+  <si>
+    <t>20:20:07</t>
+  </si>
+  <si>
+    <t>01:15:26</t>
+  </si>
+  <si>
+    <t>02:53:03</t>
+  </si>
+  <si>
+    <t>02:03:15</t>
+  </si>
+  <si>
+    <t>03:40:14</t>
+  </si>
+  <si>
+    <t>20:18:03</t>
+  </si>
+  <si>
+    <t>01:13:19</t>
+  </si>
+  <si>
+    <t>02:50:29</t>
+  </si>
+  <si>
+    <t>00:23:16</t>
+  </si>
+  <si>
+    <t>02:00:38</t>
+  </si>
+  <si>
+    <t>23:33:05</t>
+  </si>
+  <si>
+    <t>01:10:40</t>
   </si>
   <si>
     <t>02:57:54</t>
@@ -397,55 +337,46 @@
     <t>21:12:09</t>
   </si>
   <si>
-    <t>02:07:34</t>
-  </si>
-  <si>
-    <t>03:45:59</t>
-  </si>
-  <si>
-    <t>20:22:55</t>
-  </si>
-  <si>
-    <t>01:16:45</t>
-  </si>
-  <si>
-    <t>02:56:23</t>
-  </si>
-  <si>
-    <t>02:06:28</t>
-  </si>
-  <si>
-    <t>03:42:11</t>
-  </si>
-  <si>
-    <t>20:19:12</t>
-  </si>
-  <si>
-    <t>01:16:13</t>
-  </si>
-  <si>
-    <t>02:53:22</t>
-  </si>
-  <si>
-    <t>00:25:39</t>
-  </si>
-  <si>
-    <t>02:03:55</t>
-  </si>
-  <si>
-    <t>23:34:35</t>
-  </si>
-  <si>
-    <t>03:50:04</t>
-  </si>
-  <si>
-    <t>05:26:32</t>
-  </si>
-  <si>
-    <t>20:27:31</t>
-  </si>
-  <si>
-    <t>22:04:17</t>
+    <t>02:07:33</t>
+  </si>
+  <si>
+    <t>03:45:58</t>
+  </si>
+  <si>
+    <t>20:22:53</t>
+  </si>
+  <si>
+    <t>01:16:43</t>
+  </si>
+  <si>
+    <t>02:56:22</t>
+  </si>
+  <si>
+    <t>02:06:25</t>
+  </si>
+  <si>
+    <t>03:42:08</t>
+  </si>
+  <si>
+    <t>20:19:08</t>
+  </si>
+  <si>
+    <t>01:16:09</t>
+  </si>
+  <si>
+    <t>02:53:18</t>
+  </si>
+  <si>
+    <t>00:25:33</t>
+  </si>
+  <si>
+    <t>02:03:50</t>
+  </si>
+  <si>
+    <t>23:34:28</t>
+  </si>
+  <si>
+    <t>01:13:58</t>
   </si>
   <si>
     <t>03:00:14</t>
@@ -457,69 +388,57 @@
     <t>21:14:48</t>
   </si>
   <si>
-    <t>02:10:12</t>
+    <t>02:10:11</t>
   </si>
   <si>
     <t>03:48:06</t>
   </si>
   <si>
-    <t>20:25:15</t>
-  </si>
-  <si>
-    <t>01:19:59</t>
-  </si>
-  <si>
-    <t>02:58:29</t>
-  </si>
-  <si>
-    <t>02:08:37</t>
-  </si>
-  <si>
-    <t>03:44:57</t>
-  </si>
-  <si>
-    <t>20:22:35</t>
-  </si>
-  <si>
-    <t>01:18:32</t>
-  </si>
-  <si>
-    <t>02:55:39</t>
-  </si>
-  <si>
-    <t>00:28:14</t>
-  </si>
-  <si>
-    <t>02:06:03</t>
-  </si>
-  <si>
-    <t>23:37:45</t>
+    <t>20:25:14</t>
+  </si>
+  <si>
+    <t>01:19:57</t>
+  </si>
+  <si>
+    <t>02:58:27</t>
+  </si>
+  <si>
+    <t>02:08:34</t>
+  </si>
+  <si>
+    <t>03:44:55</t>
+  </si>
+  <si>
+    <t>20:22:32</t>
+  </si>
+  <si>
+    <t>01:18:28</t>
+  </si>
+  <si>
+    <t>02:55:35</t>
+  </si>
+  <si>
+    <t>00:28:09</t>
+  </si>
+  <si>
+    <t>02:05:57</t>
+  </si>
+  <si>
+    <t>23:37:37</t>
+  </si>
+  <si>
+    <t>01:16:03</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
     <t>8°</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>05:25:15</t>
-  </si>
-  <si>
-    <t>20:26:31</t>
-  </si>
-  <si>
-    <t>21:59:24</t>
-  </si>
-  <si>
     <t>21:12:40</t>
   </si>
   <si>
@@ -535,13 +454,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>1</t>
+    <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -575,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,13 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,7 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,7 +548,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -712,6 +652,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1115,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1193,49 +1145,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L2" s="4">
-        <v>-35.6</v>
+        <v>-43.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="O2" s="6">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="P2" s="7">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1249,52 +1201,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="L3" s="4">
-        <v>-17.3</v>
+        <v>-27.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="O3" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" s="8">
         <v>0</v>
       </c>
       <c r="Q3" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3" s="8">
         <v>0</v>
@@ -1305,49 +1257,49 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="L4" s="4">
-        <v>-11</v>
+        <v>-21</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O4" s="9">
-        <v>1</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>146</v>
+      </c>
+      <c r="O4" s="10">
+        <v>20</v>
+      </c>
+      <c r="P4" s="11">
+        <v>16</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1361,43 +1313,43 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="L5" s="4">
-        <v>-30.2</v>
+        <v>-49.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="O5" s="9">
         <v>0</v>
@@ -1417,43 +1369,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="L6" s="4">
-        <v>-43.4</v>
+        <v>-36.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="O6" s="9">
         <v>0</v>
@@ -1473,49 +1425,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="L7" s="4">
-        <v>-27.3</v>
+        <v>-10.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
+        <v>146</v>
+      </c>
+      <c r="O7" s="6">
+        <v>69</v>
+      </c>
+      <c r="P7" s="12">
+        <v>63</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
@@ -1529,49 +1481,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="L8" s="4">
-        <v>-21</v>
+        <v>-51.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="O8" s="9">
-        <v>12</v>
-      </c>
-      <c r="P8" s="8">
-        <v>2</v>
+        <v>147</v>
+      </c>
+      <c r="O8" s="6">
+        <v>68</v>
+      </c>
+      <c r="P8" s="12">
+        <v>65</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1585,55 +1537,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L9" s="4">
-        <v>-49.1</v>
+        <v>-44.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="O9" s="6">
+        <v>66</v>
+      </c>
+      <c r="P9" s="12">
+        <v>65</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
       </c>
       <c r="R9" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1641,49 +1593,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L10" s="4">
-        <v>-36.4</v>
+        <v>-49.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="O10" s="6">
+        <v>41</v>
+      </c>
+      <c r="P10" s="13">
+        <v>41</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1697,49 +1649,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="L11" s="4">
-        <v>-10.9</v>
+        <v>-37.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="O11" s="10">
-        <v>69</v>
-      </c>
-      <c r="P11" s="11">
-        <v>67</v>
+        <v>145</v>
+      </c>
+      <c r="O11" s="6">
+        <v>44</v>
+      </c>
+      <c r="P11" s="14">
+        <v>44</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1753,49 +1705,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="L12" s="4">
-        <v>-51.9</v>
+        <v>-11</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O12" s="10">
-        <v>70</v>
-      </c>
-      <c r="P12" s="12">
-        <v>68</v>
+        <v>147</v>
+      </c>
+      <c r="O12" s="6">
+        <v>56</v>
+      </c>
+      <c r="P12" s="15">
+        <v>56</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1809,49 +1761,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L13" s="4">
-        <v>-44.2</v>
+        <v>-52.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O13" s="10">
-        <v>70</v>
-      </c>
-      <c r="P13" s="12">
-        <v>69</v>
+        <v>145</v>
+      </c>
+      <c r="O13" s="6">
+        <v>45</v>
+      </c>
+      <c r="P13" s="14">
+        <v>45</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1865,49 +1817,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L14" s="4">
-        <v>-49.9</v>
+        <v>-45.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="O14" s="6">
-        <v>32</v>
-      </c>
-      <c r="P14" s="13">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="P14" s="14">
+        <v>47</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1921,49 +1873,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L15" s="4">
-        <v>-37.2</v>
+        <v>-51.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O15" s="6">
-        <v>29</v>
-      </c>
-      <c r="P15" s="13">
-        <v>29</v>
+        <v>145</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1977,55 +1929,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="L16" s="4">
-        <v>-11</v>
+        <v>-50.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="O16" s="9">
-        <v>2</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="P16" s="16">
+        <v>7</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
       </c>
       <c r="R16" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2033,55 +1985,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L17" s="4">
-        <v>-52.6</v>
+        <v>-47</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O17" s="9">
-        <v>2</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0</v>
+        <v>147</v>
+      </c>
+      <c r="O17" s="6">
+        <v>78</v>
+      </c>
+      <c r="P17" s="17">
+        <v>31</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>51</v>
+      </c>
+      <c r="R17" s="16">
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2089,246 +2041,114 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L18" s="4">
-        <v>-45</v>
+        <v>-53.4</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O18" s="9">
-        <v>1</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2">
-        <v>17</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-51.6</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="2">
-        <v>49</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-50.8</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" s="6">
         <v>79</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-47</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>174</v>
+      <c r="P18" s="7">
+        <v>48</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>31</v>
+      </c>
+      <c r="R18" s="16">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2347,12 +2167,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2369,22 +2189,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="145">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260826--01</t>
-  </si>
-  <si>
-    <t>20260826--02</t>
-  </si>
-  <si>
-    <t>20260826--03</t>
-  </si>
-  <si>
     <t>20260827--01</t>
   </si>
   <si>
@@ -121,16 +112,16 @@
     <t>20260901--01</t>
   </si>
   <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>04:27</t>
+    <t>20260902--01</t>
+  </si>
+  <si>
+    <t>20260902--02</t>
+  </si>
+  <si>
+    <t>20260902--03</t>
+  </si>
+  <si>
+    <t>04:28</t>
   </si>
   <si>
     <t>06:28</t>
@@ -160,10 +151,10 @@
     <t>05:37</t>
   </si>
   <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>06:24</t>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>06:23</t>
   </si>
   <si>
     <t>02:46</t>
@@ -172,280 +163,280 @@
     <t>06:36</t>
   </si>
   <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:49:58</t>
-  </si>
-  <si>
-    <t>04:27:09</t>
-  </si>
-  <si>
-    <t>21:05:07</t>
-  </si>
-  <si>
     <t>02:00:28</t>
   </si>
   <si>
-    <t>03:37:23</t>
-  </si>
-  <si>
-    <t>20:15:01</t>
-  </si>
-  <si>
-    <t>01:10:54</t>
-  </si>
-  <si>
-    <t>02:47:39</t>
-  </si>
-  <si>
-    <t>01:57:55</t>
-  </si>
-  <si>
-    <t>03:35:34</t>
-  </si>
-  <si>
-    <t>20:13:36</t>
-  </si>
-  <si>
-    <t>01:08:10</t>
-  </si>
-  <si>
-    <t>02:45:23</t>
-  </si>
-  <si>
-    <t>00:18:23</t>
-  </si>
-  <si>
-    <t>01:55:18</t>
-  </si>
-  <si>
-    <t>23:28:32</t>
-  </si>
-  <si>
-    <t>01:05:16</t>
-  </si>
-  <si>
-    <t>02:52:18</t>
-  </si>
-  <si>
-    <t>04:29:25</t>
-  </si>
-  <si>
-    <t>21:07:45</t>
+    <t>03:37:24</t>
+  </si>
+  <si>
+    <t>20:15:02</t>
+  </si>
+  <si>
+    <t>01:10:55</t>
+  </si>
+  <si>
+    <t>02:47:40</t>
+  </si>
+  <si>
+    <t>01:57:57</t>
+  </si>
+  <si>
+    <t>03:35:36</t>
+  </si>
+  <si>
+    <t>20:13:39</t>
+  </si>
+  <si>
+    <t>01:08:14</t>
+  </si>
+  <si>
+    <t>02:45:26</t>
+  </si>
+  <si>
+    <t>00:18:28</t>
+  </si>
+  <si>
+    <t>01:55:23</t>
+  </si>
+  <si>
+    <t>23:28:38</t>
+  </si>
+  <si>
+    <t>01:05:23</t>
+  </si>
+  <si>
+    <t>00:15:23</t>
+  </si>
+  <si>
+    <t>01:53:03</t>
+  </si>
+  <si>
+    <t>23:25:22</t>
   </si>
   <si>
     <t>02:03:06</t>
   </si>
   <si>
-    <t>03:39:30</t>
-  </si>
-  <si>
-    <t>20:17:21</t>
-  </si>
-  <si>
-    <t>01:14:09</t>
-  </si>
-  <si>
-    <t>02:49:45</t>
-  </si>
-  <si>
-    <t>02:00:05</t>
-  </si>
-  <si>
-    <t>03:38:20</t>
-  </si>
-  <si>
-    <t>20:16:59</t>
-  </si>
-  <si>
-    <t>01:10:29</t>
-  </si>
-  <si>
-    <t>02:47:41</t>
-  </si>
-  <si>
-    <t>00:20:59</t>
-  </si>
-  <si>
-    <t>01:57:26</t>
-  </si>
-  <si>
-    <t>23:31:42</t>
-  </si>
-  <si>
-    <t>01:07:22</t>
-  </si>
-  <si>
-    <t>02:55:06</t>
-  </si>
-  <si>
-    <t>04:32:18</t>
-  </si>
-  <si>
-    <t>21:09:57</t>
+    <t>03:39:31</t>
+  </si>
+  <si>
+    <t>20:17:22</t>
+  </si>
+  <si>
+    <t>01:14:10</t>
+  </si>
+  <si>
+    <t>02:49:46</t>
+  </si>
+  <si>
+    <t>02:00:07</t>
+  </si>
+  <si>
+    <t>03:38:22</t>
+  </si>
+  <si>
+    <t>20:17:02</t>
+  </si>
+  <si>
+    <t>01:10:32</t>
+  </si>
+  <si>
+    <t>02:47:44</t>
+  </si>
+  <si>
+    <t>00:21:03</t>
+  </si>
+  <si>
+    <t>01:57:31</t>
+  </si>
+  <si>
+    <t>23:31:48</t>
+  </si>
+  <si>
+    <t>01:07:28</t>
+  </si>
+  <si>
+    <t>00:17:32</t>
+  </si>
+  <si>
+    <t>01:55:54</t>
+  </si>
+  <si>
+    <t>23:27:40</t>
   </si>
   <si>
     <t>02:05:20</t>
   </si>
   <si>
-    <t>03:42:44</t>
-  </si>
-  <si>
-    <t>20:20:07</t>
-  </si>
-  <si>
-    <t>01:15:26</t>
-  </si>
-  <si>
-    <t>02:53:03</t>
-  </si>
-  <si>
-    <t>02:03:15</t>
-  </si>
-  <si>
-    <t>03:40:14</t>
-  </si>
-  <si>
-    <t>20:18:03</t>
-  </si>
-  <si>
-    <t>01:13:19</t>
-  </si>
-  <si>
-    <t>02:50:29</t>
-  </si>
-  <si>
-    <t>00:23:16</t>
-  </si>
-  <si>
-    <t>02:00:38</t>
-  </si>
-  <si>
-    <t>23:33:05</t>
-  </si>
-  <si>
-    <t>01:10:40</t>
-  </si>
-  <si>
-    <t>02:57:54</t>
-  </si>
-  <si>
-    <t>04:35:12</t>
-  </si>
-  <si>
-    <t>21:12:09</t>
-  </si>
-  <si>
-    <t>02:07:33</t>
-  </si>
-  <si>
-    <t>03:45:58</t>
-  </si>
-  <si>
-    <t>20:22:53</t>
-  </si>
-  <si>
-    <t>01:16:43</t>
-  </si>
-  <si>
-    <t>02:56:22</t>
-  </si>
-  <si>
-    <t>02:06:25</t>
-  </si>
-  <si>
-    <t>03:42:08</t>
-  </si>
-  <si>
-    <t>20:19:08</t>
+    <t>03:42:45</t>
+  </si>
+  <si>
+    <t>20:20:08</t>
+  </si>
+  <si>
+    <t>01:15:27</t>
+  </si>
+  <si>
+    <t>02:53:04</t>
+  </si>
+  <si>
+    <t>02:03:17</t>
+  </si>
+  <si>
+    <t>03:40:16</t>
+  </si>
+  <si>
+    <t>20:18:06</t>
+  </si>
+  <si>
+    <t>01:13:22</t>
+  </si>
+  <si>
+    <t>02:50:33</t>
+  </si>
+  <si>
+    <t>00:23:20</t>
+  </si>
+  <si>
+    <t>02:00:43</t>
+  </si>
+  <si>
+    <t>23:33:11</t>
+  </si>
+  <si>
+    <t>01:10:46</t>
+  </si>
+  <si>
+    <t>00:20:43</t>
+  </si>
+  <si>
+    <t>01:57:40</t>
+  </si>
+  <si>
+    <t>23:30:32</t>
+  </si>
+  <si>
+    <t>02:07:34</t>
+  </si>
+  <si>
+    <t>03:45:59</t>
+  </si>
+  <si>
+    <t>20:22:54</t>
+  </si>
+  <si>
+    <t>01:16:44</t>
+  </si>
+  <si>
+    <t>02:56:23</t>
+  </si>
+  <si>
+    <t>02:06:27</t>
+  </si>
+  <si>
+    <t>03:42:10</t>
+  </si>
+  <si>
+    <t>20:19:11</t>
+  </si>
+  <si>
+    <t>01:16:12</t>
+  </si>
+  <si>
+    <t>02:53:21</t>
+  </si>
+  <si>
+    <t>00:25:38</t>
+  </si>
+  <si>
+    <t>02:03:54</t>
+  </si>
+  <si>
+    <t>23:34:34</t>
+  </si>
+  <si>
+    <t>01:14:04</t>
+  </si>
+  <si>
+    <t>00:23:53</t>
+  </si>
+  <si>
+    <t>01:59:25</t>
+  </si>
+  <si>
+    <t>23:33:23</t>
+  </si>
+  <si>
+    <t>02:10:12</t>
+  </si>
+  <si>
+    <t>03:48:06</t>
+  </si>
+  <si>
+    <t>20:25:15</t>
+  </si>
+  <si>
+    <t>01:19:58</t>
+  </si>
+  <si>
+    <t>02:58:28</t>
+  </si>
+  <si>
+    <t>02:08:36</t>
+  </si>
+  <si>
+    <t>03:44:57</t>
+  </si>
+  <si>
+    <t>20:22:35</t>
+  </si>
+  <si>
+    <t>01:18:31</t>
+  </si>
+  <si>
+    <t>02:55:39</t>
+  </si>
+  <si>
+    <t>00:28:13</t>
+  </si>
+  <si>
+    <t>02:06:02</t>
+  </si>
+  <si>
+    <t>23:37:43</t>
   </si>
   <si>
     <t>01:16:09</t>
   </si>
   <si>
-    <t>02:53:18</t>
-  </si>
-  <si>
-    <t>00:25:33</t>
-  </si>
-  <si>
-    <t>02:03:50</t>
-  </si>
-  <si>
-    <t>23:34:28</t>
-  </si>
-  <si>
-    <t>01:13:58</t>
-  </si>
-  <si>
-    <t>03:00:14</t>
-  </si>
-  <si>
-    <t>04:37:28</t>
-  </si>
-  <si>
-    <t>21:14:48</t>
-  </si>
-  <si>
-    <t>02:10:11</t>
-  </si>
-  <si>
-    <t>03:48:06</t>
-  </si>
-  <si>
-    <t>20:25:14</t>
-  </si>
-  <si>
-    <t>01:19:57</t>
-  </si>
-  <si>
-    <t>02:58:27</t>
-  </si>
-  <si>
-    <t>02:08:34</t>
-  </si>
-  <si>
-    <t>03:44:55</t>
-  </si>
-  <si>
-    <t>20:22:32</t>
-  </si>
-  <si>
-    <t>01:18:28</t>
-  </si>
-  <si>
-    <t>02:55:35</t>
-  </si>
-  <si>
-    <t>00:28:09</t>
-  </si>
-  <si>
-    <t>02:05:57</t>
-  </si>
-  <si>
-    <t>23:37:37</t>
-  </si>
-  <si>
-    <t>01:16:03</t>
+    <t>00:26:02</t>
+  </si>
+  <si>
+    <t>02:02:16</t>
+  </si>
+  <si>
+    <t>23:35:41</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>8°</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>21:12:40</t>
-  </si>
-  <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
@@ -491,7 +482,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,7 +497,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,61 +539,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -613,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -655,15 +628,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1145,7 +1109,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>35</v>
@@ -1175,19 +1139,19 @@
         <v>53</v>
       </c>
       <c r="L2" s="4">
-        <v>-43.4</v>
+        <v>-49.1</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="O2" s="6">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="P2" s="7">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1201,7 +1165,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>36</v>
@@ -1231,19 +1195,19 @@
         <v>54</v>
       </c>
       <c r="L3" s="4">
-        <v>-27.3</v>
+        <v>-36.4</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
+      <c r="O3" s="6">
+        <v>17</v>
+      </c>
+      <c r="P3" s="7">
+        <v>14</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1257,13 +1221,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>55</v>
@@ -1284,22 +1248,22 @@
         <v>139</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-10.9</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="4">
-        <v>-21</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O4" s="10">
-        <v>20</v>
-      </c>
-      <c r="P4" s="11">
-        <v>16</v>
+      <c r="O4" s="9">
+        <v>74</v>
+      </c>
+      <c r="P4" s="10">
+        <v>70</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1313,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>38</v>
@@ -1343,19 +1307,19 @@
         <v>56</v>
       </c>
       <c r="L5" s="4">
-        <v>-49.1</v>
+        <v>-51.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O5" s="9">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="P5" s="11">
+        <v>54</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1369,7 +1333,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>39</v>
@@ -1399,19 +1363,19 @@
         <v>57</v>
       </c>
       <c r="L6" s="4">
-        <v>-36.4</v>
+        <v>-44.2</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="O6" s="9">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="P6" s="11">
+        <v>54</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1425,7 +1389,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>40</v>
@@ -1449,25 +1413,25 @@
         <v>126</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-49.9</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-10.9</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O7" s="6">
-        <v>69</v>
+        <v>142</v>
+      </c>
+      <c r="O7" s="9">
+        <v>48</v>
       </c>
       <c r="P7" s="12">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
@@ -1481,7 +1445,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>41</v>
@@ -1511,19 +1475,19 @@
         <v>59</v>
       </c>
       <c r="L8" s="4">
-        <v>-51.9</v>
+        <v>-37.2</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O8" s="6">
-        <v>68</v>
+      <c r="O8" s="9">
+        <v>50</v>
       </c>
       <c r="P8" s="12">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1537,7 +1501,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>42</v>
@@ -1561,31 +1525,31 @@
         <v>128</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="L9" s="4">
-        <v>-44.2</v>
+        <v>-11</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O9" s="6">
-        <v>66</v>
-      </c>
-      <c r="P9" s="12">
-        <v>65</v>
+        <v>18</v>
+      </c>
+      <c r="P9" s="13">
+        <v>7</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
       </c>
       <c r="R9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1593,7 +1557,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>43</v>
@@ -1623,19 +1587,19 @@
         <v>61</v>
       </c>
       <c r="L10" s="4">
-        <v>-49.9</v>
+        <v>-52.6</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O10" s="6">
-        <v>41</v>
-      </c>
-      <c r="P10" s="13">
-        <v>41</v>
+      <c r="O10" s="9">
+        <v>48</v>
+      </c>
+      <c r="P10" s="12">
+        <v>48</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1649,7 +1613,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>44</v>
@@ -1679,19 +1643,19 @@
         <v>62</v>
       </c>
       <c r="L11" s="4">
-        <v>-37.2</v>
+        <v>-45</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O11" s="6">
-        <v>44</v>
-      </c>
-      <c r="P11" s="14">
-        <v>44</v>
+      <c r="O11" s="9">
+        <v>48</v>
+      </c>
+      <c r="P11" s="12">
+        <v>48</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1705,7 +1669,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>45</v>
@@ -1729,31 +1693,31 @@
         <v>131</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-51.6</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-11</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="N12" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="O12" s="6">
-        <v>56</v>
-      </c>
-      <c r="P12" s="15">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
       </c>
       <c r="R12" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1761,7 +1725,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>46</v>
@@ -1791,25 +1755,25 @@
         <v>64</v>
       </c>
       <c r="L13" s="4">
-        <v>-52.6</v>
+        <v>-50.8</v>
       </c>
       <c r="M13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O13" s="6">
-        <v>45</v>
-      </c>
-      <c r="P13" s="14">
-        <v>45</v>
+      <c r="O13" s="9">
+        <v>82</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="R13" s="14">
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1817,7 +1781,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>47</v>
@@ -1847,19 +1811,19 @@
         <v>65</v>
       </c>
       <c r="L14" s="4">
-        <v>-45.1</v>
+        <v>-47</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O14" s="6">
-        <v>47</v>
-      </c>
-      <c r="P14" s="14">
-        <v>47</v>
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1873,7 +1837,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
@@ -1903,15 +1867,15 @@
         <v>66</v>
       </c>
       <c r="L15" s="4">
-        <v>-51.6</v>
+        <v>-53.4</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O15" s="9">
+      <c r="O15" s="6">
         <v>0</v>
       </c>
       <c r="P15" s="8">
@@ -1929,7 +1893,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>49</v>
@@ -1959,25 +1923,25 @@
         <v>67</v>
       </c>
       <c r="L16" s="4">
-        <v>-50.8</v>
+        <v>-52.1</v>
       </c>
       <c r="M16" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O16" s="9">
-        <v>7</v>
-      </c>
-      <c r="P16" s="16">
-        <v>7</v>
+      <c r="O16" s="6">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
       </c>
       <c r="R16" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1985,7 +1949,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>50</v>
@@ -2015,25 +1979,25 @@
         <v>68</v>
       </c>
       <c r="L17" s="4">
-        <v>-47</v>
+        <v>-51.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O17" s="6">
-        <v>78</v>
-      </c>
-      <c r="P17" s="17">
-        <v>31</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>51</v>
-      </c>
-      <c r="R17" s="16">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2041,7 +2005,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>51</v>
@@ -2071,25 +2035,25 @@
         <v>69</v>
       </c>
       <c r="L18" s="4">
-        <v>-53.4</v>
+        <v>-47.4</v>
       </c>
       <c r="M18" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="O18" s="6">
-        <v>79</v>
-      </c>
-      <c r="P18" s="7">
-        <v>48</v>
-      </c>
-      <c r="Q18" s="17">
-        <v>31</v>
-      </c>
-      <c r="R18" s="16">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="138">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260827--01</t>
-  </si>
-  <si>
-    <t>20260827--02</t>
-  </si>
-  <si>
-    <t>20260827--03</t>
-  </si>
-  <si>
     <t>20260828--01</t>
   </si>
   <si>
@@ -121,13 +112,10 @@
     <t>20260902--03</t>
   </si>
   <si>
-    <t>04:28</t>
-  </si>
-  <si>
-    <t>06:28</t>
-  </si>
-  <si>
-    <t>05:32</t>
+    <t>20260903--01</t>
+  </si>
+  <si>
+    <t>20260903--02</t>
   </si>
   <si>
     <t>02:34</t>
@@ -172,18 +160,15 @@
     <t>05:43</t>
   </si>
   <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:38</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:00:28</t>
-  </si>
-  <si>
-    <t>03:37:24</t>
-  </si>
-  <si>
-    <t>20:15:02</t>
-  </si>
-  <si>
     <t>01:10:55</t>
   </si>
   <si>
@@ -226,13 +211,10 @@
     <t>23:25:22</t>
   </si>
   <si>
-    <t>02:03:06</t>
-  </si>
-  <si>
-    <t>03:39:31</t>
-  </si>
-  <si>
-    <t>20:17:22</t>
+    <t>01:02:36</t>
+  </si>
+  <si>
+    <t>22:35:20</t>
   </si>
   <si>
     <t>01:14:10</t>
@@ -277,13 +259,10 @@
     <t>23:27:40</t>
   </si>
   <si>
-    <t>02:05:20</t>
-  </si>
-  <si>
-    <t>03:42:45</t>
-  </si>
-  <si>
-    <t>20:20:08</t>
+    <t>01:04:55</t>
+  </si>
+  <si>
+    <t>22:37:54</t>
   </si>
   <si>
     <t>01:15:27</t>
@@ -328,13 +307,10 @@
     <t>23:30:32</t>
   </si>
   <si>
-    <t>02:07:34</t>
-  </si>
-  <si>
-    <t>03:45:59</t>
-  </si>
-  <si>
-    <t>20:22:54</t>
+    <t>01:07:40</t>
+  </si>
+  <si>
+    <t>22:40:14</t>
   </si>
   <si>
     <t>01:16:44</t>
@@ -379,13 +355,10 @@
     <t>23:33:23</t>
   </si>
   <si>
-    <t>02:10:12</t>
-  </si>
-  <si>
-    <t>03:48:06</t>
-  </si>
-  <si>
-    <t>20:25:15</t>
+    <t>01:10:25</t>
+  </si>
+  <si>
+    <t>22:42:32</t>
   </si>
   <si>
     <t>01:19:58</t>
@@ -430,25 +403,31 @@
     <t>23:35:41</t>
   </si>
   <si>
+    <t>01:12:44</t>
+  </si>
+  <si>
+    <t>22:45:07</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>22:35:21</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -482,7 +461,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -497,13 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,19 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -628,6 +619,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1031,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1109,49 +1106,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L2" s="4">
-        <v>-49.1</v>
+        <v>-51.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="O2" s="6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="P2" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1165,49 +1162,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>80</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="L3" s="4">
-        <v>-36.4</v>
+        <v>-44.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="O3" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P3" s="7">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1221,49 +1218,49 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="L4" s="4">
-        <v>-10.9</v>
+        <v>-49.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="O4" s="9">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="P4" s="10">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1277,49 +1274,49 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L5" s="4">
-        <v>-51.9</v>
+        <v>-37.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="O5" s="9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P5" s="11">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1333,43 +1330,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="L6" s="4">
-        <v>-44.2</v>
+        <v>-11</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="O6" s="9">
         <v>54</v>
@@ -1389,49 +1386,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L7" s="4">
-        <v>-49.9</v>
+        <v>-52.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="O7" s="9">
-        <v>48</v>
-      </c>
-      <c r="P7" s="12">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="P7" s="10">
+        <v>42</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
@@ -1445,49 +1442,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L8" s="4">
-        <v>-37.2</v>
+        <v>-45</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O8" s="9">
-        <v>50</v>
+        <v>137</v>
+      </c>
+      <c r="O8" s="6">
+        <v>23</v>
       </c>
       <c r="P8" s="12">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1501,49 +1498,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="L9" s="4">
-        <v>-11</v>
+        <v>-51.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O9" s="6">
-        <v>18</v>
-      </c>
-      <c r="P9" s="13">
-        <v>7</v>
+        <v>137</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1557,49 +1554,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L10" s="4">
-        <v>-52.6</v>
+        <v>-50.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" s="9">
-        <v>48</v>
-      </c>
-      <c r="P10" s="12">
-        <v>48</v>
+        <v>137</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1613,55 +1610,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L11" s="4">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" s="9">
-        <v>48</v>
-      </c>
-      <c r="P11" s="12">
-        <v>48</v>
+        <v>136</v>
+      </c>
+      <c r="O11" s="6">
+        <v>29</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="8">
-        <v>0</v>
+      <c r="R11" s="14">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1669,46 +1666,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L12" s="4">
-        <v>-51.6</v>
+        <v>-53.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="O12" s="6">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1716,8 +1713,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="8">
-        <v>1</v>
+      <c r="R12" s="15">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1725,46 +1722,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L13" s="4">
-        <v>-50.8</v>
+        <v>-52.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="9">
-        <v>82</v>
+        <v>137</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1772,8 +1769,8 @@
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="14">
-        <v>62</v>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1781,45 +1778,45 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L14" s="4">
-        <v>-47</v>
+        <v>-51.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O14" s="6">
+        <v>136</v>
+      </c>
+      <c r="O14" s="13">
         <v>0</v>
       </c>
       <c r="P14" s="8">
@@ -1837,52 +1834,52 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-47.4</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-53.4</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="N15" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="O15" s="13">
+        <v>1</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
       <c r="Q15" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="8">
         <v>0</v>
@@ -1893,46 +1890,46 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L16" s="4">
-        <v>-52.1</v>
+        <v>-54.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="O16" s="13">
+        <v>1</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
@@ -1941,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1949,46 +1946,46 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="L17" s="4">
-        <v>-51.7</v>
+        <v>-40</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="O17" s="13">
+        <v>8</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
@@ -1996,123 +1993,67 @@
       <c r="Q17" s="8">
         <v>0</v>
       </c>
-      <c r="R17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>27</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-47.4</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O18" s="6">
-        <v>0</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
-        <v>0</v>
+      <c r="R17" s="16">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2131,12 +2072,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2153,22 +2094,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="146">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260828--01</t>
-  </si>
-  <si>
-    <t>20260828--02</t>
-  </si>
-  <si>
     <t>20260829--01</t>
   </si>
   <si>
@@ -118,10 +112,13 @@
     <t>20260903--02</t>
   </si>
   <si>
-    <t>02:34</t>
-  </si>
-  <si>
-    <t>06:37</t>
+    <t>20260904--01</t>
+  </si>
+  <si>
+    <t>20260904--02</t>
+  </si>
+  <si>
+    <t>20260904--03</t>
   </si>
   <si>
     <t>06:20</t>
@@ -166,15 +163,15 @@
     <t>04:38</t>
   </si>
   <si>
+    <t>02:51</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:10:55</t>
-  </si>
-  <si>
-    <t>02:47:40</t>
-  </si>
-  <si>
     <t>01:57:57</t>
   </si>
   <si>
@@ -217,10 +214,13 @@
     <t>22:35:20</t>
   </si>
   <si>
-    <t>01:14:10</t>
-  </si>
-  <si>
-    <t>02:49:46</t>
+    <t>00:12:15</t>
+  </si>
+  <si>
+    <t>21:45:14</t>
+  </si>
+  <si>
+    <t>23:21:58</t>
   </si>
   <si>
     <t>02:00:07</t>
@@ -265,10 +265,13 @@
     <t>22:37:54</t>
   </si>
   <si>
-    <t>01:15:27</t>
-  </si>
-  <si>
-    <t>02:53:04</t>
+    <t>00:14:23</t>
+  </si>
+  <si>
+    <t>21:48:22</t>
+  </si>
+  <si>
+    <t>23:24:04</t>
   </si>
   <si>
     <t>02:03:17</t>
@@ -313,10 +316,13 @@
     <t>22:40:14</t>
   </si>
   <si>
-    <t>01:16:44</t>
-  </si>
-  <si>
-    <t>02:56:23</t>
+    <t>00:17:34</t>
+  </si>
+  <si>
+    <t>21:49:48</t>
+  </si>
+  <si>
+    <t>23:27:21</t>
   </si>
   <si>
     <t>02:06:27</t>
@@ -361,10 +367,13 @@
     <t>22:42:32</t>
   </si>
   <si>
-    <t>01:19:58</t>
-  </si>
-  <si>
-    <t>02:58:28</t>
+    <t>00:20:44</t>
+  </si>
+  <si>
+    <t>21:51:13</t>
+  </si>
+  <si>
+    <t>23:30:38</t>
   </si>
   <si>
     <t>02:08:36</t>
@@ -409,25 +418,40 @@
     <t>22:45:07</t>
   </si>
   <si>
+    <t>00:22:52</t>
+  </si>
+  <si>
+    <t>21:54:21</t>
+  </si>
+  <si>
+    <t>23:32:44</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>6°</t>
+  </si>
+  <si>
     <t>22:35:21</t>
   </si>
   <si>
+    <t>21:47:12</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -461,7 +485,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,13 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +530,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,25 +566,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -625,6 +673,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1106,49 +1166,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-49.9</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O2" s="6">
         <v>83</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-51.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" s="6">
-        <v>22</v>
-      </c>
       <c r="P2" s="7">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1162,49 +1222,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L3" s="4">
-        <v>-44.2</v>
+        <v>-37.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O3" s="6">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="P3" s="7">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1218,49 +1278,49 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="L4" s="4">
-        <v>-49.9</v>
+        <v>-11</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="O4" s="9">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P4" s="10">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1274,49 +1334,49 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="4">
-        <v>-37.2</v>
+        <v>-52.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O5" s="9">
-        <v>53</v>
+        <v>144</v>
+      </c>
+      <c r="O5" s="6">
+        <v>52</v>
       </c>
       <c r="P5" s="11">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1330,49 +1390,49 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="L6" s="4">
-        <v>-11</v>
+        <v>-45</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O6" s="9">
-        <v>54</v>
-      </c>
-      <c r="P6" s="11">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="O6" s="6">
+        <v>45</v>
+      </c>
+      <c r="P6" s="12">
+        <v>45</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1386,55 +1446,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-51.6</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O7" s="6">
         <v>50</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-52.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O7" s="9">
-        <v>42</v>
-      </c>
-      <c r="P7" s="10">
-        <v>42</v>
+      <c r="P7" s="13">
+        <v>28</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>0</v>
+      <c r="R7" s="12">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1442,55 +1502,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" s="4">
-        <v>-45</v>
+        <v>-50.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O8" s="6">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="P8" s="12">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="8">
-        <v>0</v>
+      <c r="R8" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1498,45 +1558,45 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L9" s="4">
-        <v>-51.6</v>
+        <v>-47</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O9" s="13">
+        <v>145</v>
+      </c>
+      <c r="O9" s="15">
         <v>0</v>
       </c>
       <c r="P9" s="8">
@@ -1554,46 +1614,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L10" s="4">
-        <v>-50.8</v>
+        <v>-53.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O10" s="15">
+        <v>2</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1602,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1610,46 +1670,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L11" s="4">
-        <v>-47</v>
+        <v>-52.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O11" s="6">
-        <v>29</v>
+        <v>144</v>
+      </c>
+      <c r="O11" s="9">
+        <v>25</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1657,8 +1717,8 @@
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="14">
-        <v>29</v>
+      <c r="R11" s="16">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1666,46 +1726,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L12" s="4">
-        <v>-53.4</v>
+        <v>-51.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O12" s="6">
-        <v>18</v>
+        <v>145</v>
+      </c>
+      <c r="O12" s="15">
+        <v>14</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1713,8 +1773,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="15">
-        <v>15</v>
+      <c r="R12" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1722,46 +1782,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L13" s="4">
-        <v>-52.1</v>
+        <v>-47.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O13" s="13">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O13" s="6">
+        <v>61</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1769,8 +1829,8 @@
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="R13" s="18">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1778,46 +1838,46 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L14" s="4">
-        <v>-51.7</v>
+        <v>-54.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O14" s="13">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O14" s="6">
+        <v>85</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
@@ -1825,8 +1885,8 @@
       <c r="Q14" s="8">
         <v>0</v>
       </c>
-      <c r="R14" s="8">
-        <v>0</v>
+      <c r="R14" s="19">
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1834,55 +1894,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="L15" s="4">
-        <v>-47.4</v>
+        <v>-40</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O15" s="13">
-        <v>1</v>
+        <v>144</v>
+      </c>
+      <c r="O15" s="9">
+        <v>22</v>
       </c>
       <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>1</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>14</v>
+      </c>
+      <c r="R15" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1890,49 +1950,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L16" s="4">
-        <v>-54.1</v>
+        <v>-52.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O16" s="13">
-        <v>1</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O16" s="15">
+        <v>5</v>
+      </c>
+      <c r="P16" s="14">
+        <v>4</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -1946,114 +2006,170 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-31.2</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O17" s="9">
+        <v>38</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>31</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>87</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-40</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N17" s="1" t="s">
+      <c r="D18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="O17" s="13">
-        <v>8</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="16">
-        <v>8</v>
+      <c r="K18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-47.7</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O18" s="9">
+        <v>21</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="20">
+        <v>21</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2072,12 +2188,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2094,22 +2210,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="131">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260829--01</t>
-  </si>
-  <si>
-    <t>20260829--02</t>
-  </si>
-  <si>
-    <t>20260829--03</t>
-  </si>
-  <si>
     <t>20260830--01</t>
   </si>
   <si>
@@ -121,49 +112,46 @@
     <t>20260904--03</t>
   </si>
   <si>
+    <t>20260905--01</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>02:44</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>03:48</t>
-  </si>
-  <si>
-    <t>02:09</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>02:46</t>
-  </si>
-  <si>
-    <t>06:36</t>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:37</t>
   </si>
   <si>
     <t>06:21</t>
   </si>
   <si>
-    <t>03:31</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>02:51</t>
+    <t>02:49</t>
   </si>
   <si>
     <t>06:34</t>
@@ -172,19 +160,10 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>01:57:57</t>
-  </si>
-  <si>
-    <t>03:35:36</t>
-  </si>
-  <si>
-    <t>20:13:39</t>
-  </si>
-  <si>
-    <t>01:08:14</t>
-  </si>
-  <si>
-    <t>02:45:26</t>
+    <t>01:08:15</t>
+  </si>
+  <si>
+    <t>02:45:28</t>
   </si>
   <si>
     <t>00:18:28</t>
@@ -193,97 +172,85 @@
     <t>01:55:23</t>
   </si>
   <si>
-    <t>23:28:38</t>
-  </si>
-  <si>
-    <t>01:05:23</t>
-  </si>
-  <si>
-    <t>00:15:23</t>
-  </si>
-  <si>
-    <t>01:53:03</t>
-  </si>
-  <si>
-    <t>23:25:22</t>
-  </si>
-  <si>
-    <t>01:02:36</t>
-  </si>
-  <si>
-    <t>22:35:20</t>
-  </si>
-  <si>
-    <t>00:12:15</t>
-  </si>
-  <si>
-    <t>21:45:14</t>
-  </si>
-  <si>
-    <t>23:21:58</t>
-  </si>
-  <si>
-    <t>02:00:07</t>
-  </si>
-  <si>
-    <t>03:38:22</t>
-  </si>
-  <si>
-    <t>20:17:02</t>
-  </si>
-  <si>
-    <t>01:10:32</t>
-  </si>
-  <si>
-    <t>02:47:44</t>
-  </si>
-  <si>
-    <t>00:21:03</t>
+    <t>23:28:37</t>
+  </si>
+  <si>
+    <t>01:05:21</t>
+  </si>
+  <si>
+    <t>00:15:19</t>
+  </si>
+  <si>
+    <t>01:52:58</t>
+  </si>
+  <si>
+    <t>23:25:15</t>
+  </si>
+  <si>
+    <t>01:02:28</t>
+  </si>
+  <si>
+    <t>22:35:08</t>
+  </si>
+  <si>
+    <t>00:12:03</t>
+  </si>
+  <si>
+    <t>21:44:57</t>
+  </si>
+  <si>
+    <t>23:21:41</t>
+  </si>
+  <si>
+    <t>22:31:19</t>
+  </si>
+  <si>
+    <t>01:10:34</t>
+  </si>
+  <si>
+    <t>02:47:45</t>
+  </si>
+  <si>
+    <t>00:21:04</t>
   </si>
   <si>
     <t>01:57:31</t>
   </si>
   <si>
-    <t>23:31:48</t>
-  </si>
-  <si>
-    <t>01:07:28</t>
-  </si>
-  <si>
-    <t>00:17:32</t>
-  </si>
-  <si>
-    <t>01:55:54</t>
-  </si>
-  <si>
-    <t>23:27:40</t>
-  </si>
-  <si>
-    <t>01:04:55</t>
-  </si>
-  <si>
-    <t>22:37:54</t>
-  </si>
-  <si>
-    <t>00:14:23</t>
-  </si>
-  <si>
-    <t>21:48:22</t>
-  </si>
-  <si>
-    <t>23:24:04</t>
-  </si>
-  <si>
-    <t>02:03:17</t>
-  </si>
-  <si>
-    <t>03:40:16</t>
-  </si>
-  <si>
-    <t>20:18:06</t>
-  </si>
-  <si>
-    <t>01:13:22</t>
+    <t>23:31:47</t>
+  </si>
+  <si>
+    <t>01:07:27</t>
+  </si>
+  <si>
+    <t>00:17:28</t>
+  </si>
+  <si>
+    <t>01:55:49</t>
+  </si>
+  <si>
+    <t>23:27:33</t>
+  </si>
+  <si>
+    <t>01:04:47</t>
+  </si>
+  <si>
+    <t>22:37:43</t>
+  </si>
+  <si>
+    <t>00:14:11</t>
+  </si>
+  <si>
+    <t>21:48:06</t>
+  </si>
+  <si>
+    <t>23:23:47</t>
+  </si>
+  <si>
+    <t>22:33:28</t>
+  </si>
+  <si>
+    <t>01:13:23</t>
   </si>
   <si>
     <t>02:50:33</t>
@@ -292,160 +259,148 @@
     <t>00:23:20</t>
   </si>
   <si>
-    <t>02:00:43</t>
-  </si>
-  <si>
-    <t>23:33:11</t>
-  </si>
-  <si>
-    <t>01:10:46</t>
-  </si>
-  <si>
-    <t>00:20:43</t>
-  </si>
-  <si>
-    <t>01:57:40</t>
-  </si>
-  <si>
-    <t>23:30:32</t>
-  </si>
-  <si>
-    <t>01:07:40</t>
-  </si>
-  <si>
-    <t>22:40:14</t>
-  </si>
-  <si>
-    <t>00:17:34</t>
-  </si>
-  <si>
-    <t>21:49:48</t>
-  </si>
-  <si>
-    <t>23:27:21</t>
-  </si>
-  <si>
-    <t>02:06:27</t>
-  </si>
-  <si>
-    <t>03:42:10</t>
-  </si>
-  <si>
-    <t>20:19:11</t>
-  </si>
-  <si>
-    <t>01:16:12</t>
+    <t>02:00:42</t>
+  </si>
+  <si>
+    <t>23:33:09</t>
+  </si>
+  <si>
+    <t>01:10:44</t>
+  </si>
+  <si>
+    <t>00:20:38</t>
+  </si>
+  <si>
+    <t>01:57:35</t>
+  </si>
+  <si>
+    <t>23:30:24</t>
+  </si>
+  <si>
+    <t>01:07:32</t>
+  </si>
+  <si>
+    <t>22:40:01</t>
+  </si>
+  <si>
+    <t>00:17:22</t>
+  </si>
+  <si>
+    <t>21:49:31</t>
+  </si>
+  <si>
+    <t>23:27:04</t>
+  </si>
+  <si>
+    <t>22:36:38</t>
+  </si>
+  <si>
+    <t>01:16:13</t>
   </si>
   <si>
     <t>02:53:21</t>
   </si>
   <si>
-    <t>00:25:38</t>
+    <t>00:25:37</t>
   </si>
   <si>
     <t>02:03:54</t>
   </si>
   <si>
-    <t>23:34:34</t>
-  </si>
-  <si>
-    <t>01:14:04</t>
-  </si>
-  <si>
-    <t>00:23:53</t>
-  </si>
-  <si>
-    <t>01:59:25</t>
-  </si>
-  <si>
-    <t>23:33:23</t>
-  </si>
-  <si>
-    <t>01:10:25</t>
-  </si>
-  <si>
-    <t>22:42:32</t>
-  </si>
-  <si>
-    <t>00:20:44</t>
-  </si>
-  <si>
-    <t>21:51:13</t>
-  </si>
-  <si>
-    <t>23:30:38</t>
-  </si>
-  <si>
-    <t>02:08:36</t>
-  </si>
-  <si>
-    <t>03:44:57</t>
-  </si>
-  <si>
-    <t>20:22:35</t>
-  </si>
-  <si>
-    <t>01:18:31</t>
+    <t>23:34:31</t>
+  </si>
+  <si>
+    <t>01:14:02</t>
+  </si>
+  <si>
+    <t>00:23:48</t>
+  </si>
+  <si>
+    <t>01:59:21</t>
+  </si>
+  <si>
+    <t>23:33:15</t>
+  </si>
+  <si>
+    <t>01:10:17</t>
+  </si>
+  <si>
+    <t>22:42:20</t>
+  </si>
+  <si>
+    <t>00:20:32</t>
+  </si>
+  <si>
+    <t>21:50:55</t>
+  </si>
+  <si>
+    <t>23:30:21</t>
+  </si>
+  <si>
+    <t>22:39:48</t>
+  </si>
+  <si>
+    <t>01:18:32</t>
   </si>
   <si>
     <t>02:55:39</t>
   </si>
   <si>
-    <t>00:28:13</t>
-  </si>
-  <si>
-    <t>02:06:02</t>
-  </si>
-  <si>
-    <t>23:37:43</t>
-  </si>
-  <si>
-    <t>01:16:09</t>
-  </si>
-  <si>
-    <t>00:26:02</t>
-  </si>
-  <si>
-    <t>02:02:16</t>
-  </si>
-  <si>
-    <t>23:35:41</t>
-  </si>
-  <si>
-    <t>01:12:44</t>
-  </si>
-  <si>
-    <t>22:45:07</t>
-  </si>
-  <si>
-    <t>00:22:52</t>
-  </si>
-  <si>
-    <t>21:54:21</t>
-  </si>
-  <si>
-    <t>23:32:44</t>
+    <t>00:28:12</t>
+  </si>
+  <si>
+    <t>02:06:01</t>
+  </si>
+  <si>
+    <t>23:37:41</t>
+  </si>
+  <si>
+    <t>01:16:07</t>
+  </si>
+  <si>
+    <t>00:25:57</t>
+  </si>
+  <si>
+    <t>02:02:11</t>
+  </si>
+  <si>
+    <t>23:35:32</t>
+  </si>
+  <si>
+    <t>01:12:35</t>
+  </si>
+  <si>
+    <t>22:44:54</t>
+  </si>
+  <si>
+    <t>00:22:39</t>
+  </si>
+  <si>
+    <t>21:54:03</t>
+  </si>
+  <si>
+    <t>23:32:26</t>
+  </si>
+  <si>
+    <t>22:41:57</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>6°</t>
   </si>
   <si>
-    <t>22:35:21</t>
-  </si>
-  <si>
-    <t>21:47:12</t>
+    <t>22:35:09</t>
+  </si>
+  <si>
+    <t>21:46:56</t>
+  </si>
+  <si>
+    <t>22:31:26</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>A+B</t>
   </si>
   <si>
     <t>3</t>
@@ -506,7 +461,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +473,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,61 +539,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1088,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1166,49 +1121,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L2" s="4">
-        <v>-49.9</v>
+        <v>-52.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="O2" s="6">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P2" s="7">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1222,49 +1177,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L3" s="4">
-        <v>-37.2</v>
+        <v>-45</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="O3" s="6">
-        <v>83</v>
-      </c>
-      <c r="P3" s="7">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="P3" s="9">
+        <v>84</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1278,55 +1233,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="L4" s="4">
-        <v>-11</v>
+        <v>-51.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O4" s="9">
-        <v>42</v>
-      </c>
-      <c r="P4" s="10">
-        <v>42</v>
+        <v>129</v>
+      </c>
+      <c r="O4" s="10">
+        <v>10</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>0</v>
+      <c r="R4" s="11">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1334,55 +1289,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L5" s="4">
-        <v>-52.6</v>
+        <v>-50.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="O5" s="6">
-        <v>52</v>
-      </c>
-      <c r="P5" s="11">
-        <v>52</v>
+        <v>69</v>
+      </c>
+      <c r="P5" s="12">
+        <v>59</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="R5" s="13">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1390,49 +1345,49 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L6" s="4">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O6" s="6">
-        <v>45</v>
-      </c>
-      <c r="P6" s="12">
-        <v>45</v>
+        <v>130</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1446,55 +1401,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L7" s="4">
-        <v>-51.6</v>
+        <v>-53.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O7" s="6">
-        <v>50</v>
-      </c>
-      <c r="P7" s="13">
-        <v>28</v>
+        <v>129</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="12">
-        <v>43</v>
+      <c r="R7" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1502,55 +1457,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L8" s="4">
-        <v>-50.8</v>
+        <v>-52.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O8" s="6">
-        <v>47</v>
-      </c>
-      <c r="P8" s="12">
-        <v>47</v>
+        <v>129</v>
+      </c>
+      <c r="O8" s="10">
+        <v>1</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="14">
-        <v>6</v>
+      <c r="R8" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1558,46 +1513,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L9" s="4">
-        <v>-47</v>
+        <v>-51.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O9" s="15">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="O9" s="14">
+        <v>24</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1605,8 +1560,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="8">
-        <v>0</v>
+      <c r="R9" s="15">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1614,46 +1569,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-47.4</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-53.4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O10" s="15">
-        <v>2</v>
+        <v>129</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1662,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1670,46 +1625,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-54.1</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-52.1</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O11" s="9">
-        <v>25</v>
+      <c r="O11" s="10">
+        <v>4</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1718,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="16">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1726,55 +1681,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="L12" s="4">
-        <v>-51.7</v>
+        <v>-39.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O12" s="15">
-        <v>14</v>
+        <v>129</v>
+      </c>
+      <c r="O12" s="6">
+        <v>83</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="8">
-        <v>0</v>
+      <c r="Q12" s="7">
+        <v>82</v>
       </c>
       <c r="R12" s="17">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1782,55 +1737,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L13" s="4">
-        <v>-47.4</v>
+        <v>-52.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="O13" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="18">
-        <v>57</v>
+      <c r="Q13" s="18">
+        <v>28</v>
+      </c>
+      <c r="R13" s="19">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1838,55 +1793,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="L14" s="4">
-        <v>-54.1</v>
+        <v>-31.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O14" s="6">
-        <v>85</v>
+        <v>130</v>
+      </c>
+      <c r="O14" s="10">
+        <v>14</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="19">
-        <v>75</v>
+      <c r="Q14" s="20">
+        <v>13</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1894,55 +1849,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="L15" s="4">
-        <v>-40</v>
+        <v>-47.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O15" s="9">
-        <v>22</v>
+        <v>129</v>
+      </c>
+      <c r="O15" s="10">
+        <v>12</v>
       </c>
       <c r="P15" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>14</v>
-      </c>
-      <c r="R15" s="17">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>12</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1950,49 +1905,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="L16" s="4">
-        <v>-52.6</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O16" s="15">
-        <v>5</v>
-      </c>
-      <c r="P16" s="14">
-        <v>4</v>
+        <v>129</v>
+      </c>
+      <c r="O16" s="10">
+        <v>2</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2001,175 +1956,63 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-31.2</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O17" s="9">
-        <v>38</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>31</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>87</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-47.7</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O18" s="9">
-        <v>21</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="20">
-        <v>21</v>
-      </c>
-      <c r="R18" s="8">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2188,12 +2031,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2210,22 +2053,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="138">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260830--01</t>
-  </si>
-  <si>
-    <t>20260830--02</t>
-  </si>
-  <si>
     <t>20260831--01</t>
   </si>
   <si>
@@ -115,10 +109,13 @@
     <t>20260905--01</t>
   </si>
   <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>05:36</t>
+    <t>20260906--01</t>
+  </si>
+  <si>
+    <t>20260906--02</t>
+  </si>
+  <si>
+    <t>20260906--03</t>
   </si>
   <si>
     <t>04:33</t>
@@ -157,15 +154,12 @@
     <t>06:34</t>
   </si>
   <si>
+    <t>03:27</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:08:15</t>
-  </si>
-  <si>
-    <t>02:45:28</t>
-  </si>
-  <si>
     <t>00:18:28</t>
   </si>
   <si>
@@ -205,10 +199,13 @@
     <t>22:31:19</t>
   </si>
   <si>
-    <t>01:10:34</t>
-  </si>
-  <si>
-    <t>02:47:45</t>
+    <t>00:08:58</t>
+  </si>
+  <si>
+    <t>21:40:55</t>
+  </si>
+  <si>
+    <t>23:18:07</t>
   </si>
   <si>
     <t>00:21:04</t>
@@ -250,10 +247,13 @@
     <t>22:33:28</t>
   </si>
   <si>
-    <t>01:13:23</t>
-  </si>
-  <si>
-    <t>02:50:33</t>
+    <t>00:11:50</t>
+  </si>
+  <si>
+    <t>21:43:13</t>
+  </si>
+  <si>
+    <t>23:20:26</t>
   </si>
   <si>
     <t>00:23:20</t>
@@ -295,10 +295,13 @@
     <t>22:36:38</t>
   </si>
   <si>
-    <t>01:16:13</t>
-  </si>
-  <si>
-    <t>02:53:21</t>
+    <t>00:13:33</t>
+  </si>
+  <si>
+    <t>21:46:04</t>
+  </si>
+  <si>
+    <t>23:23:11</t>
   </si>
   <si>
     <t>00:25:37</t>
@@ -340,10 +343,13 @@
     <t>22:39:48</t>
   </si>
   <si>
-    <t>01:18:32</t>
-  </si>
-  <si>
-    <t>02:55:39</t>
+    <t>00:15:17</t>
+  </si>
+  <si>
+    <t>21:48:55</t>
+  </si>
+  <si>
+    <t>23:25:56</t>
   </si>
   <si>
     <t>00:28:12</t>
@@ -385,12 +391,24 @@
     <t>22:41:57</t>
   </si>
   <si>
+    <t>00:18:09</t>
+  </si>
+  <si>
+    <t>21:51:13</t>
+  </si>
+  <si>
+    <t>23:28:14</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
     <t>6°</t>
   </si>
   <si>
+    <t>9°</t>
+  </si>
+  <si>
     <t>22:35:09</t>
   </si>
   <si>
@@ -398,6 +416,9 @@
   </si>
   <si>
     <t>22:31:26</t>
+  </si>
+  <si>
+    <t>21:43:06</t>
   </si>
   <si>
     <t>B</t>
@@ -455,13 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,25 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,25 +548,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1043,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1121,10 +1142,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -1133,43 +1154,43 @@
         <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>48</v>
       </c>
       <c r="L2" s="4">
-        <v>-52.6</v>
+        <v>-51.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="O2" s="6">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="P2" s="7">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
-        <v>0</v>
+      <c r="R2" s="9">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1177,10 +1198,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -1189,43 +1210,43 @@
         <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>49</v>
       </c>
       <c r="L3" s="4">
-        <v>-45</v>
+        <v>-50.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="O3" s="6">
-        <v>84</v>
-      </c>
-      <c r="P3" s="9">
-        <v>84</v>
+        <v>30</v>
+      </c>
+      <c r="P3" s="10">
+        <v>30</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
-        <v>0</v>
+      <c r="R3" s="11">
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1233,10 +1254,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -1245,34 +1266,34 @@
         <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L4" s="4">
-        <v>-51.6</v>
+        <v>-47</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O4" s="10">
-        <v>10</v>
+        <v>137</v>
+      </c>
+      <c r="O4" s="12">
+        <v>0</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
@@ -1280,8 +1301,8 @@
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="11">
-        <v>10</v>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1289,10 +1310,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>47</v>
@@ -1301,43 +1322,43 @@
         <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>51</v>
       </c>
       <c r="L5" s="4">
-        <v>-50.8</v>
+        <v>-53.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O5" s="6">
-        <v>69</v>
-      </c>
-      <c r="P5" s="12">
-        <v>59</v>
+        <v>136</v>
+      </c>
+      <c r="O5" s="12">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="13">
-        <v>53</v>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1345,10 +1366,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -1357,34 +1378,34 @@
         <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="L6" s="4">
-        <v>-47</v>
+        <v>-52.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="O6" s="6">
+        <v>37</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1392,8 +1413,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="R6" s="13">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1401,10 +1422,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -1413,34 +1434,34 @@
         <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L7" s="4">
-        <v>-53.4</v>
+        <v>-51.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="O7" s="14">
+        <v>65</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1448,8 +1469,8 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>0</v>
+      <c r="R7" s="15">
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1457,10 +1478,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
@@ -1469,34 +1490,34 @@
         <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>54</v>
       </c>
       <c r="L8" s="4">
-        <v>-52.1</v>
+        <v>-47.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O8" s="10">
-        <v>1</v>
+        <v>136</v>
+      </c>
+      <c r="O8" s="12">
+        <v>0</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1505,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1513,10 +1534,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -1525,34 +1546,34 @@
         <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>55</v>
       </c>
       <c r="L9" s="4">
-        <v>-51.7</v>
+        <v>-54.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O9" s="14">
-        <v>24</v>
+        <v>136</v>
+      </c>
+      <c r="O9" s="12">
+        <v>1</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1560,8 +1581,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="15">
-        <v>24</v>
+      <c r="R9" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1569,10 +1590,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
@@ -1581,43 +1602,43 @@
         <v>56</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="L10" s="4">
-        <v>-47.4</v>
+        <v>-39.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O10" s="10">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="O10" s="6">
+        <v>25</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
+      <c r="Q10" s="9">
+        <v>15</v>
+      </c>
+      <c r="R10" s="16">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1625,10 +1646,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -1637,42 +1658,42 @@
         <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>57</v>
       </c>
       <c r="L11" s="4">
-        <v>-54.1</v>
+        <v>-52.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O11" s="10">
-        <v>4</v>
+        <v>136</v>
+      </c>
+      <c r="O11" s="12">
+        <v>14</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="16">
+      <c r="Q11" s="9">
+        <v>14</v>
+      </c>
+      <c r="R11" s="17">
         <v>3</v>
       </c>
     </row>
@@ -1681,10 +1702,10 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -1693,43 +1714,43 @@
         <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="L12" s="4">
-        <v>-39.9</v>
+        <v>-31.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O12" s="6">
-        <v>83</v>
+        <v>137</v>
+      </c>
+      <c r="O12" s="12">
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="7">
-        <v>82</v>
-      </c>
-      <c r="R12" s="17">
-        <v>50</v>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1737,10 +1758,10 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>47</v>
@@ -1749,43 +1770,43 @@
         <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>59</v>
       </c>
       <c r="L13" s="4">
-        <v>-52.6</v>
+        <v>-47.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O13" s="6">
-        <v>60</v>
+        <v>136</v>
+      </c>
+      <c r="O13" s="12">
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="18">
-        <v>28</v>
-      </c>
-      <c r="R13" s="19">
-        <v>39</v>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1793,10 +1814,10 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
@@ -1805,43 +1826,43 @@
         <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L14" s="4">
-        <v>-31.1</v>
+        <v>-40</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O14" s="10">
-        <v>14</v>
+        <v>136</v>
+      </c>
+      <c r="O14" s="6">
+        <v>45</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="20">
-        <v>13</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="18">
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1849,7 +1870,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>46</v>
@@ -1861,43 +1882,43 @@
         <v>61</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>61</v>
       </c>
       <c r="L15" s="4">
-        <v>-47.6</v>
+        <v>-53.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O15" s="10">
-        <v>12</v>
+        <v>137</v>
+      </c>
+      <c r="O15" s="14">
+        <v>90</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="11">
-        <v>12</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="19">
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1905,10 +1926,10 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -1917,102 +1938,158 @@
         <v>62</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-31</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O16" s="14">
+        <v>57</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="20">
+        <v>10</v>
+      </c>
+      <c r="R16" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>25</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L16" s="4">
-        <v>-40</v>
-      </c>
-      <c r="M16" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O16" s="10">
+      <c r="K17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-47.8</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O17" s="14">
+        <v>72</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
         <v>2</v>
       </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>1</v>
+      <c r="R17" s="9">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2031,12 +2108,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2053,22 +2130,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="136">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260831--01</t>
-  </si>
-  <si>
-    <t>20260831--02</t>
-  </si>
-  <si>
-    <t>20260831--03</t>
-  </si>
-  <si>
     <t>20260901--01</t>
   </si>
   <si>
@@ -118,13 +109,10 @@
     <t>20260906--03</t>
   </si>
   <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>02:44</t>
+    <t>20260907--01</t>
+  </si>
+  <si>
+    <t>20260907--02</t>
   </si>
   <si>
     <t>06:35</t>
@@ -133,271 +121,265 @@
     <t>06:20</t>
   </si>
   <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:30</t>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>02:49</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>05:28</t>
   </si>
   <si>
     <t>04:37</t>
   </si>
   <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>02:49</t>
-  </si>
-  <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>03:27</t>
-  </si>
-  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:18:28</t>
-  </si>
-  <si>
-    <t>01:55:23</t>
-  </si>
-  <si>
-    <t>23:28:37</t>
+    <t>01:40</t>
   </si>
   <si>
     <t>01:05:21</t>
   </si>
   <si>
-    <t>00:15:19</t>
-  </si>
-  <si>
-    <t>01:52:58</t>
-  </si>
-  <si>
-    <t>23:25:15</t>
-  </si>
-  <si>
-    <t>01:02:28</t>
-  </si>
-  <si>
-    <t>22:35:08</t>
-  </si>
-  <si>
-    <t>00:12:03</t>
-  </si>
-  <si>
-    <t>21:44:57</t>
-  </si>
-  <si>
-    <t>23:21:41</t>
-  </si>
-  <si>
-    <t>22:31:19</t>
-  </si>
-  <si>
-    <t>00:08:58</t>
-  </si>
-  <si>
-    <t>21:40:55</t>
-  </si>
-  <si>
-    <t>23:18:07</t>
-  </si>
-  <si>
-    <t>00:21:04</t>
-  </si>
-  <si>
-    <t>01:57:31</t>
-  </si>
-  <si>
-    <t>23:31:47</t>
+    <t>00:15:20</t>
+  </si>
+  <si>
+    <t>01:53:00</t>
+  </si>
+  <si>
+    <t>23:25:18</t>
+  </si>
+  <si>
+    <t>01:02:31</t>
+  </si>
+  <si>
+    <t>22:35:13</t>
+  </si>
+  <si>
+    <t>00:12:08</t>
+  </si>
+  <si>
+    <t>21:45:04</t>
+  </si>
+  <si>
+    <t>23:21:48</t>
+  </si>
+  <si>
+    <t>22:31:29</t>
+  </si>
+  <si>
+    <t>00:09:08</t>
+  </si>
+  <si>
+    <t>21:41:08</t>
+  </si>
+  <si>
+    <t>23:18:21</t>
+  </si>
+  <si>
+    <t>20:50:46</t>
+  </si>
+  <si>
+    <t>22:27:40</t>
   </si>
   <si>
     <t>01:07:27</t>
   </si>
   <si>
-    <t>00:17:28</t>
-  </si>
-  <si>
-    <t>01:55:49</t>
-  </si>
-  <si>
-    <t>23:27:33</t>
-  </si>
-  <si>
-    <t>01:04:47</t>
-  </si>
-  <si>
-    <t>22:37:43</t>
-  </si>
-  <si>
-    <t>00:14:11</t>
-  </si>
-  <si>
-    <t>21:48:06</t>
-  </si>
-  <si>
-    <t>23:23:47</t>
-  </si>
-  <si>
-    <t>22:33:28</t>
-  </si>
-  <si>
-    <t>00:11:50</t>
-  </si>
-  <si>
-    <t>21:43:13</t>
-  </si>
-  <si>
-    <t>23:20:26</t>
-  </si>
-  <si>
-    <t>00:23:20</t>
-  </si>
-  <si>
-    <t>02:00:42</t>
-  </si>
-  <si>
-    <t>23:33:09</t>
-  </si>
-  <si>
-    <t>01:10:44</t>
-  </si>
-  <si>
-    <t>00:20:38</t>
-  </si>
-  <si>
-    <t>01:57:35</t>
-  </si>
-  <si>
-    <t>23:30:24</t>
-  </si>
-  <si>
-    <t>01:07:32</t>
-  </si>
-  <si>
-    <t>22:40:01</t>
-  </si>
-  <si>
-    <t>00:17:22</t>
-  </si>
-  <si>
-    <t>21:49:31</t>
-  </si>
-  <si>
-    <t>23:27:04</t>
-  </si>
-  <si>
-    <t>22:36:38</t>
-  </si>
-  <si>
-    <t>00:13:33</t>
-  </si>
-  <si>
-    <t>21:46:04</t>
-  </si>
-  <si>
-    <t>23:23:11</t>
-  </si>
-  <si>
-    <t>00:25:37</t>
-  </si>
-  <si>
-    <t>02:03:54</t>
-  </si>
-  <si>
-    <t>23:34:31</t>
+    <t>00:17:29</t>
+  </si>
+  <si>
+    <t>01:55:51</t>
+  </si>
+  <si>
+    <t>23:27:36</t>
+  </si>
+  <si>
+    <t>01:04:49</t>
+  </si>
+  <si>
+    <t>22:37:48</t>
+  </si>
+  <si>
+    <t>00:14:16</t>
+  </si>
+  <si>
+    <t>21:48:13</t>
+  </si>
+  <si>
+    <t>23:23:54</t>
+  </si>
+  <si>
+    <t>22:33:38</t>
+  </si>
+  <si>
+    <t>00:12:01</t>
+  </si>
+  <si>
+    <t>21:43:26</t>
+  </si>
+  <si>
+    <t>23:20:40</t>
+  </si>
+  <si>
+    <t>20:53:21</t>
+  </si>
+  <si>
+    <t>22:29:48</t>
+  </si>
+  <si>
+    <t>01:10:45</t>
+  </si>
+  <si>
+    <t>00:20:40</t>
+  </si>
+  <si>
+    <t>01:57:36</t>
+  </si>
+  <si>
+    <t>23:30:27</t>
+  </si>
+  <si>
+    <t>01:07:34</t>
+  </si>
+  <si>
+    <t>22:40:06</t>
+  </si>
+  <si>
+    <t>00:17:26</t>
+  </si>
+  <si>
+    <t>21:49:37</t>
+  </si>
+  <si>
+    <t>23:27:11</t>
+  </si>
+  <si>
+    <t>22:36:48</t>
+  </si>
+  <si>
+    <t>00:13:43</t>
+  </si>
+  <si>
+    <t>21:46:18</t>
+  </si>
+  <si>
+    <t>23:23:24</t>
+  </si>
+  <si>
+    <t>20:55:39</t>
+  </si>
+  <si>
+    <t>22:32:58</t>
   </si>
   <si>
     <t>01:14:02</t>
   </si>
   <si>
-    <t>00:23:48</t>
-  </si>
-  <si>
-    <t>01:59:21</t>
-  </si>
-  <si>
-    <t>23:33:15</t>
-  </si>
-  <si>
-    <t>01:10:17</t>
-  </si>
-  <si>
-    <t>22:42:20</t>
-  </si>
-  <si>
-    <t>00:20:32</t>
-  </si>
-  <si>
-    <t>21:50:55</t>
-  </si>
-  <si>
-    <t>23:30:21</t>
-  </si>
-  <si>
-    <t>22:39:48</t>
-  </si>
-  <si>
-    <t>00:15:17</t>
-  </si>
-  <si>
-    <t>21:48:55</t>
-  </si>
-  <si>
-    <t>23:25:56</t>
-  </si>
-  <si>
-    <t>00:28:12</t>
-  </si>
-  <si>
-    <t>02:06:01</t>
-  </si>
-  <si>
-    <t>23:37:41</t>
+    <t>00:23:49</t>
+  </si>
+  <si>
+    <t>01:59:22</t>
+  </si>
+  <si>
+    <t>23:33:17</t>
+  </si>
+  <si>
+    <t>01:10:20</t>
+  </si>
+  <si>
+    <t>22:42:24</t>
+  </si>
+  <si>
+    <t>00:20:36</t>
+  </si>
+  <si>
+    <t>21:51:02</t>
+  </si>
+  <si>
+    <t>23:30:28</t>
+  </si>
+  <si>
+    <t>22:39:58</t>
+  </si>
+  <si>
+    <t>00:15:26</t>
+  </si>
+  <si>
+    <t>21:49:09</t>
+  </si>
+  <si>
+    <t>23:26:08</t>
+  </si>
+  <si>
+    <t>20:57:58</t>
+  </si>
+  <si>
+    <t>22:36:08</t>
   </si>
   <si>
     <t>01:16:07</t>
   </si>
   <si>
-    <t>00:25:57</t>
-  </si>
-  <si>
-    <t>02:02:11</t>
-  </si>
-  <si>
-    <t>23:35:32</t>
-  </si>
-  <si>
-    <t>01:12:35</t>
-  </si>
-  <si>
-    <t>22:44:54</t>
-  </si>
-  <si>
-    <t>00:22:39</t>
-  </si>
-  <si>
-    <t>21:54:03</t>
-  </si>
-  <si>
-    <t>23:32:26</t>
-  </si>
-  <si>
-    <t>22:41:57</t>
-  </si>
-  <si>
-    <t>00:18:09</t>
-  </si>
-  <si>
-    <t>21:51:13</t>
-  </si>
-  <si>
-    <t>23:28:14</t>
+    <t>00:25:58</t>
+  </si>
+  <si>
+    <t>02:02:13</t>
+  </si>
+  <si>
+    <t>23:35:35</t>
+  </si>
+  <si>
+    <t>01:12:38</t>
+  </si>
+  <si>
+    <t>22:44:58</t>
+  </si>
+  <si>
+    <t>00:22:44</t>
+  </si>
+  <si>
+    <t>21:54:10</t>
+  </si>
+  <si>
+    <t>23:32:33</t>
+  </si>
+  <si>
+    <t>22:42:07</t>
+  </si>
+  <si>
+    <t>00:18:18</t>
+  </si>
+  <si>
+    <t>21:51:26</t>
+  </si>
+  <si>
+    <t>23:28:27</t>
+  </si>
+  <si>
+    <t>21:00:32</t>
+  </si>
+  <si>
+    <t>22:38:16</t>
   </si>
   <si>
     <t>0°</t>
@@ -409,25 +391,37 @@
     <t>9°</t>
   </si>
   <si>
-    <t>22:35:09</t>
-  </si>
-  <si>
-    <t>21:46:56</t>
-  </si>
-  <si>
-    <t>22:31:26</t>
-  </si>
-  <si>
-    <t>21:43:06</t>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>21:47:02</t>
+  </si>
+  <si>
+    <t>22:31:35</t>
+  </si>
+  <si>
+    <t>21:43:19</t>
+  </si>
+  <si>
+    <t>20:55:01</t>
+  </si>
+  <si>
+    <t>22:27:48</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -461,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,13 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,43 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -655,12 +637,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1064,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1142,55 +1118,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L2" s="4">
-        <v>-51.6</v>
+        <v>-53.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O2" s="6">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="P2" s="7">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>17</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1198,55 +1174,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-52.1</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O3" s="6">
+        <v>78</v>
+      </c>
+      <c r="P3" s="9">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
         <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-50.8</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O3" s="6">
-        <v>30</v>
-      </c>
-      <c r="P3" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="11">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1254,55 +1230,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L4" s="4">
-        <v>-47</v>
+        <v>-51.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O4" s="12">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="O4" s="6">
+        <v>95</v>
+      </c>
+      <c r="P4" s="9">
+        <v>54</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>0</v>
+      <c r="R4" s="7">
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1310,45 +1286,45 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L5" s="4">
-        <v>-53.4</v>
+        <v>-47.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" s="12">
+        <v>133</v>
+      </c>
+      <c r="O5" s="11">
         <v>0</v>
       </c>
       <c r="P5" s="8">
@@ -1366,46 +1342,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L6" s="4">
-        <v>-52.1</v>
+        <v>-54.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O6" s="6">
-        <v>37</v>
+        <v>133</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1413,8 +1389,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="13">
-        <v>37</v>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1422,55 +1398,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L7" s="4">
-        <v>-51.7</v>
+        <v>-40</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O7" s="14">
-        <v>65</v>
+        <v>133</v>
+      </c>
+      <c r="O7" s="12">
+        <v>41</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="15">
-        <v>65</v>
+      <c r="Q7" s="13">
+        <v>29</v>
+      </c>
+      <c r="R7" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1478,52 +1454,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L8" s="4">
-        <v>-47.4</v>
+        <v>-52.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O8" s="12">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="O8" s="11">
+        <v>2</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
       <c r="Q8" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1534,55 +1510,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-31.1</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O9" s="6">
+        <v>85</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
         <v>47</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="R9" s="9">
         <v>55</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-54.1</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O9" s="12">
-        <v>1</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1590,55 +1566,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-47.6</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="L10" s="4">
-        <v>-39.9</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O10" s="6">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="9">
-        <v>15</v>
-      </c>
-      <c r="R10" s="16">
-        <v>25</v>
+      <c r="Q10" s="13">
+        <v>28</v>
+      </c>
+      <c r="R10" s="13">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1646,55 +1622,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="L11" s="4">
-        <v>-52.6</v>
+        <v>-40</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O11" s="12">
-        <v>14</v>
+        <v>133</v>
+      </c>
+      <c r="O11" s="11">
+        <v>13</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="9">
-        <v>14</v>
-      </c>
-      <c r="R11" s="17">
-        <v>3</v>
+      <c r="Q11" s="14">
+        <v>11</v>
+      </c>
+      <c r="R11" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1702,55 +1678,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="L12" s="4">
-        <v>-31.1</v>
+        <v>-53.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="O12" s="11">
+        <v>10</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
+      <c r="Q12" s="15">
+        <v>5</v>
+      </c>
+      <c r="R12" s="15">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1758,52 +1734,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="L13" s="4">
-        <v>-47.6</v>
+        <v>-31.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O13" s="12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="8">
-        <v>0</v>
+      <c r="Q13" s="16">
+        <v>33</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1814,55 +1790,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-47.8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="L14" s="4">
-        <v>-40</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="O14" s="6">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="18">
-        <v>45</v>
+      <c r="Q14" s="17">
+        <v>49</v>
+      </c>
+      <c r="R14" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1870,55 +1846,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="L15" s="4">
-        <v>-53.1</v>
+        <v>-21.2</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O15" s="14">
+      <c r="O15" s="6">
         <v>90</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="19">
+      <c r="Q15" s="18">
         <v>90</v>
+      </c>
+      <c r="R15" s="10">
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1926,170 +1902,114 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="L16" s="4">
-        <v>-31</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O16" s="14">
-        <v>57</v>
+        <v>133</v>
+      </c>
+      <c r="O16" s="6">
+        <v>91</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="20">
-        <v>10</v>
-      </c>
-      <c r="R16" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>25</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-47.8</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O17" s="14">
-        <v>72</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>2</v>
-      </c>
-      <c r="R17" s="9">
-        <v>15</v>
+      <c r="Q16" s="18">
+        <v>91</v>
+      </c>
+      <c r="R16" s="10">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2108,12 +2028,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2130,22 +2050,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="147">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260901--01</t>
-  </si>
-  <si>
     <t>20260902--01</t>
   </si>
   <si>
@@ -115,19 +112,22 @@
     <t>20260907--02</t>
   </si>
   <si>
-    <t>06:35</t>
+    <t>20260908--01</t>
+  </si>
+  <si>
+    <t>20260908--02</t>
   </si>
   <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>03:31</t>
+    <t>03:30</t>
   </si>
   <si>
     <t>05:41</t>
   </si>
   <si>
-    <t>05:31</t>
+    <t>05:30</t>
   </si>
   <si>
     <t>04:36</t>
@@ -139,205 +139,220 @@
     <t>06:34</t>
   </si>
   <si>
-    <t>03:25</t>
+    <t>03:23</t>
   </si>
   <si>
     <t>05:43</t>
   </si>
   <si>
-    <t>05:28</t>
+    <t>05:27</t>
   </si>
   <si>
     <t>04:37</t>
   </si>
   <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>02:51</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>01:05:21</t>
-  </si>
-  <si>
-    <t>00:15:20</t>
-  </si>
-  <si>
-    <t>01:53:00</t>
-  </si>
-  <si>
-    <t>23:25:18</t>
-  </si>
-  <si>
-    <t>01:02:31</t>
-  </si>
-  <si>
-    <t>22:35:13</t>
-  </si>
-  <si>
-    <t>00:12:08</t>
-  </si>
-  <si>
-    <t>21:45:04</t>
-  </si>
-  <si>
-    <t>23:21:48</t>
-  </si>
-  <si>
-    <t>22:31:29</t>
-  </si>
-  <si>
-    <t>00:09:08</t>
-  </si>
-  <si>
-    <t>21:41:08</t>
-  </si>
-  <si>
-    <t>23:18:21</t>
-  </si>
-  <si>
-    <t>20:50:46</t>
-  </si>
-  <si>
-    <t>22:27:40</t>
-  </si>
-  <si>
-    <t>01:07:27</t>
-  </si>
-  <si>
-    <t>00:17:29</t>
-  </si>
-  <si>
-    <t>01:55:51</t>
-  </si>
-  <si>
-    <t>23:27:36</t>
-  </si>
-  <si>
-    <t>01:04:49</t>
-  </si>
-  <si>
-    <t>22:37:48</t>
-  </si>
-  <si>
-    <t>00:14:16</t>
-  </si>
-  <si>
-    <t>21:48:13</t>
-  </si>
-  <si>
-    <t>23:23:54</t>
-  </si>
-  <si>
-    <t>22:33:38</t>
-  </si>
-  <si>
-    <t>00:12:01</t>
-  </si>
-  <si>
-    <t>21:43:26</t>
-  </si>
-  <si>
-    <t>23:20:40</t>
-  </si>
-  <si>
-    <t>20:53:21</t>
-  </si>
-  <si>
-    <t>22:29:48</t>
-  </si>
-  <si>
-    <t>01:10:45</t>
+    <t>01:39</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>00:15:21</t>
+  </si>
+  <si>
+    <t>01:53:01</t>
+  </si>
+  <si>
+    <t>23:25:20</t>
+  </si>
+  <si>
+    <t>01:02:33</t>
+  </si>
+  <si>
+    <t>22:35:17</t>
+  </si>
+  <si>
+    <t>00:12:13</t>
+  </si>
+  <si>
+    <t>21:45:12</t>
+  </si>
+  <si>
+    <t>23:21:56</t>
+  </si>
+  <si>
+    <t>22:31:40</t>
+  </si>
+  <si>
+    <t>00:09:20</t>
+  </si>
+  <si>
+    <t>21:41:24</t>
+  </si>
+  <si>
+    <t>23:18:37</t>
+  </si>
+  <si>
+    <t>20:51:07</t>
+  </si>
+  <si>
+    <t>22:28:02</t>
+  </si>
+  <si>
+    <t>20:00:47</t>
+  </si>
+  <si>
+    <t>21:37:30</t>
+  </si>
+  <si>
+    <t>00:17:30</t>
+  </si>
+  <si>
+    <t>01:55:52</t>
+  </si>
+  <si>
+    <t>23:27:38</t>
+  </si>
+  <si>
+    <t>01:04:52</t>
+  </si>
+  <si>
+    <t>22:37:52</t>
+  </si>
+  <si>
+    <t>00:14:21</t>
+  </si>
+  <si>
+    <t>21:48:20</t>
+  </si>
+  <si>
+    <t>23:24:01</t>
+  </si>
+  <si>
+    <t>22:33:49</t>
+  </si>
+  <si>
+    <t>21:43:42</t>
+  </si>
+  <si>
+    <t>23:20:57</t>
+  </si>
+  <si>
+    <t>20:53:42</t>
+  </si>
+  <si>
+    <t>22:30:10</t>
+  </si>
+  <si>
+    <t>20:03:55</t>
+  </si>
+  <si>
+    <t>21:39:36</t>
   </si>
   <si>
     <t>00:20:40</t>
   </si>
   <si>
-    <t>01:57:36</t>
-  </si>
-  <si>
-    <t>23:30:27</t>
-  </si>
-  <si>
-    <t>01:07:34</t>
-  </si>
-  <si>
-    <t>22:40:06</t>
-  </si>
-  <si>
-    <t>00:17:26</t>
-  </si>
-  <si>
-    <t>21:49:37</t>
-  </si>
-  <si>
-    <t>23:27:11</t>
-  </si>
-  <si>
-    <t>22:36:48</t>
-  </si>
-  <si>
-    <t>00:13:43</t>
-  </si>
-  <si>
-    <t>21:46:18</t>
-  </si>
-  <si>
-    <t>23:23:24</t>
-  </si>
-  <si>
-    <t>20:55:39</t>
-  </si>
-  <si>
-    <t>22:32:58</t>
-  </si>
-  <si>
-    <t>01:14:02</t>
-  </si>
-  <si>
-    <t>00:23:49</t>
+    <t>01:57:37</t>
+  </si>
+  <si>
+    <t>23:30:29</t>
+  </si>
+  <si>
+    <t>01:07:37</t>
+  </si>
+  <si>
+    <t>22:40:10</t>
+  </si>
+  <si>
+    <t>00:17:31</t>
+  </si>
+  <si>
+    <t>21:49:45</t>
+  </si>
+  <si>
+    <t>23:27:18</t>
+  </si>
+  <si>
+    <t>22:36:59</t>
+  </si>
+  <si>
+    <t>00:13:55</t>
+  </si>
+  <si>
+    <t>21:46:33</t>
+  </si>
+  <si>
+    <t>23:23:41</t>
+  </si>
+  <si>
+    <t>20:56:00</t>
+  </si>
+  <si>
+    <t>22:33:20</t>
+  </si>
+  <si>
+    <t>20:05:20</t>
+  </si>
+  <si>
+    <t>21:42:53</t>
+  </si>
+  <si>
+    <t>00:23:50</t>
   </si>
   <si>
     <t>01:59:22</t>
   </si>
   <si>
-    <t>23:33:17</t>
-  </si>
-  <si>
-    <t>01:10:20</t>
-  </si>
-  <si>
-    <t>22:42:24</t>
-  </si>
-  <si>
-    <t>00:20:36</t>
-  </si>
-  <si>
-    <t>21:51:02</t>
-  </si>
-  <si>
-    <t>23:30:28</t>
-  </si>
-  <si>
-    <t>22:39:58</t>
-  </si>
-  <si>
-    <t>00:15:26</t>
-  </si>
-  <si>
-    <t>21:49:09</t>
-  </si>
-  <si>
-    <t>23:26:08</t>
-  </si>
-  <si>
-    <t>20:57:58</t>
-  </si>
-  <si>
-    <t>22:36:08</t>
-  </si>
-  <si>
-    <t>01:16:07</t>
+    <t>23:33:19</t>
+  </si>
+  <si>
+    <t>01:10:22</t>
+  </si>
+  <si>
+    <t>22:42:28</t>
+  </si>
+  <si>
+    <t>00:20:41</t>
+  </si>
+  <si>
+    <t>21:51:09</t>
+  </si>
+  <si>
+    <t>23:30:35</t>
+  </si>
+  <si>
+    <t>22:40:09</t>
+  </si>
+  <si>
+    <t>00:15:36</t>
+  </si>
+  <si>
+    <t>21:49:25</t>
+  </si>
+  <si>
+    <t>23:26:24</t>
+  </si>
+  <si>
+    <t>20:58:19</t>
+  </si>
+  <si>
+    <t>22:36:29</t>
+  </si>
+  <si>
+    <t>20:06:46</t>
+  </si>
+  <si>
+    <t>21:46:10</t>
   </si>
   <si>
     <t>00:25:58</t>
@@ -346,40 +361,46 @@
     <t>02:02:13</t>
   </si>
   <si>
-    <t>23:35:35</t>
-  </si>
-  <si>
-    <t>01:12:38</t>
-  </si>
-  <si>
-    <t>22:44:58</t>
-  </si>
-  <si>
-    <t>00:22:44</t>
-  </si>
-  <si>
-    <t>21:54:10</t>
-  </si>
-  <si>
-    <t>23:32:33</t>
-  </si>
-  <si>
-    <t>22:42:07</t>
-  </si>
-  <si>
-    <t>00:18:18</t>
-  </si>
-  <si>
-    <t>21:51:26</t>
-  </si>
-  <si>
-    <t>23:28:27</t>
-  </si>
-  <si>
-    <t>21:00:32</t>
-  </si>
-  <si>
-    <t>22:38:16</t>
+    <t>23:35:37</t>
+  </si>
+  <si>
+    <t>01:12:40</t>
+  </si>
+  <si>
+    <t>22:45:03</t>
+  </si>
+  <si>
+    <t>00:22:48</t>
+  </si>
+  <si>
+    <t>21:54:17</t>
+  </si>
+  <si>
+    <t>23:32:40</t>
+  </si>
+  <si>
+    <t>22:42:18</t>
+  </si>
+  <si>
+    <t>00:18:29</t>
+  </si>
+  <si>
+    <t>21:51:42</t>
+  </si>
+  <si>
+    <t>23:28:43</t>
+  </si>
+  <si>
+    <t>21:00:53</t>
+  </si>
+  <si>
+    <t>22:38:37</t>
+  </si>
+  <si>
+    <t>20:09:53</t>
+  </si>
+  <si>
+    <t>21:48:15</t>
   </si>
   <si>
     <t>0°</t>
@@ -394,25 +415,37 @@
     <t>17°</t>
   </si>
   <si>
-    <t>21:47:02</t>
-  </si>
-  <si>
-    <t>22:31:35</t>
-  </si>
-  <si>
-    <t>21:43:19</t>
-  </si>
-  <si>
-    <t>20:55:01</t>
-  </si>
-  <si>
-    <t>22:27:48</t>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>21:47:09</t>
+  </si>
+  <si>
+    <t>22:31:46</t>
+  </si>
+  <si>
+    <t>21:43:34</t>
+  </si>
+  <si>
+    <t>20:55:21</t>
+  </si>
+  <si>
+    <t>22:28:08</t>
+  </si>
+  <si>
+    <t>20:07:09</t>
+  </si>
+  <si>
+    <t>21:39:56</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>3</t>
@@ -455,7 +488,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,7 +509,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +521,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +533,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -634,9 +661,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1040,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1118,55 +1142,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L2" s="4">
-        <v>-53.4</v>
+        <v>-52.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="O2" s="6">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="P2" s="7">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
-        <v>0</v>
+      <c r="R2" s="9">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1174,55 +1198,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L3" s="4">
-        <v>-52.1</v>
+        <v>-51.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="O3" s="6">
-        <v>78</v>
-      </c>
-      <c r="P3" s="9">
-        <v>54</v>
+        <v>89</v>
+      </c>
+      <c r="P3" s="7">
+        <v>81</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="10">
-        <v>47</v>
+      <c r="R3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1230,55 +1254,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L4" s="4">
-        <v>-51.7</v>
+        <v>-47.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O4" s="6">
-        <v>95</v>
-      </c>
-      <c r="P4" s="9">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="O4" s="10">
+        <v>2</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="7">
-        <v>83</v>
+      <c r="R4" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1286,52 +1310,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L5" s="4">
-        <v>-47.4</v>
+        <v>-54.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O5" s="11">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O5" s="10">
+        <v>6</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
-        <v>0</v>
+      <c r="Q5" s="11">
+        <v>6</v>
       </c>
       <c r="R5" s="8">
         <v>0</v>
@@ -1342,55 +1366,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-40</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O6" s="12">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
         <v>25</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-54.1</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O6" s="11">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="R6" s="13">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1398,55 +1422,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-52.6</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O7" s="12">
+        <v>20</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>20</v>
+      </c>
+      <c r="R7" s="14">
         <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-40</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O7" s="12">
-        <v>41</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>29</v>
-      </c>
-      <c r="R7" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1454,55 +1478,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="L8" s="4">
-        <v>-52.6</v>
+        <v>-31.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O8" s="11">
-        <v>2</v>
+        <v>145</v>
+      </c>
+      <c r="O8" s="6">
+        <v>94</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="8">
-        <v>2</v>
-      </c>
-      <c r="R8" s="8">
-        <v>0</v>
+      <c r="Q8" s="15">
+        <v>89</v>
+      </c>
+      <c r="R8" s="16">
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1510,55 +1534,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="L9" s="4">
-        <v>-31.1</v>
+        <v>-47.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="O9" s="6">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="10">
-        <v>47</v>
-      </c>
-      <c r="R9" s="9">
-        <v>55</v>
+      <c r="Q9" s="7">
+        <v>81</v>
+      </c>
+      <c r="R9" s="15">
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1566,55 +1590,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="L10" s="4">
-        <v>-47.6</v>
+        <v>-40.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O10" s="6">
-        <v>59</v>
+        <v>144</v>
+      </c>
+      <c r="O10" s="12">
+        <v>39</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
       <c r="Q10" s="13">
-        <v>28</v>
-      </c>
-      <c r="R10" s="13">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="R10" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1622,55 +1646,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="L11" s="4">
-        <v>-40</v>
+        <v>-53.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O11" s="11">
-        <v>13</v>
+        <v>145</v>
+      </c>
+      <c r="O11" s="6">
+        <v>54</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="14">
-        <v>11</v>
+      <c r="Q11" s="13">
+        <v>23</v>
       </c>
       <c r="R11" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1678,55 +1702,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>57</v>
+        <v>136</v>
       </c>
       <c r="L12" s="4">
-        <v>-53.1</v>
+        <v>-31.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O12" s="11">
-        <v>10</v>
+        <v>144</v>
+      </c>
+      <c r="O12" s="10">
+        <v>6</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="15">
-        <v>5</v>
-      </c>
-      <c r="R12" s="15">
-        <v>4</v>
+      <c r="Q12" s="11">
+        <v>3</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1734,52 +1758,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="L13" s="4">
-        <v>-31.1</v>
+        <v>-47.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O13" s="12">
-        <v>35</v>
+        <v>144</v>
+      </c>
+      <c r="O13" s="10">
+        <v>6</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="16">
-        <v>33</v>
+      <c r="Q13" s="11">
+        <v>4</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1790,52 +1814,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="L14" s="4">
-        <v>-47.8</v>
+        <v>-21.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O14" s="6">
-        <v>51</v>
+        <v>146</v>
+      </c>
+      <c r="O14" s="10">
+        <v>8</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="17">
-        <v>49</v>
+      <c r="Q14" s="8">
+        <v>0</v>
       </c>
       <c r="R14" s="8">
         <v>1</v>
@@ -1846,55 +1870,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="L15" s="4">
-        <v>-21.2</v>
+        <v>-40.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O15" s="6">
-        <v>90</v>
+        <v>144</v>
+      </c>
+      <c r="O15" s="10">
+        <v>2</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="18">
-        <v>90</v>
-      </c>
-      <c r="R15" s="10">
-        <v>45</v>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1902,114 +1926,170 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L16" s="4">
-        <v>-40</v>
+        <v>-10.9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="N16" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O16" s="12">
+        <v>22</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>22</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>87</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="O16" s="6">
-        <v>91</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>91</v>
-      </c>
-      <c r="R16" s="10">
-        <v>45</v>
+      <c r="K17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-31</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="O17" s="12">
+        <v>31</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>31</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2028,12 +2108,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2050,22 +2130,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="146">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260902--01</t>
-  </si>
-  <si>
-    <t>20260902--02</t>
-  </si>
-  <si>
-    <t>20260902--03</t>
-  </si>
-  <si>
     <t>20260903--01</t>
   </si>
   <si>
@@ -118,45 +109,51 @@
     <t>20260908--02</t>
   </si>
   <si>
+    <t>20260909--01</t>
+  </si>
+  <si>
+    <t>20260909--02</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
     <t>02:49</t>
   </si>
   <si>
     <t>06:34</t>
   </si>
   <si>
+    <t>03:22</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>04:38</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>02:51</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
     <t>03:23</t>
   </si>
   <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>02:51</t>
-  </si>
-  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -166,202 +163,187 @@
     <t>00:20</t>
   </si>
   <si>
-    <t>00:15:21</t>
-  </si>
-  <si>
-    <t>01:53:01</t>
-  </si>
-  <si>
-    <t>23:25:20</t>
+    <t>02:35</t>
   </si>
   <si>
     <t>01:02:33</t>
   </si>
   <si>
-    <t>22:35:17</t>
+    <t>22:35:18</t>
   </si>
   <si>
     <t>00:12:13</t>
   </si>
   <si>
-    <t>21:45:12</t>
-  </si>
-  <si>
-    <t>23:21:56</t>
-  </si>
-  <si>
-    <t>22:31:40</t>
-  </si>
-  <si>
-    <t>00:09:20</t>
-  </si>
-  <si>
-    <t>21:41:24</t>
-  </si>
-  <si>
-    <t>23:18:37</t>
-  </si>
-  <si>
-    <t>20:51:07</t>
-  </si>
-  <si>
-    <t>22:28:02</t>
-  </si>
-  <si>
-    <t>20:00:47</t>
-  </si>
-  <si>
-    <t>21:37:30</t>
-  </si>
-  <si>
-    <t>00:17:30</t>
-  </si>
-  <si>
-    <t>01:55:52</t>
-  </si>
-  <si>
-    <t>23:27:38</t>
+    <t>21:45:13</t>
+  </si>
+  <si>
+    <t>23:21:57</t>
+  </si>
+  <si>
+    <t>22:31:43</t>
+  </si>
+  <si>
+    <t>00:09:23</t>
+  </si>
+  <si>
+    <t>21:41:29</t>
+  </si>
+  <si>
+    <t>23:18:42</t>
+  </si>
+  <si>
+    <t>20:51:13</t>
+  </si>
+  <si>
+    <t>22:28:08</t>
+  </si>
+  <si>
+    <t>20:00:56</t>
+  </si>
+  <si>
+    <t>21:37:39</t>
+  </si>
+  <si>
+    <t>20:47:12</t>
+  </si>
+  <si>
+    <t>22:24:51</t>
   </si>
   <si>
     <t>01:04:52</t>
   </si>
   <si>
-    <t>22:37:52</t>
+    <t>22:37:53</t>
   </si>
   <si>
     <t>00:14:21</t>
   </si>
   <si>
-    <t>21:48:20</t>
-  </si>
-  <si>
-    <t>23:24:01</t>
-  </si>
-  <si>
-    <t>22:33:49</t>
-  </si>
-  <si>
-    <t>21:43:42</t>
-  </si>
-  <si>
-    <t>23:20:57</t>
-  </si>
-  <si>
-    <t>20:53:42</t>
-  </si>
-  <si>
-    <t>22:30:10</t>
-  </si>
-  <si>
-    <t>20:03:55</t>
-  </si>
-  <si>
-    <t>21:39:36</t>
-  </si>
-  <si>
-    <t>00:20:40</t>
-  </si>
-  <si>
-    <t>01:57:37</t>
-  </si>
-  <si>
-    <t>23:30:29</t>
+    <t>21:48:22</t>
+  </si>
+  <si>
+    <t>23:24:03</t>
+  </si>
+  <si>
+    <t>22:33:52</t>
+  </si>
+  <si>
+    <t>00:12:17</t>
+  </si>
+  <si>
+    <t>21:43:47</t>
+  </si>
+  <si>
+    <t>23:21:01</t>
+  </si>
+  <si>
+    <t>20:53:48</t>
+  </si>
+  <si>
+    <t>22:30:17</t>
+  </si>
+  <si>
+    <t>20:04:04</t>
+  </si>
+  <si>
+    <t>21:39:45</t>
+  </si>
+  <si>
+    <t>20:49:21</t>
+  </si>
+  <si>
+    <t>22:27:45</t>
   </si>
   <si>
     <t>01:07:37</t>
   </si>
   <si>
-    <t>22:40:10</t>
-  </si>
-  <si>
-    <t>00:17:31</t>
-  </si>
-  <si>
-    <t>21:49:45</t>
-  </si>
-  <si>
-    <t>23:27:18</t>
-  </si>
-  <si>
-    <t>22:36:59</t>
-  </si>
-  <si>
-    <t>00:13:55</t>
-  </si>
-  <si>
-    <t>21:46:33</t>
-  </si>
-  <si>
-    <t>23:23:41</t>
-  </si>
-  <si>
-    <t>20:56:00</t>
-  </si>
-  <si>
-    <t>22:33:20</t>
-  </si>
-  <si>
-    <t>20:05:20</t>
-  </si>
-  <si>
-    <t>21:42:53</t>
-  </si>
-  <si>
-    <t>00:23:50</t>
-  </si>
-  <si>
-    <t>01:59:22</t>
-  </si>
-  <si>
-    <t>23:33:19</t>
+    <t>22:40:11</t>
+  </si>
+  <si>
+    <t>00:17:32</t>
+  </si>
+  <si>
+    <t>21:49:46</t>
+  </si>
+  <si>
+    <t>23:27:20</t>
+  </si>
+  <si>
+    <t>22:37:03</t>
+  </si>
+  <si>
+    <t>00:13:58</t>
+  </si>
+  <si>
+    <t>21:46:38</t>
+  </si>
+  <si>
+    <t>23:23:45</t>
+  </si>
+  <si>
+    <t>20:56:07</t>
+  </si>
+  <si>
+    <t>22:33:26</t>
+  </si>
+  <si>
+    <t>20:05:29</t>
+  </si>
+  <si>
+    <t>21:43:02</t>
+  </si>
+  <si>
+    <t>20:52:32</t>
+  </si>
+  <si>
+    <t>22:29:26</t>
   </si>
   <si>
     <t>01:10:22</t>
   </si>
   <si>
-    <t>22:42:28</t>
+    <t>22:42:29</t>
   </si>
   <si>
     <t>00:20:41</t>
   </si>
   <si>
-    <t>21:51:09</t>
-  </si>
-  <si>
-    <t>23:30:35</t>
-  </si>
-  <si>
-    <t>22:40:09</t>
-  </si>
-  <si>
-    <t>00:15:36</t>
-  </si>
-  <si>
-    <t>21:49:25</t>
-  </si>
-  <si>
-    <t>23:26:24</t>
-  </si>
-  <si>
-    <t>20:58:19</t>
-  </si>
-  <si>
-    <t>22:36:29</t>
-  </si>
-  <si>
-    <t>20:06:46</t>
-  </si>
-  <si>
-    <t>21:46:10</t>
-  </si>
-  <si>
-    <t>00:25:58</t>
-  </si>
-  <si>
-    <t>02:02:13</t>
-  </si>
-  <si>
-    <t>23:35:37</t>
+    <t>21:51:11</t>
+  </si>
+  <si>
+    <t>23:30:37</t>
+  </si>
+  <si>
+    <t>22:40:12</t>
+  </si>
+  <si>
+    <t>00:15:39</t>
+  </si>
+  <si>
+    <t>21:49:29</t>
+  </si>
+  <si>
+    <t>23:26:28</t>
+  </si>
+  <si>
+    <t>20:58:26</t>
+  </si>
+  <si>
+    <t>22:36:36</t>
+  </si>
+  <si>
+    <t>20:06:55</t>
+  </si>
+  <si>
+    <t>21:46:19</t>
+  </si>
+  <si>
+    <t>20:55:42</t>
+  </si>
+  <si>
+    <t>22:31:08</t>
   </si>
   <si>
     <t>01:12:40</t>
@@ -370,37 +352,43 @@
     <t>22:45:03</t>
   </si>
   <si>
-    <t>00:22:48</t>
-  </si>
-  <si>
-    <t>21:54:17</t>
-  </si>
-  <si>
-    <t>23:32:40</t>
-  </si>
-  <si>
-    <t>22:42:18</t>
-  </si>
-  <si>
-    <t>00:18:29</t>
-  </si>
-  <si>
-    <t>21:51:42</t>
-  </si>
-  <si>
-    <t>23:28:43</t>
-  </si>
-  <si>
-    <t>21:00:53</t>
-  </si>
-  <si>
-    <t>22:38:37</t>
-  </si>
-  <si>
-    <t>20:09:53</t>
-  </si>
-  <si>
-    <t>21:48:15</t>
+    <t>00:22:49</t>
+  </si>
+  <si>
+    <t>21:54:19</t>
+  </si>
+  <si>
+    <t>23:32:42</t>
+  </si>
+  <si>
+    <t>22:42:20</t>
+  </si>
+  <si>
+    <t>00:18:32</t>
+  </si>
+  <si>
+    <t>21:51:46</t>
+  </si>
+  <si>
+    <t>23:28:47</t>
+  </si>
+  <si>
+    <t>21:01:00</t>
+  </si>
+  <si>
+    <t>22:38:43</t>
+  </si>
+  <si>
+    <t>20:10:02</t>
+  </si>
+  <si>
+    <t>21:48:24</t>
+  </si>
+  <si>
+    <t>20:57:50</t>
+  </si>
+  <si>
+    <t>22:34:00</t>
   </si>
   <si>
     <t>0°</t>
@@ -418,25 +406,34 @@
     <t>12°</t>
   </si>
   <si>
-    <t>21:47:09</t>
-  </si>
-  <si>
-    <t>22:31:46</t>
-  </si>
-  <si>
-    <t>21:43:34</t>
-  </si>
-  <si>
-    <t>20:55:21</t>
-  </si>
-  <si>
-    <t>22:28:08</t>
-  </si>
-  <si>
-    <t>20:07:09</t>
-  </si>
-  <si>
-    <t>21:39:56</t>
+    <t>40°</t>
+  </si>
+  <si>
+    <t>21:47:10</t>
+  </si>
+  <si>
+    <t>22:31:48</t>
+  </si>
+  <si>
+    <t>21:43:38</t>
+  </si>
+  <si>
+    <t>20:55:27</t>
+  </si>
+  <si>
+    <t>22:28:15</t>
+  </si>
+  <si>
+    <t>20:07:17</t>
+  </si>
+  <si>
+    <t>21:40:05</t>
+  </si>
+  <si>
+    <t>20:51:56</t>
+  </si>
+  <si>
+    <t>22:24:44</t>
   </si>
   <si>
     <t>B</t>
@@ -488,7 +485,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,13 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,13 +518,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,37 +560,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -661,6 +664,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1064,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1142,55 +1148,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L2" s="4">
-        <v>-52.1</v>
+        <v>-54.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O2" s="6">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="P2" s="7">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>98</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1198,52 +1204,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>51</v>
       </c>
       <c r="L3" s="4">
-        <v>-51.7</v>
+        <v>-40</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O3" s="6">
-        <v>89</v>
-      </c>
-      <c r="P3" s="7">
-        <v>81</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
+        <v>143</v>
+      </c>
+      <c r="O3" s="9">
+        <v>17</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>17</v>
       </c>
       <c r="R3" s="8">
         <v>0</v>
@@ -1254,55 +1260,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="L4" s="4">
-        <v>-47.4</v>
+        <v>-52.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O4" s="10">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="O4" s="6">
+        <v>23</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>2</v>
+      <c r="Q4" s="11">
+        <v>23</v>
+      </c>
+      <c r="R4" s="11">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1310,55 +1316,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="L5" s="4">
-        <v>-54.1</v>
+        <v>-31.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="O5" s="10">
-        <v>6</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>6</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="O5" s="12">
+        <v>100</v>
+      </c>
+      <c r="P5" s="7">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>84</v>
+      </c>
+      <c r="R5" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1366,55 +1372,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>54</v>
       </c>
       <c r="L6" s="4">
-        <v>-40</v>
+        <v>-47.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O6" s="12">
-        <v>26</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>25</v>
-      </c>
-      <c r="R6" s="13">
-        <v>26</v>
+        <v>100</v>
+      </c>
+      <c r="P6" s="15">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>100</v>
+      </c>
+      <c r="R6" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1422,55 +1428,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="L7" s="4">
-        <v>-52.6</v>
+        <v>-40.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O7" s="12">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="14">
-        <v>20</v>
-      </c>
-      <c r="R7" s="14">
-        <v>18</v>
+      <c r="Q7" s="16">
+        <v>60</v>
+      </c>
+      <c r="R7" s="17">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1478,55 +1484,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="L8" s="4">
-        <v>-31.2</v>
+        <v>-53.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O8" s="6">
-        <v>94</v>
+        <v>144</v>
+      </c>
+      <c r="O8" s="12">
+        <v>99</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="15">
-        <v>89</v>
-      </c>
-      <c r="R8" s="16">
-        <v>60</v>
+      <c r="Q8" s="18">
+        <v>95</v>
+      </c>
+      <c r="R8" s="14">
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1534,55 +1540,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="L9" s="4">
-        <v>-47.7</v>
+        <v>-31.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O9" s="6">
-        <v>94</v>
+        <v>143</v>
+      </c>
+      <c r="O9" s="9">
+        <v>5</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="7">
-        <v>81</v>
-      </c>
-      <c r="R9" s="15">
-        <v>90</v>
+      <c r="Q9" s="8">
+        <v>2</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1590,55 +1596,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="L10" s="4">
-        <v>-40.1</v>
+        <v>-47.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O10" s="12">
-        <v>39</v>
+        <v>143</v>
+      </c>
+      <c r="O10" s="9">
+        <v>2</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="13">
-        <v>26</v>
-      </c>
-      <c r="R10" s="11">
-        <v>3</v>
+      <c r="Q10" s="8">
+        <v>1</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1646,7 +1652,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>41</v>
@@ -1658,25 +1664,25 @@
         <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="L11" s="4">
-        <v>-53.1</v>
+        <v>-21.3</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>141</v>
@@ -1684,14 +1690,14 @@
       <c r="N11" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="O11" s="6">
-        <v>54</v>
+      <c r="O11" s="9">
+        <v>0</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="13">
-        <v>23</v>
+      <c r="Q11" s="8">
+        <v>0</v>
       </c>
       <c r="R11" s="8">
         <v>0</v>
@@ -1702,13 +1708,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>60</v>
@@ -1717,37 +1723,37 @@
         <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L12" s="4">
-        <v>-31.1</v>
+        <v>-40.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O12" s="10">
-        <v>6</v>
+        <v>143</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="11">
-        <v>3</v>
+      <c r="Q12" s="8">
+        <v>0</v>
       </c>
       <c r="R12" s="8">
         <v>0</v>
@@ -1758,13 +1764,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>61</v>
@@ -1773,40 +1779,40 @@
         <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="L13" s="4">
-        <v>-47.9</v>
+        <v>-11</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="O13" s="10">
-        <v>6</v>
+      <c r="O13" s="9">
+        <v>2</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="11">
-        <v>4</v>
+      <c r="Q13" s="8">
+        <v>0</v>
       </c>
       <c r="R13" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1814,10 +1820,10 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -1829,31 +1835,31 @@
         <v>77</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>137</v>
       </c>
       <c r="L14" s="4">
-        <v>-21.3</v>
+        <v>-31</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O14" s="10">
-        <v>8</v>
+        <v>145</v>
+      </c>
+      <c r="O14" s="9">
+        <v>2</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
@@ -1862,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1870,13 +1876,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>63</v>
@@ -1885,40 +1891,40 @@
         <v>78</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>138</v>
       </c>
       <c r="L15" s="4">
-        <v>-40.1</v>
+        <v>-21.1</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>141</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O15" s="10">
-        <v>2</v>
+        <v>145</v>
+      </c>
+      <c r="O15" s="9">
+        <v>11</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="8">
-        <v>0</v>
+      <c r="Q15" s="15">
+        <v>5</v>
       </c>
       <c r="R15" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1926,10 +1932,10 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>46</v>
@@ -1941,155 +1947,99 @@
         <v>79</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>139</v>
       </c>
       <c r="L16" s="4">
-        <v>-10.9</v>
+        <v>-40.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O16" s="12">
-        <v>22</v>
+        <v>144</v>
+      </c>
+      <c r="O16" s="9">
+        <v>8</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="14">
-        <v>22</v>
+      <c r="Q16" s="15">
+        <v>3</v>
       </c>
       <c r="R16" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>87</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-31</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O17" s="12">
-        <v>31</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>31</v>
-      </c>
-      <c r="R17" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2108,12 +2058,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2130,22 +2080,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="149">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260903--01</t>
-  </si>
-  <si>
-    <t>20260903--02</t>
-  </si>
-  <si>
     <t>20260904--01</t>
   </si>
   <si>
@@ -115,19 +109,19 @@
     <t>20260909--02</t>
   </si>
   <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:36</t>
+    <t>20260910--01</t>
+  </si>
+  <si>
+    <t>20260910--02</t>
   </si>
   <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>02:49</t>
-  </si>
-  <si>
-    <t>06:34</t>
+    <t>02:48</t>
+  </si>
+  <si>
+    <t>06:33</t>
   </si>
   <si>
     <t>03:22</t>
@@ -148,28 +142,28 @@
     <t>02:51</t>
   </si>
   <si>
-    <t>06:21</t>
-  </si>
-  <si>
     <t>03:23</t>
   </si>
   <si>
+    <t>05:28</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:39</t>
-  </si>
-  <si>
-    <t>00:20</t>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>00:19</t>
   </si>
   <si>
     <t>02:35</t>
   </si>
   <si>
-    <t>01:02:33</t>
-  </si>
-  <si>
-    <t>22:35:18</t>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>00:21</t>
   </si>
   <si>
     <t>00:12:13</t>
@@ -181,40 +175,40 @@
     <t>23:21:57</t>
   </si>
   <si>
-    <t>22:31:43</t>
-  </si>
-  <si>
-    <t>00:09:23</t>
-  </si>
-  <si>
-    <t>21:41:29</t>
-  </si>
-  <si>
-    <t>23:18:42</t>
-  </si>
-  <si>
-    <t>20:51:13</t>
-  </si>
-  <si>
-    <t>22:28:08</t>
-  </si>
-  <si>
-    <t>20:00:56</t>
-  </si>
-  <si>
-    <t>21:37:39</t>
-  </si>
-  <si>
-    <t>20:47:12</t>
-  </si>
-  <si>
-    <t>22:24:51</t>
-  </si>
-  <si>
-    <t>01:04:52</t>
-  </si>
-  <si>
-    <t>22:37:53</t>
+    <t>22:31:42</t>
+  </si>
+  <si>
+    <t>00:09:22</t>
+  </si>
+  <si>
+    <t>21:41:28</t>
+  </si>
+  <si>
+    <t>23:18:41</t>
+  </si>
+  <si>
+    <t>20:51:12</t>
+  </si>
+  <si>
+    <t>22:28:07</t>
+  </si>
+  <si>
+    <t>20:00:53</t>
+  </si>
+  <si>
+    <t>21:37:37</t>
+  </si>
+  <si>
+    <t>20:47:08</t>
+  </si>
+  <si>
+    <t>22:24:48</t>
+  </si>
+  <si>
+    <t>19:56:40</t>
+  </si>
+  <si>
+    <t>21:33:53</t>
   </si>
   <si>
     <t>00:14:21</t>
@@ -226,169 +220,175 @@
     <t>23:24:03</t>
   </si>
   <si>
-    <t>22:33:52</t>
-  </si>
-  <si>
-    <t>00:12:17</t>
-  </si>
-  <si>
-    <t>21:43:47</t>
-  </si>
-  <si>
-    <t>23:21:01</t>
-  </si>
-  <si>
-    <t>20:53:48</t>
-  </si>
-  <si>
-    <t>22:30:17</t>
-  </si>
-  <si>
-    <t>20:04:04</t>
-  </si>
-  <si>
-    <t>21:39:45</t>
-  </si>
-  <si>
-    <t>20:49:21</t>
-  </si>
-  <si>
-    <t>22:27:45</t>
-  </si>
-  <si>
-    <t>01:07:37</t>
+    <t>22:33:51</t>
+  </si>
+  <si>
+    <t>00:12:16</t>
+  </si>
+  <si>
+    <t>21:43:46</t>
+  </si>
+  <si>
+    <t>23:21:00</t>
+  </si>
+  <si>
+    <t>20:53:46</t>
+  </si>
+  <si>
+    <t>22:30:15</t>
+  </si>
+  <si>
+    <t>20:04:01</t>
+  </si>
+  <si>
+    <t>21:39:43</t>
+  </si>
+  <si>
+    <t>20:49:18</t>
+  </si>
+  <si>
+    <t>22:27:41</t>
+  </si>
+  <si>
+    <t>19:58:59</t>
+  </si>
+  <si>
+    <t>21:36:12</t>
+  </si>
+  <si>
+    <t>00:17:31</t>
+  </si>
+  <si>
+    <t>21:49:46</t>
+  </si>
+  <si>
+    <t>23:27:19</t>
+  </si>
+  <si>
+    <t>22:37:02</t>
+  </si>
+  <si>
+    <t>00:13:57</t>
+  </si>
+  <si>
+    <t>21:46:37</t>
+  </si>
+  <si>
+    <t>23:23:44</t>
+  </si>
+  <si>
+    <t>20:56:06</t>
+  </si>
+  <si>
+    <t>22:33:25</t>
+  </si>
+  <si>
+    <t>20:05:27</t>
+  </si>
+  <si>
+    <t>21:43:00</t>
+  </si>
+  <si>
+    <t>20:52:28</t>
+  </si>
+  <si>
+    <t>22:29:23</t>
+  </si>
+  <si>
+    <t>20:01:50</t>
+  </si>
+  <si>
+    <t>21:38:56</t>
+  </si>
+  <si>
+    <t>00:20:41</t>
+  </si>
+  <si>
+    <t>21:51:10</t>
+  </si>
+  <si>
+    <t>23:30:36</t>
   </si>
   <si>
     <t>22:40:11</t>
   </si>
   <si>
-    <t>00:17:32</t>
-  </si>
-  <si>
-    <t>21:49:46</t>
-  </si>
-  <si>
-    <t>23:27:20</t>
-  </si>
-  <si>
-    <t>22:37:03</t>
-  </si>
-  <si>
-    <t>00:13:58</t>
-  </si>
-  <si>
-    <t>21:46:38</t>
-  </si>
-  <si>
-    <t>23:23:45</t>
-  </si>
-  <si>
-    <t>20:56:07</t>
-  </si>
-  <si>
-    <t>22:33:26</t>
-  </si>
-  <si>
-    <t>20:05:29</t>
-  </si>
-  <si>
-    <t>21:43:02</t>
-  </si>
-  <si>
-    <t>20:52:32</t>
-  </si>
-  <si>
-    <t>22:29:26</t>
-  </si>
-  <si>
-    <t>01:10:22</t>
-  </si>
-  <si>
-    <t>22:42:29</t>
-  </si>
-  <si>
-    <t>00:20:41</t>
-  </si>
-  <si>
-    <t>21:51:11</t>
-  </si>
-  <si>
-    <t>23:30:37</t>
-  </si>
-  <si>
-    <t>22:40:12</t>
-  </si>
-  <si>
-    <t>00:15:39</t>
-  </si>
-  <si>
-    <t>21:49:29</t>
-  </si>
-  <si>
-    <t>23:26:28</t>
-  </si>
-  <si>
-    <t>20:58:26</t>
-  </si>
-  <si>
-    <t>22:36:36</t>
-  </si>
-  <si>
-    <t>20:06:55</t>
-  </si>
-  <si>
-    <t>21:46:19</t>
-  </si>
-  <si>
-    <t>20:55:42</t>
-  </si>
-  <si>
-    <t>22:31:08</t>
-  </si>
-  <si>
-    <t>01:12:40</t>
-  </si>
-  <si>
-    <t>22:45:03</t>
-  </si>
-  <si>
-    <t>00:22:49</t>
-  </si>
-  <si>
-    <t>21:54:19</t>
-  </si>
-  <si>
-    <t>23:32:42</t>
-  </si>
-  <si>
-    <t>22:42:20</t>
-  </si>
-  <si>
-    <t>00:18:32</t>
-  </si>
-  <si>
-    <t>21:51:46</t>
-  </si>
-  <si>
-    <t>23:28:47</t>
-  </si>
-  <si>
-    <t>21:01:00</t>
-  </si>
-  <si>
-    <t>22:38:43</t>
-  </si>
-  <si>
-    <t>20:10:02</t>
-  </si>
-  <si>
-    <t>21:48:24</t>
-  </si>
-  <si>
-    <t>20:57:50</t>
-  </si>
-  <si>
-    <t>22:34:00</t>
+    <t>00:15:38</t>
+  </si>
+  <si>
+    <t>21:49:28</t>
+  </si>
+  <si>
+    <t>23:26:27</t>
+  </si>
+  <si>
+    <t>20:58:24</t>
+  </si>
+  <si>
+    <t>22:36:34</t>
+  </si>
+  <si>
+    <t>20:06:52</t>
+  </si>
+  <si>
+    <t>21:46:16</t>
+  </si>
+  <si>
+    <t>20:55:38</t>
+  </si>
+  <si>
+    <t>22:31:04</t>
+  </si>
+  <si>
+    <t>20:04:41</t>
+  </si>
+  <si>
+    <t>21:41:40</t>
+  </si>
+  <si>
+    <t>00:22:48</t>
+  </si>
+  <si>
+    <t>21:54:18</t>
+  </si>
+  <si>
+    <t>23:32:41</t>
+  </si>
+  <si>
+    <t>22:42:19</t>
+  </si>
+  <si>
+    <t>00:18:31</t>
+  </si>
+  <si>
+    <t>21:51:45</t>
+  </si>
+  <si>
+    <t>23:28:46</t>
+  </si>
+  <si>
+    <t>21:00:58</t>
+  </si>
+  <si>
+    <t>22:38:41</t>
+  </si>
+  <si>
+    <t>20:09:59</t>
+  </si>
+  <si>
+    <t>21:48:21</t>
+  </si>
+  <si>
+    <t>20:57:46</t>
+  </si>
+  <si>
+    <t>22:33:57</t>
+  </si>
+  <si>
+    <t>20:06:58</t>
+  </si>
+  <si>
+    <t>21:43:59</t>
   </si>
   <si>
     <t>0°</t>
@@ -409,31 +409,40 @@
     <t>40°</t>
   </si>
   <si>
+    <t>16°</t>
+  </si>
+  <si>
     <t>21:47:10</t>
   </si>
   <si>
     <t>22:31:48</t>
   </si>
   <si>
-    <t>21:43:38</t>
-  </si>
-  <si>
-    <t>20:55:27</t>
-  </si>
-  <si>
-    <t>22:28:15</t>
-  </si>
-  <si>
-    <t>20:07:17</t>
-  </si>
-  <si>
-    <t>21:40:05</t>
-  </si>
-  <si>
-    <t>20:51:56</t>
-  </si>
-  <si>
-    <t>22:24:44</t>
+    <t>21:43:37</t>
+  </si>
+  <si>
+    <t>20:55:26</t>
+  </si>
+  <si>
+    <t>22:28:13</t>
+  </si>
+  <si>
+    <t>20:07:15</t>
+  </si>
+  <si>
+    <t>21:40:02</t>
+  </si>
+  <si>
+    <t>20:51:53</t>
+  </si>
+  <si>
+    <t>22:24:40</t>
+  </si>
+  <si>
+    <t>20:03:46</t>
+  </si>
+  <si>
+    <t>21:36:33</t>
   </si>
   <si>
     <t>B</t>
@@ -485,7 +494,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,7 +509,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,13 +557,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,49 +587,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -613,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,6 +694,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1148,13 +1184,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>50</v>
@@ -1178,19 +1214,19 @@
         <v>50</v>
       </c>
       <c r="L2" s="4">
-        <v>-54.1</v>
+        <v>-52.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="O2" s="6">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P2" s="7">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1204,13 +1240,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>51</v>
@@ -1228,31 +1264,31 @@
         <v>111</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="L3" s="4">
-        <v>-40</v>
+        <v>-31.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="O3" s="9">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="P3" s="8">
         <v>0</v>
       </c>
       <c r="Q3" s="10">
-        <v>17</v>
-      </c>
-      <c r="R3" s="8">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="R3" s="11">
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1260,13 +1296,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>52</v>
@@ -1290,25 +1326,25 @@
         <v>52</v>
       </c>
       <c r="L4" s="4">
-        <v>-52.6</v>
+        <v>-47.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O4" s="6">
-        <v>23</v>
+        <v>146</v>
+      </c>
+      <c r="O4" s="9">
+        <v>99</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="11">
-        <v>23</v>
+      <c r="Q4" s="12">
+        <v>69</v>
       </c>
       <c r="R4" s="11">
-        <v>23</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1316,13 +1352,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>53</v>
@@ -1340,31 +1376,31 @@
         <v>113</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L5" s="4">
-        <v>-31.2</v>
+        <v>-40.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O5" s="12">
-        <v>100</v>
-      </c>
-      <c r="P5" s="7">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>84</v>
-      </c>
-      <c r="R5" s="14">
-        <v>100</v>
+        <v>146</v>
+      </c>
+      <c r="O5" s="9">
+        <v>87</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>72</v>
+      </c>
+      <c r="R5" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1372,13 +1408,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>54</v>
@@ -1402,25 +1438,25 @@
         <v>54</v>
       </c>
       <c r="L6" s="4">
-        <v>-47.7</v>
+        <v>-53.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O6" s="12">
-        <v>100</v>
-      </c>
-      <c r="P6" s="15">
-        <v>4</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>100</v>
-      </c>
-      <c r="R6" s="14">
-        <v>100</v>
+        <v>147</v>
+      </c>
+      <c r="O6" s="9">
+        <v>82</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>68</v>
+      </c>
+      <c r="R6" s="13">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1428,13 +1464,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>55</v>
@@ -1452,31 +1488,31 @@
         <v>115</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L7" s="4">
-        <v>-40.1</v>
+        <v>-31.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O7" s="12">
-        <v>72</v>
+        <v>146</v>
+      </c>
+      <c r="O7" s="9">
+        <v>52</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="16">
-        <v>60</v>
-      </c>
-      <c r="R7" s="17">
+      <c r="Q7" s="14">
         <v>37</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1484,13 +1520,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>56</v>
@@ -1514,25 +1550,25 @@
         <v>56</v>
       </c>
       <c r="L8" s="4">
-        <v>-53.1</v>
+        <v>-47.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O8" s="12">
-        <v>99</v>
+        <v>146</v>
+      </c>
+      <c r="O8" s="15">
+        <v>48</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="18">
-        <v>95</v>
-      </c>
-      <c r="R8" s="14">
-        <v>98</v>
+      <c r="Q8" s="14">
+        <v>34</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1540,13 +1576,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>57</v>
@@ -1564,28 +1600,28 @@
         <v>117</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L9" s="4">
-        <v>-31.1</v>
+        <v>-21.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O9" s="9">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="8">
-        <v>2</v>
+      <c r="Q9" s="16">
+        <v>60</v>
       </c>
       <c r="R9" s="8">
         <v>0</v>
@@ -1596,13 +1632,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>58</v>
@@ -1623,28 +1659,28 @@
         <v>125</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="L10" s="4">
-        <v>-47.9</v>
+        <v>-40.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O10" s="9">
-        <v>2</v>
+        <v>146</v>
+      </c>
+      <c r="O10" s="15">
+        <v>28</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="8">
-        <v>1</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
+      <c r="Q10" s="17">
+        <v>28</v>
+      </c>
+      <c r="R10" s="18">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1652,13 +1688,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>59</v>
@@ -1676,31 +1712,31 @@
         <v>119</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L11" s="4">
-        <v>-21.3</v>
+        <v>-10.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O11" s="9">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
-        <v>0</v>
+      <c r="Q11" s="19">
+        <v>40</v>
+      </c>
+      <c r="R11" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1708,10 +1744,10 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>46</v>
@@ -1732,31 +1768,31 @@
         <v>120</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L12" s="4">
-        <v>-40.1</v>
+        <v>-31</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O12" s="9">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="8">
-        <v>0</v>
+      <c r="Q12" s="21">
+        <v>44</v>
       </c>
       <c r="R12" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1764,13 +1800,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>61</v>
@@ -1788,31 +1824,31 @@
         <v>121</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L13" s="4">
-        <v>-11</v>
+        <v>-21.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O13" s="9">
-        <v>2</v>
+        <v>148</v>
+      </c>
+      <c r="O13" s="15">
+        <v>31</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="8">
-        <v>0</v>
+      <c r="Q13" s="17">
+        <v>30</v>
       </c>
       <c r="R13" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1820,13 +1856,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>62</v>
@@ -1844,31 +1880,31 @@
         <v>122</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L14" s="4">
-        <v>-31</v>
+        <v>-40.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O14" s="9">
-        <v>2</v>
+        <v>147</v>
+      </c>
+      <c r="O14" s="15">
+        <v>21</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="8">
-        <v>0</v>
+      <c r="Q14" s="13">
+        <v>21</v>
       </c>
       <c r="R14" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1876,13 +1912,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>63</v>
@@ -1900,31 +1936,31 @@
         <v>123</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L15" s="4">
-        <v>-21.1</v>
+        <v>-10.7</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O15" s="9">
-        <v>11</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="15">
-        <v>5</v>
+        <v>148</v>
+      </c>
+      <c r="O15" s="15">
+        <v>17</v>
+      </c>
+      <c r="P15" s="18">
+        <v>17</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
       </c>
       <c r="R15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1932,13 +1968,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>64</v>
@@ -1956,28 +1992,28 @@
         <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L16" s="4">
-        <v>-40.1</v>
+        <v>-30.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O16" s="9">
-        <v>8</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="15">
-        <v>3</v>
+        <v>148</v>
+      </c>
+      <c r="O16" s="6">
+        <v>13</v>
+      </c>
+      <c r="P16" s="18">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="136">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260904--01</t>
-  </si>
-  <si>
-    <t>20260904--02</t>
-  </si>
-  <si>
-    <t>20260904--03</t>
-  </si>
-  <si>
     <t>20260905--01</t>
   </si>
   <si>
@@ -115,43 +106,40 @@
     <t>20260910--02</t>
   </si>
   <si>
+    <t>20260911--01</t>
+  </si>
+  <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>02:48</t>
+    <t>03:22</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>02:50</t>
   </si>
   <si>
     <t>06:33</t>
   </si>
   <si>
-    <t>03:22</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>02:51</t>
-  </si>
-  <si>
-    <t>03:23</t>
-  </si>
-  <si>
     <t>05:28</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:40</t>
+    <t>01:39</t>
   </si>
   <si>
     <t>00:19</t>
@@ -163,16 +151,10 @@
     <t>04:47</t>
   </si>
   <si>
-    <t>00:21</t>
-  </si>
-  <si>
-    <t>00:12:13</t>
-  </si>
-  <si>
-    <t>21:45:13</t>
-  </si>
-  <si>
-    <t>23:21:57</t>
+    <t>00:22</t>
+  </si>
+  <si>
+    <t>03:16</t>
   </si>
   <si>
     <t>22:31:42</t>
@@ -199,25 +181,19 @@
     <t>21:37:37</t>
   </si>
   <si>
-    <t>20:47:08</t>
+    <t>20:47:09</t>
   </si>
   <si>
     <t>22:24:48</t>
   </si>
   <si>
-    <t>19:56:40</t>
+    <t>19:56:41</t>
   </si>
   <si>
     <t>21:33:53</t>
   </si>
   <si>
-    <t>00:14:21</t>
-  </si>
-  <si>
-    <t>21:48:22</t>
-  </si>
-  <si>
-    <t>23:24:03</t>
+    <t>20:43:06</t>
   </si>
   <si>
     <t>22:33:51</t>
@@ -232,13 +208,13 @@
     <t>23:21:00</t>
   </si>
   <si>
-    <t>20:53:46</t>
+    <t>20:53:47</t>
   </si>
   <si>
     <t>22:30:15</t>
   </si>
   <si>
-    <t>20:04:01</t>
+    <t>20:04:02</t>
   </si>
   <si>
     <t>21:39:43</t>
@@ -247,7 +223,7 @@
     <t>20:49:18</t>
   </si>
   <si>
-    <t>22:27:41</t>
+    <t>22:27:42</t>
   </si>
   <si>
     <t>19:58:59</t>
@@ -256,13 +232,7 @@
     <t>21:36:12</t>
   </si>
   <si>
-    <t>00:17:31</t>
-  </si>
-  <si>
-    <t>21:49:46</t>
-  </si>
-  <si>
-    <t>23:27:19</t>
+    <t>20:45:14</t>
   </si>
   <si>
     <t>22:37:02</t>
@@ -289,25 +259,19 @@
     <t>21:43:00</t>
   </si>
   <si>
-    <t>20:52:28</t>
+    <t>20:52:29</t>
   </si>
   <si>
     <t>22:29:23</t>
   </si>
   <si>
-    <t>20:01:50</t>
+    <t>20:01:51</t>
   </si>
   <si>
     <t>21:38:56</t>
   </si>
   <si>
-    <t>00:20:41</t>
-  </si>
-  <si>
-    <t>21:51:10</t>
-  </si>
-  <si>
-    <t>23:30:36</t>
+    <t>20:48:24</t>
   </si>
   <si>
     <t>22:40:11</t>
@@ -346,13 +310,7 @@
     <t>21:41:40</t>
   </si>
   <si>
-    <t>00:22:48</t>
-  </si>
-  <si>
-    <t>21:54:18</t>
-  </si>
-  <si>
-    <t>23:32:41</t>
+    <t>20:51:34</t>
   </si>
   <si>
     <t>22:42:19</t>
@@ -373,7 +331,7 @@
     <t>22:38:41</t>
   </si>
   <si>
-    <t>20:09:59</t>
+    <t>20:10:00</t>
   </si>
   <si>
     <t>21:48:21</t>
@@ -391,12 +349,12 @@
     <t>21:43:59</t>
   </si>
   <si>
+    <t>20:53:41</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
-    <t>6°</t>
-  </si>
-  <si>
     <t>9°</t>
   </si>
   <si>
@@ -412,7 +370,7 @@
     <t>16°</t>
   </si>
   <si>
-    <t>21:47:10</t>
+    <t>47°</t>
   </si>
   <si>
     <t>22:31:48</t>
@@ -436,13 +394,16 @@
     <t>20:51:53</t>
   </si>
   <si>
-    <t>22:24:40</t>
+    <t>22:24:41</t>
   </si>
   <si>
     <t>20:03:46</t>
   </si>
   <si>
-    <t>21:36:33</t>
+    <t>21:36:34</t>
+  </si>
+  <si>
+    <t>20:48:30</t>
   </si>
   <si>
     <t>B</t>
@@ -494,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -509,13 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -527,25 +482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,37 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -691,18 +628,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1106,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1184,55 +1109,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="L2" s="4">
-        <v>-52.6</v>
+        <v>-40.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="O2" s="6">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="P2" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="9">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1240,55 +1165,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="L3" s="4">
-        <v>-31.2</v>
+        <v>-53.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O3" s="9">
-        <v>99</v>
-      </c>
-      <c r="P3" s="8">
+        <v>134</v>
+      </c>
+      <c r="O3" s="6">
+        <v>80</v>
+      </c>
+      <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="10">
-        <v>89</v>
-      </c>
-      <c r="R3" s="11">
-        <v>95</v>
+        <v>58</v>
+      </c>
+      <c r="R3" s="8">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1296,55 +1221,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="L4" s="4">
-        <v>-47.7</v>
+        <v>-31.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O4" s="9">
-        <v>99</v>
-      </c>
-      <c r="P4" s="8">
+        <v>133</v>
+      </c>
+      <c r="O4" s="11">
+        <v>2</v>
+      </c>
+      <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="12">
-        <v>69</v>
-      </c>
-      <c r="R4" s="11">
-        <v>96</v>
+      <c r="Q4" s="7">
+        <v>2</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1352,55 +1277,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-47.9</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="L5" s="4">
-        <v>-40.1</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O5" s="9">
-        <v>87</v>
-      </c>
-      <c r="P5" s="8">
+      <c r="O5" s="11">
+        <v>2</v>
+      </c>
+      <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="12">
-        <v>72</v>
-      </c>
-      <c r="R5" s="8">
+      <c r="Q5" s="7">
         <v>1</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1408,55 +1333,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="L6" s="4">
-        <v>-53.1</v>
+        <v>-21.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O6" s="9">
-        <v>82</v>
-      </c>
-      <c r="P6" s="8">
+        <v>135</v>
+      </c>
+      <c r="O6" s="12">
+        <v>21</v>
+      </c>
+      <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="12">
-        <v>68</v>
-      </c>
-      <c r="R6" s="13">
-        <v>19</v>
+      <c r="Q6" s="13">
+        <v>21</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1464,54 +1389,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="L7" s="4">
-        <v>-31.1</v>
+        <v>-40.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O7" s="9">
-        <v>52</v>
-      </c>
-      <c r="P7" s="8">
+        <v>133</v>
+      </c>
+      <c r="O7" s="12">
+        <v>22</v>
+      </c>
+      <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="14">
-        <v>37</v>
-      </c>
-      <c r="R7" s="8">
+      <c r="Q7" s="13">
+        <v>22</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1520,54 +1445,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L8" s="4">
-        <v>-47.9</v>
+        <v>-10.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O8" s="15">
-        <v>48</v>
-      </c>
-      <c r="P8" s="8">
+        <v>134</v>
+      </c>
+      <c r="O8" s="11">
+        <v>13</v>
+      </c>
+      <c r="P8" s="7">
         <v>0</v>
       </c>
       <c r="Q8" s="14">
-        <v>34</v>
-      </c>
-      <c r="R8" s="8">
+        <v>13</v>
+      </c>
+      <c r="R8" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1576,54 +1501,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-31</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="L9" s="4">
-        <v>-21.3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O9" s="9">
-        <v>84</v>
-      </c>
-      <c r="P9" s="8">
+      <c r="O9" s="11">
+        <v>8</v>
+      </c>
+      <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="16">
-        <v>60</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="Q9" s="15">
+        <v>8</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1632,55 +1557,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="L10" s="4">
-        <v>-40.1</v>
+        <v>-21.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O10" s="15">
+        <v>135</v>
+      </c>
+      <c r="O10" s="12">
         <v>28</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="7">
         <v>0</v>
       </c>
-      <c r="Q10" s="17">
-        <v>28</v>
-      </c>
-      <c r="R10" s="18">
-        <v>13</v>
+      <c r="Q10" s="13">
+        <v>22</v>
+      </c>
+      <c r="R10" s="15">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1688,55 +1613,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="L11" s="4">
-        <v>-10.9</v>
+        <v>-40.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O11" s="9">
-        <v>58</v>
-      </c>
-      <c r="P11" s="8">
+        <v>134</v>
+      </c>
+      <c r="O11" s="11">
+        <v>11</v>
+      </c>
+      <c r="P11" s="7">
         <v>0</v>
       </c>
-      <c r="Q11" s="19">
-        <v>40</v>
-      </c>
-      <c r="R11" s="20">
-        <v>9</v>
+      <c r="Q11" s="15">
+        <v>8</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1744,55 +1669,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="L12" s="4">
-        <v>-31</v>
+        <v>-10.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O12" s="9">
-        <v>52</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="21">
-        <v>44</v>
-      </c>
-      <c r="R12" s="8">
+        <v>135</v>
+      </c>
+      <c r="O12" s="12">
+        <v>31</v>
+      </c>
+      <c r="P12" s="7">
         <v>1</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>26</v>
+      </c>
+      <c r="R12" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1800,54 +1725,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L13" s="4">
-        <v>-21.1</v>
+        <v>-30.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O13" s="15">
-        <v>31</v>
-      </c>
-      <c r="P13" s="8">
+        <v>135</v>
+      </c>
+      <c r="O13" s="12">
+        <v>22</v>
+      </c>
+      <c r="P13" s="7">
         <v>0</v>
       </c>
-      <c r="Q13" s="17">
-        <v>30</v>
-      </c>
-      <c r="R13" s="8">
+      <c r="Q13" s="14">
+        <v>16</v>
+      </c>
+      <c r="R13" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1856,226 +1781,102 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="L14" s="4">
-        <v>-40.1</v>
+        <v>-20.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O14" s="15">
-        <v>21</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>21</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2">
-        <v>27</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-10.7</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O15" s="15">
-        <v>17</v>
-      </c>
-      <c r="P15" s="18">
-        <v>17</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-30.8</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O16" s="6">
-        <v>13</v>
-      </c>
-      <c r="P16" s="18">
-        <v>13</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2094,12 +1895,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2116,22 +1917,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260905--01</t>
-  </si>
-  <si>
     <t>20260906--01</t>
   </si>
   <si>
@@ -109,58 +106,64 @@
     <t>20260911--01</t>
   </si>
   <si>
+    <t>20260912--01</t>
+  </si>
+  <si>
+    <t>03:22</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>02:51</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>03:22</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>06:33</t>
-  </si>
-  <si>
     <t>05:28</t>
   </si>
   <si>
+    <t>06:35</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
     <t>01:39</t>
   </si>
   <si>
-    <t>00:19</t>
+    <t>00:20</t>
   </si>
   <si>
     <t>02:35</t>
   </si>
   <si>
-    <t>04:47</t>
-  </si>
-  <si>
-    <t>00:22</t>
-  </si>
-  <si>
-    <t>03:16</t>
-  </si>
-  <si>
-    <t>22:31:42</t>
-  </si>
-  <si>
-    <t>00:09:22</t>
+    <t>04:46</t>
+  </si>
+  <si>
+    <t>00:21</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>00:09:23</t>
   </si>
   <si>
     <t>21:41:28</t>
@@ -169,34 +172,34 @@
     <t>23:18:41</t>
   </si>
   <si>
-    <t>20:51:12</t>
-  </si>
-  <si>
-    <t>22:28:07</t>
-  </si>
-  <si>
-    <t>20:00:53</t>
-  </si>
-  <si>
-    <t>21:37:37</t>
-  </si>
-  <si>
-    <t>20:47:09</t>
-  </si>
-  <si>
-    <t>22:24:48</t>
-  </si>
-  <si>
-    <t>19:56:41</t>
-  </si>
-  <si>
-    <t>21:33:53</t>
-  </si>
-  <si>
-    <t>20:43:06</t>
-  </si>
-  <si>
-    <t>22:33:51</t>
+    <t>20:51:13</t>
+  </si>
+  <si>
+    <t>22:28:08</t>
+  </si>
+  <si>
+    <t>20:00:56</t>
+  </si>
+  <si>
+    <t>21:37:39</t>
+  </si>
+  <si>
+    <t>20:47:13</t>
+  </si>
+  <si>
+    <t>22:24:52</t>
+  </si>
+  <si>
+    <t>19:56:46</t>
+  </si>
+  <si>
+    <t>21:33:59</t>
+  </si>
+  <si>
+    <t>20:43:13</t>
+  </si>
+  <si>
+    <t>19:52:32</t>
   </si>
   <si>
     <t>00:12:16</t>
@@ -205,76 +208,76 @@
     <t>21:43:46</t>
   </si>
   <si>
-    <t>23:21:00</t>
-  </si>
-  <si>
-    <t>20:53:47</t>
-  </si>
-  <si>
-    <t>22:30:15</t>
-  </si>
-  <si>
-    <t>20:04:02</t>
-  </si>
-  <si>
-    <t>21:39:43</t>
-  </si>
-  <si>
-    <t>20:49:18</t>
-  </si>
-  <si>
-    <t>22:27:42</t>
-  </si>
-  <si>
-    <t>19:58:59</t>
-  </si>
-  <si>
-    <t>21:36:12</t>
-  </si>
-  <si>
-    <t>20:45:14</t>
-  </si>
-  <si>
-    <t>22:37:02</t>
+    <t>23:21:01</t>
+  </si>
+  <si>
+    <t>20:53:48</t>
+  </si>
+  <si>
+    <t>22:30:17</t>
+  </si>
+  <si>
+    <t>20:04:04</t>
+  </si>
+  <si>
+    <t>21:39:45</t>
+  </si>
+  <si>
+    <t>20:49:22</t>
+  </si>
+  <si>
+    <t>22:27:46</t>
+  </si>
+  <si>
+    <t>19:59:05</t>
+  </si>
+  <si>
+    <t>21:36:18</t>
+  </si>
+  <si>
+    <t>20:45:22</t>
+  </si>
+  <si>
+    <t>19:54:38</t>
   </si>
   <si>
     <t>00:13:57</t>
   </si>
   <si>
-    <t>21:46:37</t>
+    <t>21:46:38</t>
   </si>
   <si>
     <t>23:23:44</t>
   </si>
   <si>
-    <t>20:56:06</t>
-  </si>
-  <si>
-    <t>22:33:25</t>
-  </si>
-  <si>
-    <t>20:05:27</t>
-  </si>
-  <si>
-    <t>21:43:00</t>
-  </si>
-  <si>
-    <t>20:52:29</t>
-  </si>
-  <si>
-    <t>22:29:23</t>
-  </si>
-  <si>
-    <t>20:01:51</t>
-  </si>
-  <si>
-    <t>21:38:56</t>
-  </si>
-  <si>
-    <t>20:48:24</t>
-  </si>
-  <si>
-    <t>22:40:11</t>
+    <t>20:56:07</t>
+  </si>
+  <si>
+    <t>22:33:27</t>
+  </si>
+  <si>
+    <t>20:05:29</t>
+  </si>
+  <si>
+    <t>21:43:03</t>
+  </si>
+  <si>
+    <t>20:52:32</t>
+  </si>
+  <si>
+    <t>22:29:27</t>
+  </si>
+  <si>
+    <t>20:01:56</t>
+  </si>
+  <si>
+    <t>21:39:02</t>
+  </si>
+  <si>
+    <t>20:48:32</t>
+  </si>
+  <si>
+    <t>19:57:56</t>
   </si>
   <si>
     <t>00:15:38</t>
@@ -283,37 +286,37 @@
     <t>21:49:28</t>
   </si>
   <si>
-    <t>23:26:27</t>
-  </si>
-  <si>
-    <t>20:58:24</t>
-  </si>
-  <si>
-    <t>22:36:34</t>
-  </si>
-  <si>
-    <t>20:06:52</t>
-  </si>
-  <si>
-    <t>21:46:16</t>
-  </si>
-  <si>
-    <t>20:55:38</t>
-  </si>
-  <si>
-    <t>22:31:04</t>
-  </si>
-  <si>
-    <t>20:04:41</t>
-  </si>
-  <si>
-    <t>21:41:40</t>
-  </si>
-  <si>
-    <t>20:51:34</t>
-  </si>
-  <si>
-    <t>22:42:19</t>
+    <t>23:26:28</t>
+  </si>
+  <si>
+    <t>20:58:25</t>
+  </si>
+  <si>
+    <t>22:36:35</t>
+  </si>
+  <si>
+    <t>20:06:55</t>
+  </si>
+  <si>
+    <t>21:46:19</t>
+  </si>
+  <si>
+    <t>20:55:42</t>
+  </si>
+  <si>
+    <t>22:31:08</t>
+  </si>
+  <si>
+    <t>20:04:47</t>
+  </si>
+  <si>
+    <t>21:41:46</t>
+  </si>
+  <si>
+    <t>20:51:42</t>
+  </si>
+  <si>
+    <t>20:01:13</t>
   </si>
   <si>
     <t>00:18:31</t>
@@ -325,31 +328,34 @@
     <t>23:28:46</t>
   </si>
   <si>
-    <t>21:00:58</t>
-  </si>
-  <si>
-    <t>22:38:41</t>
-  </si>
-  <si>
-    <t>20:10:00</t>
-  </si>
-  <si>
-    <t>21:48:21</t>
-  </si>
-  <si>
-    <t>20:57:46</t>
-  </si>
-  <si>
-    <t>22:33:57</t>
-  </si>
-  <si>
-    <t>20:06:58</t>
-  </si>
-  <si>
-    <t>21:43:59</t>
-  </si>
-  <si>
-    <t>20:53:41</t>
+    <t>21:00:59</t>
+  </si>
+  <si>
+    <t>22:38:43</t>
+  </si>
+  <si>
+    <t>20:10:02</t>
+  </si>
+  <si>
+    <t>21:48:24</t>
+  </si>
+  <si>
+    <t>20:57:50</t>
+  </si>
+  <si>
+    <t>22:34:01</t>
+  </si>
+  <si>
+    <t>20:07:04</t>
+  </si>
+  <si>
+    <t>21:44:04</t>
+  </si>
+  <si>
+    <t>20:53:49</t>
+  </si>
+  <si>
+    <t>20:03:17</t>
   </si>
   <si>
     <t>0°</t>
@@ -373,37 +379,40 @@
     <t>47°</t>
   </si>
   <si>
-    <t>22:31:48</t>
+    <t>14°</t>
   </si>
   <si>
     <t>21:43:37</t>
   </si>
   <si>
-    <t>20:55:26</t>
-  </si>
-  <si>
-    <t>22:28:13</t>
-  </si>
-  <si>
-    <t>20:07:15</t>
-  </si>
-  <si>
-    <t>21:40:02</t>
-  </si>
-  <si>
-    <t>20:51:53</t>
-  </si>
-  <si>
-    <t>22:24:41</t>
-  </si>
-  <si>
-    <t>20:03:46</t>
-  </si>
-  <si>
-    <t>21:36:34</t>
-  </si>
-  <si>
-    <t>20:48:30</t>
+    <t>20:55:27</t>
+  </si>
+  <si>
+    <t>22:28:14</t>
+  </si>
+  <si>
+    <t>20:07:17</t>
+  </si>
+  <si>
+    <t>21:40:05</t>
+  </si>
+  <si>
+    <t>20:51:57</t>
+  </si>
+  <si>
+    <t>22:24:44</t>
+  </si>
+  <si>
+    <t>20:03:51</t>
+  </si>
+  <si>
+    <t>21:36:39</t>
+  </si>
+  <si>
+    <t>20:48:37</t>
+  </si>
+  <si>
+    <t>20:00:40</t>
   </si>
   <si>
     <t>B</t>
@@ -415,10 +424,10 @@
     <t>A</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -455,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,19 +491,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,37 +509,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,18 +601,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,55 +1082,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="L2" s="4">
-        <v>-40.1</v>
+        <v>-53.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O2" s="6">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="8">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="R2" s="9">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1165,55 +1138,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="L3" s="4">
-        <v>-53.1</v>
+        <v>-31.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O3" s="6">
-        <v>80</v>
+        <v>137</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>58</v>
-      </c>
-      <c r="R3" s="8">
-        <v>48</v>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1221,52 +1194,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="L4" s="4">
-        <v>-31.1</v>
+        <v>-47.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O4" s="11">
-        <v>2</v>
+        <v>137</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
       <c r="Q4" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" s="7">
         <v>0</v>
@@ -1277,52 +1250,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="L5" s="4">
-        <v>-47.9</v>
+        <v>-21.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O5" s="11">
-        <v>2</v>
+        <v>138</v>
+      </c>
+      <c r="O5" s="10">
+        <v>3</v>
       </c>
       <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
         <v>1</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>3</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1333,7 +1306,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>35</v>
@@ -1342,43 +1315,43 @@
         <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>114</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L6" s="4">
-        <v>-21.3</v>
+        <v>-40.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O6" s="12">
-        <v>21</v>
+        <v>137</v>
+      </c>
+      <c r="O6" s="10">
+        <v>1</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="13">
-        <v>21</v>
+      <c r="Q6" s="7">
+        <v>1</v>
       </c>
       <c r="R6" s="7">
         <v>0</v>
@@ -1389,52 +1362,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L7" s="4">
-        <v>-40.1</v>
+        <v>-11</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O7" s="12">
-        <v>22</v>
+        <v>136</v>
+      </c>
+      <c r="O7" s="10">
+        <v>1</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="13">
-        <v>22</v>
+      <c r="Q7" s="7">
+        <v>1</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -1445,52 +1418,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L8" s="4">
-        <v>-10.9</v>
+        <v>-31</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O8" s="11">
-        <v>13</v>
+        <v>138</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="14">
-        <v>13</v>
+      <c r="Q8" s="7">
+        <v>0</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -1501,52 +1474,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L9" s="4">
-        <v>-31</v>
+        <v>-21.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O9" s="11">
-        <v>8</v>
+        <v>138</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="15">
-        <v>8</v>
+      <c r="Q9" s="7">
+        <v>0</v>
       </c>
       <c r="R9" s="7">
         <v>0</v>
@@ -1557,55 +1530,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L10" s="4">
-        <v>-21.1</v>
+        <v>-40.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O10" s="12">
-        <v>28</v>
+        <v>136</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0</v>
       </c>
       <c r="P10" s="7">
         <v>0</v>
       </c>
-      <c r="Q10" s="13">
-        <v>22</v>
-      </c>
-      <c r="R10" s="15">
-        <v>8</v>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1613,52 +1586,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L11" s="4">
-        <v>-40.1</v>
+        <v>-10.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O11" s="11">
-        <v>11</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="15">
-        <v>8</v>
+        <v>138</v>
+      </c>
+      <c r="O11" s="12">
+        <v>37</v>
+      </c>
+      <c r="P11" s="13">
+        <v>37</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
       </c>
       <c r="R11" s="7">
         <v>0</v>
@@ -1669,55 +1642,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>117</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L12" s="4">
-        <v>-10.7</v>
+        <v>-30.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O12" s="12">
-        <v>31</v>
-      </c>
-      <c r="P12" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>26</v>
-      </c>
-      <c r="R12" s="17">
-        <v>4</v>
+        <v>37</v>
+      </c>
+      <c r="P12" s="13">
+        <v>37</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1725,55 +1698,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L13" s="4">
-        <v>-30.8</v>
+        <v>-20.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O13" s="12">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P13" s="7">
         <v>0</v>
       </c>
-      <c r="Q13" s="14">
-        <v>16</v>
+      <c r="Q13" s="7">
+        <v>0</v>
       </c>
       <c r="R13" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1781,43 +1754,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L14" s="4">
-        <v>-20.8</v>
+        <v>-10.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
+      </c>
+      <c r="O14" s="10">
+        <v>7</v>
+      </c>
+      <c r="P14" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="129">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260906--01</t>
-  </si>
-  <si>
-    <t>20260906--02</t>
-  </si>
-  <si>
-    <t>20260906--03</t>
-  </si>
-  <si>
     <t>20260907--01</t>
   </si>
   <si>
@@ -109,46 +100,49 @@
     <t>20260912--01</t>
   </si>
   <si>
-    <t>03:22</t>
+    <t>20260913--01</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>03:23</t>
   </si>
   <si>
     <t>05:42</t>
   </si>
   <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>02:51</t>
+    <t>05:28</t>
   </si>
   <si>
     <t>06:34</t>
   </si>
   <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>05:28</t>
-  </si>
-  <si>
-    <t>06:35</t>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>01:39</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:39</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>02:35</t>
+    <t>00:19</t>
+  </si>
+  <si>
+    <t>02:34</t>
   </si>
   <si>
     <t>04:46</t>
@@ -160,202 +154,178 @@
     <t>03:15</t>
   </si>
   <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>00:09:23</t>
-  </si>
-  <si>
-    <t>21:41:28</t>
-  </si>
-  <si>
-    <t>23:18:41</t>
-  </si>
-  <si>
-    <t>20:51:13</t>
-  </si>
-  <si>
-    <t>22:28:08</t>
-  </si>
-  <si>
-    <t>20:00:56</t>
-  </si>
-  <si>
-    <t>21:37:39</t>
-  </si>
-  <si>
-    <t>20:47:13</t>
-  </si>
-  <si>
-    <t>22:24:52</t>
-  </si>
-  <si>
-    <t>19:56:46</t>
-  </si>
-  <si>
-    <t>21:33:59</t>
-  </si>
-  <si>
-    <t>20:43:13</t>
-  </si>
-  <si>
-    <t>19:52:32</t>
-  </si>
-  <si>
-    <t>00:12:16</t>
-  </si>
-  <si>
-    <t>21:43:46</t>
-  </si>
-  <si>
-    <t>23:21:01</t>
-  </si>
-  <si>
-    <t>20:53:48</t>
-  </si>
-  <si>
-    <t>22:30:17</t>
-  </si>
-  <si>
-    <t>20:04:04</t>
-  </si>
-  <si>
-    <t>21:39:45</t>
-  </si>
-  <si>
-    <t>20:49:22</t>
-  </si>
-  <si>
-    <t>22:27:46</t>
-  </si>
-  <si>
-    <t>19:59:05</t>
-  </si>
-  <si>
-    <t>21:36:18</t>
-  </si>
-  <si>
-    <t>20:45:22</t>
-  </si>
-  <si>
-    <t>19:54:38</t>
-  </si>
-  <si>
-    <t>00:13:57</t>
-  </si>
-  <si>
-    <t>21:46:38</t>
-  </si>
-  <si>
-    <t>23:23:44</t>
-  </si>
-  <si>
-    <t>20:56:07</t>
-  </si>
-  <si>
-    <t>22:33:27</t>
-  </si>
-  <si>
-    <t>20:05:29</t>
-  </si>
-  <si>
-    <t>21:43:03</t>
-  </si>
-  <si>
-    <t>20:52:32</t>
-  </si>
-  <si>
-    <t>22:29:27</t>
-  </si>
-  <si>
-    <t>20:01:56</t>
-  </si>
-  <si>
-    <t>21:39:02</t>
-  </si>
-  <si>
-    <t>20:48:32</t>
-  </si>
-  <si>
-    <t>19:57:56</t>
-  </si>
-  <si>
-    <t>00:15:38</t>
-  </si>
-  <si>
-    <t>21:49:28</t>
-  </si>
-  <si>
-    <t>23:26:28</t>
-  </si>
-  <si>
-    <t>20:58:25</t>
-  </si>
-  <si>
-    <t>22:36:35</t>
-  </si>
-  <si>
-    <t>20:06:55</t>
-  </si>
-  <si>
-    <t>21:46:19</t>
-  </si>
-  <si>
-    <t>20:55:42</t>
-  </si>
-  <si>
-    <t>22:31:08</t>
-  </si>
-  <si>
-    <t>20:04:47</t>
-  </si>
-  <si>
-    <t>21:41:46</t>
-  </si>
-  <si>
-    <t>20:51:42</t>
-  </si>
-  <si>
-    <t>20:01:13</t>
-  </si>
-  <si>
-    <t>00:18:31</t>
-  </si>
-  <si>
-    <t>21:51:45</t>
-  </si>
-  <si>
-    <t>23:28:46</t>
-  </si>
-  <si>
-    <t>21:00:59</t>
-  </si>
-  <si>
-    <t>22:38:43</t>
-  </si>
-  <si>
-    <t>20:10:02</t>
-  </si>
-  <si>
-    <t>21:48:24</t>
-  </si>
-  <si>
-    <t>20:57:50</t>
-  </si>
-  <si>
-    <t>22:34:01</t>
-  </si>
-  <si>
-    <t>20:07:04</t>
-  </si>
-  <si>
-    <t>21:44:04</t>
-  </si>
-  <si>
-    <t>20:53:49</t>
-  </si>
-  <si>
-    <t>20:03:17</t>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>03:13</t>
+  </si>
+  <si>
+    <t>20:51:12</t>
+  </si>
+  <si>
+    <t>22:28:07</t>
+  </si>
+  <si>
+    <t>20:00:54</t>
+  </si>
+  <si>
+    <t>21:37:38</t>
+  </si>
+  <si>
+    <t>20:47:10</t>
+  </si>
+  <si>
+    <t>22:24:50</t>
+  </si>
+  <si>
+    <t>19:56:43</t>
+  </si>
+  <si>
+    <t>21:33:56</t>
+  </si>
+  <si>
+    <t>20:43:10</t>
+  </si>
+  <si>
+    <t>19:52:28</t>
+  </si>
+  <si>
+    <t>20:39:26</t>
+  </si>
+  <si>
+    <t>20:53:47</t>
+  </si>
+  <si>
+    <t>22:30:16</t>
+  </si>
+  <si>
+    <t>20:04:03</t>
+  </si>
+  <si>
+    <t>21:39:44</t>
+  </si>
+  <si>
+    <t>20:49:20</t>
+  </si>
+  <si>
+    <t>22:27:43</t>
+  </si>
+  <si>
+    <t>19:59:02</t>
+  </si>
+  <si>
+    <t>21:36:15</t>
+  </si>
+  <si>
+    <t>20:45:18</t>
+  </si>
+  <si>
+    <t>19:54:34</t>
+  </si>
+  <si>
+    <t>20:42:17</t>
+  </si>
+  <si>
+    <t>20:56:06</t>
+  </si>
+  <si>
+    <t>22:33:25</t>
+  </si>
+  <si>
+    <t>20:05:28</t>
+  </si>
+  <si>
+    <t>21:43:01</t>
+  </si>
+  <si>
+    <t>20:52:30</t>
+  </si>
+  <si>
+    <t>22:29:25</t>
+  </si>
+  <si>
+    <t>20:01:53</t>
+  </si>
+  <si>
+    <t>21:38:59</t>
+  </si>
+  <si>
+    <t>20:48:28</t>
+  </si>
+  <si>
+    <t>19:57:51</t>
+  </si>
+  <si>
+    <t>20:44:02</t>
+  </si>
+  <si>
+    <t>20:58:24</t>
+  </si>
+  <si>
+    <t>22:36:34</t>
+  </si>
+  <si>
+    <t>20:06:53</t>
+  </si>
+  <si>
+    <t>21:46:17</t>
+  </si>
+  <si>
+    <t>20:55:40</t>
+  </si>
+  <si>
+    <t>22:31:06</t>
+  </si>
+  <si>
+    <t>20:04:44</t>
+  </si>
+  <si>
+    <t>21:41:43</t>
+  </si>
+  <si>
+    <t>20:51:38</t>
+  </si>
+  <si>
+    <t>20:01:08</t>
+  </si>
+  <si>
+    <t>20:45:47</t>
+  </si>
+  <si>
+    <t>21:00:58</t>
+  </si>
+  <si>
+    <t>22:38:42</t>
+  </si>
+  <si>
+    <t>20:10:00</t>
+  </si>
+  <si>
+    <t>21:48:22</t>
+  </si>
+  <si>
+    <t>20:57:48</t>
+  </si>
+  <si>
+    <t>22:33:58</t>
+  </si>
+  <si>
+    <t>20:07:01</t>
+  </si>
+  <si>
+    <t>21:44:01</t>
+  </si>
+  <si>
+    <t>20:53:45</t>
+  </si>
+  <si>
+    <t>20:03:13</t>
+  </si>
+  <si>
+    <t>20:48:38</t>
+  </si>
+  <si>
+    <t>17°</t>
   </si>
   <si>
     <t>0°</t>
@@ -364,9 +334,6 @@
     <t>9°</t>
   </si>
   <si>
-    <t>17°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
@@ -382,55 +349,58 @@
     <t>14°</t>
   </si>
   <si>
-    <t>21:43:37</t>
-  </si>
-  <si>
-    <t>20:55:27</t>
-  </si>
-  <si>
-    <t>22:28:14</t>
-  </si>
-  <si>
-    <t>20:07:17</t>
-  </si>
-  <si>
-    <t>21:40:05</t>
-  </si>
-  <si>
-    <t>20:51:57</t>
-  </si>
-  <si>
-    <t>22:24:44</t>
-  </si>
-  <si>
-    <t>20:03:51</t>
-  </si>
-  <si>
-    <t>21:36:39</t>
-  </si>
-  <si>
-    <t>20:48:37</t>
-  </si>
-  <si>
-    <t>20:00:40</t>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>20:55:26</t>
+  </si>
+  <si>
+    <t>22:28:13</t>
+  </si>
+  <si>
+    <t>20:07:16</t>
+  </si>
+  <si>
+    <t>21:40:03</t>
+  </si>
+  <si>
+    <t>20:51:54</t>
+  </si>
+  <si>
+    <t>22:24:42</t>
+  </si>
+  <si>
+    <t>20:03:48</t>
+  </si>
+  <si>
+    <t>21:36:36</t>
+  </si>
+  <si>
+    <t>20:48:33</t>
+  </si>
+  <si>
+    <t>20:00:35</t>
+  </si>
+  <si>
+    <t>20:45:30</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -479,7 +449,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,37 +461,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1004,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1082,55 +1052,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="L2" s="4">
-        <v>-53.1</v>
+        <v>-21.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="O2" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>57</v>
-      </c>
-      <c r="R2" s="9">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1138,45 +1108,45 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="L3" s="4">
-        <v>-31.1</v>
+        <v>-40.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O3" s="10">
+        <v>127</v>
+      </c>
+      <c r="O3" s="6">
         <v>0</v>
       </c>
       <c r="P3" s="7">
@@ -1194,52 +1164,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-11</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="O4" s="8">
         <v>41</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-47.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O4" s="10">
-        <v>0</v>
-      </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="7">
-        <v>0</v>
+      <c r="Q4" s="9">
+        <v>16</v>
       </c>
       <c r="R4" s="7">
         <v>0</v>
@@ -1250,52 +1220,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-31</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="L5" s="4">
-        <v>-21.3</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O5" s="10">
-        <v>3</v>
+        <v>126</v>
+      </c>
+      <c r="O5" s="8">
+        <v>48</v>
       </c>
       <c r="P5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>24</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1306,52 +1276,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="L6" s="4">
-        <v>-40.1</v>
+        <v>-21.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O6" s="10">
-        <v>1</v>
+        <v>126</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
       <c r="Q6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="7">
         <v>0</v>
@@ -1362,55 +1332,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="L7" s="4">
-        <v>-11</v>
+        <v>-40.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O7" s="10">
+        <v>128</v>
+      </c>
+      <c r="O7" s="6">
         <v>1</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
       </c>
       <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>1</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1418,49 +1388,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-10.7</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L8" s="4">
-        <v>-31</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
+      <c r="O8" s="11">
+        <v>41</v>
+      </c>
+      <c r="P8" s="12">
+        <v>41</v>
       </c>
       <c r="Q8" s="7">
         <v>0</v>
@@ -1474,49 +1444,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L9" s="4">
-        <v>-21.1</v>
+        <v>-30.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O9" s="10">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="O9" s="11">
+        <v>41</v>
+      </c>
+      <c r="P9" s="12">
+        <v>41</v>
       </c>
       <c r="Q9" s="7">
         <v>0</v>
@@ -1530,49 +1500,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="L10" s="4">
-        <v>-40.1</v>
+        <v>-20.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O10" s="10">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="O10" s="6">
+        <v>5</v>
+      </c>
+      <c r="P10" s="13">
+        <v>5</v>
       </c>
       <c r="Q10" s="7">
         <v>0</v>
@@ -1586,49 +1556,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L11" s="4">
-        <v>-10.7</v>
+        <v>-10.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O11" s="12">
-        <v>37</v>
-      </c>
-      <c r="P11" s="13">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
       </c>
       <c r="Q11" s="7">
         <v>0</v>
@@ -1642,226 +1612,114 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="L12" s="4">
-        <v>-30.8</v>
+        <v>-20.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O12" s="12">
-        <v>37</v>
-      </c>
-      <c r="P12" s="13">
-        <v>37</v>
+        <v>128</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
       </c>
       <c r="Q12" s="7">
         <v>0</v>
       </c>
       <c r="R12" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2">
-        <v>47</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-20.9</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O13" s="12">
-        <v>27</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2">
-        <v>86</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-10.4</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O14" s="10">
-        <v>7</v>
-      </c>
-      <c r="P14" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A12">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B12">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J12">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K12">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1880,12 +1738,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M12">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N12">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1902,22 +1760,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O12">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P12">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q12">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R12">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="120">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260907--01</t>
-  </si>
-  <si>
-    <t>20260907--02</t>
-  </si>
-  <si>
     <t>20260908--01</t>
   </si>
   <si>
@@ -103,10 +97,7 @@
     <t>20260913--01</t>
   </si>
   <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>06:18</t>
+    <t>20260914--01</t>
   </si>
   <si>
     <t>02:50</t>
@@ -130,216 +121,198 @@
     <t>06:34</t>
   </si>
   <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>01:39</t>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>02:35</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:19</t>
-  </si>
-  <si>
-    <t>02:34</t>
-  </si>
-  <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>00:21</t>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>00:22</t>
+  </si>
+  <si>
+    <t>03:16</t>
+  </si>
+  <si>
+    <t>06:01</t>
   </si>
   <si>
     <t>03:15</t>
   </si>
   <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>03:13</t>
-  </si>
-  <si>
-    <t>20:51:12</t>
-  </si>
-  <si>
-    <t>22:28:07</t>
-  </si>
-  <si>
-    <t>20:00:54</t>
-  </si>
-  <si>
-    <t>21:37:38</t>
-  </si>
-  <si>
-    <t>20:47:10</t>
-  </si>
-  <si>
-    <t>22:24:50</t>
-  </si>
-  <si>
-    <t>19:56:43</t>
-  </si>
-  <si>
-    <t>21:33:56</t>
-  </si>
-  <si>
-    <t>20:43:10</t>
-  </si>
-  <si>
-    <t>19:52:28</t>
-  </si>
-  <si>
-    <t>20:39:26</t>
-  </si>
-  <si>
-    <t>20:53:47</t>
-  </si>
-  <si>
-    <t>22:30:16</t>
-  </si>
-  <si>
-    <t>20:04:03</t>
-  </si>
-  <si>
-    <t>21:39:44</t>
-  </si>
-  <si>
-    <t>20:49:20</t>
-  </si>
-  <si>
-    <t>22:27:43</t>
-  </si>
-  <si>
-    <t>19:59:02</t>
-  </si>
-  <si>
-    <t>21:36:15</t>
-  </si>
-  <si>
-    <t>20:45:18</t>
-  </si>
-  <si>
-    <t>19:54:34</t>
-  </si>
-  <si>
-    <t>20:42:17</t>
-  </si>
-  <si>
-    <t>20:56:06</t>
-  </si>
-  <si>
-    <t>22:33:25</t>
-  </si>
-  <si>
-    <t>20:05:28</t>
-  </si>
-  <si>
-    <t>21:43:01</t>
-  </si>
-  <si>
-    <t>20:52:30</t>
-  </si>
-  <si>
-    <t>22:29:25</t>
-  </si>
-  <si>
-    <t>20:01:53</t>
-  </si>
-  <si>
-    <t>21:38:59</t>
-  </si>
-  <si>
-    <t>20:48:28</t>
-  </si>
-  <si>
-    <t>19:57:51</t>
-  </si>
-  <si>
-    <t>20:44:02</t>
-  </si>
-  <si>
-    <t>20:58:24</t>
-  </si>
-  <si>
-    <t>22:36:34</t>
-  </si>
-  <si>
-    <t>20:06:53</t>
-  </si>
-  <si>
-    <t>21:46:17</t>
-  </si>
-  <si>
-    <t>20:55:40</t>
-  </si>
-  <si>
-    <t>22:31:06</t>
-  </si>
-  <si>
-    <t>20:04:44</t>
-  </si>
-  <si>
-    <t>21:41:43</t>
-  </si>
-  <si>
-    <t>20:51:38</t>
-  </si>
-  <si>
-    <t>20:01:08</t>
-  </si>
-  <si>
-    <t>20:45:47</t>
-  </si>
-  <si>
-    <t>21:00:58</t>
-  </si>
-  <si>
-    <t>22:38:42</t>
-  </si>
-  <si>
-    <t>20:10:00</t>
-  </si>
-  <si>
-    <t>21:48:22</t>
-  </si>
-  <si>
-    <t>20:57:48</t>
-  </si>
-  <si>
-    <t>22:33:58</t>
-  </si>
-  <si>
-    <t>20:07:01</t>
-  </si>
-  <si>
-    <t>21:44:01</t>
-  </si>
-  <si>
-    <t>20:53:45</t>
-  </si>
-  <si>
-    <t>20:03:13</t>
-  </si>
-  <si>
-    <t>20:48:38</t>
-  </si>
-  <si>
-    <t>17°</t>
+    <t>20:00:53</t>
+  </si>
+  <si>
+    <t>21:37:36</t>
+  </si>
+  <si>
+    <t>20:47:08</t>
+  </si>
+  <si>
+    <t>22:24:47</t>
+  </si>
+  <si>
+    <t>19:56:39</t>
+  </si>
+  <si>
+    <t>21:33:51</t>
+  </si>
+  <si>
+    <t>20:43:03</t>
+  </si>
+  <si>
+    <t>19:52:19</t>
+  </si>
+  <si>
+    <t>20:39:14</t>
+  </si>
+  <si>
+    <t>19:48:04</t>
+  </si>
+  <si>
+    <t>20:04:01</t>
+  </si>
+  <si>
+    <t>21:39:42</t>
+  </si>
+  <si>
+    <t>20:49:17</t>
+  </si>
+  <si>
+    <t>22:27:40</t>
+  </si>
+  <si>
+    <t>19:58:57</t>
+  </si>
+  <si>
+    <t>21:36:10</t>
+  </si>
+  <si>
+    <t>20:45:11</t>
+  </si>
+  <si>
+    <t>19:54:25</t>
+  </si>
+  <si>
+    <t>20:42:04</t>
+  </si>
+  <si>
+    <t>19:50:22</t>
+  </si>
+  <si>
+    <t>20:05:26</t>
+  </si>
+  <si>
+    <t>21:42:59</t>
+  </si>
+  <si>
+    <t>20:52:27</t>
+  </si>
+  <si>
+    <t>22:29:22</t>
+  </si>
+  <si>
+    <t>20:01:49</t>
+  </si>
+  <si>
+    <t>21:38:55</t>
+  </si>
+  <si>
+    <t>20:48:22</t>
+  </si>
+  <si>
+    <t>19:57:42</t>
+  </si>
+  <si>
+    <t>20:43:50</t>
+  </si>
+  <si>
+    <t>19:53:09</t>
+  </si>
+  <si>
+    <t>20:06:51</t>
+  </si>
+  <si>
+    <t>21:46:15</t>
+  </si>
+  <si>
+    <t>20:55:37</t>
+  </si>
+  <si>
+    <t>22:31:03</t>
+  </si>
+  <si>
+    <t>20:04:39</t>
+  </si>
+  <si>
+    <t>21:41:38</t>
+  </si>
+  <si>
+    <t>20:51:31</t>
+  </si>
+  <si>
+    <t>20:00:59</t>
+  </si>
+  <si>
+    <t>20:45:36</t>
+  </si>
+  <si>
+    <t>19:55:55</t>
+  </si>
+  <si>
+    <t>20:09:59</t>
+  </si>
+  <si>
+    <t>21:48:20</t>
+  </si>
+  <si>
+    <t>20:57:45</t>
+  </si>
+  <si>
+    <t>22:33:56</t>
+  </si>
+  <si>
+    <t>20:06:56</t>
+  </si>
+  <si>
+    <t>21:43:57</t>
+  </si>
+  <si>
+    <t>20:53:38</t>
+  </si>
+  <si>
+    <t>20:03:03</t>
+  </si>
+  <si>
+    <t>20:48:26</t>
+  </si>
+  <si>
+    <t>19:58:12</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>40°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>40°</t>
-  </si>
-  <si>
     <t>16°</t>
   </si>
   <si>
@@ -352,37 +325,40 @@
     <t>11°</t>
   </si>
   <si>
-    <t>20:55:26</t>
-  </si>
-  <si>
-    <t>22:28:13</t>
-  </si>
-  <si>
-    <t>20:07:16</t>
-  </si>
-  <si>
-    <t>21:40:03</t>
-  </si>
-  <si>
-    <t>20:51:54</t>
-  </si>
-  <si>
-    <t>22:24:42</t>
-  </si>
-  <si>
-    <t>20:03:48</t>
-  </si>
-  <si>
-    <t>21:36:36</t>
-  </si>
-  <si>
-    <t>20:48:33</t>
-  </si>
-  <si>
-    <t>20:00:35</t>
-  </si>
-  <si>
-    <t>20:45:30</t>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>20:07:14</t>
+  </si>
+  <si>
+    <t>21:40:02</t>
+  </si>
+  <si>
+    <t>20:51:52</t>
+  </si>
+  <si>
+    <t>22:24:39</t>
+  </si>
+  <si>
+    <t>20:03:44</t>
+  </si>
+  <si>
+    <t>21:36:32</t>
+  </si>
+  <si>
+    <t>20:48:27</t>
+  </si>
+  <si>
+    <t>20:00:26</t>
+  </si>
+  <si>
+    <t>20:45:19</t>
+  </si>
+  <si>
+    <t>19:57:28</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
@@ -391,16 +367,13 @@
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -434,7 +407,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,31 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,15 +517,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -974,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1052,52 +998,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="L2" s="4">
-        <v>-21.3</v>
+        <v>-10.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
+      <c r="Q2" s="8">
+        <v>25</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -1108,52 +1054,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>87</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="L3" s="4">
-        <v>-40.1</v>
+        <v>-31</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="O3" s="9">
+        <v>3</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
@@ -1164,52 +1110,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="L4" s="4">
-        <v>-11</v>
+        <v>-21.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O4" s="8">
-        <v>41</v>
+        <v>118</v>
+      </c>
+      <c r="O4" s="9">
+        <v>2</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="9">
-        <v>16</v>
+      <c r="Q4" s="7">
+        <v>2</v>
       </c>
       <c r="R4" s="7">
         <v>0</v>
@@ -1220,52 +1166,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="L5" s="4">
-        <v>-31</v>
+        <v>-40.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O5" s="8">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="O5" s="9">
+        <v>4</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
       <c r="Q5" s="10">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1276,46 +1222,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="L6" s="4">
-        <v>-21.1</v>
+        <v>-10.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="O6" s="9">
+        <v>1</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1332,46 +1278,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L7" s="4">
-        <v>-40.1</v>
+        <v>-30.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O7" s="6">
-        <v>1</v>
+        <v>118</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1380,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1388,55 +1334,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-20.8</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L8" s="4">
-        <v>-10.7</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O8" s="11">
-        <v>41</v>
-      </c>
-      <c r="P8" s="12">
-        <v>41</v>
+      <c r="O8" s="9">
+        <v>5</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
       </c>
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="7">
-        <v>0</v>
+      <c r="R8" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1444,49 +1390,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L9" s="4">
-        <v>-30.8</v>
+        <v>-10.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O9" s="11">
-        <v>41</v>
-      </c>
-      <c r="P9" s="12">
-        <v>41</v>
+        <v>118</v>
+      </c>
+      <c r="O9" s="9">
+        <v>6</v>
+      </c>
+      <c r="P9" s="10">
+        <v>6</v>
       </c>
       <c r="Q9" s="7">
         <v>0</v>
@@ -1500,49 +1446,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L10" s="4">
-        <v>-20.9</v>
+        <v>-20.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O10" s="6">
-        <v>5</v>
-      </c>
-      <c r="P10" s="13">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
       </c>
       <c r="Q10" s="7">
         <v>0</v>
@@ -1556,170 +1502,114 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="L11" s="4">
-        <v>-10.4</v>
+        <v>-9.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="O11" s="6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
       </c>
-      <c r="Q11" s="7">
-        <v>0</v>
+      <c r="Q11" s="8">
+        <v>27</v>
       </c>
       <c r="R11" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="2">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-20.5</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A12">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B12">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H12">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J12">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K12">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L12">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1738,12 +1628,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M12">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N12">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1760,22 +1650,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O12">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P12">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q12">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R12">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260908--01</t>
-  </si>
-  <si>
-    <t>20260908--02</t>
-  </si>
-  <si>
     <t>20260909--01</t>
   </si>
   <si>
@@ -100,37 +94,31 @@
     <t>20260914--01</t>
   </si>
   <si>
-    <t>02:50</t>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>03:22</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>06:20</t>
   </si>
   <si>
     <t>06:33</t>
   </si>
   <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>03:23</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:28</t>
-  </si>
-  <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>02:35</t>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>02:34</t>
   </si>
   <si>
     <t>00:00</t>
@@ -139,7 +127,7 @@
     <t>04:47</t>
   </si>
   <si>
-    <t>00:22</t>
+    <t>00:21</t>
   </si>
   <si>
     <t>03:16</t>
@@ -148,174 +136,141 @@
     <t>06:01</t>
   </si>
   <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>20:00:53</t>
-  </si>
-  <si>
-    <t>21:37:36</t>
-  </si>
-  <si>
-    <t>20:47:08</t>
-  </si>
-  <si>
-    <t>22:24:47</t>
-  </si>
-  <si>
-    <t>19:56:39</t>
-  </si>
-  <si>
-    <t>21:33:51</t>
-  </si>
-  <si>
-    <t>20:43:03</t>
-  </si>
-  <si>
-    <t>19:52:19</t>
-  </si>
-  <si>
-    <t>20:39:14</t>
-  </si>
-  <si>
-    <t>19:48:04</t>
-  </si>
-  <si>
-    <t>20:04:01</t>
-  </si>
-  <si>
-    <t>21:39:42</t>
-  </si>
-  <si>
-    <t>20:49:17</t>
-  </si>
-  <si>
-    <t>22:27:40</t>
-  </si>
-  <si>
-    <t>19:58:57</t>
-  </si>
-  <si>
-    <t>21:36:10</t>
-  </si>
-  <si>
-    <t>20:45:11</t>
-  </si>
-  <si>
-    <t>19:54:25</t>
-  </si>
-  <si>
-    <t>20:42:04</t>
-  </si>
-  <si>
-    <t>19:50:22</t>
-  </si>
-  <si>
-    <t>20:05:26</t>
-  </si>
-  <si>
-    <t>21:42:59</t>
-  </si>
-  <si>
-    <t>20:52:27</t>
-  </si>
-  <si>
-    <t>22:29:22</t>
-  </si>
-  <si>
-    <t>20:01:49</t>
-  </si>
-  <si>
-    <t>21:38:55</t>
-  </si>
-  <si>
-    <t>20:48:22</t>
-  </si>
-  <si>
-    <t>19:57:42</t>
-  </si>
-  <si>
-    <t>20:43:50</t>
-  </si>
-  <si>
-    <t>19:53:09</t>
-  </si>
-  <si>
-    <t>20:06:51</t>
-  </si>
-  <si>
-    <t>21:46:15</t>
-  </si>
-  <si>
-    <t>20:55:37</t>
-  </si>
-  <si>
-    <t>22:31:03</t>
-  </si>
-  <si>
-    <t>20:04:39</t>
-  </si>
-  <si>
-    <t>21:41:38</t>
-  </si>
-  <si>
-    <t>20:51:31</t>
-  </si>
-  <si>
-    <t>20:00:59</t>
-  </si>
-  <si>
-    <t>20:45:36</t>
-  </si>
-  <si>
-    <t>19:55:55</t>
-  </si>
-  <si>
-    <t>20:09:59</t>
-  </si>
-  <si>
-    <t>21:48:20</t>
-  </si>
-  <si>
-    <t>20:57:45</t>
-  </si>
-  <si>
-    <t>22:33:56</t>
-  </si>
-  <si>
-    <t>20:06:56</t>
-  </si>
-  <si>
-    <t>21:43:57</t>
-  </si>
-  <si>
-    <t>20:53:38</t>
-  </si>
-  <si>
-    <t>20:03:03</t>
-  </si>
-  <si>
-    <t>20:48:26</t>
-  </si>
-  <si>
-    <t>19:58:12</t>
-  </si>
-  <si>
-    <t>9°</t>
+    <t>03:17</t>
+  </si>
+  <si>
+    <t>20:47:04</t>
+  </si>
+  <si>
+    <t>22:24:43</t>
+  </si>
+  <si>
+    <t>19:56:32</t>
+  </si>
+  <si>
+    <t>21:33:44</t>
+  </si>
+  <si>
+    <t>20:42:50</t>
+  </si>
+  <si>
+    <t>19:52:00</t>
+  </si>
+  <si>
+    <t>20:38:45</t>
+  </si>
+  <si>
+    <t>19:47:27</t>
+  </si>
+  <si>
+    <t>20:49:14</t>
+  </si>
+  <si>
+    <t>22:27:37</t>
+  </si>
+  <si>
+    <t>19:58:50</t>
+  </si>
+  <si>
+    <t>21:36:03</t>
+  </si>
+  <si>
+    <t>20:44:58</t>
+  </si>
+  <si>
+    <t>19:54:06</t>
+  </si>
+  <si>
+    <t>20:41:35</t>
+  </si>
+  <si>
+    <t>19:49:45</t>
+  </si>
+  <si>
+    <t>20:52:24</t>
+  </si>
+  <si>
+    <t>22:29:18</t>
+  </si>
+  <si>
+    <t>20:01:41</t>
+  </si>
+  <si>
+    <t>21:38:47</t>
+  </si>
+  <si>
+    <t>20:48:09</t>
+  </si>
+  <si>
+    <t>19:57:23</t>
+  </si>
+  <si>
+    <t>20:43:22</t>
+  </si>
+  <si>
+    <t>19:52:32</t>
+  </si>
+  <si>
+    <t>20:55:33</t>
+  </si>
+  <si>
+    <t>22:30:59</t>
+  </si>
+  <si>
+    <t>20:04:31</t>
+  </si>
+  <si>
+    <t>21:41:31</t>
+  </si>
+  <si>
+    <t>20:51:18</t>
+  </si>
+  <si>
+    <t>20:00:39</t>
+  </si>
+  <si>
+    <t>20:45:10</t>
+  </si>
+  <si>
+    <t>19:55:19</t>
+  </si>
+  <si>
+    <t>20:57:41</t>
+  </si>
+  <si>
+    <t>22:33:52</t>
+  </si>
+  <si>
+    <t>20:06:48</t>
+  </si>
+  <si>
+    <t>21:43:49</t>
+  </si>
+  <si>
+    <t>20:53:25</t>
+  </si>
+  <si>
+    <t>20:02:44</t>
+  </si>
+  <si>
+    <t>20:47:58</t>
+  </si>
+  <si>
+    <t>19:57:36</t>
+  </si>
+  <si>
+    <t>40°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>16°</t>
   </si>
   <si>
     <t>12°</t>
   </si>
   <si>
-    <t>40°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>47°</t>
   </si>
   <si>
@@ -328,49 +283,43 @@
     <t>3°</t>
   </si>
   <si>
-    <t>20:07:14</t>
-  </si>
-  <si>
-    <t>21:40:02</t>
-  </si>
-  <si>
-    <t>20:51:52</t>
-  </si>
-  <si>
-    <t>22:24:39</t>
-  </si>
-  <si>
-    <t>20:03:44</t>
-  </si>
-  <si>
-    <t>21:36:32</t>
-  </si>
-  <si>
-    <t>20:48:27</t>
-  </si>
-  <si>
-    <t>20:00:26</t>
-  </si>
-  <si>
-    <t>20:45:19</t>
-  </si>
-  <si>
-    <t>19:57:28</t>
+    <t>20:51:48</t>
+  </si>
+  <si>
+    <t>22:24:35</t>
+  </si>
+  <si>
+    <t>20:03:37</t>
+  </si>
+  <si>
+    <t>21:36:24</t>
+  </si>
+  <si>
+    <t>20:48:14</t>
+  </si>
+  <si>
+    <t>20:00:07</t>
+  </si>
+  <si>
+    <t>20:44:52</t>
+  </si>
+  <si>
+    <t>19:56:53</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>1</t>
@@ -407,7 +356,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,7 +371,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +383,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,7 +454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -517,6 +484,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -920,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -998,52 +974,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="L2" s="4">
-        <v>-10.9</v>
+        <v>-21.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="O2" s="6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>25</v>
+      <c r="Q2" s="7">
+        <v>0</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -1054,52 +1030,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="L3" s="4">
-        <v>-31</v>
+        <v>-40</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="9">
-        <v>3</v>
+        <v>101</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
@@ -1110,52 +1086,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-10.7</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-21.1</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O4" s="9">
-        <v>2</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="O4" s="8">
+        <v>40</v>
+      </c>
+      <c r="P4" s="9">
+        <v>40</v>
       </c>
       <c r="Q4" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" s="7">
         <v>0</v>
@@ -1166,52 +1142,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="L5" s="4">
-        <v>-40.1</v>
+        <v>-30.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O5" s="9">
-        <v>4</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="O5" s="10">
+        <v>34</v>
+      </c>
+      <c r="P5" s="11">
+        <v>34</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1222,55 +1198,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="L6" s="4">
-        <v>-10.7</v>
+        <v>-20.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O6" s="9">
+        <v>100</v>
+      </c>
+      <c r="O6" s="10">
+        <v>18</v>
+      </c>
+      <c r="P6" s="12">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
         <v>1</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1278,45 +1254,45 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="L7" s="4">
-        <v>-30.8</v>
+        <v>-10.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O7" s="9">
+        <v>100</v>
+      </c>
+      <c r="O7" s="6">
         <v>0</v>
       </c>
       <c r="P7" s="7">
@@ -1334,55 +1310,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="L8" s="4">
-        <v>-20.8</v>
+        <v>-20.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O8" s="9">
-        <v>5</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="O8" s="6">
+        <v>6</v>
+      </c>
+      <c r="P8" s="13">
+        <v>4</v>
       </c>
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="10">
-        <v>3</v>
+      <c r="R8" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1390,226 +1366,114 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="L9" s="4">
-        <v>-10.4</v>
+        <v>-9.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O9" s="9">
+        <v>102</v>
+      </c>
+      <c r="O9" s="6">
         <v>6</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13">
         <v>6</v>
       </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
       <c r="R9" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-20.5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-9.9</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O11" s="6">
-        <v>27</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>27</v>
-      </c>
-      <c r="R11" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1628,12 +1492,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1650,22 +1514,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260909--01</t>
-  </si>
-  <si>
-    <t>20260909--02</t>
-  </si>
-  <si>
     <t>20260910--01</t>
   </si>
   <si>
@@ -94,16 +88,10 @@
     <t>20260914--01</t>
   </si>
   <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>03:22</t>
-  </si>
-  <si>
     <t>05:41</t>
   </si>
   <si>
-    <t>05:28</t>
+    <t>05:27</t>
   </si>
   <si>
     <t>06:20</t>
@@ -118,12 +106,6 @@
     <t>05:34</t>
   </si>
   <si>
-    <t>02:34</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
     <t>04:47</t>
   </si>
   <si>
@@ -133,40 +115,28 @@
     <t>03:16</t>
   </si>
   <si>
-    <t>06:01</t>
+    <t>06:02</t>
   </si>
   <si>
     <t>03:17</t>
   </si>
   <si>
-    <t>20:47:04</t>
-  </si>
-  <si>
-    <t>22:24:43</t>
-  </si>
-  <si>
     <t>19:56:32</t>
   </si>
   <si>
-    <t>21:33:44</t>
+    <t>21:33:43</t>
   </si>
   <si>
     <t>20:42:50</t>
   </si>
   <si>
-    <t>19:52:00</t>
-  </si>
-  <si>
-    <t>20:38:45</t>
-  </si>
-  <si>
-    <t>19:47:27</t>
-  </si>
-  <si>
-    <t>20:49:14</t>
-  </si>
-  <si>
-    <t>22:27:37</t>
+    <t>19:51:59</t>
+  </si>
+  <si>
+    <t>20:38:44</t>
+  </si>
+  <si>
+    <t>19:47:25</t>
   </si>
   <si>
     <t>19:58:50</t>
@@ -178,19 +148,13 @@
     <t>20:44:58</t>
   </si>
   <si>
-    <t>19:54:06</t>
-  </si>
-  <si>
-    <t>20:41:35</t>
-  </si>
-  <si>
-    <t>19:49:45</t>
-  </si>
-  <si>
-    <t>20:52:24</t>
-  </si>
-  <si>
-    <t>22:29:18</t>
+    <t>19:54:05</t>
+  </si>
+  <si>
+    <t>20:41:34</t>
+  </si>
+  <si>
+    <t>19:49:43</t>
   </si>
   <si>
     <t>20:01:41</t>
@@ -199,46 +163,34 @@
     <t>21:38:47</t>
   </si>
   <si>
-    <t>20:48:09</t>
-  </si>
-  <si>
-    <t>19:57:23</t>
-  </si>
-  <si>
-    <t>20:43:22</t>
-  </si>
-  <si>
-    <t>19:52:32</t>
-  </si>
-  <si>
-    <t>20:55:33</t>
-  </si>
-  <si>
-    <t>22:30:59</t>
+    <t>20:48:08</t>
+  </si>
+  <si>
+    <t>19:57:22</t>
+  </si>
+  <si>
+    <t>20:43:21</t>
+  </si>
+  <si>
+    <t>19:52:30</t>
   </si>
   <si>
     <t>20:04:31</t>
   </si>
   <si>
-    <t>21:41:31</t>
+    <t>21:41:30</t>
   </si>
   <si>
     <t>20:51:18</t>
   </si>
   <si>
-    <t>20:00:39</t>
-  </si>
-  <si>
-    <t>20:45:10</t>
-  </si>
-  <si>
-    <t>19:55:19</t>
-  </si>
-  <si>
-    <t>20:57:41</t>
-  </si>
-  <si>
-    <t>22:33:52</t>
+    <t>20:00:38</t>
+  </si>
+  <si>
+    <t>20:45:09</t>
+  </si>
+  <si>
+    <t>19:55:17</t>
   </si>
   <si>
     <t>20:06:48</t>
@@ -250,19 +202,13 @@
     <t>20:53:25</t>
   </si>
   <si>
-    <t>20:02:44</t>
-  </si>
-  <si>
-    <t>20:47:58</t>
-  </si>
-  <si>
-    <t>19:57:36</t>
-  </si>
-  <si>
-    <t>40°</t>
-  </si>
-  <si>
-    <t>0°</t>
+    <t>20:02:43</t>
+  </si>
+  <si>
+    <t>20:47:57</t>
+  </si>
+  <si>
+    <t>19:57:34</t>
   </si>
   <si>
     <t>16°</t>
@@ -283,12 +229,6 @@
     <t>3°</t>
   </si>
   <si>
-    <t>20:51:48</t>
-  </si>
-  <si>
-    <t>22:24:35</t>
-  </si>
-  <si>
     <t>20:03:37</t>
   </si>
   <si>
@@ -301,16 +241,13 @@
     <t>20:00:07</t>
   </si>
   <si>
-    <t>20:44:52</t>
-  </si>
-  <si>
-    <t>19:56:53</t>
+    <t>20:44:51</t>
+  </si>
+  <si>
+    <t>19:56:51</t>
   </si>
   <si>
     <t>A+B</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>A</t>
@@ -356,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,7 +308,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,25 +326,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +338,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -490,9 +421,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -896,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -974,54 +902,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L2" s="4">
-        <v>-21.1</v>
+        <v>-10.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1030,54 +958,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L3" s="4">
-        <v>-40</v>
+        <v>-30.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+        <v>79</v>
+      </c>
+      <c r="O3" s="9">
+        <v>21</v>
+      </c>
+      <c r="P3" s="10">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1086,54 +1014,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L4" s="4">
-        <v>-10.7</v>
+        <v>-20.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O4" s="8">
-        <v>40</v>
-      </c>
-      <c r="P4" s="9">
-        <v>40</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
+        <v>79</v>
+      </c>
+      <c r="O4" s="11">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1142,54 +1070,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="L5" s="4">
-        <v>-30.8</v>
+        <v>-10.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O5" s="10">
-        <v>34</v>
-      </c>
-      <c r="P5" s="11">
-        <v>34</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
+        <v>79</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1198,55 +1126,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="K6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-20.3</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-20.8</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O6" s="10">
-        <v>18</v>
-      </c>
-      <c r="P6" s="12">
-        <v>18</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+        <v>80</v>
+      </c>
+      <c r="O6" s="11">
+        <v>4</v>
+      </c>
+      <c r="P6" s="8">
         <v>1</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1254,226 +1182,114 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="K7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-9.9</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-10.3</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>14</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-20.4</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O8" s="6">
-        <v>6</v>
-      </c>
-      <c r="P8" s="13">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-9.9</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="O9" s="6">
-        <v>6</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>6</v>
-      </c>
-      <c r="R9" s="7">
+        <v>81</v>
+      </c>
+      <c r="O7" s="9">
+        <v>12</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>12</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1492,12 +1308,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1514,22 +1330,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260910--01</t>
-  </si>
-  <si>
-    <t>20260910--02</t>
-  </si>
-  <si>
     <t>20260911--01</t>
   </si>
   <si>
@@ -88,12 +82,6 @@
     <t>20260914--01</t>
   </si>
   <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>05:27</t>
-  </si>
-  <si>
     <t>06:20</t>
   </si>
   <si>
@@ -106,12 +94,6 @@
     <t>05:34</t>
   </si>
   <si>
-    <t>04:47</t>
-  </si>
-  <si>
-    <t>00:21</t>
-  </si>
-  <si>
     <t>03:16</t>
   </si>
   <si>
@@ -121,12 +103,6 @@
     <t>03:17</t>
   </si>
   <si>
-    <t>19:56:32</t>
-  </si>
-  <si>
-    <t>21:33:43</t>
-  </si>
-  <si>
     <t>20:42:50</t>
   </si>
   <si>
@@ -139,12 +115,6 @@
     <t>19:47:25</t>
   </si>
   <si>
-    <t>19:58:50</t>
-  </si>
-  <si>
-    <t>21:36:03</t>
-  </si>
-  <si>
     <t>20:44:58</t>
   </si>
   <si>
@@ -157,12 +127,6 @@
     <t>19:49:43</t>
   </si>
   <si>
-    <t>20:01:41</t>
-  </si>
-  <si>
-    <t>21:38:47</t>
-  </si>
-  <si>
     <t>20:48:08</t>
   </si>
   <si>
@@ -175,12 +139,6 @@
     <t>19:52:30</t>
   </si>
   <si>
-    <t>20:04:31</t>
-  </si>
-  <si>
-    <t>21:41:30</t>
-  </si>
-  <si>
     <t>20:51:18</t>
   </si>
   <si>
@@ -193,12 +151,6 @@
     <t>19:55:17</t>
   </si>
   <si>
-    <t>20:06:48</t>
-  </si>
-  <si>
-    <t>21:43:49</t>
-  </si>
-  <si>
     <t>20:53:25</t>
   </si>
   <si>
@@ -211,12 +163,6 @@
     <t>19:57:34</t>
   </si>
   <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
     <t>47°</t>
   </si>
   <si>
@@ -227,12 +173,6 @@
   </si>
   <si>
     <t>3°</t>
-  </si>
-  <si>
-    <t>20:03:37</t>
-  </si>
-  <si>
-    <t>21:36:24</t>
   </si>
   <si>
     <t>20:48:14</t>
@@ -293,7 +233,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,13 +248,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,25 +260,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -409,18 +325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -824,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -902,54 +806,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="4">
+        <v>-20.8</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-10.7</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="O2" s="6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -958,54 +862,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="L3" s="4">
-        <v>-30.8</v>
+        <v>-10.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O3" s="9">
-        <v>21</v>
-      </c>
-      <c r="P3" s="10">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
+        <v>59</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1014,54 +918,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="L4" s="4">
-        <v>-20.8</v>
+        <v>-20.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" s="11">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
+        <v>60</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1070,226 +974,114 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="L5" s="4">
-        <v>-10.3</v>
+        <v>-9.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="11">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
+        <v>61</v>
+      </c>
+      <c r="O5" s="6">
+        <v>7</v>
+      </c>
+      <c r="P5" s="7">
         <v>0</v>
       </c>
       <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-20.3</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O6" s="11">
-        <v>4</v>
-      </c>
-      <c r="P6" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-9.9</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O7" s="9">
-        <v>12</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>12</v>
-      </c>
-      <c r="R7" s="8">
+        <v>7</v>
+      </c>
+      <c r="R5" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A5">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B5">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J5">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K5">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1308,12 +1100,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M5">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N5">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1330,22 +1122,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O5">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P5">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q5">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R5">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260911--01</t>
-  </si>
-  <si>
     <t>20260912--01</t>
   </si>
   <si>
@@ -82,9 +79,6 @@
     <t>20260914--01</t>
   </si>
   <si>
-    <t>06:20</t>
-  </si>
-  <si>
     <t>06:33</t>
   </si>
   <si>
@@ -94,18 +88,12 @@
     <t>05:34</t>
   </si>
   <si>
-    <t>03:16</t>
-  </si>
-  <si>
     <t>06:02</t>
   </si>
   <si>
     <t>03:17</t>
   </si>
   <si>
-    <t>20:42:50</t>
-  </si>
-  <si>
     <t>19:51:59</t>
   </si>
   <si>
@@ -115,9 +103,6 @@
     <t>19:47:25</t>
   </si>
   <si>
-    <t>20:44:58</t>
-  </si>
-  <si>
     <t>19:54:05</t>
   </si>
   <si>
@@ -127,9 +112,6 @@
     <t>19:49:43</t>
   </si>
   <si>
-    <t>20:48:08</t>
-  </si>
-  <si>
     <t>19:57:22</t>
   </si>
   <si>
@@ -139,9 +121,6 @@
     <t>19:52:30</t>
   </si>
   <si>
-    <t>20:51:18</t>
-  </si>
-  <si>
     <t>20:00:38</t>
   </si>
   <si>
@@ -151,9 +130,6 @@
     <t>19:55:17</t>
   </si>
   <si>
-    <t>20:53:25</t>
-  </si>
-  <si>
     <t>20:02:43</t>
   </si>
   <si>
@@ -163,9 +139,6 @@
     <t>19:57:34</t>
   </si>
   <si>
-    <t>47°</t>
-  </si>
-  <si>
     <t>14°</t>
   </si>
   <si>
@@ -173,9 +146,6 @@
   </si>
   <si>
     <t>3°</t>
-  </si>
-  <si>
-    <t>20:48:14</t>
   </si>
   <si>
     <t>20:00:07</t>
@@ -233,7 +203,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,12 +225,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -301,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -322,9 +286,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -728,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -806,43 +767,43 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>85</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-10.3</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="N2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-20.8</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
@@ -862,43 +823,43 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-20.3</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-10.3</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
@@ -918,44 +879,44 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-9.9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-20.3</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="O4" s="6">
         <v>0</v>
       </c>
@@ -966,122 +927,66 @@
         <v>0</v>
       </c>
       <c r="R4" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-9.9</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O5" s="6">
-        <v>7</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>7</v>
-      </c>
-      <c r="R5" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A5">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B5">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J5">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K5">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L5">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1100,12 +1005,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M5">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N5">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1122,22 +1027,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O5">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P5">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -70,87 +70,57 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260912--01</t>
-  </si>
-  <si>
     <t>20260913--01</t>
   </si>
   <si>
     <t>20260914--01</t>
   </si>
   <si>
-    <t>06:33</t>
-  </si>
-  <si>
     <t>03:35</t>
   </si>
   <si>
     <t>05:34</t>
   </si>
   <si>
-    <t>06:02</t>
-  </si>
-  <si>
     <t>03:17</t>
   </si>
   <si>
-    <t>19:51:59</t>
-  </si>
-  <si>
     <t>20:38:44</t>
   </si>
   <si>
     <t>19:47:25</t>
   </si>
   <si>
-    <t>19:54:05</t>
-  </si>
-  <si>
     <t>20:41:34</t>
   </si>
   <si>
     <t>19:49:43</t>
   </si>
   <si>
-    <t>19:57:22</t>
-  </si>
-  <si>
     <t>20:43:21</t>
   </si>
   <si>
     <t>19:52:30</t>
   </si>
   <si>
-    <t>20:00:38</t>
-  </si>
-  <si>
     <t>20:45:09</t>
   </si>
   <si>
     <t>19:55:17</t>
   </si>
   <si>
-    <t>20:02:43</t>
-  </si>
-  <si>
     <t>20:47:57</t>
   </si>
   <si>
     <t>19:57:34</t>
   </si>
   <si>
-    <t>14°</t>
-  </si>
-  <si>
     <t>11°</t>
   </si>
   <si>
     <t>3°</t>
   </si>
   <si>
-    <t>20:00:07</t>
-  </si>
-  <si>
     <t>20:44:51</t>
   </si>
   <si>
@@ -161,9 +131,6 @@
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -203,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +192,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -286,6 +259,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -689,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -767,43 +743,43 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="L2" s="4">
-        <v>-10.3</v>
+        <v>-20.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
@@ -823,170 +799,114 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="L3" s="4">
-        <v>-20.3</v>
+        <v>-9.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O3" s="6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>0</v>
+      <c r="Q3" s="8">
+        <v>9</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-9.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1005,12 +925,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1027,22 +947,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -70,70 +70,34 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260913--01</t>
-  </si>
-  <si>
     <t>20260914--01</t>
   </si>
   <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>03:17</t>
-  </si>
-  <si>
-    <t>20:38:44</t>
-  </si>
-  <si>
-    <t>19:47:25</t>
-  </si>
-  <si>
-    <t>20:41:34</t>
-  </si>
-  <si>
-    <t>19:49:43</t>
-  </si>
-  <si>
-    <t>20:43:21</t>
-  </si>
-  <si>
-    <t>19:52:30</t>
-  </si>
-  <si>
-    <t>20:45:09</t>
-  </si>
-  <si>
-    <t>19:55:17</t>
-  </si>
-  <si>
-    <t>20:47:57</t>
-  </si>
-  <si>
-    <t>19:57:34</t>
-  </si>
-  <si>
-    <t>11°</t>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>19:47:46</t>
+  </si>
+  <si>
+    <t>19:50:04</t>
+  </si>
+  <si>
+    <t>19:52:51</t>
+  </si>
+  <si>
+    <t>19:55:37</t>
+  </si>
+  <si>
+    <t>19:57:54</t>
   </si>
   <si>
     <t>3°</t>
   </si>
   <si>
-    <t>20:44:51</t>
-  </si>
-  <si>
-    <t>19:56:51</t>
-  </si>
-  <si>
-    <t>A+B</t>
+    <t>19:57:10</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>1</t>
@@ -197,7 +161,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -743,170 +707,114 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-9.9</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-20.3</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
+      <c r="Q2" s="8">
+        <v>6</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-9.9</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="6">
-        <v>9</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>9</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -925,12 +833,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -947,22 +855,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -68,39 +68,6 @@
   </si>
   <si>
     <t>Vysoká</t>
-  </si>
-  <si>
-    <t>20260914--01</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>19:47:46</t>
-  </si>
-  <si>
-    <t>19:50:04</t>
-  </si>
-  <si>
-    <t>19:52:51</t>
-  </si>
-  <si>
-    <t>19:55:37</t>
-  </si>
-  <si>
-    <t>19:57:54</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>19:57:10</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -110,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,15 +93,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,24 +104,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -218,15 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -702,119 +635,63 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-9.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="6">
-        <v>6</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>6</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A1:A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B1:B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C1:C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D1:D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E1:E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F1:F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G1:G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H1:H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I1:I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J1:J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K1:K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L1:L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -833,12 +710,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M1:M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N1:N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -855,22 +732,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O1:O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P1:P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q1:Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R1:R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -68,6 +68,39 @@
   </si>
   <si>
     <t>Vysoká</t>
+  </si>
+  <si>
+    <t>20260924--01</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>06:20:04</t>
+  </si>
+  <si>
+    <t>06:22:23</t>
+  </si>
+  <si>
+    <t>06:25:06</t>
+  </si>
+  <si>
+    <t>06:27:50</t>
+  </si>
+  <si>
+    <t>06:30:11</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -77,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +126,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +144,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +224,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -635,63 +711,119 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-7.5</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="6">
+        <v>87</v>
+      </c>
+      <c r="P2" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>71</v>
+      </c>
+      <c r="R2" s="9">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H2">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -710,12 +842,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N2">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -732,22 +864,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O2">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P2">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q2">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R2">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t>Datum</t>
   </si>
@@ -73,34 +73,67 @@
     <t>20260924--01</t>
   </si>
   <si>
+    <t>20260925--01</t>
+  </si>
+  <si>
     <t>05:27</t>
   </si>
   <si>
+    <t>03:04</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
     <t>06:20:04</t>
   </si>
   <si>
+    <t>05:29:06</t>
+  </si>
+  <si>
     <t>06:22:23</t>
   </si>
   <si>
+    <t>05:32:05</t>
+  </si>
+  <si>
     <t>06:25:06</t>
   </si>
   <si>
+    <t>05:33:37</t>
+  </si>
+  <si>
     <t>06:27:50</t>
   </si>
   <si>
+    <t>05:35:09</t>
+  </si>
+  <si>
     <t>06:30:11</t>
   </si>
   <si>
+    <t>05:38:10</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>05:31:03</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -134,7 +167,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,13 +194,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -208,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -235,6 +274,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -638,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -719,111 +761,167 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L2" s="4">
         <v>-7.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="6">
+        <v>55</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>16</v>
+      </c>
+      <c r="R2" s="9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="6">
-        <v>87</v>
-      </c>
-      <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>71</v>
-      </c>
-      <c r="R2" s="9">
-        <v>52</v>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-19</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="6">
+        <v>70</v>
+      </c>
+      <c r="P3" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>57</v>
+      </c>
+      <c r="R3" s="9">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -842,12 +940,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -864,22 +962,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>Datum</t>
   </si>
@@ -76,12 +76,18 @@
     <t>20260925--01</t>
   </si>
   <si>
+    <t>20260926--01</t>
+  </si>
+  <si>
     <t>05:27</t>
   </si>
   <si>
     <t>03:04</t>
   </si>
   <si>
+    <t>06:35</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -91,39 +97,60 @@
     <t>05:29:06</t>
   </si>
   <si>
+    <t>06:13:22</t>
+  </si>
+  <si>
     <t>06:22:23</t>
   </si>
   <si>
     <t>05:32:05</t>
   </si>
   <si>
+    <t>06:15:27</t>
+  </si>
+  <si>
     <t>06:25:06</t>
   </si>
   <si>
     <t>05:33:37</t>
   </si>
   <si>
+    <t>06:18:44</t>
+  </si>
+  <si>
     <t>06:27:50</t>
   </si>
   <si>
     <t>05:35:09</t>
   </si>
   <si>
+    <t>06:22:02</t>
+  </si>
+  <si>
     <t>06:30:11</t>
   </si>
   <si>
     <t>05:38:10</t>
   </si>
   <si>
+    <t>06:24:08</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
     <t>7°</t>
   </si>
   <si>
+    <t>9°</t>
+  </si>
+  <si>
     <t>05:31:03</t>
   </si>
   <si>
+    <t>06:15:17</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
@@ -134,6 +161,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -167,7 +197,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,19 +224,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -247,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -277,6 +313,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -680,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -761,52 +800,52 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L2" s="4">
         <v>-7.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="O2" s="6">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="R2" s="9">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -817,111 +856,155 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L3" s="4">
         <v>-19</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="6">
+        <v>69</v>
+      </c>
+      <c r="P3" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>58</v>
+      </c>
+      <c r="R3" s="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>84</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="6">
-        <v>70</v>
-      </c>
-      <c r="P3" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>57</v>
-      </c>
-      <c r="R3" s="9">
-        <v>40</v>
+      <c r="J4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -940,12 +1023,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -962,22 +1045,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
   <si>
     <t>Datum</t>
   </si>
@@ -79,61 +79,85 @@
     <t>20260926--01</t>
   </si>
   <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>03:04</t>
-  </si>
-  <si>
-    <t>06:35</t>
+    <t>20260927--01</t>
+  </si>
+  <si>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>03:09</t>
+  </si>
+  <si>
+    <t>06:37</t>
+  </si>
+  <si>
+    <t>06:15</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>06:20:04</t>
-  </si>
-  <si>
-    <t>05:29:06</t>
-  </si>
-  <si>
-    <t>06:13:22</t>
-  </si>
-  <si>
-    <t>06:22:23</t>
-  </si>
-  <si>
-    <t>05:32:05</t>
-  </si>
-  <si>
-    <t>06:15:27</t>
-  </si>
-  <si>
-    <t>06:25:06</t>
-  </si>
-  <si>
-    <t>05:33:37</t>
-  </si>
-  <si>
-    <t>06:18:44</t>
-  </si>
-  <si>
-    <t>06:27:50</t>
-  </si>
-  <si>
-    <t>05:35:09</t>
-  </si>
-  <si>
-    <t>06:22:02</t>
-  </si>
-  <si>
-    <t>06:30:11</t>
-  </si>
-  <si>
-    <t>05:38:10</t>
-  </si>
-  <si>
-    <t>06:24:08</t>
+    <t>03:38</t>
+  </si>
+  <si>
+    <t>06:20:21</t>
+  </si>
+  <si>
+    <t>05:29:27</t>
+  </si>
+  <si>
+    <t>06:13:49</t>
+  </si>
+  <si>
+    <t>05:22:19</t>
+  </si>
+  <si>
+    <t>06:22:40</t>
+  </si>
+  <si>
+    <t>05:32:25</t>
+  </si>
+  <si>
+    <t>06:15:54</t>
+  </si>
+  <si>
+    <t>05:24:28</t>
+  </si>
+  <si>
+    <t>06:25:24</t>
+  </si>
+  <si>
+    <t>05:33:59</t>
+  </si>
+  <si>
+    <t>06:19:12</t>
+  </si>
+  <si>
+    <t>05:27:34</t>
+  </si>
+  <si>
+    <t>06:28:08</t>
+  </si>
+  <si>
+    <t>05:35:34</t>
+  </si>
+  <si>
+    <t>06:22:31</t>
+  </si>
+  <si>
+    <t>05:30:43</t>
+  </si>
+  <si>
+    <t>06:30:29</t>
+  </si>
+  <si>
+    <t>05:38:33</t>
+  </si>
+  <si>
+    <t>06:24:37</t>
+  </si>
+  <si>
+    <t>05:32:53</t>
   </si>
   <si>
     <t>-</t>
@@ -145,10 +169,16 @@
     <t>9°</t>
   </si>
   <si>
-    <t>05:31:03</t>
-  </si>
-  <si>
-    <t>06:15:17</t>
+    <t>38°</t>
+  </si>
+  <si>
+    <t>05:31:24</t>
+  </si>
+  <si>
+    <t>06:15:44</t>
+  </si>
+  <si>
+    <t>05:27:05</t>
   </si>
   <si>
     <t>A+B</t>
@@ -197,7 +227,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,19 +260,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -283,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -316,6 +352,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -719,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -800,43 +839,43 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L2" s="4">
-        <v>-7.5</v>
+        <v>-7.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="O2" s="6">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -845,7 +884,7 @@
         <v>41</v>
       </c>
       <c r="R2" s="9">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -856,52 +895,52 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L3" s="4">
-        <v>-19</v>
+        <v>-18.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="O3" s="6">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="P3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="10">
-        <v>58</v>
-      </c>
-      <c r="R3" s="11">
-        <v>32</v>
+        <v>73</v>
+      </c>
+      <c r="R3" s="8">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -909,102 +948,158 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-9.1</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="6">
+        <v>87</v>
+      </c>
+      <c r="P4" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>87</v>
+      </c>
+      <c r="R4" s="12">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>49</v>
+      <c r="H5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-20.4</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A5">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B5">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J5">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K5">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1023,12 +1118,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M5">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N5">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1045,22 +1140,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O5">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P5">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q5">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R5">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>Datum</t>
   </si>
@@ -82,7 +82,13 @@
     <t>20260927--01</t>
   </si>
   <si>
-    <t>05:28</t>
+    <t>20260928--01</t>
+  </si>
+  <si>
+    <t>20260928--02</t>
+  </si>
+  <si>
+    <t>05:29</t>
   </si>
   <si>
     <t>03:09</t>
@@ -94,70 +100,112 @@
     <t>06:15</t>
   </si>
   <si>
+    <t>05:08</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
     <t>03:38</t>
   </si>
   <si>
+    <t>00:16</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
     <t>06:20:21</t>
   </si>
   <si>
-    <t>05:29:27</t>
-  </si>
-  <si>
-    <t>06:13:49</t>
-  </si>
-  <si>
-    <t>05:22:19</t>
+    <t>05:29:28</t>
+  </si>
+  <si>
+    <t>06:13:50</t>
+  </si>
+  <si>
+    <t>05:22:20</t>
+  </si>
+  <si>
+    <t>04:31:01</t>
+  </si>
+  <si>
+    <t>06:07:45</t>
   </si>
   <si>
     <t>06:22:40</t>
   </si>
   <si>
-    <t>05:32:25</t>
-  </si>
-  <si>
-    <t>06:15:54</t>
-  </si>
-  <si>
-    <t>05:24:28</t>
+    <t>05:32:26</t>
+  </si>
+  <si>
+    <t>06:15:55</t>
+  </si>
+  <si>
+    <t>05:24:29</t>
+  </si>
+  <si>
+    <t>04:33:25</t>
+  </si>
+  <si>
+    <t>06:09:59</t>
   </si>
   <si>
     <t>06:25:24</t>
   </si>
   <si>
-    <t>05:33:59</t>
-  </si>
-  <si>
-    <t>06:19:12</t>
-  </si>
-  <si>
-    <t>05:27:34</t>
-  </si>
-  <si>
-    <t>06:28:08</t>
-  </si>
-  <si>
-    <t>05:35:34</t>
-  </si>
-  <si>
-    <t>06:22:31</t>
-  </si>
-  <si>
-    <t>05:30:43</t>
-  </si>
-  <si>
-    <t>06:30:29</t>
-  </si>
-  <si>
-    <t>05:38:33</t>
-  </si>
-  <si>
-    <t>06:24:37</t>
-  </si>
-  <si>
-    <t>05:32:53</t>
+    <t>05:34:00</t>
+  </si>
+  <si>
+    <t>06:19:13</t>
+  </si>
+  <si>
+    <t>05:27:36</t>
+  </si>
+  <si>
+    <t>04:35:58</t>
+  </si>
+  <si>
+    <t>06:12:57</t>
+  </si>
+  <si>
+    <t>06:28:09</t>
+  </si>
+  <si>
+    <t>05:35:35</t>
+  </si>
+  <si>
+    <t>06:22:32</t>
+  </si>
+  <si>
+    <t>05:30:44</t>
+  </si>
+  <si>
+    <t>04:38:33</t>
+  </si>
+  <si>
+    <t>06:15:56</t>
+  </si>
+  <si>
+    <t>06:30:30</t>
+  </si>
+  <si>
+    <t>05:38:34</t>
+  </si>
+  <si>
+    <t>06:24:38</t>
+  </si>
+  <si>
+    <t>05:32:54</t>
+  </si>
+  <si>
+    <t>04:40:58</t>
+  </si>
+  <si>
+    <t>06:18:11</t>
   </si>
   <si>
     <t>-</t>
@@ -172,13 +220,25 @@
     <t>38°</t>
   </si>
   <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
     <t>05:31:24</t>
   </si>
   <si>
     <t>06:15:44</t>
   </si>
   <si>
-    <t>05:27:05</t>
+    <t>05:27:06</t>
+  </si>
+  <si>
+    <t>04:38:17</t>
+  </si>
+  <si>
+    <t>06:11:01</t>
   </si>
   <si>
     <t>A+B</t>
@@ -227,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,19 +314,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -278,7 +344,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,6 +445,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -758,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -839,52 +944,52 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="L2" s="4">
         <v>-7.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="O2" s="6">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="R2" s="9">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -895,52 +1000,52 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="L3" s="4">
         <v>-18.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O3" s="6">
-        <v>87</v>
+        <v>78</v>
+      </c>
+      <c r="O3" s="10">
+        <v>38</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>73</v>
-      </c>
-      <c r="R3" s="8">
-        <v>39</v>
+      <c r="Q3" s="11">
+        <v>31</v>
+      </c>
+      <c r="R3" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -951,52 +1056,52 @@
         <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L4" s="4">
         <v>-9.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="O4" s="6">
         <v>87</v>
       </c>
-      <c r="P4" s="11">
-        <v>6</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>87</v>
-      </c>
-      <c r="R4" s="12">
-        <v>87</v>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>43</v>
+      </c>
+      <c r="R4" s="14">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1007,99 +1112,223 @@
         <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="L5" s="4">
         <v>-20.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="6">
+        <v>93</v>
+      </c>
+      <c r="P5" s="15">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>90</v>
+      </c>
+      <c r="R5" s="14">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-31.5</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" s="10">
+        <v>36</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>36</v>
+      </c>
+      <c r="R6" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>30</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>57</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-10.7</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="6">
+        <v>50</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>34</v>
+      </c>
+      <c r="R7" s="17">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A5">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B5">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J5">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K5">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L5">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1118,12 +1347,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M5">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N5">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1140,22 +1369,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O5">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P5">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
   <si>
     <t>Datum</t>
   </si>
@@ -88,6 +88,12 @@
     <t>20260928--02</t>
   </si>
   <si>
+    <t>20260929--01</t>
+  </si>
+  <si>
+    <t>20260929--02</t>
+  </si>
+  <si>
     <t>05:29</t>
   </si>
   <si>
@@ -106,6 +112,12 @@
     <t>05:57</t>
   </si>
   <si>
+    <t>02:04</t>
+  </si>
+  <si>
+    <t>06:29</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
     <t>04:55</t>
   </si>
   <si>
+    <t>02:21</t>
+  </si>
+  <si>
     <t>06:20:21</t>
   </si>
   <si>
@@ -136,6 +151,12 @@
     <t>06:07:45</t>
   </si>
   <si>
+    <t>03:39:58</t>
+  </si>
+  <si>
+    <t>05:15:46</t>
+  </si>
+  <si>
     <t>06:22:40</t>
   </si>
   <si>
@@ -154,6 +175,12 @@
     <t>06:09:59</t>
   </si>
   <si>
+    <t>03:43:18</t>
+  </si>
+  <si>
+    <t>05:17:52</t>
+  </si>
+  <si>
     <t>06:25:24</t>
   </si>
   <si>
@@ -172,6 +199,12 @@
     <t>06:12:57</t>
   </si>
   <si>
+    <t>03:44:20</t>
+  </si>
+  <si>
+    <t>05:21:06</t>
+  </si>
+  <si>
     <t>06:28:09</t>
   </si>
   <si>
@@ -190,6 +223,12 @@
     <t>06:15:56</t>
   </si>
   <si>
+    <t>03:45:22</t>
+  </si>
+  <si>
+    <t>05:24:21</t>
+  </si>
+  <si>
     <t>06:30:30</t>
   </si>
   <si>
@@ -208,6 +247,12 @@
     <t>06:18:11</t>
   </si>
   <si>
+    <t>03:48:44</t>
+  </si>
+  <si>
+    <t>05:26:29</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -226,6 +271,12 @@
     <t>17°</t>
   </si>
   <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>39°</t>
+  </si>
+  <si>
     <t>05:31:24</t>
   </si>
   <si>
@@ -241,10 +292,16 @@
     <t>06:11:01</t>
   </si>
   <si>
+    <t>05:22:00</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>2</t>
@@ -287,7 +344,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,7 +359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -314,7 +371,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,19 +395,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,25 +413,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -460,6 +523,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -863,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -944,52 +1010,52 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="L2" s="4">
         <v>-7.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="O2" s="6">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="R2" s="9">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1000,52 +1066,52 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="L3" s="4">
         <v>-18.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="O3" s="10">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="11">
-        <v>31</v>
-      </c>
-      <c r="R3" s="12">
-        <v>5</v>
+        <v>63</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1056,52 +1122,52 @@
         <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L4" s="4">
         <v>-9.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" s="6">
-        <v>87</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="O4" s="10">
+        <v>100</v>
+      </c>
+      <c r="P4" s="12">
+        <v>3</v>
       </c>
       <c r="Q4" s="13">
-        <v>43</v>
-      </c>
-      <c r="R4" s="14">
-        <v>48</v>
+        <v>100</v>
+      </c>
+      <c r="R4" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1112,52 +1178,52 @@
         <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="L5" s="4">
         <v>-20.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O5" s="6">
-        <v>93</v>
-      </c>
-      <c r="P5" s="15">
-        <v>62</v>
-      </c>
-      <c r="Q5" s="16">
-        <v>90</v>
-      </c>
-      <c r="R5" s="14">
-        <v>52</v>
+        <v>96</v>
+      </c>
+      <c r="O5" s="10">
+        <v>61</v>
+      </c>
+      <c r="P5" s="14">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>39</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1168,52 +1234,52 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="L6" s="4">
         <v>-31.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="O6" s="10">
-        <v>36</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>36</v>
-      </c>
-      <c r="R6" s="12">
-        <v>5</v>
+        <v>74</v>
+      </c>
+      <c r="P6" s="16">
+        <v>56</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>74</v>
+      </c>
+      <c r="R6" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1224,111 +1290,223 @@
         <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="L7" s="4">
         <v>-10.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="N7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O7" s="10">
+        <v>55</v>
+      </c>
+      <c r="P7" s="8">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>43</v>
+      </c>
+      <c r="R7" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="6">
-        <v>50</v>
-      </c>
-      <c r="P7" s="7">
+      <c r="J8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-42.4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O8" s="18">
+        <v>15</v>
+      </c>
+      <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="8">
-        <v>34</v>
-      </c>
-      <c r="R7" s="17">
-        <v>15</v>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>55</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-22.1</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="6">
+        <v>16</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>4</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1347,12 +1525,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1369,22 +1547,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
   <si>
     <t>Datum</t>
   </si>
@@ -94,6 +94,12 @@
     <t>20260929--02</t>
   </si>
   <si>
+    <t>20260930--01</t>
+  </si>
+  <si>
+    <t>20260930--02</t>
+  </si>
+  <si>
     <t>05:29</t>
   </si>
   <si>
@@ -106,22 +112,28 @@
     <t>06:15</t>
   </si>
   <si>
-    <t>05:08</t>
+    <t>05:09</t>
   </si>
   <si>
     <t>05:57</t>
   </si>
   <si>
-    <t>02:04</t>
+    <t>02:03</t>
   </si>
   <si>
     <t>06:29</t>
   </si>
   <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:38</t>
+    <t>03:37</t>
   </si>
   <si>
     <t>00:16</t>
@@ -133,124 +145,154 @@
     <t>02:21</t>
   </si>
   <si>
-    <t>06:20:21</t>
-  </si>
-  <si>
-    <t>05:29:28</t>
-  </si>
-  <si>
-    <t>06:13:50</t>
-  </si>
-  <si>
-    <t>05:22:20</t>
-  </si>
-  <si>
-    <t>04:31:01</t>
-  </si>
-  <si>
-    <t>06:07:45</t>
-  </si>
-  <si>
-    <t>03:39:58</t>
-  </si>
-  <si>
-    <t>05:15:46</t>
-  </si>
-  <si>
-    <t>06:22:40</t>
-  </si>
-  <si>
-    <t>05:32:26</t>
-  </si>
-  <si>
-    <t>06:15:55</t>
-  </si>
-  <si>
-    <t>05:24:29</t>
-  </si>
-  <si>
-    <t>04:33:25</t>
-  </si>
-  <si>
-    <t>06:09:59</t>
-  </si>
-  <si>
-    <t>03:43:18</t>
-  </si>
-  <si>
-    <t>05:17:52</t>
-  </si>
-  <si>
-    <t>06:25:24</t>
-  </si>
-  <si>
-    <t>05:34:00</t>
-  </si>
-  <si>
-    <t>06:19:13</t>
-  </si>
-  <si>
-    <t>05:27:36</t>
-  </si>
-  <si>
-    <t>04:35:58</t>
-  </si>
-  <si>
-    <t>06:12:57</t>
-  </si>
-  <si>
-    <t>03:44:20</t>
-  </si>
-  <si>
-    <t>05:21:06</t>
-  </si>
-  <si>
-    <t>06:28:09</t>
-  </si>
-  <si>
-    <t>05:35:35</t>
-  </si>
-  <si>
-    <t>06:22:32</t>
-  </si>
-  <si>
-    <t>05:30:44</t>
-  </si>
-  <si>
-    <t>04:38:33</t>
-  </si>
-  <si>
-    <t>06:15:56</t>
-  </si>
-  <si>
-    <t>03:45:22</t>
-  </si>
-  <si>
-    <t>05:24:21</t>
-  </si>
-  <si>
-    <t>06:30:30</t>
-  </si>
-  <si>
-    <t>05:38:34</t>
-  </si>
-  <si>
-    <t>06:24:38</t>
-  </si>
-  <si>
-    <t>05:32:54</t>
-  </si>
-  <si>
-    <t>04:40:58</t>
-  </si>
-  <si>
-    <t>06:18:11</t>
-  </si>
-  <si>
-    <t>03:48:44</t>
-  </si>
-  <si>
-    <t>05:26:29</t>
+    <t>02:55</t>
+  </si>
+  <si>
+    <t>06:20:20</t>
+  </si>
+  <si>
+    <t>05:29:26</t>
+  </si>
+  <si>
+    <t>06:13:48</t>
+  </si>
+  <si>
+    <t>05:22:18</t>
+  </si>
+  <si>
+    <t>04:30:58</t>
+  </si>
+  <si>
+    <t>06:07:41</t>
+  </si>
+  <si>
+    <t>03:39:54</t>
+  </si>
+  <si>
+    <t>05:15:42</t>
+  </si>
+  <si>
+    <t>04:23:50</t>
+  </si>
+  <si>
+    <t>06:01:52</t>
+  </si>
+  <si>
+    <t>06:22:39</t>
+  </si>
+  <si>
+    <t>05:32:24</t>
+  </si>
+  <si>
+    <t>06:15:53</t>
+  </si>
+  <si>
+    <t>05:24:26</t>
+  </si>
+  <si>
+    <t>04:33:21</t>
+  </si>
+  <si>
+    <t>06:09:56</t>
+  </si>
+  <si>
+    <t>03:43:15</t>
+  </si>
+  <si>
+    <t>05:17:48</t>
+  </si>
+  <si>
+    <t>04:25:55</t>
+  </si>
+  <si>
+    <t>06:04:43</t>
+  </si>
+  <si>
+    <t>06:25:23</t>
+  </si>
+  <si>
+    <t>05:33:58</t>
+  </si>
+  <si>
+    <t>06:19:11</t>
+  </si>
+  <si>
+    <t>05:27:33</t>
+  </si>
+  <si>
+    <t>04:35:55</t>
+  </si>
+  <si>
+    <t>06:12:53</t>
+  </si>
+  <si>
+    <t>03:44:16</t>
+  </si>
+  <si>
+    <t>05:21:02</t>
+  </si>
+  <si>
+    <t>04:29:10</t>
+  </si>
+  <si>
+    <t>06:06:33</t>
+  </si>
+  <si>
+    <t>06:28:08</t>
+  </si>
+  <si>
+    <t>05:35:33</t>
+  </si>
+  <si>
+    <t>06:22:30</t>
+  </si>
+  <si>
+    <t>05:30:41</t>
+  </si>
+  <si>
+    <t>04:38:30</t>
+  </si>
+  <si>
+    <t>03:45:18</t>
+  </si>
+  <si>
+    <t>05:24:17</t>
+  </si>
+  <si>
+    <t>04:32:28</t>
+  </si>
+  <si>
+    <t>06:08:23</t>
+  </si>
+  <si>
+    <t>06:30:29</t>
+  </si>
+  <si>
+    <t>05:38:32</t>
+  </si>
+  <si>
+    <t>06:24:36</t>
+  </si>
+  <si>
+    <t>05:32:52</t>
+  </si>
+  <si>
+    <t>04:40:54</t>
+  </si>
+  <si>
+    <t>06:18:08</t>
+  </si>
+  <si>
+    <t>03:48:40</t>
+  </si>
+  <si>
+    <t>05:26:25</t>
+  </si>
+  <si>
+    <t>04:34:34</t>
+  </si>
+  <si>
+    <t>06:11:16</t>
   </si>
   <si>
     <t>-</t>
@@ -277,22 +319,34 @@
     <t>39°</t>
   </si>
   <si>
-    <t>05:31:24</t>
-  </si>
-  <si>
-    <t>06:15:44</t>
-  </si>
-  <si>
-    <t>05:27:06</t>
-  </si>
-  <si>
-    <t>04:38:17</t>
-  </si>
-  <si>
-    <t>06:11:01</t>
-  </si>
-  <si>
-    <t>05:22:00</t>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>05:31:23</t>
+  </si>
+  <si>
+    <t>06:15:42</t>
+  </si>
+  <si>
+    <t>05:27:04</t>
+  </si>
+  <si>
+    <t>04:38:14</t>
+  </si>
+  <si>
+    <t>06:10:58</t>
+  </si>
+  <si>
+    <t>05:21:56</t>
+  </si>
+  <si>
+    <t>04:32:45</t>
+  </si>
+  <si>
+    <t>06:05:28</t>
   </si>
   <si>
     <t>A+B</t>
@@ -311,6 +365,9 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -344,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,7 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,19 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,25 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,13 +470,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -526,6 +595,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -929,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1010,52 +1085,52 @@
         <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="L2" s="4">
         <v>-7.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="O2" s="6">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="R2" s="9">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1066,52 +1141,52 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L3" s="4">
         <v>-18.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O3" s="10">
-        <v>64</v>
+        <v>115</v>
+      </c>
+      <c r="O3" s="6">
+        <v>89</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="11">
-        <v>63</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
+      <c r="Q3" s="10">
+        <v>68</v>
+      </c>
+      <c r="R3" s="11">
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1122,52 +1197,52 @@
         <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="L4" s="4">
         <v>-9.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="12">
+        <v>66</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>87</v>
+      </c>
+      <c r="R4" s="9">
         <v>98</v>
-      </c>
-      <c r="O4" s="10">
-        <v>100</v>
-      </c>
-      <c r="P4" s="12">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>100</v>
-      </c>
-      <c r="R4" s="13">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1178,52 +1253,52 @@
         <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="L5" s="4">
         <v>-20.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O5" s="6">
+        <v>97</v>
+      </c>
+      <c r="P5" s="14">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="15">
         <v>96</v>
       </c>
-      <c r="O5" s="10">
-        <v>61</v>
-      </c>
-      <c r="P5" s="14">
-        <v>47</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>39</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="R5" s="15">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1234,52 +1309,52 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="L6" s="4">
         <v>-31.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O6" s="10">
-        <v>74</v>
-      </c>
-      <c r="P6" s="16">
-        <v>56</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>74</v>
+        <v>114</v>
+      </c>
+      <c r="O6" s="6">
+        <v>97</v>
+      </c>
+      <c r="P6" s="13">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>90</v>
       </c>
       <c r="R6" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1290,52 +1365,52 @@
         <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="L7" s="4">
         <v>-10.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O7" s="10">
-        <v>55</v>
-      </c>
-      <c r="P7" s="8">
-        <v>23</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>43</v>
-      </c>
-      <c r="R7" s="12">
-        <v>5</v>
+        <v>114</v>
+      </c>
+      <c r="O7" s="6">
+        <v>80</v>
+      </c>
+      <c r="P7" s="17">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>37</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1346,49 +1421,49 @@
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L8" s="4">
         <v>-42.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O8" s="18">
-        <v>15</v>
+        <v>115</v>
+      </c>
+      <c r="O8" s="19">
+        <v>1</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
       <c r="Q8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -1402,111 +1477,223 @@
         <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L9" s="4">
         <v>-22.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O9" s="6">
-        <v>16</v>
+        <v>114</v>
+      </c>
+      <c r="O9" s="19">
+        <v>2</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="12">
-        <v>4</v>
+      <c r="Q9" s="7">
+        <v>1</v>
       </c>
       <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>73</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-33.2</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O10" s="19">
+        <v>5</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O11" s="19">
+        <v>5</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="20">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1525,12 +1712,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1547,22 +1734,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="128">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260924--01</t>
-  </si>
-  <si>
     <t>20260925--01</t>
   </si>
   <si>
@@ -100,10 +97,13 @@
     <t>20260930--02</t>
   </si>
   <si>
-    <t>05:29</t>
-  </si>
-  <si>
-    <t>03:09</t>
+    <t>20261001--01</t>
+  </si>
+  <si>
+    <t>20261001--02</t>
+  </si>
+  <si>
+    <t>03:08</t>
   </si>
   <si>
     <t>06:37</t>
@@ -112,190 +112,214 @@
     <t>06:15</t>
   </si>
   <si>
-    <t>05:09</t>
+    <t>05:07</t>
   </si>
   <si>
     <t>05:57</t>
   </si>
   <si>
-    <t>02:03</t>
+    <t>01:59</t>
   </si>
   <si>
     <t>06:29</t>
   </si>
   <si>
-    <t>06:33</t>
-  </si>
-  <si>
-    <t>03:40</t>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>03:41</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:38</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>04:54</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:37</t>
-  </si>
-  <si>
-    <t>00:16</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>02:21</t>
+    <t>02:20</t>
   </si>
   <si>
     <t>02:55</t>
   </si>
   <si>
-    <t>06:20:20</t>
-  </si>
-  <si>
-    <t>05:29:26</t>
-  </si>
-  <si>
-    <t>06:13:48</t>
-  </si>
-  <si>
-    <t>05:22:18</t>
-  </si>
-  <si>
-    <t>04:30:58</t>
-  </si>
-  <si>
-    <t>06:07:41</t>
-  </si>
-  <si>
-    <t>03:39:54</t>
-  </si>
-  <si>
-    <t>05:15:42</t>
-  </si>
-  <si>
-    <t>04:23:50</t>
-  </si>
-  <si>
-    <t>06:01:52</t>
-  </si>
-  <si>
-    <t>06:22:39</t>
+    <t>00:53</t>
+  </si>
+  <si>
+    <t>05:29:25</t>
+  </si>
+  <si>
+    <t>06:13:45</t>
+  </si>
+  <si>
+    <t>05:22:12</t>
+  </si>
+  <si>
+    <t>04:30:49</t>
+  </si>
+  <si>
+    <t>06:07:32</t>
+  </si>
+  <si>
+    <t>03:39:41</t>
+  </si>
+  <si>
+    <t>05:15:28</t>
+  </si>
+  <si>
+    <t>04:23:31</t>
+  </si>
+  <si>
+    <t>06:01:32</t>
+  </si>
+  <si>
+    <t>03:31:42</t>
+  </si>
+  <si>
+    <t>05:09:01</t>
   </si>
   <si>
     <t>05:32:24</t>
   </si>
   <si>
-    <t>06:15:53</t>
-  </si>
-  <si>
-    <t>05:24:26</t>
-  </si>
-  <si>
-    <t>04:33:21</t>
-  </si>
-  <si>
-    <t>06:09:56</t>
-  </si>
-  <si>
-    <t>03:43:15</t>
-  </si>
-  <si>
-    <t>05:17:48</t>
-  </si>
-  <si>
-    <t>04:25:55</t>
-  </si>
-  <si>
-    <t>06:04:43</t>
-  </si>
-  <si>
-    <t>06:25:23</t>
-  </si>
-  <si>
-    <t>05:33:58</t>
-  </si>
-  <si>
-    <t>06:19:11</t>
-  </si>
-  <si>
-    <t>05:27:33</t>
-  </si>
-  <si>
-    <t>04:35:55</t>
-  </si>
-  <si>
-    <t>06:12:53</t>
-  </si>
-  <si>
-    <t>03:44:16</t>
-  </si>
-  <si>
-    <t>05:21:02</t>
-  </si>
-  <si>
-    <t>04:29:10</t>
-  </si>
-  <si>
-    <t>06:06:33</t>
-  </si>
-  <si>
-    <t>06:28:08</t>
-  </si>
-  <si>
-    <t>05:35:33</t>
-  </si>
-  <si>
-    <t>06:22:30</t>
-  </si>
-  <si>
-    <t>05:30:41</t>
-  </si>
-  <si>
-    <t>04:38:30</t>
-  </si>
-  <si>
-    <t>03:45:18</t>
-  </si>
-  <si>
-    <t>05:24:17</t>
-  </si>
-  <si>
-    <t>04:32:28</t>
-  </si>
-  <si>
-    <t>06:08:23</t>
-  </si>
-  <si>
-    <t>06:30:29</t>
-  </si>
-  <si>
-    <t>05:38:32</t>
-  </si>
-  <si>
-    <t>06:24:36</t>
-  </si>
-  <si>
-    <t>05:32:52</t>
-  </si>
-  <si>
-    <t>04:40:54</t>
-  </si>
-  <si>
-    <t>06:18:08</t>
-  </si>
-  <si>
-    <t>03:48:40</t>
-  </si>
-  <si>
-    <t>05:26:25</t>
-  </si>
-  <si>
-    <t>04:34:34</t>
-  </si>
-  <si>
-    <t>06:11:16</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>06:15:50</t>
+  </si>
+  <si>
+    <t>05:24:21</t>
+  </si>
+  <si>
+    <t>04:33:13</t>
+  </si>
+  <si>
+    <t>06:09:46</t>
+  </si>
+  <si>
+    <t>03:43:03</t>
+  </si>
+  <si>
+    <t>05:17:34</t>
+  </si>
+  <si>
+    <t>04:25:36</t>
+  </si>
+  <si>
+    <t>06:04:23</t>
+  </si>
+  <si>
+    <t>03:33:53</t>
+  </si>
+  <si>
+    <t>05:11:25</t>
+  </si>
+  <si>
+    <t>05:33:57</t>
+  </si>
+  <si>
+    <t>06:19:08</t>
+  </si>
+  <si>
+    <t>05:27:27</t>
+  </si>
+  <si>
+    <t>04:35:46</t>
+  </si>
+  <si>
+    <t>06:12:44</t>
+  </si>
+  <si>
+    <t>03:44:02</t>
+  </si>
+  <si>
+    <t>05:20:48</t>
+  </si>
+  <si>
+    <t>04:28:51</t>
+  </si>
+  <si>
+    <t>06:06:13</t>
+  </si>
+  <si>
+    <t>03:36:53</t>
+  </si>
+  <si>
+    <t>05:14:00</t>
+  </si>
+  <si>
+    <t>05:35:32</t>
+  </si>
+  <si>
+    <t>06:22:27</t>
+  </si>
+  <si>
+    <t>05:30:36</t>
+  </si>
+  <si>
+    <t>04:38:20</t>
+  </si>
+  <si>
+    <t>06:15:43</t>
+  </si>
+  <si>
+    <t>03:45:02</t>
+  </si>
+  <si>
+    <t>05:24:03</t>
+  </si>
+  <si>
+    <t>04:32:08</t>
+  </si>
+  <si>
+    <t>06:08:04</t>
+  </si>
+  <si>
+    <t>03:39:55</t>
+  </si>
+  <si>
+    <t>05:16:36</t>
+  </si>
+  <si>
+    <t>05:38:31</t>
+  </si>
+  <si>
+    <t>06:24:33</t>
+  </si>
+  <si>
+    <t>05:32:46</t>
+  </si>
+  <si>
+    <t>04:40:45</t>
+  </si>
+  <si>
+    <t>06:17:59</t>
+  </si>
+  <si>
+    <t>03:48:25</t>
+  </si>
+  <si>
+    <t>05:26:11</t>
+  </si>
+  <si>
+    <t>04:34:14</t>
+  </si>
+  <si>
+    <t>06:10:56</t>
+  </si>
+  <si>
+    <t>03:42:07</t>
+  </si>
+  <si>
+    <t>05:19:02</t>
   </si>
   <si>
     <t>7°</t>
@@ -322,49 +346,55 @@
     <t>8°</t>
   </si>
   <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>05:31:23</t>
-  </si>
-  <si>
-    <t>06:15:42</t>
-  </si>
-  <si>
-    <t>05:27:04</t>
-  </si>
-  <si>
-    <t>04:38:14</t>
-  </si>
-  <si>
-    <t>06:10:58</t>
-  </si>
-  <si>
-    <t>05:21:56</t>
-  </si>
-  <si>
-    <t>04:32:45</t>
-  </si>
-  <si>
-    <t>06:05:28</t>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>05:31:22</t>
+  </si>
+  <si>
+    <t>06:15:40</t>
+  </si>
+  <si>
+    <t>05:26:58</t>
+  </si>
+  <si>
+    <t>04:38:05</t>
+  </si>
+  <si>
+    <t>06:10:49</t>
+  </si>
+  <si>
+    <t>05:21:43</t>
+  </si>
+  <si>
+    <t>04:32:27</t>
+  </si>
+  <si>
+    <t>06:05:09</t>
+  </si>
+  <si>
+    <t>05:15:43</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>3</t>
@@ -401,7 +431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,7 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,49 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -589,18 +595,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1004,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1082,55 +1076,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="L2" s="4">
-        <v>-7.4</v>
+        <v>-18.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="R2" s="9">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1138,55 +1132,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L3" s="4">
-        <v>-18.9</v>
+        <v>-9.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O3" s="6">
-        <v>89</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>68</v>
-      </c>
-      <c r="R3" s="11">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="P3" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>90</v>
+      </c>
+      <c r="R3" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1194,55 +1188,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L4" s="4">
-        <v>-9.1</v>
+        <v>-20.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="12">
-        <v>66</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>87</v>
-      </c>
-      <c r="R4" s="9">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="P4" s="13">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>88</v>
+      </c>
+      <c r="R4" s="14">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1250,55 +1244,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L5" s="4">
-        <v>-20.4</v>
+        <v>-31.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="O5" s="6">
-        <v>97</v>
-      </c>
-      <c r="P5" s="14">
-        <v>57</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>96</v>
-      </c>
-      <c r="R5" s="15">
-        <v>97</v>
+        <v>69</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>8</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1306,55 +1300,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L6" s="4">
-        <v>-31.5</v>
+        <v>-10.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="O6" s="6">
-        <v>97</v>
-      </c>
-      <c r="P6" s="13">
-        <v>87</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>90</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="P6" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>2</v>
+      </c>
+      <c r="R6" s="9">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1362,52 +1356,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="L7" s="4">
-        <v>-10.7</v>
+        <v>-42.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="O7" s="6">
-        <v>80</v>
-      </c>
-      <c r="P7" s="17">
-        <v>51</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>37</v>
+        <v>124</v>
+      </c>
+      <c r="O7" s="15">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -1418,52 +1412,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="L8" s="4">
-        <v>-42.4</v>
+        <v>-22.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O8" s="19">
-        <v>1</v>
+        <v>126</v>
+      </c>
+      <c r="O8" s="15">
+        <v>6</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
-        <v>1</v>
+      <c r="Q8" s="10">
+        <v>6</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -1474,55 +1468,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L9" s="4">
-        <v>-22.1</v>
+        <v>-33.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="O9" s="19">
+        <v>127</v>
+      </c>
+      <c r="O9" s="16">
+        <v>31</v>
+      </c>
+      <c r="P9" s="7">
         <v>2</v>
       </c>
-      <c r="P9" s="7">
+      <c r="Q9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="7">
-        <v>1</v>
-      </c>
-      <c r="R9" s="7">
-        <v>0</v>
+      <c r="R9" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1530,55 +1524,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L10" s="4">
-        <v>-33.2</v>
+        <v>-12.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O10" s="19">
-        <v>5</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
+        <v>124</v>
+      </c>
+      <c r="O10" s="6">
+        <v>65</v>
+      </c>
+      <c r="P10" s="10">
+        <v>3</v>
       </c>
       <c r="Q10" s="7">
         <v>0</v>
       </c>
-      <c r="R10" s="20">
-        <v>5</v>
+      <c r="R10" s="9">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1586,46 +1580,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="L11" s="4">
-        <v>-12.3</v>
+        <v>-44.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O11" s="19">
-        <v>5</v>
+        <v>127</v>
+      </c>
+      <c r="O11" s="6">
+        <v>69</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
@@ -1633,67 +1627,123 @@
       <c r="Q11" s="7">
         <v>0</v>
       </c>
-      <c r="R11" s="20">
-        <v>5</v>
+      <c r="R11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-23.8</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="O12" s="6">
+        <v>64</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A12">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B12">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J12">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K12">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1712,12 +1762,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M12">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N12">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1734,22 +1784,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O12">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P12">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q12">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R12">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="135">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260925--01</t>
-  </si>
-  <si>
     <t>20260926--01</t>
   </si>
   <si>
@@ -103,7 +100,10 @@
     <t>20261001--02</t>
   </si>
   <si>
-    <t>03:08</t>
+    <t>20261002--01</t>
+  </si>
+  <si>
+    <t>20261002--02</t>
   </si>
   <si>
     <t>06:37</t>
@@ -136,6 +136,12 @@
     <t>05:11</t>
   </si>
   <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
     <t>03:38</t>
   </si>
   <si>
@@ -157,9 +163,6 @@
     <t>00:53</t>
   </si>
   <si>
-    <t>05:29:25</t>
-  </si>
-  <si>
     <t>06:13:45</t>
   </si>
   <si>
@@ -190,7 +193,10 @@
     <t>05:09:01</t>
   </si>
   <si>
-    <t>05:32:24</t>
+    <t>02:40:05</t>
+  </si>
+  <si>
+    <t>04:16:34</t>
   </si>
   <si>
     <t>06:15:50</t>
@@ -223,7 +229,10 @@
     <t>05:11:25</t>
   </si>
   <si>
-    <t>05:33:57</t>
+    <t>02:42:36</t>
+  </si>
+  <si>
+    <t>04:18:46</t>
   </si>
   <si>
     <t>06:19:08</t>
@@ -256,7 +265,10 @@
     <t>05:14:00</t>
   </si>
   <si>
-    <t>05:35:32</t>
+    <t>02:44:54</t>
+  </si>
+  <si>
+    <t>04:21:47</t>
   </si>
   <si>
     <t>06:22:27</t>
@@ -289,7 +301,10 @@
     <t>05:16:36</t>
   </si>
   <si>
-    <t>05:38:31</t>
+    <t>02:47:13</t>
+  </si>
+  <si>
+    <t>04:24:50</t>
   </si>
   <si>
     <t>06:24:33</t>
@@ -322,7 +337,10 @@
     <t>05:19:02</t>
   </si>
   <si>
-    <t>7°</t>
+    <t>02:49:44</t>
+  </si>
+  <si>
+    <t>04:27:03</t>
   </si>
   <si>
     <t>9°</t>
@@ -352,7 +370,7 @@
     <t>15°</t>
   </si>
   <si>
-    <t>05:31:22</t>
+    <t>4°</t>
   </si>
   <si>
     <t>06:15:40</t>
@@ -379,6 +397,9 @@
     <t>05:15:43</t>
   </si>
   <si>
+    <t>04:26:07</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -388,13 +409,13 @@
     <t>B</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>3</t>
@@ -431,7 +452,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,19 +473,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,31 +521,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -547,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,6 +622,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -998,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1076,55 +1106,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="L2" s="4">
-        <v>-18.9</v>
+        <v>-9.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="O2" s="6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="8">
-        <v>75</v>
-      </c>
-      <c r="R2" s="9">
-        <v>10</v>
+        <v>94</v>
+      </c>
+      <c r="R2" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1132,54 +1162,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="L3" s="4">
-        <v>-9.1</v>
+        <v>-20.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
       </c>
-      <c r="P3" s="10">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="11">
+      <c r="P3" s="9">
         <v>90</v>
       </c>
-      <c r="R3" s="12">
+      <c r="Q3" s="8">
+        <v>97</v>
+      </c>
+      <c r="R3" s="7">
         <v>100</v>
       </c>
     </row>
@@ -1188,55 +1218,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="L4" s="4">
-        <v>-20.4</v>
+        <v>-31.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O4" s="6">
-        <v>99</v>
-      </c>
-      <c r="P4" s="13">
-        <v>52</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>88</v>
-      </c>
-      <c r="R4" s="14">
+        <v>100</v>
+      </c>
+      <c r="P4" s="8">
+        <v>96</v>
+      </c>
+      <c r="Q4" s="10">
         <v>63</v>
+      </c>
+      <c r="R4" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1244,54 +1274,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="L5" s="4">
-        <v>-31.6</v>
+        <v>-10.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O5" s="6">
-        <v>69</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>8</v>
-      </c>
-      <c r="R5" s="7">
+        <v>98</v>
+      </c>
+      <c r="P5" s="8">
+        <v>96</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>53</v>
+      </c>
+      <c r="R5" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1300,55 +1330,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L6" s="4">
-        <v>-10.7</v>
+        <v>-42.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O6" s="6">
-        <v>71</v>
-      </c>
-      <c r="P6" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>2</v>
-      </c>
-      <c r="R6" s="9">
-        <v>10</v>
+        <v>133</v>
+      </c>
+      <c r="O6" s="13">
+        <v>14</v>
+      </c>
+      <c r="P6" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>14</v>
+      </c>
+      <c r="R6" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1356,54 +1386,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="L7" s="4">
-        <v>-42.4</v>
+        <v>-22.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O7" s="15">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+        <v>132</v>
+      </c>
+      <c r="O7" s="13">
+        <v>12</v>
+      </c>
+      <c r="P7" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>12</v>
+      </c>
+      <c r="R7" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1412,54 +1442,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="L8" s="4">
-        <v>-22.1</v>
+        <v>-33.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O8" s="15">
+        <v>134</v>
+      </c>
+      <c r="O8" s="13">
+        <v>8</v>
+      </c>
+      <c r="P8" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="14">
         <v>6</v>
       </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>6</v>
-      </c>
-      <c r="R8" s="7">
+      <c r="R8" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1468,55 +1498,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="L9" s="4">
-        <v>-33.2</v>
+        <v>-12.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O9" s="16">
-        <v>31</v>
-      </c>
-      <c r="P9" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="7">
+        <v>133</v>
+      </c>
+      <c r="O9" s="13">
+        <v>16</v>
+      </c>
+      <c r="P9" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>16</v>
+      </c>
+      <c r="R9" s="11">
         <v>0</v>
-      </c>
-      <c r="R9" s="10">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1524,55 +1554,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="L10" s="4">
-        <v>-12.3</v>
+        <v>-44.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O10" s="6">
-        <v>65</v>
-      </c>
-      <c r="P10" s="10">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="7">
+        <v>134</v>
+      </c>
+      <c r="O10" s="13">
+        <v>16</v>
+      </c>
+      <c r="P10" s="11">
         <v>0</v>
       </c>
-      <c r="R10" s="9">
-        <v>9</v>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1580,55 +1610,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="L11" s="4">
-        <v>-44.2</v>
+        <v>-23.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="O11" s="6">
-        <v>69</v>
-      </c>
-      <c r="P11" s="7">
+        <v>53</v>
+      </c>
+      <c r="P11" s="11">
         <v>0</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="11">
         <v>0</v>
       </c>
-      <c r="R11" s="7">
-        <v>0</v>
+      <c r="R11" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1636,114 +1666,170 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="L12" s="4">
-        <v>-23.8</v>
+        <v>-54.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O12" s="6">
-        <v>64</v>
-      </c>
-      <c r="P12" s="7">
+        <v>134</v>
+      </c>
+      <c r="O12" s="17">
+        <v>30</v>
+      </c>
+      <c r="P12" s="14">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="11">
         <v>0</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="R12" s="11">
         <v>0</v>
       </c>
-      <c r="R12" s="7">
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-35</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O13" s="6">
+        <v>56</v>
+      </c>
+      <c r="P13" s="16">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>0</v>
+      </c>
+      <c r="R13" s="11">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A12">
+  <conditionalFormatting sqref="A2:A13">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B12">
+  <conditionalFormatting sqref="B2:B13">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H12">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
+  <conditionalFormatting sqref="I2:I13">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J12">
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K12">
+  <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L12">
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1762,12 +1848,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M12">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N12">
+  <conditionalFormatting sqref="N2:N13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1784,22 +1870,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O12">
+  <conditionalFormatting sqref="O2:O13">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P12">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q12">
+  <conditionalFormatting sqref="Q2:Q13">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R12">
+  <conditionalFormatting sqref="R2:R13">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="140">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260926--01</t>
-  </si>
-  <si>
     <t>20260927--01</t>
   </si>
   <si>
@@ -106,7 +103,10 @@
     <t>20261002--02</t>
   </si>
   <si>
-    <t>06:37</t>
+    <t>20261003--01</t>
+  </si>
+  <si>
+    <t>20261003--02</t>
   </si>
   <si>
     <t>06:15</t>
@@ -118,7 +118,7 @@
     <t>05:57</t>
   </si>
   <si>
-    <t>01:59</t>
+    <t>01:55</t>
   </si>
   <si>
     <t>06:29</t>
@@ -127,22 +127,28 @@
     <t>06:32</t>
   </si>
   <si>
-    <t>03:41</t>
-  </si>
-  <si>
-    <t>06:02</t>
+    <t>03:43</t>
+  </si>
+  <si>
+    <t>06:01</t>
   </si>
   <si>
     <t>05:11</t>
   </si>
   <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>03:38</t>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>01:36</t>
+  </si>
+  <si>
+    <t>03:37</t>
   </si>
   <si>
     <t>00:15</t>
@@ -154,262 +160,271 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>02:55</t>
-  </si>
-  <si>
-    <t>00:53</t>
-  </si>
-  <si>
-    <t>06:13:45</t>
-  </si>
-  <si>
-    <t>05:22:12</t>
-  </si>
-  <si>
-    <t>04:30:49</t>
-  </si>
-  <si>
-    <t>06:07:32</t>
-  </si>
-  <si>
-    <t>03:39:41</t>
-  </si>
-  <si>
-    <t>05:15:28</t>
-  </si>
-  <si>
-    <t>04:23:31</t>
-  </si>
-  <si>
-    <t>06:01:32</t>
-  </si>
-  <si>
-    <t>03:31:42</t>
-  </si>
-  <si>
-    <t>05:09:01</t>
-  </si>
-  <si>
-    <t>02:40:05</t>
-  </si>
-  <si>
-    <t>04:16:34</t>
-  </si>
-  <si>
-    <t>06:15:50</t>
-  </si>
-  <si>
-    <t>05:24:21</t>
-  </si>
-  <si>
-    <t>04:33:13</t>
-  </si>
-  <si>
-    <t>06:09:46</t>
-  </si>
-  <si>
-    <t>03:43:03</t>
-  </si>
-  <si>
-    <t>05:17:34</t>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>02:54</t>
+  </si>
+  <si>
+    <t>00:52</t>
+  </si>
+  <si>
+    <t>05:22:08</t>
+  </si>
+  <si>
+    <t>04:30:41</t>
+  </si>
+  <si>
+    <t>06:07:24</t>
+  </si>
+  <si>
+    <t>03:39:29</t>
+  </si>
+  <si>
+    <t>05:15:15</t>
+  </si>
+  <si>
+    <t>04:23:13</t>
+  </si>
+  <si>
+    <t>06:01:13</t>
+  </si>
+  <si>
+    <t>03:31:18</t>
+  </si>
+  <si>
+    <t>05:08:35</t>
+  </si>
+  <si>
+    <t>02:39:34</t>
+  </si>
+  <si>
+    <t>04:16:02</t>
+  </si>
+  <si>
+    <t>03:23:33</t>
+  </si>
+  <si>
+    <t>05:02:00</t>
+  </si>
+  <si>
+    <t>05:24:16</t>
+  </si>
+  <si>
+    <t>04:33:05</t>
+  </si>
+  <si>
+    <t>06:09:38</t>
+  </si>
+  <si>
+    <t>03:42:53</t>
+  </si>
+  <si>
+    <t>05:17:21</t>
+  </si>
+  <si>
+    <t>04:25:18</t>
+  </si>
+  <si>
+    <t>06:04:03</t>
+  </si>
+  <si>
+    <t>03:33:29</t>
+  </si>
+  <si>
+    <t>05:11:00</t>
+  </si>
+  <si>
+    <t>02:42:05</t>
+  </si>
+  <si>
+    <t>04:18:13</t>
+  </si>
+  <si>
+    <t>03:25:38</t>
+  </si>
+  <si>
+    <t>05:05:36</t>
+  </si>
+  <si>
+    <t>05:27:23</t>
+  </si>
+  <si>
+    <t>04:35:38</t>
+  </si>
+  <si>
+    <t>06:12:36</t>
+  </si>
+  <si>
+    <t>03:43:50</t>
+  </si>
+  <si>
+    <t>05:20:35</t>
+  </si>
+  <si>
+    <t>04:28:33</t>
+  </si>
+  <si>
+    <t>06:05:54</t>
+  </si>
+  <si>
+    <t>03:36:29</t>
+  </si>
+  <si>
+    <t>05:13:35</t>
+  </si>
+  <si>
+    <t>02:44:22</t>
+  </si>
+  <si>
+    <t>04:21:15</t>
+  </si>
+  <si>
+    <t>03:28:53</t>
+  </si>
+  <si>
+    <t>05:06:24</t>
+  </si>
+  <si>
+    <t>05:30:31</t>
+  </si>
+  <si>
+    <t>04:38:12</t>
+  </si>
+  <si>
+    <t>06:15:35</t>
+  </si>
+  <si>
+    <t>03:44:48</t>
+  </si>
+  <si>
+    <t>05:23:50</t>
+  </si>
+  <si>
+    <t>04:31:50</t>
+  </si>
+  <si>
+    <t>06:07:46</t>
+  </si>
+  <si>
+    <t>03:39:30</t>
+  </si>
+  <si>
+    <t>05:16:11</t>
+  </si>
+  <si>
+    <t>02:46:39</t>
+  </si>
+  <si>
+    <t>04:24:18</t>
+  </si>
+  <si>
+    <t>03:32:09</t>
+  </si>
+  <si>
+    <t>05:07:12</t>
+  </si>
+  <si>
+    <t>05:32:41</t>
+  </si>
+  <si>
+    <t>04:40:37</t>
+  </si>
+  <si>
+    <t>06:17:51</t>
+  </si>
+  <si>
+    <t>03:48:13</t>
+  </si>
+  <si>
+    <t>05:25:58</t>
+  </si>
+  <si>
+    <t>04:33:56</t>
+  </si>
+  <si>
+    <t>06:10:37</t>
+  </si>
+  <si>
+    <t>03:41:42</t>
+  </si>
+  <si>
+    <t>05:18:38</t>
+  </si>
+  <si>
+    <t>02:49:12</t>
+  </si>
+  <si>
+    <t>04:26:31</t>
+  </si>
+  <si>
+    <t>03:34:15</t>
+  </si>
+  <si>
+    <t>05:10:48</t>
+  </si>
+  <si>
+    <t>38°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>39°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>05:26:54</t>
+  </si>
+  <si>
+    <t>04:37:57</t>
+  </si>
+  <si>
+    <t>06:10:41</t>
+  </si>
+  <si>
+    <t>05:21:31</t>
+  </si>
+  <si>
+    <t>04:32:09</t>
+  </si>
+  <si>
+    <t>06:04:52</t>
+  </si>
+  <si>
+    <t>05:15:19</t>
   </si>
   <si>
     <t>04:25:36</t>
   </si>
   <si>
-    <t>06:04:23</t>
-  </si>
-  <si>
-    <t>03:33:53</t>
-  </si>
-  <si>
-    <t>05:11:25</t>
-  </si>
-  <si>
-    <t>02:42:36</t>
-  </si>
-  <si>
-    <t>04:18:46</t>
-  </si>
-  <si>
-    <t>06:19:08</t>
-  </si>
-  <si>
-    <t>05:27:27</t>
-  </si>
-  <si>
-    <t>04:35:46</t>
-  </si>
-  <si>
-    <t>06:12:44</t>
-  </si>
-  <si>
-    <t>03:44:02</t>
-  </si>
-  <si>
-    <t>05:20:48</t>
-  </si>
-  <si>
-    <t>04:28:51</t>
-  </si>
-  <si>
-    <t>06:06:13</t>
-  </si>
-  <si>
-    <t>03:36:53</t>
-  </si>
-  <si>
-    <t>05:14:00</t>
-  </si>
-  <si>
-    <t>02:44:54</t>
-  </si>
-  <si>
-    <t>04:21:47</t>
-  </si>
-  <si>
-    <t>06:22:27</t>
-  </si>
-  <si>
-    <t>05:30:36</t>
-  </si>
-  <si>
-    <t>04:38:20</t>
-  </si>
-  <si>
-    <t>06:15:43</t>
-  </si>
-  <si>
-    <t>03:45:02</t>
-  </si>
-  <si>
-    <t>05:24:03</t>
-  </si>
-  <si>
-    <t>04:32:08</t>
-  </si>
-  <si>
-    <t>06:08:04</t>
-  </si>
-  <si>
-    <t>03:39:55</t>
-  </si>
-  <si>
-    <t>05:16:36</t>
-  </si>
-  <si>
-    <t>02:47:13</t>
-  </si>
-  <si>
-    <t>04:24:50</t>
-  </si>
-  <si>
-    <t>06:24:33</t>
-  </si>
-  <si>
-    <t>05:32:46</t>
-  </si>
-  <si>
-    <t>04:40:45</t>
-  </si>
-  <si>
-    <t>06:17:59</t>
-  </si>
-  <si>
-    <t>03:48:25</t>
-  </si>
-  <si>
-    <t>05:26:11</t>
-  </si>
-  <si>
-    <t>04:34:14</t>
-  </si>
-  <si>
-    <t>06:10:56</t>
-  </si>
-  <si>
-    <t>03:42:07</t>
-  </si>
-  <si>
-    <t>05:19:02</t>
-  </si>
-  <si>
-    <t>02:49:44</t>
-  </si>
-  <si>
-    <t>04:27:03</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>38°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>39°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>06:15:40</t>
-  </si>
-  <si>
-    <t>05:26:58</t>
-  </si>
-  <si>
-    <t>04:38:05</t>
-  </si>
-  <si>
-    <t>06:10:49</t>
-  </si>
-  <si>
-    <t>05:21:43</t>
-  </si>
-  <si>
-    <t>04:32:27</t>
-  </si>
-  <si>
-    <t>06:05:09</t>
-  </si>
-  <si>
-    <t>05:15:43</t>
-  </si>
-  <si>
-    <t>04:26:07</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>05:08:26</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>2</t>
@@ -452,7 +467,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,25 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,19 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -622,9 +631,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1106,43 +1112,43 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L2" s="4">
-        <v>-9.1</v>
+        <v>-20.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="O2" s="6">
         <v>100</v>
@@ -1151,7 +1157,7 @@
         <v>100</v>
       </c>
       <c r="Q2" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R2" s="7">
         <v>100</v>
@@ -1162,55 +1168,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="L3" s="4">
-        <v>-20.4</v>
+        <v>-31.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O3" s="6">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="P3" s="9">
-        <v>90</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>97</v>
-      </c>
-      <c r="R3" s="7">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1218,55 +1224,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L4" s="4">
-        <v>-31.6</v>
+        <v>-10.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="8">
-        <v>96</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>63</v>
+        <v>95</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
       </c>
       <c r="R4" s="11">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1274,54 +1280,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="L5" s="4">
-        <v>-10.7</v>
+        <v>-42.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O5" s="6">
-        <v>98</v>
-      </c>
-      <c r="P5" s="8">
-        <v>96</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>53</v>
-      </c>
-      <c r="R5" s="11">
+        <v>138</v>
+      </c>
+      <c r="O5" s="12">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1330,54 +1336,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="L6" s="4">
-        <v>-42.4</v>
+        <v>-22.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O6" s="13">
-        <v>14</v>
-      </c>
-      <c r="P6" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>14</v>
-      </c>
-      <c r="R6" s="11">
+        <v>137</v>
+      </c>
+      <c r="O6" s="12">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1386,55 +1392,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="L7" s="4">
-        <v>-22.1</v>
+        <v>-33.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O7" s="13">
-        <v>12</v>
-      </c>
-      <c r="P7" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>12</v>
-      </c>
-      <c r="R7" s="11">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="O7" s="12">
+        <v>6</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1442,55 +1448,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L8" s="4">
-        <v>-33.2</v>
+        <v>-12.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O8" s="13">
+        <v>138</v>
+      </c>
+      <c r="O8" s="12">
         <v>8</v>
       </c>
-      <c r="P8" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>6</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0</v>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="14">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1498,54 +1504,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="L9" s="4">
-        <v>-12.3</v>
+        <v>-44.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O9" s="13">
-        <v>16</v>
-      </c>
-      <c r="P9" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="15">
-        <v>16</v>
-      </c>
-      <c r="R9" s="11">
+        <v>139</v>
+      </c>
+      <c r="O9" s="12">
+        <v>13</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1554,55 +1560,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="L10" s="4">
-        <v>-44.2</v>
+        <v>-23.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O10" s="13">
-        <v>16</v>
-      </c>
-      <c r="P10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0</v>
-      </c>
-      <c r="R10" s="11">
-        <v>1</v>
+        <v>137</v>
+      </c>
+      <c r="O10" s="12">
+        <v>8</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1610,55 +1616,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="L11" s="4">
-        <v>-23.8</v>
+        <v>-54.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="O11" s="6">
-        <v>53</v>
-      </c>
-      <c r="P11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11">
+        <v>96</v>
+      </c>
+      <c r="P11" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="9">
         <v>0</v>
       </c>
       <c r="R11" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1666,55 +1672,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="L12" s="4">
-        <v>-54.1</v>
+        <v>-35.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O12" s="17">
-        <v>30</v>
-      </c>
-      <c r="P12" s="14">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>0</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="O12" s="6">
+        <v>97</v>
+      </c>
+      <c r="P12" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="14">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1722,114 +1728,170 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="L13" s="4">
-        <v>-35</v>
+        <v>-46.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="N13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O13" s="6">
+        <v>44</v>
+      </c>
+      <c r="P13" s="15">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="O13" s="6">
-        <v>56</v>
-      </c>
-      <c r="P13" s="16">
-        <v>9</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>0</v>
-      </c>
-      <c r="R13" s="11">
+      <c r="L14" s="4">
+        <v>-25.7</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O14" s="6">
+        <v>50</v>
+      </c>
+      <c r="P14" s="16">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A13">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D13">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J13">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K13">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L13">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1848,12 +1910,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M13">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N13">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1870,22 +1932,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O13">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P13">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q13">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R13">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="145">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260927--01</t>
-  </si>
-  <si>
     <t>20260928--01</t>
   </si>
   <si>
@@ -109,7 +106,10 @@
     <t>20261003--02</t>
   </si>
   <si>
-    <t>06:15</t>
+    <t>20261004--01</t>
+  </si>
+  <si>
+    <t>20261004--02</t>
   </si>
   <si>
     <t>05:07</t>
@@ -148,7 +148,10 @@
     <t>01:36</t>
   </si>
   <si>
-    <t>03:37</t>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>04:09</t>
   </si>
   <si>
     <t>00:15</t>
@@ -169,9 +172,6 @@
     <t>00:52</t>
   </si>
   <si>
-    <t>05:22:08</t>
-  </si>
-  <si>
     <t>04:30:41</t>
   </si>
   <si>
@@ -208,7 +208,10 @@
     <t>05:02:00</t>
   </si>
   <si>
-    <t>05:24:16</t>
+    <t>02:31:12</t>
+  </si>
+  <si>
+    <t>04:08:59</t>
   </si>
   <si>
     <t>04:33:05</t>
@@ -247,7 +250,10 @@
     <t>05:05:36</t>
   </si>
   <si>
-    <t>05:27:23</t>
+    <t>02:33:17</t>
+  </si>
+  <si>
+    <t>04:11:40</t>
   </si>
   <si>
     <t>04:35:38</t>
@@ -286,7 +292,10 @@
     <t>05:06:24</t>
   </si>
   <si>
-    <t>05:30:31</t>
+    <t>02:36:29</t>
+  </si>
+  <si>
+    <t>04:13:44</t>
   </si>
   <si>
     <t>04:38:12</t>
@@ -325,7 +334,10 @@
     <t>05:07:12</t>
   </si>
   <si>
-    <t>05:32:41</t>
+    <t>02:39:42</t>
+  </si>
+  <si>
+    <t>04:15:49</t>
   </si>
   <si>
     <t>04:40:37</t>
@@ -364,7 +376,10 @@
     <t>05:10:48</t>
   </si>
   <si>
-    <t>38°</t>
+    <t>02:41:49</t>
+  </si>
+  <si>
+    <t>04:18:32</t>
   </si>
   <si>
     <t>11°</t>
@@ -394,9 +409,6 @@
     <t>7°</t>
   </si>
   <si>
-    <t>05:26:54</t>
-  </si>
-  <si>
     <t>04:37:57</t>
   </si>
   <si>
@@ -419,6 +431,9 @@
   </si>
   <si>
     <t>05:08:26</t>
+  </si>
+  <si>
+    <t>04:18:27</t>
   </si>
   <si>
     <t>A+B</t>
@@ -467,7 +482,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,19 +497,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,25 +509,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +539,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -625,12 +628,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1034,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1112,55 +1109,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="L2" s="4">
-        <v>-20.5</v>
+        <v>-31.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="P2" s="7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>95</v>
-      </c>
-      <c r="R2" s="7">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="R2" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1168,55 +1165,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L3" s="4">
-        <v>-31.6</v>
+        <v>-10.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O3" s="6">
-        <v>83</v>
-      </c>
-      <c r="P3" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="9">
+        <v>142</v>
+      </c>
+      <c r="O3" s="9">
+        <v>95</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
         <v>0</v>
       </c>
       <c r="R3" s="10">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1224,55 +1221,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="L4" s="4">
-        <v>-10.7</v>
+        <v>-42.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O4" s="6">
-        <v>95</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="11">
-        <v>88</v>
+        <v>0</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1280,54 +1277,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="L5" s="4">
-        <v>-42.5</v>
+        <v>-22.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O5" s="12">
-        <v>0</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
+        <v>142</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1336,54 +1333,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L6" s="4">
-        <v>-22.2</v>
+        <v>-33.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O6" s="12">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9">
+        <v>144</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1392,55 +1389,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L7" s="4">
-        <v>-33.3</v>
+        <v>-12.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O7" s="12">
-        <v>6</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>4</v>
+        <v>143</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1448,55 +1445,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-44.3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O8" s="6">
         <v>14</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-12.4</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O8" s="12">
-        <v>8</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="14">
-        <v>8</v>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1504,54 +1501,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="L9" s="4">
-        <v>-44.3</v>
+        <v>-23.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O9" s="12">
-        <v>13</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
+        <v>142</v>
+      </c>
+      <c r="O9" s="6">
+        <v>5</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1560,55 +1557,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="L10" s="4">
-        <v>-23.9</v>
+        <v>-54.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O10" s="12">
-        <v>8</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O10" s="9">
+        <v>53</v>
+      </c>
+      <c r="P10" s="12">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1616,55 +1613,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="L11" s="4">
-        <v>-54.2</v>
+        <v>-35.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O11" s="6">
-        <v>96</v>
-      </c>
-      <c r="P11" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="9">
+        <v>144</v>
+      </c>
+      <c r="O11" s="9">
+        <v>65</v>
+      </c>
+      <c r="P11" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="7">
         <v>0</v>
       </c>
       <c r="R11" s="14">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1672,55 +1669,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="L12" s="4">
-        <v>-35.1</v>
+        <v>-46.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="O12" s="6">
-        <v>97</v>
-      </c>
-      <c r="P12" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="14">
         <v>10</v>
+      </c>
+      <c r="P12" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1728,55 +1725,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="L13" s="4">
-        <v>-46.1</v>
+        <v>-25.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O13" s="6">
-        <v>44</v>
-      </c>
-      <c r="P13" s="15">
-        <v>19</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P13" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1784,114 +1781,170 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="L14" s="4">
-        <v>-25.7</v>
+        <v>-56</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="O14" s="6">
-        <v>50</v>
-      </c>
-      <c r="P14" s="16">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="9">
+        <v>2</v>
+      </c>
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>1</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-36.9</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O15" s="6">
+        <v>2</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>1</v>
+      </c>
+      <c r="R15" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A15">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B15">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C15">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D15">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E15">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F15">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I15">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J15">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K15">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1910,12 +1963,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M15">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N15">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1932,22 +1985,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O15">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q15">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R15">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="139">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260928--01</t>
-  </si>
-  <si>
-    <t>20260928--02</t>
-  </si>
-  <si>
     <t>20260929--01</t>
   </si>
   <si>
@@ -112,280 +106,274 @@
     <t>20261004--02</t>
   </si>
   <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>01:55</t>
+    <t>20261005--01</t>
+  </si>
+  <si>
+    <t>20261005--02</t>
+  </si>
+  <si>
+    <t>01:57</t>
   </si>
   <si>
     <t>06:29</t>
   </si>
   <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>03:43</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>04:34</t>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>03:42</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>04:36</t>
   </si>
   <si>
     <t>06:05</t>
   </si>
   <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>01:36</t>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>01:33</t>
   </si>
   <si>
     <t>06:25</t>
   </si>
   <si>
-    <t>04:09</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>04:54</t>
+    <t>04:07</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>05:27</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:19</t>
-  </si>
-  <si>
-    <t>02:54</t>
-  </si>
-  <si>
-    <t>00:52</t>
-  </si>
-  <si>
-    <t>04:30:41</t>
-  </si>
-  <si>
-    <t>06:07:24</t>
-  </si>
-  <si>
-    <t>03:39:29</t>
-  </si>
-  <si>
-    <t>05:15:15</t>
-  </si>
-  <si>
-    <t>04:23:13</t>
-  </si>
-  <si>
-    <t>06:01:13</t>
-  </si>
-  <si>
-    <t>03:31:18</t>
-  </si>
-  <si>
-    <t>05:08:35</t>
-  </si>
-  <si>
-    <t>02:39:34</t>
-  </si>
-  <si>
-    <t>04:16:02</t>
-  </si>
-  <si>
-    <t>03:23:33</t>
-  </si>
-  <si>
-    <t>05:02:00</t>
-  </si>
-  <si>
-    <t>02:31:12</t>
-  </si>
-  <si>
-    <t>04:08:59</t>
-  </si>
-  <si>
-    <t>04:33:05</t>
-  </si>
-  <si>
-    <t>06:09:38</t>
-  </si>
-  <si>
-    <t>03:42:53</t>
-  </si>
-  <si>
-    <t>05:17:21</t>
-  </si>
-  <si>
-    <t>04:25:18</t>
-  </si>
-  <si>
-    <t>06:04:03</t>
-  </si>
-  <si>
-    <t>03:33:29</t>
-  </si>
-  <si>
-    <t>05:11:00</t>
-  </si>
-  <si>
-    <t>02:42:05</t>
-  </si>
-  <si>
-    <t>04:18:13</t>
-  </si>
-  <si>
-    <t>03:25:38</t>
-  </si>
-  <si>
-    <t>05:05:36</t>
-  </si>
-  <si>
-    <t>02:33:17</t>
-  </si>
-  <si>
-    <t>04:11:40</t>
-  </si>
-  <si>
-    <t>04:35:38</t>
-  </si>
-  <si>
-    <t>06:12:36</t>
-  </si>
-  <si>
-    <t>03:43:50</t>
-  </si>
-  <si>
-    <t>05:20:35</t>
-  </si>
-  <si>
-    <t>04:28:33</t>
-  </si>
-  <si>
-    <t>06:05:54</t>
-  </si>
-  <si>
-    <t>03:36:29</t>
-  </si>
-  <si>
-    <t>05:13:35</t>
-  </si>
-  <si>
-    <t>02:44:22</t>
-  </si>
-  <si>
-    <t>04:21:15</t>
-  </si>
-  <si>
-    <t>03:28:53</t>
-  </si>
-  <si>
-    <t>05:06:24</t>
-  </si>
-  <si>
-    <t>02:36:29</t>
-  </si>
-  <si>
-    <t>04:13:44</t>
-  </si>
-  <si>
-    <t>04:38:12</t>
-  </si>
-  <si>
-    <t>06:15:35</t>
-  </si>
-  <si>
-    <t>03:44:48</t>
-  </si>
-  <si>
-    <t>05:23:50</t>
-  </si>
-  <si>
-    <t>04:31:50</t>
-  </si>
-  <si>
-    <t>06:07:46</t>
-  </si>
-  <si>
-    <t>03:39:30</t>
-  </si>
-  <si>
-    <t>05:16:11</t>
-  </si>
-  <si>
-    <t>02:46:39</t>
-  </si>
-  <si>
-    <t>04:24:18</t>
-  </si>
-  <si>
-    <t>03:32:09</t>
-  </si>
-  <si>
-    <t>05:07:12</t>
-  </si>
-  <si>
-    <t>02:39:42</t>
-  </si>
-  <si>
-    <t>04:15:49</t>
-  </si>
-  <si>
-    <t>04:40:37</t>
-  </si>
-  <si>
-    <t>06:17:51</t>
-  </si>
-  <si>
-    <t>03:48:13</t>
-  </si>
-  <si>
-    <t>05:25:58</t>
-  </si>
-  <si>
-    <t>04:33:56</t>
-  </si>
-  <si>
-    <t>06:10:37</t>
-  </si>
-  <si>
-    <t>03:41:42</t>
-  </si>
-  <si>
-    <t>05:18:38</t>
-  </si>
-  <si>
-    <t>02:49:12</t>
-  </si>
-  <si>
-    <t>04:26:31</t>
-  </si>
-  <si>
-    <t>03:34:15</t>
-  </si>
-  <si>
-    <t>05:10:48</t>
-  </si>
-  <si>
-    <t>02:41:49</t>
-  </si>
-  <si>
-    <t>04:18:32</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>17°</t>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>02:55</t>
+  </si>
+  <si>
+    <t>00:54</t>
+  </si>
+  <si>
+    <t>03:39:33</t>
+  </si>
+  <si>
+    <t>05:15:20</t>
+  </si>
+  <si>
+    <t>04:23:22</t>
+  </si>
+  <si>
+    <t>06:01:22</t>
+  </si>
+  <si>
+    <t>03:31:32</t>
+  </si>
+  <si>
+    <t>05:08:50</t>
+  </si>
+  <si>
+    <t>02:39:55</t>
+  </si>
+  <si>
+    <t>04:16:23</t>
+  </si>
+  <si>
+    <t>03:24:03</t>
+  </si>
+  <si>
+    <t>05:02:31</t>
+  </si>
+  <si>
+    <t>02:31:51</t>
+  </si>
+  <si>
+    <t>04:09:40</t>
+  </si>
+  <si>
+    <t>01:39:49</t>
+  </si>
+  <si>
+    <t>03:16:53</t>
+  </si>
+  <si>
+    <t>03:42:56</t>
+  </si>
+  <si>
+    <t>05:17:26</t>
+  </si>
+  <si>
+    <t>04:25:26</t>
+  </si>
+  <si>
+    <t>06:04:13</t>
+  </si>
+  <si>
+    <t>03:33:43</t>
+  </si>
+  <si>
+    <t>05:11:15</t>
+  </si>
+  <si>
+    <t>02:42:26</t>
+  </si>
+  <si>
+    <t>04:18:35</t>
+  </si>
+  <si>
+    <t>03:26:09</t>
+  </si>
+  <si>
+    <t>05:06:08</t>
+  </si>
+  <si>
+    <t>02:33:57</t>
+  </si>
+  <si>
+    <t>04:12:22</t>
+  </si>
+  <si>
+    <t>01:42:03</t>
+  </si>
+  <si>
+    <t>03:19:13</t>
+  </si>
+  <si>
+    <t>03:43:55</t>
+  </si>
+  <si>
+    <t>05:20:40</t>
+  </si>
+  <si>
+    <t>04:28:42</t>
+  </si>
+  <si>
+    <t>06:06:04</t>
+  </si>
+  <si>
+    <t>03:36:43</t>
+  </si>
+  <si>
+    <t>05:13:50</t>
+  </si>
+  <si>
+    <t>02:44:43</t>
+  </si>
+  <si>
+    <t>04:21:37</t>
+  </si>
+  <si>
+    <t>03:29:23</t>
+  </si>
+  <si>
+    <t>05:06:55</t>
+  </si>
+  <si>
+    <t>02:37:09</t>
+  </si>
+  <si>
+    <t>04:14:25</t>
+  </si>
+  <si>
+    <t>01:44:54</t>
+  </si>
+  <si>
+    <t>03:21:56</t>
+  </si>
+  <si>
+    <t>03:44:53</t>
+  </si>
+  <si>
+    <t>05:23:55</t>
+  </si>
+  <si>
+    <t>04:31:59</t>
+  </si>
+  <si>
+    <t>06:07:55</t>
+  </si>
+  <si>
+    <t>03:39:45</t>
+  </si>
+  <si>
+    <t>05:16:27</t>
+  </si>
+  <si>
+    <t>02:47:02</t>
+  </si>
+  <si>
+    <t>04:24:40</t>
+  </si>
+  <si>
+    <t>03:32:39</t>
+  </si>
+  <si>
+    <t>05:07:41</t>
+  </si>
+  <si>
+    <t>02:40:22</t>
+  </si>
+  <si>
+    <t>04:16:29</t>
+  </si>
+  <si>
+    <t>01:47:46</t>
+  </si>
+  <si>
+    <t>03:24:40</t>
+  </si>
+  <si>
+    <t>03:48:18</t>
+  </si>
+  <si>
+    <t>05:26:03</t>
+  </si>
+  <si>
+    <t>04:34:06</t>
+  </si>
+  <si>
+    <t>06:10:47</t>
+  </si>
+  <si>
+    <t>03:41:57</t>
+  </si>
+  <si>
+    <t>05:18:53</t>
+  </si>
+  <si>
+    <t>02:49:34</t>
+  </si>
+  <si>
+    <t>04:26:53</t>
+  </si>
+  <si>
+    <t>03:34:46</t>
+  </si>
+  <si>
+    <t>05:11:20</t>
+  </si>
+  <si>
+    <t>02:42:29</t>
+  </si>
+  <si>
+    <t>04:19:13</t>
+  </si>
+  <si>
+    <t>01:50:01</t>
+  </si>
+  <si>
+    <t>03:27:01</t>
   </si>
   <si>
     <t>0°</t>
@@ -409,43 +397,37 @@
     <t>7°</t>
   </si>
   <si>
-    <t>04:37:57</t>
-  </si>
-  <si>
-    <t>06:10:41</t>
-  </si>
-  <si>
-    <t>05:21:31</t>
-  </si>
-  <si>
-    <t>04:32:09</t>
-  </si>
-  <si>
-    <t>06:04:52</t>
-  </si>
-  <si>
-    <t>05:15:19</t>
-  </si>
-  <si>
-    <t>04:25:36</t>
-  </si>
-  <si>
-    <t>05:08:26</t>
-  </si>
-  <si>
-    <t>04:18:27</t>
+    <t>05:21:35</t>
+  </si>
+  <si>
+    <t>04:32:18</t>
+  </si>
+  <si>
+    <t>06:05:00</t>
+  </si>
+  <si>
+    <t>05:15:33</t>
+  </si>
+  <si>
+    <t>04:25:57</t>
+  </si>
+  <si>
+    <t>05:08:55</t>
+  </si>
+  <si>
+    <t>04:19:05</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>3</t>
@@ -482,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,7 +503,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,13 +527,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -628,6 +622,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,7 +1109,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>32</v>
@@ -1118,46 +1118,46 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="L2" s="4">
-        <v>-31.6</v>
+        <v>-42.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="O2" s="6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>3</v>
-      </c>
-      <c r="R2" s="8">
-        <v>4</v>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1165,7 +1165,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>33</v>
@@ -1174,37 +1174,37 @@
         <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L3" s="4">
-        <v>-10.7</v>
+        <v>-22.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O3" s="9">
-        <v>95</v>
+        <v>137</v>
+      </c>
+      <c r="O3" s="6">
+        <v>2</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
@@ -1212,8 +1212,8 @@
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="10">
-        <v>42</v>
+      <c r="R3" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1221,43 +1221,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="L4" s="4">
-        <v>-42.5</v>
+        <v>-33.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -1277,46 +1277,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L5" s="4">
-        <v>-22.2</v>
+        <v>-12.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="O5" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -1324,8 +1324,8 @@
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="R5" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1333,46 +1333,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-44.2</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="L6" s="4">
-        <v>-33.3</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
+        <v>138</v>
+      </c>
+      <c r="O6" s="9">
+        <v>52</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1380,8 +1380,8 @@
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="7">
-        <v>0</v>
+      <c r="R6" s="10">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1389,46 +1389,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-23.8</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="L7" s="4">
-        <v>-12.4</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="O7" s="11">
+        <v>43</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1445,55 +1445,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L8" s="4">
-        <v>-44.3</v>
+        <v>-54.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O8" s="6">
-        <v>14</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
+        <v>138</v>
+      </c>
+      <c r="O8" s="9">
+        <v>99</v>
+      </c>
+      <c r="P8" s="8">
+        <v>6</v>
       </c>
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="11">
-        <v>14</v>
+      <c r="R8" s="12">
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1501,49 +1501,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L9" s="4">
-        <v>-23.9</v>
+        <v>-35</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="6">
-        <v>5</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
+        <v>138</v>
+      </c>
+      <c r="O9" s="11">
+        <v>20</v>
+      </c>
+      <c r="P9" s="13">
+        <v>13</v>
       </c>
       <c r="Q9" s="7">
         <v>0</v>
@@ -1557,55 +1557,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-46</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O10" s="9">
         <v>60</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="P10" s="14">
         <v>60</v>
       </c>
-      <c r="L10" s="4">
-        <v>-54.2</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O10" s="9">
-        <v>53</v>
-      </c>
-      <c r="P10" s="12">
-        <v>12</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
-        <v>53</v>
+      <c r="Q10" s="13">
+        <v>16</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1613,55 +1613,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-25.6</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O11" s="9">
         <v>61</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-35.1</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O11" s="9">
-        <v>65</v>
-      </c>
-      <c r="P11" s="11">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="14">
-        <v>20</v>
+      <c r="P11" s="14">
+        <v>61</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>25</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1669,55 +1669,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4">
-        <v>-46.1</v>
+        <v>-55.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O12" s="6">
-        <v>10</v>
-      </c>
-      <c r="P12" s="12">
-        <v>10</v>
+        <v>138</v>
+      </c>
+      <c r="O12" s="11">
+        <v>23</v>
+      </c>
+      <c r="P12" s="8">
+        <v>7</v>
       </c>
       <c r="Q12" s="7">
         <v>0</v>
       </c>
-      <c r="R12" s="7">
-        <v>0</v>
+      <c r="R12" s="16">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1725,55 +1725,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-36.8</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L13" s="4">
-        <v>-25.7</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="6">
-        <v>4</v>
+      <c r="O13" s="11">
+        <v>21</v>
       </c>
       <c r="P13" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q13" s="7">
         <v>0</v>
       </c>
-      <c r="R13" s="7">
-        <v>1</v>
+      <c r="R13" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1781,52 +1781,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L14" s="4">
-        <v>-56</v>
+        <v>-63.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O14" s="6">
-        <v>2</v>
+        <v>138</v>
+      </c>
+      <c r="O14" s="9">
+        <v>100</v>
       </c>
       <c r="P14" s="7">
         <v>0</v>
       </c>
-      <c r="Q14" s="7">
-        <v>1</v>
+      <c r="Q14" s="13">
+        <v>14</v>
       </c>
       <c r="R14" s="7">
         <v>0</v>
@@ -1837,52 +1837,52 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="L15" s="4">
-        <v>-36.9</v>
+        <v>-47.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O15" s="6">
-        <v>2</v>
+        <v>138</v>
+      </c>
+      <c r="O15" s="9">
+        <v>100</v>
       </c>
       <c r="P15" s="7">
         <v>0</v>
       </c>
-      <c r="Q15" s="7">
-        <v>1</v>
+      <c r="Q15" s="13">
+        <v>17</v>
       </c>
       <c r="R15" s="7">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="136">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260929--01</t>
-  </si>
-  <si>
-    <t>20260929--02</t>
-  </si>
-  <si>
     <t>20260930--01</t>
   </si>
   <si>
@@ -112,16 +106,16 @@
     <t>20261005--02</t>
   </si>
   <si>
-    <t>01:57</t>
-  </si>
-  <si>
-    <t>06:29</t>
+    <t>20261006--01</t>
+  </si>
+  <si>
+    <t>20261006--02</t>
   </si>
   <si>
     <t>06:33</t>
   </si>
   <si>
-    <t>03:42</t>
+    <t>03:43</t>
   </si>
   <si>
     <t>06:02</t>
@@ -130,7 +124,7 @@
     <t>05:12</t>
   </si>
   <si>
-    <t>04:36</t>
+    <t>04:37</t>
   </si>
   <si>
     <t>06:05</t>
@@ -142,252 +136,252 @@
     <t>01:33</t>
   </si>
   <si>
-    <t>06:25</t>
+    <t>06:26</t>
   </si>
   <si>
     <t>04:07</t>
   </si>
   <si>
-    <t>05:43</t>
+    <t>05:44</t>
   </si>
   <si>
     <t>05:27</t>
   </si>
   <si>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:20</t>
-  </si>
-  <si>
     <t>02:55</t>
   </si>
   <si>
     <t>00:54</t>
   </si>
   <si>
-    <t>03:39:33</t>
-  </si>
-  <si>
-    <t>05:15:20</t>
-  </si>
-  <si>
-    <t>04:23:22</t>
-  </si>
-  <si>
-    <t>06:01:22</t>
-  </si>
-  <si>
-    <t>03:31:32</t>
-  </si>
-  <si>
-    <t>05:08:50</t>
-  </si>
-  <si>
-    <t>02:39:55</t>
-  </si>
-  <si>
-    <t>04:16:23</t>
-  </si>
-  <si>
-    <t>03:24:03</t>
-  </si>
-  <si>
-    <t>05:02:31</t>
-  </si>
-  <si>
-    <t>02:31:51</t>
-  </si>
-  <si>
-    <t>04:09:40</t>
-  </si>
-  <si>
-    <t>01:39:49</t>
-  </si>
-  <si>
-    <t>03:16:53</t>
-  </si>
-  <si>
-    <t>03:42:56</t>
-  </si>
-  <si>
-    <t>05:17:26</t>
-  </si>
-  <si>
-    <t>04:25:26</t>
-  </si>
-  <si>
-    <t>06:04:13</t>
-  </si>
-  <si>
-    <t>03:33:43</t>
-  </si>
-  <si>
-    <t>05:11:15</t>
-  </si>
-  <si>
-    <t>02:42:26</t>
-  </si>
-  <si>
-    <t>04:18:35</t>
-  </si>
-  <si>
-    <t>03:26:09</t>
-  </si>
-  <si>
-    <t>05:06:08</t>
-  </si>
-  <si>
-    <t>02:33:57</t>
-  </si>
-  <si>
-    <t>04:12:22</t>
-  </si>
-  <si>
-    <t>01:42:03</t>
-  </si>
-  <si>
-    <t>03:19:13</t>
-  </si>
-  <si>
-    <t>03:43:55</t>
-  </si>
-  <si>
-    <t>05:20:40</t>
-  </si>
-  <si>
-    <t>04:28:42</t>
-  </si>
-  <si>
-    <t>06:06:04</t>
-  </si>
-  <si>
-    <t>03:36:43</t>
-  </si>
-  <si>
-    <t>05:13:50</t>
-  </si>
-  <si>
-    <t>02:44:43</t>
-  </si>
-  <si>
-    <t>04:21:37</t>
-  </si>
-  <si>
-    <t>03:29:23</t>
-  </si>
-  <si>
-    <t>05:06:55</t>
-  </si>
-  <si>
-    <t>02:37:09</t>
-  </si>
-  <si>
-    <t>04:14:25</t>
-  </si>
-  <si>
-    <t>01:44:54</t>
-  </si>
-  <si>
-    <t>03:21:56</t>
-  </si>
-  <si>
-    <t>03:44:53</t>
-  </si>
-  <si>
-    <t>05:23:55</t>
-  </si>
-  <si>
-    <t>04:31:59</t>
-  </si>
-  <si>
-    <t>06:07:55</t>
-  </si>
-  <si>
-    <t>03:39:45</t>
-  </si>
-  <si>
-    <t>05:16:27</t>
-  </si>
-  <si>
-    <t>02:47:02</t>
-  </si>
-  <si>
-    <t>04:24:40</t>
-  </si>
-  <si>
-    <t>03:32:39</t>
-  </si>
-  <si>
-    <t>05:07:41</t>
-  </si>
-  <si>
-    <t>02:40:22</t>
+    <t>04:23:23</t>
+  </si>
+  <si>
+    <t>06:01:24</t>
+  </si>
+  <si>
+    <t>03:31:36</t>
+  </si>
+  <si>
+    <t>05:08:54</t>
+  </si>
+  <si>
+    <t>02:40:01</t>
   </si>
   <si>
     <t>04:16:29</t>
   </si>
   <si>
-    <t>01:47:46</t>
-  </si>
-  <si>
-    <t>03:24:40</t>
-  </si>
-  <si>
-    <t>03:48:18</t>
-  </si>
-  <si>
-    <t>05:26:03</t>
-  </si>
-  <si>
-    <t>04:34:06</t>
-  </si>
-  <si>
-    <t>06:10:47</t>
-  </si>
-  <si>
-    <t>03:41:57</t>
-  </si>
-  <si>
-    <t>05:18:53</t>
-  </si>
-  <si>
-    <t>02:49:34</t>
-  </si>
-  <si>
-    <t>04:26:53</t>
-  </si>
-  <si>
-    <t>03:34:46</t>
-  </si>
-  <si>
-    <t>05:11:20</t>
-  </si>
-  <si>
-    <t>02:42:29</t>
-  </si>
-  <si>
-    <t>04:19:13</t>
-  </si>
-  <si>
-    <t>01:50:01</t>
-  </si>
-  <si>
-    <t>03:27:01</t>
+    <t>03:24:13</t>
+  </si>
+  <si>
+    <t>05:02:41</t>
+  </si>
+  <si>
+    <t>02:32:04</t>
+  </si>
+  <si>
+    <t>04:09:54</t>
+  </si>
+  <si>
+    <t>01:40:06</t>
+  </si>
+  <si>
+    <t>03:17:11</t>
+  </si>
+  <si>
+    <t>00:48:22</t>
+  </si>
+  <si>
+    <t>02:24:35</t>
+  </si>
+  <si>
+    <t>04:25:28</t>
+  </si>
+  <si>
+    <t>06:04:14</t>
+  </si>
+  <si>
+    <t>03:33:46</t>
+  </si>
+  <si>
+    <t>05:11:18</t>
+  </si>
+  <si>
+    <t>02:42:31</t>
+  </si>
+  <si>
+    <t>04:18:41</t>
+  </si>
+  <si>
+    <t>03:26:18</t>
+  </si>
+  <si>
+    <t>05:06:18</t>
+  </si>
+  <si>
+    <t>02:34:10</t>
+  </si>
+  <si>
+    <t>04:12:36</t>
+  </si>
+  <si>
+    <t>01:42:20</t>
+  </si>
+  <si>
+    <t>03:19:31</t>
+  </si>
+  <si>
+    <t>00:51:05</t>
+  </si>
+  <si>
+    <t>02:26:44</t>
+  </si>
+  <si>
+    <t>04:28:43</t>
+  </si>
+  <si>
+    <t>06:06:05</t>
+  </si>
+  <si>
+    <t>03:36:47</t>
+  </si>
+  <si>
+    <t>05:13:54</t>
+  </si>
+  <si>
+    <t>02:44:49</t>
+  </si>
+  <si>
+    <t>04:21:43</t>
+  </si>
+  <si>
+    <t>03:29:32</t>
+  </si>
+  <si>
+    <t>05:07:04</t>
+  </si>
+  <si>
+    <t>02:37:22</t>
+  </si>
+  <si>
+    <t>04:14:39</t>
+  </si>
+  <si>
+    <t>01:45:11</t>
+  </si>
+  <si>
+    <t>03:22:14</t>
+  </si>
+  <si>
+    <t>00:53:00</t>
+  </si>
+  <si>
+    <t>02:29:50</t>
+  </si>
+  <si>
+    <t>04:32:01</t>
+  </si>
+  <si>
+    <t>06:07:57</t>
+  </si>
+  <si>
+    <t>03:39:48</t>
+  </si>
+  <si>
+    <t>05:16:30</t>
+  </si>
+  <si>
+    <t>02:47:08</t>
+  </si>
+  <si>
+    <t>04:24:46</t>
+  </si>
+  <si>
+    <t>03:32:48</t>
+  </si>
+  <si>
+    <t>05:07:51</t>
+  </si>
+  <si>
+    <t>02:40:36</t>
+  </si>
+  <si>
+    <t>04:16:43</t>
+  </si>
+  <si>
+    <t>01:48:04</t>
+  </si>
+  <si>
+    <t>03:24:58</t>
+  </si>
+  <si>
+    <t>00:54:57</t>
+  </si>
+  <si>
+    <t>02:32:57</t>
+  </si>
+  <si>
+    <t>04:34:07</t>
+  </si>
+  <si>
+    <t>06:10:49</t>
+  </si>
+  <si>
+    <t>03:42:00</t>
+  </si>
+  <si>
+    <t>05:18:57</t>
+  </si>
+  <si>
+    <t>02:49:40</t>
+  </si>
+  <si>
+    <t>04:26:59</t>
+  </si>
+  <si>
+    <t>03:34:55</t>
+  </si>
+  <si>
+    <t>05:11:30</t>
+  </si>
+  <si>
+    <t>02:42:43</t>
+  </si>
+  <si>
+    <t>04:19:26</t>
+  </si>
+  <si>
+    <t>01:50:19</t>
+  </si>
+  <si>
+    <t>03:27:20</t>
+  </si>
+  <si>
+    <t>00:57:41</t>
+  </si>
+  <si>
+    <t>02:35:07</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>13°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>39°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
     <t>15°</t>
   </si>
   <si>
@@ -397,25 +391,22 @@
     <t>7°</t>
   </si>
   <si>
-    <t>05:21:35</t>
-  </si>
-  <si>
-    <t>04:32:18</t>
-  </si>
-  <si>
-    <t>06:05:00</t>
-  </si>
-  <si>
-    <t>05:15:33</t>
-  </si>
-  <si>
-    <t>04:25:57</t>
-  </si>
-  <si>
-    <t>05:08:55</t>
-  </si>
-  <si>
-    <t>04:19:05</t>
+    <t>04:32:19</t>
+  </si>
+  <si>
+    <t>06:05:02</t>
+  </si>
+  <si>
+    <t>05:15:36</t>
+  </si>
+  <si>
+    <t>04:26:03</t>
+  </si>
+  <si>
+    <t>05:09:04</t>
+  </si>
+  <si>
+    <t>04:19:18</t>
   </si>
   <si>
     <t>B</t>
@@ -424,13 +415,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -464,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,13 +482,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,19 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -628,6 +631,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,7 +1118,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>32</v>
@@ -1118,37 +1127,37 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="L2" s="4">
-        <v>-42.5</v>
+        <v>-33.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1165,7 +1174,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>33</v>
@@ -1174,37 +1183,37 @@
         <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L3" s="4">
-        <v>-22.1</v>
+        <v>-12.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O3" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
@@ -1213,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1221,7 +1230,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
@@ -1230,46 +1239,46 @@
         <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="L4" s="4">
-        <v>-33.3</v>
+        <v>-44.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="O4" s="8">
+        <v>71</v>
       </c>
       <c r="P4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="7">
-        <v>0</v>
+      <c r="R4" s="9">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1277,7 +1286,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>35</v>
@@ -1286,46 +1295,46 @@
         <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L5" s="4">
-        <v>-12.4</v>
+        <v>-23.8</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" s="6">
-        <v>5</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
+      <c r="O5" s="10">
+        <v>20</v>
+      </c>
+      <c r="P5" s="11">
+        <v>4</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>3</v>
+      <c r="R5" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1333,7 +1342,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>36</v>
@@ -1342,46 +1351,46 @@
         <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L6" s="4">
-        <v>-44.2</v>
+        <v>-54.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O6" s="9">
-        <v>52</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="O6" s="8">
+        <v>98</v>
+      </c>
+      <c r="P6" s="12">
+        <v>75</v>
       </c>
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="10">
-        <v>9</v>
+      <c r="R6" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1389,49 +1398,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L7" s="4">
-        <v>-23.8</v>
+        <v>-35</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O7" s="11">
-        <v>43</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="O7" s="8">
+        <v>98</v>
+      </c>
+      <c r="P7" s="13">
+        <v>86</v>
       </c>
       <c r="Q7" s="7">
         <v>0</v>
@@ -1445,7 +1454,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>38</v>
@@ -1454,46 +1463,46 @@
         <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L8" s="4">
-        <v>-54.1</v>
+        <v>-46</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O8" s="9">
-        <v>99</v>
-      </c>
-      <c r="P8" s="8">
-        <v>6</v>
+        <v>133</v>
+      </c>
+      <c r="O8" s="8">
+        <v>52</v>
+      </c>
+      <c r="P8" s="14">
+        <v>52</v>
       </c>
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="12">
-        <v>78</v>
+      <c r="R8" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1501,7 +1510,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
@@ -1510,43 +1519,43 @@
         <v>46</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-25.5</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="L9" s="4">
-        <v>-35</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O9" s="11">
-        <v>20</v>
-      </c>
-      <c r="P9" s="13">
-        <v>13</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
+      <c r="O9" s="10">
+        <v>11</v>
+      </c>
+      <c r="P9" s="15">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>7</v>
       </c>
       <c r="R9" s="7">
         <v>0</v>
@@ -1557,7 +1566,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>40</v>
@@ -1566,43 +1575,43 @@
         <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L10" s="4">
-        <v>-46</v>
+        <v>-55.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O10" s="9">
-        <v>60</v>
-      </c>
-      <c r="P10" s="14">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>16</v>
+        <v>133</v>
+      </c>
+      <c r="O10" s="10">
+        <v>14</v>
+      </c>
+      <c r="P10" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>4</v>
       </c>
       <c r="R10" s="7">
         <v>0</v>
@@ -1613,7 +1622,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>41</v>
@@ -1622,46 +1631,46 @@
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L11" s="4">
-        <v>-25.6</v>
+        <v>-36.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O11" s="9">
-        <v>61</v>
-      </c>
-      <c r="P11" s="14">
-        <v>61</v>
-      </c>
-      <c r="Q11" s="15">
+        <v>133</v>
+      </c>
+      <c r="O11" s="10">
         <v>25</v>
       </c>
+      <c r="P11" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>7</v>
+      </c>
       <c r="R11" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1669,7 +1678,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>42</v>
@@ -1678,46 +1687,46 @@
         <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L12" s="4">
-        <v>-55.8</v>
+        <v>-63.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O12" s="11">
-        <v>23</v>
-      </c>
-      <c r="P12" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="16">
-        <v>20</v>
+        <v>133</v>
+      </c>
+      <c r="O12" s="8">
+        <v>87</v>
+      </c>
+      <c r="P12" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>65</v>
+      </c>
+      <c r="R12" s="15">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1725,7 +1734,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
@@ -1734,46 +1743,46 @@
         <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-47.8</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="L13" s="4">
-        <v>-36.8</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O13" s="11">
-        <v>21</v>
-      </c>
-      <c r="P13" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q13" s="7">
+      <c r="O13" s="8">
+        <v>90</v>
+      </c>
+      <c r="P13" s="7">
         <v>0</v>
       </c>
-      <c r="R13" s="13">
-        <v>17</v>
+      <c r="Q13" s="17">
+        <v>60</v>
+      </c>
+      <c r="R13" s="15">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1781,7 +1790,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>44</v>
@@ -1790,46 +1799,46 @@
         <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L14" s="4">
-        <v>-63.5</v>
+        <v>-66.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O14" s="9">
-        <v>100</v>
+        <v>133</v>
+      </c>
+      <c r="O14" s="8">
+        <v>72</v>
       </c>
       <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>14</v>
-      </c>
-      <c r="R14" s="7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>72</v>
+      </c>
+      <c r="R14" s="9">
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1837,7 +1846,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>45</v>
@@ -1846,46 +1855,46 @@
         <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L15" s="4">
-        <v>-47.8</v>
+        <v>-57.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O15" s="9">
-        <v>100</v>
+        <v>133</v>
+      </c>
+      <c r="O15" s="8">
+        <v>83</v>
       </c>
       <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>17</v>
-      </c>
-      <c r="R15" s="7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>58</v>
+      </c>
+      <c r="R15" s="17">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="130">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260930--01</t>
-  </si>
-  <si>
-    <t>20260930--02</t>
-  </si>
-  <si>
     <t>20261001--01</t>
   </si>
   <si>
@@ -112,10 +106,10 @@
     <t>20261006--02</t>
   </si>
   <si>
-    <t>06:33</t>
-  </si>
-  <si>
-    <t>03:43</t>
+    <t>20261007--01</t>
+  </si>
+  <si>
+    <t>20261007--02</t>
   </si>
   <si>
     <t>06:02</t>
@@ -130,10 +124,10 @@
     <t>06:05</t>
   </si>
   <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>01:33</t>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>01:34</t>
   </si>
   <si>
     <t>06:26</t>
@@ -145,112 +139,106 @@
     <t>05:44</t>
   </si>
   <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>03:52</t>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>03:54</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
+    <t>02:28</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:55</t>
-  </si>
-  <si>
     <t>00:54</t>
   </si>
   <si>
-    <t>04:23:23</t>
-  </si>
-  <si>
-    <t>06:01:24</t>
-  </si>
-  <si>
     <t>03:31:36</t>
   </si>
   <si>
     <t>05:08:54</t>
   </si>
   <si>
-    <t>02:40:01</t>
-  </si>
-  <si>
-    <t>04:16:29</t>
-  </si>
-  <si>
-    <t>03:24:13</t>
-  </si>
-  <si>
-    <t>05:02:41</t>
-  </si>
-  <si>
-    <t>02:32:04</t>
-  </si>
-  <si>
-    <t>04:09:54</t>
-  </si>
-  <si>
-    <t>01:40:06</t>
-  </si>
-  <si>
-    <t>03:17:11</t>
-  </si>
-  <si>
-    <t>00:48:22</t>
-  </si>
-  <si>
-    <t>02:24:35</t>
-  </si>
-  <si>
-    <t>04:25:28</t>
-  </si>
-  <si>
-    <t>06:04:14</t>
-  </si>
-  <si>
-    <t>03:33:46</t>
-  </si>
-  <si>
-    <t>05:11:18</t>
-  </si>
-  <si>
-    <t>02:42:31</t>
-  </si>
-  <si>
-    <t>04:18:41</t>
-  </si>
-  <si>
-    <t>03:26:18</t>
-  </si>
-  <si>
-    <t>05:06:18</t>
-  </si>
-  <si>
-    <t>02:34:10</t>
-  </si>
-  <si>
-    <t>04:12:36</t>
-  </si>
-  <si>
-    <t>01:42:20</t>
-  </si>
-  <si>
-    <t>03:19:31</t>
-  </si>
-  <si>
-    <t>00:51:05</t>
-  </si>
-  <si>
-    <t>02:26:44</t>
-  </si>
-  <si>
-    <t>04:28:43</t>
-  </si>
-  <si>
-    <t>06:06:05</t>
+    <t>02:40:02</t>
+  </si>
+  <si>
+    <t>04:16:31</t>
+  </si>
+  <si>
+    <t>03:24:16</t>
+  </si>
+  <si>
+    <t>05:02:44</t>
+  </si>
+  <si>
+    <t>02:32:10</t>
+  </si>
+  <si>
+    <t>04:09:59</t>
+  </si>
+  <si>
+    <t>01:40:14</t>
+  </si>
+  <si>
+    <t>03:17:19</t>
+  </si>
+  <si>
+    <t>00:48:33</t>
+  </si>
+  <si>
+    <t>02:24:46</t>
+  </si>
+  <si>
+    <t>01:32:22</t>
+  </si>
+  <si>
+    <t>03:10:40</t>
+  </si>
+  <si>
+    <t>03:33:47</t>
+  </si>
+  <si>
+    <t>05:11:19</t>
+  </si>
+  <si>
+    <t>02:42:33</t>
+  </si>
+  <si>
+    <t>04:18:43</t>
+  </si>
+  <si>
+    <t>03:26:21</t>
+  </si>
+  <si>
+    <t>05:06:21</t>
+  </si>
+  <si>
+    <t>02:34:15</t>
+  </si>
+  <si>
+    <t>04:12:41</t>
+  </si>
+  <si>
+    <t>01:42:28</t>
+  </si>
+  <si>
+    <t>03:19:40</t>
+  </si>
+  <si>
+    <t>00:51:15</t>
+  </si>
+  <si>
+    <t>02:26:55</t>
+  </si>
+  <si>
+    <t>01:34:26</t>
+  </si>
+  <si>
+    <t>03:13:54</t>
   </si>
   <si>
     <t>03:36:47</t>
@@ -259,124 +247,124 @@
     <t>05:13:54</t>
   </si>
   <si>
-    <t>02:44:49</t>
-  </si>
-  <si>
-    <t>04:21:43</t>
-  </si>
-  <si>
-    <t>03:29:32</t>
-  </si>
-  <si>
-    <t>05:07:04</t>
-  </si>
-  <si>
-    <t>02:37:22</t>
-  </si>
-  <si>
-    <t>04:14:39</t>
-  </si>
-  <si>
-    <t>01:45:11</t>
-  </si>
-  <si>
-    <t>03:22:14</t>
-  </si>
-  <si>
-    <t>00:53:00</t>
-  </si>
-  <si>
-    <t>02:29:50</t>
-  </si>
-  <si>
-    <t>04:32:01</t>
-  </si>
-  <si>
-    <t>06:07:57</t>
-  </si>
-  <si>
-    <t>03:39:48</t>
-  </si>
-  <si>
-    <t>05:16:30</t>
-  </si>
-  <si>
-    <t>02:47:08</t>
-  </si>
-  <si>
-    <t>04:24:46</t>
-  </si>
-  <si>
-    <t>03:32:48</t>
-  </si>
-  <si>
-    <t>05:07:51</t>
-  </si>
-  <si>
-    <t>02:40:36</t>
-  </si>
-  <si>
-    <t>04:16:43</t>
-  </si>
-  <si>
-    <t>01:48:04</t>
-  </si>
-  <si>
-    <t>03:24:58</t>
-  </si>
-  <si>
-    <t>00:54:57</t>
-  </si>
-  <si>
-    <t>02:32:57</t>
-  </si>
-  <si>
-    <t>04:34:07</t>
-  </si>
-  <si>
-    <t>06:10:49</t>
-  </si>
-  <si>
-    <t>03:42:00</t>
+    <t>02:44:51</t>
+  </si>
+  <si>
+    <t>04:21:44</t>
+  </si>
+  <si>
+    <t>03:29:35</t>
+  </si>
+  <si>
+    <t>05:07:08</t>
+  </si>
+  <si>
+    <t>02:37:27</t>
+  </si>
+  <si>
+    <t>04:14:44</t>
+  </si>
+  <si>
+    <t>01:45:19</t>
+  </si>
+  <si>
+    <t>03:22:22</t>
+  </si>
+  <si>
+    <t>00:53:12</t>
+  </si>
+  <si>
+    <t>02:30:01</t>
+  </si>
+  <si>
+    <t>01:37:40</t>
+  </si>
+  <si>
+    <t>03:15:08</t>
+  </si>
+  <si>
+    <t>03:39:49</t>
+  </si>
+  <si>
+    <t>05:16:31</t>
+  </si>
+  <si>
+    <t>02:47:10</t>
+  </si>
+  <si>
+    <t>04:24:48</t>
+  </si>
+  <si>
+    <t>03:32:52</t>
+  </si>
+  <si>
+    <t>05:07:55</t>
+  </si>
+  <si>
+    <t>02:40:41</t>
+  </si>
+  <si>
+    <t>04:16:48</t>
+  </si>
+  <si>
+    <t>01:48:12</t>
+  </si>
+  <si>
+    <t>03:25:06</t>
+  </si>
+  <si>
+    <t>00:55:09</t>
+  </si>
+  <si>
+    <t>02:33:08</t>
+  </si>
+  <si>
+    <t>01:40:57</t>
+  </si>
+  <si>
+    <t>03:16:22</t>
+  </si>
+  <si>
+    <t>03:42:01</t>
   </si>
   <si>
     <t>05:18:57</t>
   </si>
   <si>
-    <t>02:49:40</t>
-  </si>
-  <si>
-    <t>04:26:59</t>
-  </si>
-  <si>
-    <t>03:34:55</t>
-  </si>
-  <si>
-    <t>05:11:30</t>
-  </si>
-  <si>
-    <t>02:42:43</t>
-  </si>
-  <si>
-    <t>04:19:26</t>
-  </si>
-  <si>
-    <t>01:50:19</t>
-  </si>
-  <si>
-    <t>03:27:20</t>
-  </si>
-  <si>
-    <t>00:57:41</t>
-  </si>
-  <si>
-    <t>02:35:07</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>13°</t>
+    <t>02:49:42</t>
+  </si>
+  <si>
+    <t>04:27:01</t>
+  </si>
+  <si>
+    <t>03:34:59</t>
+  </si>
+  <si>
+    <t>05:11:33</t>
+  </si>
+  <si>
+    <t>02:42:48</t>
+  </si>
+  <si>
+    <t>04:19:32</t>
+  </si>
+  <si>
+    <t>01:50:27</t>
+  </si>
+  <si>
+    <t>03:27:28</t>
+  </si>
+  <si>
+    <t>00:57:52</t>
+  </si>
+  <si>
+    <t>02:35:19</t>
+  </si>
+  <si>
+    <t>01:43:03</t>
+  </si>
+  <si>
+    <t>03:19:38</t>
   </si>
   <si>
     <t>0°</t>
@@ -391,22 +379,16 @@
     <t>7°</t>
   </si>
   <si>
-    <t>04:32:19</t>
-  </si>
-  <si>
-    <t>06:05:02</t>
-  </si>
-  <si>
-    <t>05:15:36</t>
-  </si>
-  <si>
-    <t>04:26:03</t>
-  </si>
-  <si>
-    <t>05:09:04</t>
-  </si>
-  <si>
-    <t>04:19:18</t>
+    <t>05:15:37</t>
+  </si>
+  <si>
+    <t>04:26:04</t>
+  </si>
+  <si>
+    <t>05:09:07</t>
+  </si>
+  <si>
+    <t>04:19:23</t>
   </si>
   <si>
     <t>B</t>
@@ -418,10 +400,10 @@
     <t>3</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -455,7 +437,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,7 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,43 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -637,6 +631,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,55 +1118,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-44.2</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="L2" s="4">
-        <v>-33.3</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="O2" s="6">
+        <v>8</v>
+      </c>
+      <c r="P2" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>1</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1174,54 +1174,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-23.8</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L3" s="4">
-        <v>-12.4</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O3" s="6">
-        <v>1</v>
-      </c>
-      <c r="P3" s="7">
+        <v>128</v>
+      </c>
+      <c r="O3" s="9">
+        <v>34</v>
+      </c>
+      <c r="P3" s="10">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1230,55 +1230,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L4" s="4">
-        <v>-44.2</v>
+        <v>-54.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O4" s="8">
-        <v>71</v>
-      </c>
-      <c r="P4" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="7">
+        <v>127</v>
+      </c>
+      <c r="O4" s="11">
+        <v>100</v>
+      </c>
+      <c r="P4" s="12">
+        <v>99</v>
+      </c>
+      <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="9">
-        <v>45</v>
+      <c r="R4" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1286,55 +1286,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-35</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O5" s="11">
+        <v>98</v>
+      </c>
+      <c r="P5" s="13">
+        <v>86</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="14">
         <v>66</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-23.8</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O5" s="10">
-        <v>20</v>
-      </c>
-      <c r="P5" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1342,55 +1342,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L6" s="4">
-        <v>-54.1</v>
+        <v>-46</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O6" s="8">
-        <v>98</v>
-      </c>
-      <c r="P6" s="12">
-        <v>75</v>
-      </c>
-      <c r="Q6" s="7">
+        <v>127</v>
+      </c>
+      <c r="O6" s="11">
+        <v>61</v>
+      </c>
+      <c r="P6" s="15">
+        <v>61</v>
+      </c>
+      <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="7">
-        <v>1</v>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1398,54 +1398,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="L7" s="4">
-        <v>-35</v>
+        <v>-25.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O7" s="8">
-        <v>98</v>
-      </c>
-      <c r="P7" s="13">
-        <v>86</v>
-      </c>
-      <c r="Q7" s="7">
+        <v>129</v>
+      </c>
+      <c r="O7" s="11">
+        <v>53</v>
+      </c>
+      <c r="P7" s="16">
+        <v>53</v>
+      </c>
+      <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1454,54 +1454,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L8" s="4">
-        <v>-46</v>
+        <v>-55.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O8" s="8">
-        <v>52</v>
-      </c>
-      <c r="P8" s="14">
-        <v>52</v>
-      </c>
-      <c r="Q8" s="7">
+        <v>127</v>
+      </c>
+      <c r="O8" s="6">
+        <v>3</v>
+      </c>
+      <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="7">
+      <c r="Q8" s="17">
+        <v>3</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1510,54 +1510,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="L9" s="4">
-        <v>-25.5</v>
+        <v>-36.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O9" s="10">
-        <v>11</v>
-      </c>
-      <c r="P9" s="15">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>7</v>
-      </c>
-      <c r="R9" s="7">
+        <v>127</v>
+      </c>
+      <c r="O9" s="6">
+        <v>5</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>5</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1566,54 +1566,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L10" s="4">
-        <v>-55.8</v>
+        <v>-63.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O10" s="10">
-        <v>14</v>
-      </c>
-      <c r="P10" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>4</v>
-      </c>
-      <c r="R10" s="7">
+        <v>127</v>
+      </c>
+      <c r="O10" s="11">
+        <v>89</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>53</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1622,55 +1622,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="L11" s="4">
-        <v>-36.8</v>
+        <v>-47.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O11" s="10">
-        <v>25</v>
-      </c>
-      <c r="P11" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>7</v>
-      </c>
-      <c r="R11" s="7">
-        <v>1</v>
+        <v>127</v>
+      </c>
+      <c r="O11" s="11">
+        <v>84</v>
+      </c>
+      <c r="P11" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>41</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1678,55 +1678,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L12" s="4">
-        <v>-63.5</v>
+        <v>-66.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O12" s="8">
-        <v>87</v>
-      </c>
-      <c r="P12" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>65</v>
-      </c>
-      <c r="R12" s="15">
-        <v>9</v>
+        <v>127</v>
+      </c>
+      <c r="O12" s="11">
+        <v>96</v>
+      </c>
+      <c r="P12" s="17">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>89</v>
+      </c>
+      <c r="R12" s="7">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1734,55 +1734,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L13" s="4">
-        <v>-47.8</v>
+        <v>-57.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O13" s="8">
+        <v>127</v>
+      </c>
+      <c r="O13" s="11">
         <v>90</v>
       </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>60</v>
-      </c>
-      <c r="R13" s="15">
-        <v>9</v>
+      <c r="P13" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>59</v>
+      </c>
+      <c r="R13" s="13">
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1790,55 +1790,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L14" s="4">
-        <v>-66.7</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O14" s="8">
-        <v>72</v>
-      </c>
-      <c r="P14" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="18">
-        <v>72</v>
-      </c>
-      <c r="R14" s="9">
-        <v>44</v>
+        <v>127</v>
+      </c>
+      <c r="O14" s="11">
+        <v>98</v>
+      </c>
+      <c r="P14" s="17">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>84</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1846,55 +1846,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L15" s="4">
-        <v>-57.6</v>
+        <v>-49.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O15" s="8">
-        <v>83</v>
-      </c>
-      <c r="P15" s="7">
+        <v>129</v>
+      </c>
+      <c r="O15" s="11">
+        <v>94</v>
+      </c>
+      <c r="P15" s="8">
         <v>1</v>
       </c>
-      <c r="Q15" s="17">
-        <v>58</v>
-      </c>
-      <c r="R15" s="17">
-        <v>62</v>
+      <c r="Q15" s="20">
+        <v>74</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="131">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261001--01</t>
-  </si>
-  <si>
-    <t>20261001--02</t>
-  </si>
-  <si>
     <t>20261002--01</t>
   </si>
   <si>
@@ -112,10 +106,13 @@
     <t>20261007--02</t>
   </si>
   <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>05:12</t>
+    <t>20261008--01</t>
+  </si>
+  <si>
+    <t>20261008--02</t>
+  </si>
+  <si>
+    <t>20261008--03</t>
   </si>
   <si>
     <t>04:37</t>
@@ -151,18 +148,18 @@
     <t>02:28</t>
   </si>
   <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:54</t>
-  </si>
-  <si>
-    <t>03:31:36</t>
-  </si>
-  <si>
-    <t>05:08:54</t>
-  </si>
-  <si>
     <t>02:40:02</t>
   </si>
   <si>
@@ -172,37 +169,40 @@
     <t>03:24:16</t>
   </si>
   <si>
-    <t>05:02:44</t>
+    <t>05:02:45</t>
   </si>
   <si>
     <t>02:32:10</t>
   </si>
   <si>
-    <t>04:09:59</t>
-  </si>
-  <si>
-    <t>01:40:14</t>
-  </si>
-  <si>
-    <t>03:17:19</t>
-  </si>
-  <si>
-    <t>00:48:33</t>
-  </si>
-  <si>
-    <t>02:24:46</t>
-  </si>
-  <si>
-    <t>01:32:22</t>
-  </si>
-  <si>
-    <t>03:10:40</t>
-  </si>
-  <si>
-    <t>03:33:47</t>
-  </si>
-  <si>
-    <t>05:11:19</t>
+    <t>04:10:00</t>
+  </si>
+  <si>
+    <t>01:40:16</t>
+  </si>
+  <si>
+    <t>03:17:21</t>
+  </si>
+  <si>
+    <t>00:48:35</t>
+  </si>
+  <si>
+    <t>02:24:49</t>
+  </si>
+  <si>
+    <t>01:32:25</t>
+  </si>
+  <si>
+    <t>03:10:43</t>
+  </si>
+  <si>
+    <t>00:40:11</t>
+  </si>
+  <si>
+    <t>02:17:48</t>
+  </si>
+  <si>
+    <t>23:48:09</t>
   </si>
   <si>
     <t>02:42:33</t>
@@ -217,34 +217,37 @@
     <t>05:06:21</t>
   </si>
   <si>
-    <t>02:34:15</t>
-  </si>
-  <si>
-    <t>04:12:41</t>
-  </si>
-  <si>
-    <t>01:42:28</t>
-  </si>
-  <si>
-    <t>03:19:40</t>
-  </si>
-  <si>
-    <t>00:51:15</t>
-  </si>
-  <si>
-    <t>02:26:55</t>
-  </si>
-  <si>
-    <t>01:34:26</t>
-  </si>
-  <si>
-    <t>03:13:54</t>
-  </si>
-  <si>
-    <t>03:36:47</t>
-  </si>
-  <si>
-    <t>05:13:54</t>
+    <t>02:34:16</t>
+  </si>
+  <si>
+    <t>04:12:42</t>
+  </si>
+  <si>
+    <t>01:42:29</t>
+  </si>
+  <si>
+    <t>03:19:41</t>
+  </si>
+  <si>
+    <t>00:51:17</t>
+  </si>
+  <si>
+    <t>02:26:57</t>
+  </si>
+  <si>
+    <t>01:34:29</t>
+  </si>
+  <si>
+    <t>03:13:57</t>
+  </si>
+  <si>
+    <t>00:42:17</t>
+  </si>
+  <si>
+    <t>02:20:22</t>
+  </si>
+  <si>
+    <t>23:50:27</t>
   </si>
   <si>
     <t>02:44:51</t>
@@ -253,40 +256,43 @@
     <t>04:21:44</t>
   </si>
   <si>
-    <t>03:29:35</t>
+    <t>03:29:36</t>
   </si>
   <si>
     <t>05:07:08</t>
   </si>
   <si>
-    <t>02:37:27</t>
-  </si>
-  <si>
-    <t>04:14:44</t>
-  </si>
-  <si>
-    <t>01:45:19</t>
-  </si>
-  <si>
-    <t>03:22:22</t>
-  </si>
-  <si>
-    <t>00:53:12</t>
-  </si>
-  <si>
-    <t>02:30:01</t>
-  </si>
-  <si>
-    <t>01:37:40</t>
-  </si>
-  <si>
-    <t>03:15:08</t>
-  </si>
-  <si>
-    <t>03:39:49</t>
-  </si>
-  <si>
-    <t>05:16:31</t>
+    <t>02:37:28</t>
+  </si>
+  <si>
+    <t>04:14:45</t>
+  </si>
+  <si>
+    <t>01:45:21</t>
+  </si>
+  <si>
+    <t>03:22:24</t>
+  </si>
+  <si>
+    <t>00:53:13</t>
+  </si>
+  <si>
+    <t>02:30:03</t>
+  </si>
+  <si>
+    <t>01:37:43</t>
+  </si>
+  <si>
+    <t>03:15:11</t>
+  </si>
+  <si>
+    <t>00:45:25</t>
+  </si>
+  <si>
+    <t>02:22:37</t>
+  </si>
+  <si>
+    <t>23:53:07</t>
   </si>
   <si>
     <t>02:47:10</t>
@@ -301,34 +307,37 @@
     <t>05:07:55</t>
   </si>
   <si>
-    <t>02:40:41</t>
-  </si>
-  <si>
-    <t>04:16:48</t>
-  </si>
-  <si>
-    <t>01:48:12</t>
-  </si>
-  <si>
-    <t>03:25:06</t>
-  </si>
-  <si>
-    <t>00:55:09</t>
-  </si>
-  <si>
-    <t>02:33:08</t>
-  </si>
-  <si>
-    <t>01:40:57</t>
-  </si>
-  <si>
-    <t>03:16:22</t>
-  </si>
-  <si>
-    <t>03:42:01</t>
-  </si>
-  <si>
-    <t>05:18:57</t>
+    <t>02:40:42</t>
+  </si>
+  <si>
+    <t>04:16:49</t>
+  </si>
+  <si>
+    <t>01:48:13</t>
+  </si>
+  <si>
+    <t>03:25:07</t>
+  </si>
+  <si>
+    <t>00:55:11</t>
+  </si>
+  <si>
+    <t>02:33:10</t>
+  </si>
+  <si>
+    <t>01:41:00</t>
+  </si>
+  <si>
+    <t>03:16:25</t>
+  </si>
+  <si>
+    <t>00:48:34</t>
+  </si>
+  <si>
+    <t>02:24:53</t>
+  </si>
+  <si>
+    <t>23:55:47</t>
   </si>
   <si>
     <t>02:49:42</t>
@@ -340,67 +349,61 @@
     <t>03:34:59</t>
   </si>
   <si>
-    <t>05:11:33</t>
-  </si>
-  <si>
-    <t>02:42:48</t>
-  </si>
-  <si>
-    <t>04:19:32</t>
-  </si>
-  <si>
-    <t>01:50:27</t>
-  </si>
-  <si>
-    <t>03:27:28</t>
-  </si>
-  <si>
-    <t>00:57:52</t>
-  </si>
-  <si>
-    <t>02:35:19</t>
-  </si>
-  <si>
-    <t>01:43:03</t>
-  </si>
-  <si>
-    <t>03:19:38</t>
+    <t>05:11:34</t>
+  </si>
+  <si>
+    <t>02:42:49</t>
+  </si>
+  <si>
+    <t>04:19:33</t>
+  </si>
+  <si>
+    <t>01:50:29</t>
+  </si>
+  <si>
+    <t>03:27:29</t>
+  </si>
+  <si>
+    <t>00:57:54</t>
+  </si>
+  <si>
+    <t>02:35:21</t>
+  </si>
+  <si>
+    <t>01:43:06</t>
+  </si>
+  <si>
+    <t>00:50:42</t>
+  </si>
+  <si>
+    <t>02:27:29</t>
+  </si>
+  <si>
+    <t>23:58:07</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>15°</t>
-  </si>
-  <si>
     <t>4°</t>
   </si>
   <si>
     <t>7°</t>
   </si>
   <si>
-    <t>05:15:37</t>
-  </si>
-  <si>
     <t>04:26:04</t>
   </si>
   <si>
     <t>05:09:07</t>
   </si>
   <si>
-    <t>04:19:23</t>
+    <t>04:19:24</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -452,13 +455,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +473,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +485,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +503,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +533,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1040,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1118,55 +1121,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L2" s="4">
-        <v>-44.2</v>
+        <v>-54.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O2" s="6">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="P2" s="7">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
-        <v>1</v>
+      <c r="R2" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1174,55 +1177,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.8</v>
+        <v>-35</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O3" s="9">
-        <v>34</v>
+        <v>129</v>
+      </c>
+      <c r="O3" s="6">
+        <v>100</v>
       </c>
       <c r="P3" s="10">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
-        <v>0</v>
+      <c r="R3" s="11">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1230,55 +1233,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L4" s="4">
-        <v>-54.1</v>
+        <v>-46</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O4" s="11">
-        <v>100</v>
+        <v>129</v>
+      </c>
+      <c r="O4" s="6">
+        <v>58</v>
       </c>
       <c r="P4" s="12">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="12">
-        <v>100</v>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1286,55 +1289,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="L5" s="4">
-        <v>-35</v>
+        <v>-25.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O5" s="11">
-        <v>98</v>
+        <v>130</v>
+      </c>
+      <c r="O5" s="6">
+        <v>57</v>
       </c>
       <c r="P5" s="13">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
       <c r="R5" s="14">
-        <v>66</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1342,55 +1345,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L6" s="4">
-        <v>-46</v>
+        <v>-55.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O6" s="11">
-        <v>61</v>
-      </c>
-      <c r="P6" s="15">
-        <v>61</v>
+        <v>129</v>
+      </c>
+      <c r="O6" s="6">
+        <v>95</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="R6" s="11">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1398,55 +1401,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L7" s="4">
-        <v>-25.5</v>
+        <v>-36.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="O7" s="11">
-        <v>53</v>
-      </c>
-      <c r="P7" s="16">
-        <v>53</v>
-      </c>
-      <c r="Q7" s="8">
+      <c r="O7" s="6">
+        <v>96</v>
+      </c>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
+      <c r="Q7" s="15">
+        <v>28</v>
+      </c>
       <c r="R7" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1454,52 +1457,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8" s="4">
-        <v>-55.8</v>
+        <v>-63.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O8" s="6">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="17">
-        <v>3</v>
+      <c r="Q8" s="15">
+        <v>28</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1510,52 +1513,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="L9" s="4">
-        <v>-36.7</v>
+        <v>-47.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O9" s="6">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="17">
-        <v>5</v>
+      <c r="Q9" s="11">
+        <v>10</v>
       </c>
       <c r="R9" s="8">
         <v>0</v>
@@ -1566,52 +1569,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L10" s="4">
-        <v>-63.5</v>
+        <v>-66.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O10" s="11">
-        <v>89</v>
+        <v>129</v>
+      </c>
+      <c r="O10" s="6">
+        <v>51</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
       <c r="Q10" s="16">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1622,52 +1625,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L11" s="4">
-        <v>-47.7</v>
+        <v>-57.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O11" s="11">
-        <v>84</v>
-      </c>
-      <c r="P11" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>41</v>
+        <v>129</v>
+      </c>
+      <c r="O11" s="6">
+        <v>86</v>
+      </c>
+      <c r="P11" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>6</v>
       </c>
       <c r="R11" s="8">
         <v>0</v>
@@ -1678,55 +1681,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-64.90000000000001</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O12" s="6">
+        <v>78</v>
+      </c>
+      <c r="P12" s="17">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="13">
         <v>57</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-66.7</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O12" s="11">
-        <v>96</v>
-      </c>
-      <c r="P12" s="17">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="19">
-        <v>89</v>
-      </c>
-      <c r="R12" s="7">
-        <v>10</v>
+      <c r="R12" s="16">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1734,55 +1737,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L13" s="4">
-        <v>-57.5</v>
+        <v>-49.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O13" s="11">
-        <v>90</v>
-      </c>
-      <c r="P13" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>59</v>
-      </c>
-      <c r="R13" s="13">
-        <v>87</v>
+        <v>130</v>
+      </c>
+      <c r="O13" s="6">
+        <v>74</v>
+      </c>
+      <c r="P13" s="18">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>64</v>
+      </c>
+      <c r="R13" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1790,55 +1793,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L14" s="4">
-        <v>-64.90000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O14" s="11">
-        <v>98</v>
-      </c>
-      <c r="P14" s="17">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>84</v>
-      </c>
-      <c r="R14" s="8">
+        <v>129</v>
+      </c>
+      <c r="O14" s="6">
+        <v>50</v>
+      </c>
+      <c r="P14" s="14">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="8">
         <v>0</v>
+      </c>
+      <c r="R14" s="19">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1846,114 +1849,170 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L15" s="4">
-        <v>-49.5</v>
+        <v>-59.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="O15" s="11">
-        <v>94</v>
-      </c>
-      <c r="P15" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="20">
-        <v>74</v>
-      </c>
-      <c r="R15" s="8">
+      <c r="O15" s="6">
+        <v>47</v>
+      </c>
+      <c r="P15" s="16">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="20">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-63.7</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O16" s="6">
+        <v>97</v>
+      </c>
+      <c r="P16" s="13">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>24</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A15">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B15">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C15">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D15">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E15">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F15">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J15">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K15">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L15">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1972,12 +2031,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M15">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1994,22 +2053,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O15">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P15">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q15">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R15">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="141">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261002--01</t>
-  </si>
-  <si>
-    <t>20261002--02</t>
-  </si>
-  <si>
     <t>20261003--01</t>
   </si>
   <si>
@@ -115,10 +109,13 @@
     <t>20261008--03</t>
   </si>
   <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>06:05</t>
+    <t>20261009--01</t>
+  </si>
+  <si>
+    <t>20261009--02</t>
+  </si>
+  <si>
+    <t>20261009--03</t>
   </si>
   <si>
     <t>06:31</t>
@@ -139,12 +136,15 @@
     <t>05:26</t>
   </si>
   <si>
-    <t>03:54</t>
+    <t>03:53</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
+    <t>06:30</t>
+  </si>
+  <si>
     <t>02:28</t>
   </si>
   <si>
@@ -157,58 +157,64 @@
     <t>05:20</t>
   </si>
   <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>01:36</t>
+  </si>
+  <si>
+    <t>02:47</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:40:02</t>
-  </si>
-  <si>
-    <t>04:16:31</t>
-  </si>
-  <si>
     <t>03:24:16</t>
   </si>
   <si>
-    <t>05:02:45</t>
+    <t>05:02:44</t>
   </si>
   <si>
     <t>02:32:10</t>
   </si>
   <si>
-    <t>04:10:00</t>
-  </si>
-  <si>
-    <t>01:40:16</t>
-  </si>
-  <si>
-    <t>03:17:21</t>
-  </si>
-  <si>
-    <t>00:48:35</t>
-  </si>
-  <si>
-    <t>02:24:49</t>
-  </si>
-  <si>
-    <t>01:32:25</t>
-  </si>
-  <si>
-    <t>03:10:43</t>
-  </si>
-  <si>
-    <t>00:40:11</t>
-  </si>
-  <si>
-    <t>02:17:48</t>
-  </si>
-  <si>
-    <t>23:48:09</t>
-  </si>
-  <si>
-    <t>02:42:33</t>
-  </si>
-  <si>
-    <t>04:18:43</t>
+    <t>04:09:59</t>
+  </si>
+  <si>
+    <t>01:40:15</t>
+  </si>
+  <si>
+    <t>03:17:20</t>
+  </si>
+  <si>
+    <t>00:48:34</t>
+  </si>
+  <si>
+    <t>02:24:47</t>
+  </si>
+  <si>
+    <t>01:32:23</t>
+  </si>
+  <si>
+    <t>03:10:41</t>
+  </si>
+  <si>
+    <t>00:40:09</t>
+  </si>
+  <si>
+    <t>02:17:46</t>
+  </si>
+  <si>
+    <t>23:48:07</t>
+  </si>
+  <si>
+    <t>01:24:57</t>
+  </si>
+  <si>
+    <t>06:20:22</t>
+  </si>
+  <si>
+    <t>22:56:20</t>
   </si>
   <si>
     <t>03:26:21</t>
@@ -217,88 +223,94 @@
     <t>05:06:21</t>
   </si>
   <si>
-    <t>02:34:16</t>
-  </si>
-  <si>
-    <t>04:12:42</t>
-  </si>
-  <si>
-    <t>01:42:29</t>
-  </si>
-  <si>
-    <t>03:19:41</t>
-  </si>
-  <si>
-    <t>00:51:17</t>
-  </si>
-  <si>
-    <t>02:26:57</t>
-  </si>
-  <si>
-    <t>01:34:29</t>
-  </si>
-  <si>
-    <t>03:13:57</t>
-  </si>
-  <si>
-    <t>00:42:17</t>
-  </si>
-  <si>
-    <t>02:20:22</t>
-  </si>
-  <si>
-    <t>23:50:27</t>
-  </si>
-  <si>
-    <t>02:44:51</t>
-  </si>
-  <si>
-    <t>04:21:44</t>
-  </si>
-  <si>
-    <t>03:29:36</t>
+    <t>02:34:15</t>
+  </si>
+  <si>
+    <t>04:12:41</t>
+  </si>
+  <si>
+    <t>01:42:28</t>
+  </si>
+  <si>
+    <t>03:19:40</t>
+  </si>
+  <si>
+    <t>00:51:16</t>
+  </si>
+  <si>
+    <t>02:26:56</t>
+  </si>
+  <si>
+    <t>01:34:28</t>
+  </si>
+  <si>
+    <t>03:13:55</t>
+  </si>
+  <si>
+    <t>00:42:15</t>
+  </si>
+  <si>
+    <t>02:20:20</t>
+  </si>
+  <si>
+    <t>23:50:25</t>
+  </si>
+  <si>
+    <t>01:27:13</t>
+  </si>
+  <si>
+    <t>06:23:58</t>
+  </si>
+  <si>
+    <t>22:59:23</t>
+  </si>
+  <si>
+    <t>03:29:35</t>
   </si>
   <si>
     <t>05:07:08</t>
   </si>
   <si>
-    <t>02:37:28</t>
-  </si>
-  <si>
-    <t>04:14:45</t>
-  </si>
-  <si>
-    <t>01:45:21</t>
-  </si>
-  <si>
-    <t>03:22:24</t>
-  </si>
-  <si>
-    <t>00:53:13</t>
-  </si>
-  <si>
-    <t>02:30:03</t>
-  </si>
-  <si>
-    <t>01:37:43</t>
-  </si>
-  <si>
-    <t>03:15:11</t>
-  </si>
-  <si>
-    <t>00:45:25</t>
-  </si>
-  <si>
-    <t>02:22:37</t>
-  </si>
-  <si>
-    <t>23:53:07</t>
-  </si>
-  <si>
-    <t>02:47:10</t>
-  </si>
-  <si>
-    <t>04:24:48</t>
+    <t>02:37:27</t>
+  </si>
+  <si>
+    <t>04:14:44</t>
+  </si>
+  <si>
+    <t>01:45:20</t>
+  </si>
+  <si>
+    <t>03:22:23</t>
+  </si>
+  <si>
+    <t>00:53:12</t>
+  </si>
+  <si>
+    <t>02:30:01</t>
+  </si>
+  <si>
+    <t>01:37:42</t>
+  </si>
+  <si>
+    <t>03:15:09</t>
+  </si>
+  <si>
+    <t>00:45:23</t>
+  </si>
+  <si>
+    <t>02:22:35</t>
+  </si>
+  <si>
+    <t>23:53:05</t>
+  </si>
+  <si>
+    <t>01:30:03</t>
+  </si>
+  <si>
+    <t>06:24:46</t>
+  </si>
+  <si>
+    <t>23:00:46</t>
   </si>
   <si>
     <t>03:32:52</t>
@@ -307,100 +319,118 @@
     <t>05:07:55</t>
   </si>
   <si>
-    <t>02:40:42</t>
-  </si>
-  <si>
-    <t>04:16:49</t>
-  </si>
-  <si>
-    <t>01:48:13</t>
-  </si>
-  <si>
-    <t>03:25:07</t>
-  </si>
-  <si>
-    <t>00:55:11</t>
-  </si>
-  <si>
-    <t>02:33:10</t>
-  </si>
-  <si>
-    <t>01:41:00</t>
-  </si>
-  <si>
-    <t>03:16:25</t>
-  </si>
-  <si>
-    <t>00:48:34</t>
-  </si>
-  <si>
-    <t>02:24:53</t>
-  </si>
-  <si>
-    <t>23:55:47</t>
-  </si>
-  <si>
-    <t>02:49:42</t>
-  </si>
-  <si>
-    <t>04:27:01</t>
+    <t>02:40:41</t>
+  </si>
+  <si>
+    <t>04:16:48</t>
+  </si>
+  <si>
+    <t>01:48:12</t>
+  </si>
+  <si>
+    <t>03:25:06</t>
+  </si>
+  <si>
+    <t>00:55:09</t>
+  </si>
+  <si>
+    <t>02:33:09</t>
+  </si>
+  <si>
+    <t>01:40:58</t>
+  </si>
+  <si>
+    <t>03:16:23</t>
+  </si>
+  <si>
+    <t>00:48:32</t>
+  </si>
+  <si>
+    <t>02:24:51</t>
+  </si>
+  <si>
+    <t>23:55:45</t>
+  </si>
+  <si>
+    <t>01:32:53</t>
+  </si>
+  <si>
+    <t>06:25:34</t>
+  </si>
+  <si>
+    <t>23:02:10</t>
   </si>
   <si>
     <t>03:34:59</t>
   </si>
   <si>
-    <t>05:11:34</t>
-  </si>
-  <si>
-    <t>02:42:49</t>
-  </si>
-  <si>
-    <t>04:19:33</t>
-  </si>
-  <si>
-    <t>01:50:29</t>
-  </si>
-  <si>
-    <t>03:27:29</t>
-  </si>
-  <si>
-    <t>00:57:54</t>
-  </si>
-  <si>
-    <t>02:35:21</t>
-  </si>
-  <si>
-    <t>01:43:06</t>
-  </si>
-  <si>
-    <t>00:50:42</t>
-  </si>
-  <si>
-    <t>02:27:29</t>
-  </si>
-  <si>
-    <t>23:58:07</t>
+    <t>05:11:33</t>
+  </si>
+  <si>
+    <t>02:42:48</t>
+  </si>
+  <si>
+    <t>04:19:32</t>
+  </si>
+  <si>
+    <t>01:50:28</t>
+  </si>
+  <si>
+    <t>03:27:28</t>
+  </si>
+  <si>
+    <t>00:57:53</t>
+  </si>
+  <si>
+    <t>02:35:19</t>
+  </si>
+  <si>
+    <t>01:43:04</t>
+  </si>
+  <si>
+    <t>03:19:39</t>
+  </si>
+  <si>
+    <t>00:50:40</t>
+  </si>
+  <si>
+    <t>02:27:27</t>
+  </si>
+  <si>
+    <t>23:58:05</t>
+  </si>
+  <si>
+    <t>01:35:11</t>
+  </si>
+  <si>
+    <t>06:29:11</t>
+  </si>
+  <si>
+    <t>23:05:14</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>4°</t>
-  </si>
-  <si>
     <t>7°</t>
   </si>
   <si>
-    <t>04:26:04</t>
+    <t>1°</t>
   </si>
   <si>
     <t>05:09:07</t>
   </si>
   <si>
-    <t>04:19:24</t>
+    <t>04:19:23</t>
+  </si>
+  <si>
+    <t>06:20:41</t>
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>3</t>
@@ -461,7 +491,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,7 +509,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,7 +521,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,25 +539,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,13 +569,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1043,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1121,49 +1151,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L2" s="4">
-        <v>-54.1</v>
+        <v>-46</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O2" s="6">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="P2" s="7">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1177,55 +1207,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="L3" s="4">
-        <v>-35</v>
+        <v>-25.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="10">
-        <v>100</v>
+        <v>140</v>
+      </c>
+      <c r="O3" s="10">
+        <v>18</v>
+      </c>
+      <c r="P3" s="11">
+        <v>12</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="11">
-        <v>10</v>
+      <c r="R3" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1233,55 +1263,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L4" s="4">
-        <v>-46</v>
+        <v>-55.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O4" s="6">
-        <v>58</v>
-      </c>
-      <c r="P4" s="12">
-        <v>58</v>
-      </c>
-      <c r="Q4" s="8">
+        <v>88</v>
+      </c>
+      <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>0</v>
+      <c r="Q4" s="9">
+        <v>3</v>
+      </c>
+      <c r="R4" s="12">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1289,55 +1319,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="L5" s="4">
-        <v>-25.5</v>
+        <v>-36.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="O5" s="6">
-        <v>57</v>
-      </c>
-      <c r="P5" s="13">
-        <v>57</v>
-      </c>
-      <c r="Q5" s="8">
+        <v>88</v>
+      </c>
+      <c r="P5" s="8">
         <v>0</v>
       </c>
+      <c r="Q5" s="13">
+        <v>14</v>
+      </c>
       <c r="R5" s="14">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1345,55 +1375,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L6" s="4">
-        <v>-55.8</v>
+        <v>-63.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O6" s="6">
-        <v>95</v>
+        <v>139</v>
+      </c>
+      <c r="O6" s="15">
+        <v>12</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="11">
-        <v>10</v>
+      <c r="Q6" s="11">
+        <v>12</v>
+      </c>
+      <c r="R6" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1401,55 +1431,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="L7" s="4">
-        <v>-36.7</v>
+        <v>-47.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O7" s="6">
-        <v>96</v>
+        <v>139</v>
+      </c>
+      <c r="O7" s="15">
+        <v>13</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="15">
-        <v>28</v>
+      <c r="Q7" s="13">
+        <v>13</v>
       </c>
       <c r="R7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1457,52 +1487,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L8" s="4">
-        <v>-63.5</v>
+        <v>-66.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O8" s="6">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="15">
-        <v>28</v>
+      <c r="Q8" s="16">
+        <v>33</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1513,52 +1543,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L9" s="4">
-        <v>-47.7</v>
+        <v>-57.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O9" s="6">
-        <v>46</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>10</v>
+        <v>92</v>
+      </c>
+      <c r="P9" s="17">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>14</v>
       </c>
       <c r="R9" s="8">
         <v>0</v>
@@ -1569,55 +1599,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L10" s="4">
-        <v>-66.7</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O10" s="6">
-        <v>51</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>13</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="O10" s="10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>4</v>
+      </c>
+      <c r="R10" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1625,55 +1655,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L11" s="4">
-        <v>-57.5</v>
+        <v>-49.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O11" s="6">
-        <v>86</v>
-      </c>
-      <c r="P11" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>6</v>
-      </c>
-      <c r="R11" s="8">
+        <v>140</v>
+      </c>
+      <c r="O11" s="10">
+        <v>11</v>
+      </c>
+      <c r="P11" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="8">
         <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1681,55 +1711,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L12" s="4">
-        <v>-64.90000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O12" s="6">
-        <v>78</v>
-      </c>
-      <c r="P12" s="17">
-        <v>65</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>57</v>
-      </c>
-      <c r="R12" s="16">
-        <v>16</v>
+        <v>83</v>
+      </c>
+      <c r="P12" s="18">
+        <v>83</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="18">
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1737,55 +1767,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-59.2</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O13" s="6">
+        <v>93</v>
+      </c>
+      <c r="P13" s="12">
         <v>70</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-49.5</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O13" s="6">
-        <v>74</v>
-      </c>
-      <c r="P13" s="18">
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="19">
         <v>38</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>64</v>
-      </c>
-      <c r="R13" s="9">
-        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1793,55 +1823,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L14" s="4">
-        <v>-67.40000000000001</v>
+        <v>-63.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O14" s="6">
-        <v>50</v>
-      </c>
-      <c r="P14" s="14">
-        <v>25</v>
+        <v>85</v>
+      </c>
+      <c r="P14" s="16">
+        <v>33</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
       </c>
-      <c r="R14" s="19">
-        <v>19</v>
+      <c r="R14" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1849,55 +1879,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L15" s="4">
-        <v>-59.2</v>
+        <v>-66.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O15" s="6">
-        <v>47</v>
-      </c>
-      <c r="P15" s="16">
-        <v>16</v>
+        <v>82</v>
+      </c>
+      <c r="P15" s="17">
+        <v>19</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="20">
-        <v>47</v>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1905,114 +1935,170 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="L16" s="4">
-        <v>-63.7</v>
+        <v>-9.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="O16" s="6">
-        <v>97</v>
-      </c>
-      <c r="P16" s="13">
-        <v>55</v>
-      </c>
-      <c r="Q16" s="14">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="P16" s="20">
+        <v>52</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-55.7</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O17" s="6">
+        <v>45</v>
+      </c>
+      <c r="P17" s="19">
+        <v>38</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2031,12 +2117,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2053,22 +2139,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="139">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261003--01</t>
-  </si>
-  <si>
-    <t>20261003--02</t>
-  </si>
-  <si>
     <t>20261004--01</t>
   </si>
   <si>
@@ -118,33 +112,33 @@
     <t>20261009--03</t>
   </si>
   <si>
+    <t>20261010--01</t>
+  </si>
+  <si>
+    <t>20261010--02</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>04:07</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>03:53</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
     <t>06:31</t>
   </si>
   <si>
-    <t>01:34</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>04:07</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>03:53</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
     <t>02:28</t>
   </si>
   <si>
@@ -154,169 +148,169 @@
     <t>04:31</t>
   </si>
   <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>01:36</t>
-  </si>
-  <si>
-    <t>02:47</t>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>01:33</t>
+  </si>
+  <si>
+    <t>02:44</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:29</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:24:16</t>
-  </si>
-  <si>
-    <t>05:02:44</t>
-  </si>
-  <si>
-    <t>02:32:10</t>
+    <t>02:32:09</t>
   </si>
   <si>
     <t>04:09:59</t>
   </si>
   <si>
-    <t>01:40:15</t>
-  </si>
-  <si>
-    <t>03:17:20</t>
-  </si>
-  <si>
-    <t>00:48:34</t>
-  </si>
-  <si>
-    <t>02:24:47</t>
-  </si>
-  <si>
-    <t>01:32:23</t>
-  </si>
-  <si>
-    <t>03:10:41</t>
-  </si>
-  <si>
-    <t>00:40:09</t>
-  </si>
-  <si>
-    <t>02:17:46</t>
-  </si>
-  <si>
-    <t>23:48:07</t>
-  </si>
-  <si>
-    <t>01:24:57</t>
-  </si>
-  <si>
-    <t>06:20:22</t>
-  </si>
-  <si>
-    <t>22:56:20</t>
-  </si>
-  <si>
-    <t>03:26:21</t>
-  </si>
-  <si>
-    <t>05:06:21</t>
-  </si>
-  <si>
-    <t>02:34:15</t>
+    <t>01:40:13</t>
+  </si>
+  <si>
+    <t>03:17:18</t>
+  </si>
+  <si>
+    <t>00:48:31</t>
+  </si>
+  <si>
+    <t>02:24:44</t>
+  </si>
+  <si>
+    <t>01:32:18</t>
+  </si>
+  <si>
+    <t>03:10:35</t>
+  </si>
+  <si>
+    <t>00:40:01</t>
+  </si>
+  <si>
+    <t>02:17:38</t>
+  </si>
+  <si>
+    <t>23:47:56</t>
+  </si>
+  <si>
+    <t>01:24:46</t>
+  </si>
+  <si>
+    <t>06:20:10</t>
+  </si>
+  <si>
+    <t>22:56:07</t>
+  </si>
+  <si>
+    <t>00:32:01</t>
+  </si>
+  <si>
+    <t>23:39:25</t>
+  </si>
+  <si>
+    <t>02:34:14</t>
   </si>
   <si>
     <t>04:12:41</t>
   </si>
   <si>
-    <t>01:42:28</t>
-  </si>
-  <si>
-    <t>03:19:40</t>
-  </si>
-  <si>
-    <t>00:51:16</t>
-  </si>
-  <si>
-    <t>02:26:56</t>
-  </si>
-  <si>
-    <t>01:34:28</t>
-  </si>
-  <si>
-    <t>03:13:55</t>
-  </si>
-  <si>
-    <t>00:42:15</t>
-  </si>
-  <si>
-    <t>02:20:20</t>
-  </si>
-  <si>
-    <t>23:50:25</t>
-  </si>
-  <si>
-    <t>01:27:13</t>
-  </si>
-  <si>
-    <t>06:23:58</t>
-  </si>
-  <si>
-    <t>22:59:23</t>
-  </si>
-  <si>
-    <t>03:29:35</t>
-  </si>
-  <si>
-    <t>05:07:08</t>
-  </si>
-  <si>
-    <t>02:37:27</t>
+    <t>01:42:27</t>
+  </si>
+  <si>
+    <t>03:19:38</t>
+  </si>
+  <si>
+    <t>00:51:13</t>
+  </si>
+  <si>
+    <t>02:26:53</t>
+  </si>
+  <si>
+    <t>01:34:22</t>
+  </si>
+  <si>
+    <t>03:13:50</t>
+  </si>
+  <si>
+    <t>00:42:08</t>
+  </si>
+  <si>
+    <t>02:20:12</t>
+  </si>
+  <si>
+    <t>23:50:15</t>
+  </si>
+  <si>
+    <t>01:27:02</t>
+  </si>
+  <si>
+    <t>06:23:48</t>
+  </si>
+  <si>
+    <t>22:59:11</t>
+  </si>
+  <si>
+    <t>00:34:08</t>
+  </si>
+  <si>
+    <t>23:41:29</t>
+  </si>
+  <si>
+    <t>02:37:26</t>
   </si>
   <si>
     <t>04:14:44</t>
   </si>
   <si>
-    <t>01:45:20</t>
-  </si>
-  <si>
-    <t>03:22:23</t>
-  </si>
-  <si>
-    <t>00:53:12</t>
-  </si>
-  <si>
-    <t>02:30:01</t>
-  </si>
-  <si>
-    <t>01:37:42</t>
-  </si>
-  <si>
-    <t>03:15:09</t>
-  </si>
-  <si>
-    <t>00:45:23</t>
-  </si>
-  <si>
-    <t>02:22:35</t>
-  </si>
-  <si>
-    <t>23:53:05</t>
-  </si>
-  <si>
-    <t>01:30:03</t>
-  </si>
-  <si>
-    <t>06:24:46</t>
-  </si>
-  <si>
-    <t>23:00:46</t>
-  </si>
-  <si>
-    <t>03:32:52</t>
-  </si>
-  <si>
-    <t>05:07:55</t>
+    <t>01:45:18</t>
+  </si>
+  <si>
+    <t>03:22:21</t>
+  </si>
+  <si>
+    <t>00:53:09</t>
+  </si>
+  <si>
+    <t>02:29:58</t>
+  </si>
+  <si>
+    <t>01:37:36</t>
+  </si>
+  <si>
+    <t>03:15:04</t>
+  </si>
+  <si>
+    <t>00:45:16</t>
+  </si>
+  <si>
+    <t>02:22:27</t>
+  </si>
+  <si>
+    <t>23:52:54</t>
+  </si>
+  <si>
+    <t>01:29:52</t>
+  </si>
+  <si>
+    <t>06:24:35</t>
+  </si>
+  <si>
+    <t>23:00:33</t>
+  </si>
+  <si>
+    <t>00:37:17</t>
+  </si>
+  <si>
+    <t>23:44:43</t>
   </si>
   <si>
     <t>02:40:41</t>
@@ -325,106 +319,106 @@
     <t>04:16:48</t>
   </si>
   <si>
-    <t>01:48:12</t>
-  </si>
-  <si>
-    <t>03:25:06</t>
-  </si>
-  <si>
-    <t>00:55:09</t>
-  </si>
-  <si>
-    <t>02:33:09</t>
-  </si>
-  <si>
-    <t>01:40:58</t>
-  </si>
-  <si>
-    <t>03:16:23</t>
-  </si>
-  <si>
-    <t>00:48:32</t>
-  </si>
-  <si>
-    <t>02:24:51</t>
-  </si>
-  <si>
-    <t>23:55:45</t>
-  </si>
-  <si>
-    <t>01:32:53</t>
-  </si>
-  <si>
-    <t>06:25:34</t>
-  </si>
-  <si>
-    <t>23:02:10</t>
-  </si>
-  <si>
-    <t>03:34:59</t>
-  </si>
-  <si>
-    <t>05:11:33</t>
+    <t>01:48:11</t>
+  </si>
+  <si>
+    <t>03:25:04</t>
+  </si>
+  <si>
+    <t>00:55:06</t>
+  </si>
+  <si>
+    <t>02:33:06</t>
+  </si>
+  <si>
+    <t>01:40:53</t>
+  </si>
+  <si>
+    <t>03:16:18</t>
+  </si>
+  <si>
+    <t>00:48:25</t>
+  </si>
+  <si>
+    <t>02:24:43</t>
+  </si>
+  <si>
+    <t>23:55:34</t>
+  </si>
+  <si>
+    <t>01:32:43</t>
+  </si>
+  <si>
+    <t>06:25:21</t>
+  </si>
+  <si>
+    <t>23:01:55</t>
+  </si>
+  <si>
+    <t>00:40:27</t>
+  </si>
+  <si>
+    <t>23:47:58</t>
   </si>
   <si>
     <t>02:42:48</t>
   </si>
   <si>
-    <t>04:19:32</t>
-  </si>
-  <si>
-    <t>01:50:28</t>
-  </si>
-  <si>
-    <t>03:27:28</t>
-  </si>
-  <si>
-    <t>00:57:53</t>
-  </si>
-  <si>
-    <t>02:35:19</t>
-  </si>
-  <si>
-    <t>01:43:04</t>
-  </si>
-  <si>
-    <t>03:19:39</t>
-  </si>
-  <si>
-    <t>00:50:40</t>
-  </si>
-  <si>
-    <t>02:27:27</t>
-  </si>
-  <si>
-    <t>23:58:05</t>
-  </si>
-  <si>
-    <t>01:35:11</t>
-  </si>
-  <si>
-    <t>06:29:11</t>
-  </si>
-  <si>
-    <t>23:05:14</t>
+    <t>04:19:31</t>
+  </si>
+  <si>
+    <t>01:50:26</t>
+  </si>
+  <si>
+    <t>03:27:26</t>
+  </si>
+  <si>
+    <t>00:57:49</t>
+  </si>
+  <si>
+    <t>02:35:16</t>
+  </si>
+  <si>
+    <t>01:42:59</t>
+  </si>
+  <si>
+    <t>03:19:34</t>
+  </si>
+  <si>
+    <t>00:50:33</t>
+  </si>
+  <si>
+    <t>02:27:19</t>
+  </si>
+  <si>
+    <t>23:57:54</t>
+  </si>
+  <si>
+    <t>01:35:00</t>
+  </si>
+  <si>
+    <t>06:28:59</t>
+  </si>
+  <si>
+    <t>23:04:59</t>
+  </si>
+  <si>
+    <t>00:42:36</t>
+  </si>
+  <si>
+    <t>23:50:03</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>7°</t>
-  </si>
-  <si>
     <t>1°</t>
   </si>
   <si>
-    <t>05:09:07</t>
-  </si>
-  <si>
     <t>04:19:23</t>
   </si>
   <si>
-    <t>06:20:41</t>
+    <t>06:20:31</t>
   </si>
   <si>
     <t>B</t>
@@ -470,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,7 +485,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,55 +497,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,7 +521,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -670,6 +676,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1151,7 +1163,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>34</v>
@@ -1181,25 +1193,25 @@
         <v>51</v>
       </c>
       <c r="L2" s="4">
-        <v>-46</v>
+        <v>-55.8</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="O2" s="6">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
       <c r="R2" s="9">
-        <v>6</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1207,7 +1219,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>35</v>
@@ -1231,31 +1243,31 @@
         <v>116</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L3" s="4">
-        <v>-25.5</v>
+        <v>-36.7</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O3" s="10">
-        <v>18</v>
-      </c>
-      <c r="P3" s="11">
-        <v>12</v>
+      <c r="O3" s="6">
+        <v>100</v>
+      </c>
+      <c r="P3" s="10">
+        <v>36</v>
       </c>
       <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="R3" s="11">
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1263,7 +1275,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>36</v>
@@ -1293,25 +1305,25 @@
         <v>53</v>
       </c>
       <c r="L4" s="4">
-        <v>-55.8</v>
+        <v>-63.5</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="O4" s="6">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="9">
-        <v>3</v>
+      <c r="Q4" s="8">
+        <v>0</v>
       </c>
       <c r="R4" s="12">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1319,7 +1331,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>37</v>
@@ -1346,28 +1358,28 @@
         <v>131</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-47.7</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="L5" s="4">
-        <v>-36.7</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="O5" s="6">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
       <c r="Q5" s="13">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R5" s="14">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1375,7 +1387,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>38</v>
@@ -1405,25 +1417,25 @@
         <v>55</v>
       </c>
       <c r="L6" s="4">
-        <v>-63.5</v>
+        <v>-66.7</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="O6" s="15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="11">
-        <v>12</v>
-      </c>
-      <c r="R6" s="9">
-        <v>3</v>
+      <c r="Q6" s="16">
+        <v>5</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1431,7 +1443,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>39</v>
@@ -1461,22 +1473,22 @@
         <v>56</v>
       </c>
       <c r="L7" s="4">
-        <v>-47.7</v>
+        <v>-57.5</v>
       </c>
       <c r="M7" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="O7" s="15">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="13">
-        <v>13</v>
+      <c r="Q7" s="16">
+        <v>5</v>
       </c>
       <c r="R7" s="8">
         <v>0</v>
@@ -1487,7 +1499,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>40</v>
@@ -1517,22 +1529,22 @@
         <v>57</v>
       </c>
       <c r="L8" s="4">
-        <v>-66.7</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="O8" s="6">
-        <v>89</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>33</v>
+        <v>73</v>
+      </c>
+      <c r="P8" s="17">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1543,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>41</v>
@@ -1573,22 +1585,22 @@
         <v>58</v>
       </c>
       <c r="L9" s="4">
-        <v>-57.5</v>
+        <v>-49.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O9" s="6">
-        <v>92</v>
-      </c>
-      <c r="P9" s="17">
-        <v>18</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>14</v>
+        <v>67</v>
+      </c>
+      <c r="P9" s="18">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
       </c>
       <c r="R9" s="8">
         <v>0</v>
@@ -1599,7 +1611,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>42</v>
@@ -1629,25 +1641,25 @@
         <v>59</v>
       </c>
       <c r="L10" s="4">
-        <v>-64.90000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O10" s="10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="11">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>4</v>
-      </c>
-      <c r="R10" s="17">
-        <v>19</v>
+      <c r="O10" s="6">
+        <v>94</v>
+      </c>
+      <c r="P10" s="19">
+        <v>57</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1655,7 +1667,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>43</v>
@@ -1685,25 +1697,25 @@
         <v>60</v>
       </c>
       <c r="L11" s="4">
-        <v>-49.5</v>
+        <v>-59.2</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O11" s="10">
-        <v>11</v>
-      </c>
-      <c r="P11" s="9">
-        <v>4</v>
+      <c r="O11" s="6">
+        <v>88</v>
+      </c>
+      <c r="P11" s="14">
+        <v>52</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="11">
-        <v>11</v>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1711,7 +1723,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>44</v>
@@ -1741,25 +1753,25 @@
         <v>61</v>
       </c>
       <c r="L12" s="4">
-        <v>-67.40000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O12" s="6">
-        <v>83</v>
-      </c>
-      <c r="P12" s="18">
-        <v>83</v>
+      <c r="O12" s="20">
+        <v>37</v>
+      </c>
+      <c r="P12" s="10">
+        <v>37</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="18">
-        <v>83</v>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1767,7 +1779,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>45</v>
@@ -1797,25 +1809,25 @@
         <v>62</v>
       </c>
       <c r="L13" s="4">
-        <v>-59.2</v>
+        <v>-66.3</v>
       </c>
       <c r="M13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O13" s="6">
-        <v>93</v>
-      </c>
-      <c r="P13" s="12">
-        <v>70</v>
+      <c r="O13" s="20">
+        <v>15</v>
+      </c>
+      <c r="P13" s="21">
+        <v>15</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="19">
-        <v>38</v>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1823,13 +1835,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>63</v>
@@ -1847,31 +1859,31 @@
         <v>127</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="L14" s="4">
-        <v>-63.7</v>
+        <v>-9.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O14" s="6">
-        <v>85</v>
-      </c>
-      <c r="P14" s="16">
-        <v>33</v>
+        <v>138</v>
+      </c>
+      <c r="O14" s="20">
+        <v>19</v>
+      </c>
+      <c r="P14" s="13">
+        <v>19</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
       </c>
       <c r="R14" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1879,7 +1891,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>47</v>
@@ -1909,19 +1921,19 @@
         <v>64</v>
       </c>
       <c r="L15" s="4">
-        <v>-66.3</v>
+        <v>-55.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O15" s="6">
-        <v>82</v>
-      </c>
-      <c r="P15" s="17">
-        <v>19</v>
+        <v>53</v>
+      </c>
+      <c r="P15" s="19">
+        <v>53</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1935,13 +1947,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>65</v>
@@ -1959,25 +1971,25 @@
         <v>129</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="L16" s="4">
-        <v>-9.4</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O16" s="6">
-        <v>52</v>
-      </c>
-      <c r="P16" s="20">
-        <v>52</v>
+        <v>47</v>
+      </c>
+      <c r="P16" s="22">
+        <v>47</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -1991,7 +2003,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>49</v>
@@ -2021,19 +2033,19 @@
         <v>66</v>
       </c>
       <c r="L17" s="4">
-        <v>-55.7</v>
+        <v>-63.2</v>
       </c>
       <c r="M17" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O17" s="6">
-        <v>45</v>
-      </c>
-      <c r="P17" s="19">
-        <v>38</v>
+      <c r="O17" s="20">
+        <v>5</v>
+      </c>
+      <c r="P17" s="16">
+        <v>5</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261004--01</t>
-  </si>
-  <si>
-    <t>20261004--02</t>
-  </si>
-  <si>
     <t>20261005--01</t>
   </si>
   <si>
@@ -118,295 +112,322 @@
     <t>20261010--02</t>
   </si>
   <si>
+    <t>20261011--01</t>
+  </si>
+  <si>
+    <t>20261011--02</t>
+  </si>
+  <si>
+    <t>20261011--03</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>02:29</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>02:37</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
     <t>06:27</t>
   </si>
   <si>
-    <t>04:07</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>03:53</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>02:28</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
-    <t>05:19</t>
-  </si>
-  <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>01:33</t>
-  </si>
-  <si>
-    <t>02:44</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:29</t>
+    <t>03:16</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>06:00</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:32:09</t>
-  </si>
-  <si>
-    <t>04:09:59</t>
-  </si>
-  <si>
-    <t>01:40:13</t>
-  </si>
-  <si>
-    <t>03:17:18</t>
-  </si>
-  <si>
-    <t>00:48:31</t>
-  </si>
-  <si>
-    <t>02:24:44</t>
-  </si>
-  <si>
-    <t>01:32:18</t>
-  </si>
-  <si>
-    <t>03:10:35</t>
-  </si>
-  <si>
-    <t>00:40:01</t>
-  </si>
-  <si>
-    <t>02:17:38</t>
-  </si>
-  <si>
-    <t>23:47:56</t>
-  </si>
-  <si>
-    <t>01:24:46</t>
-  </si>
-  <si>
-    <t>06:20:10</t>
-  </si>
-  <si>
-    <t>22:56:07</t>
-  </si>
-  <si>
-    <t>00:32:01</t>
-  </si>
-  <si>
-    <t>23:39:25</t>
-  </si>
-  <si>
-    <t>02:34:14</t>
-  </si>
-  <si>
-    <t>04:12:41</t>
-  </si>
-  <si>
-    <t>01:42:27</t>
-  </si>
-  <si>
-    <t>03:19:38</t>
-  </si>
-  <si>
-    <t>00:51:13</t>
-  </si>
-  <si>
-    <t>02:26:53</t>
-  </si>
-  <si>
-    <t>01:34:22</t>
-  </si>
-  <si>
-    <t>03:13:50</t>
-  </si>
-  <si>
-    <t>00:42:08</t>
-  </si>
-  <si>
-    <t>02:20:12</t>
-  </si>
-  <si>
-    <t>23:50:15</t>
-  </si>
-  <si>
-    <t>01:27:02</t>
-  </si>
-  <si>
-    <t>06:23:48</t>
-  </si>
-  <si>
-    <t>22:59:11</t>
-  </si>
-  <si>
-    <t>00:34:08</t>
-  </si>
-  <si>
-    <t>23:41:29</t>
-  </si>
-  <si>
-    <t>02:37:26</t>
-  </si>
-  <si>
-    <t>04:14:44</t>
-  </si>
-  <si>
-    <t>01:45:18</t>
-  </si>
-  <si>
-    <t>03:22:21</t>
-  </si>
-  <si>
-    <t>00:53:09</t>
-  </si>
-  <si>
-    <t>02:29:58</t>
-  </si>
-  <si>
-    <t>01:37:36</t>
-  </si>
-  <si>
-    <t>03:15:04</t>
-  </si>
-  <si>
-    <t>00:45:16</t>
-  </si>
-  <si>
-    <t>02:22:27</t>
-  </si>
-  <si>
-    <t>23:52:54</t>
-  </si>
-  <si>
-    <t>01:29:52</t>
-  </si>
-  <si>
-    <t>06:24:35</t>
-  </si>
-  <si>
-    <t>23:00:33</t>
-  </si>
-  <si>
-    <t>00:37:17</t>
-  </si>
-  <si>
-    <t>23:44:43</t>
-  </si>
-  <si>
-    <t>02:40:41</t>
-  </si>
-  <si>
-    <t>04:16:48</t>
-  </si>
-  <si>
-    <t>01:48:11</t>
-  </si>
-  <si>
-    <t>03:25:04</t>
-  </si>
-  <si>
-    <t>00:55:06</t>
-  </si>
-  <si>
-    <t>02:33:06</t>
-  </si>
-  <si>
-    <t>01:40:53</t>
-  </si>
-  <si>
-    <t>03:16:18</t>
-  </si>
-  <si>
-    <t>00:48:25</t>
-  </si>
-  <si>
-    <t>02:24:43</t>
-  </si>
-  <si>
-    <t>23:55:34</t>
-  </si>
-  <si>
-    <t>01:32:43</t>
-  </si>
-  <si>
-    <t>06:25:21</t>
-  </si>
-  <si>
-    <t>23:01:55</t>
-  </si>
-  <si>
-    <t>00:40:27</t>
-  </si>
-  <si>
-    <t>23:47:58</t>
-  </si>
-  <si>
-    <t>02:42:48</t>
-  </si>
-  <si>
-    <t>04:19:31</t>
-  </si>
-  <si>
-    <t>01:50:26</t>
-  </si>
-  <si>
-    <t>03:27:26</t>
-  </si>
-  <si>
-    <t>00:57:49</t>
-  </si>
-  <si>
-    <t>02:35:16</t>
-  </si>
-  <si>
-    <t>01:42:59</t>
-  </si>
-  <si>
-    <t>03:19:34</t>
-  </si>
-  <si>
-    <t>00:50:33</t>
-  </si>
-  <si>
-    <t>02:27:19</t>
-  </si>
-  <si>
-    <t>23:57:54</t>
-  </si>
-  <si>
-    <t>01:35:00</t>
-  </si>
-  <si>
-    <t>06:28:59</t>
-  </si>
-  <si>
-    <t>23:04:59</t>
-  </si>
-  <si>
-    <t>00:42:36</t>
-  </si>
-  <si>
-    <t>23:50:03</t>
+    <t>01:40:12</t>
+  </si>
+  <si>
+    <t>03:17:17</t>
+  </si>
+  <si>
+    <t>00:48:27</t>
+  </si>
+  <si>
+    <t>02:24:40</t>
+  </si>
+  <si>
+    <t>01:32:09</t>
+  </si>
+  <si>
+    <t>03:10:26</t>
+  </si>
+  <si>
+    <t>00:39:45</t>
+  </si>
+  <si>
+    <t>02:17:21</t>
+  </si>
+  <si>
+    <t>23:47:31</t>
+  </si>
+  <si>
+    <t>01:24:19</t>
+  </si>
+  <si>
+    <t>06:19:42</t>
+  </si>
+  <si>
+    <t>22:55:31</t>
+  </si>
+  <si>
+    <t>00:31:23</t>
+  </si>
+  <si>
+    <t>23:38:33</t>
+  </si>
+  <si>
+    <t>01:16:36</t>
+  </si>
+  <si>
+    <t>06:10:53</t>
+  </si>
+  <si>
+    <t>22:45:52</t>
+  </si>
+  <si>
+    <t>01:42:26</t>
+  </si>
+  <si>
+    <t>03:19:37</t>
+  </si>
+  <si>
+    <t>00:51:10</t>
+  </si>
+  <si>
+    <t>02:26:49</t>
+  </si>
+  <si>
+    <t>01:34:13</t>
+  </si>
+  <si>
+    <t>03:13:40</t>
+  </si>
+  <si>
+    <t>00:41:52</t>
+  </si>
+  <si>
+    <t>02:19:55</t>
+  </si>
+  <si>
+    <t>23:49:50</t>
+  </si>
+  <si>
+    <t>01:26:35</t>
+  </si>
+  <si>
+    <t>06:23:23</t>
+  </si>
+  <si>
+    <t>22:58:37</t>
+  </si>
+  <si>
+    <t>00:33:30</t>
+  </si>
+  <si>
+    <t>23:40:38</t>
+  </si>
+  <si>
+    <t>01:19:33</t>
+  </si>
+  <si>
+    <t>06:13:20</t>
+  </si>
+  <si>
+    <t>22:48:02</t>
+  </si>
+  <si>
+    <t>01:45:17</t>
+  </si>
+  <si>
+    <t>03:22:20</t>
+  </si>
+  <si>
+    <t>00:53:05</t>
+  </si>
+  <si>
+    <t>02:29:54</t>
+  </si>
+  <si>
+    <t>01:37:27</t>
+  </si>
+  <si>
+    <t>03:14:54</t>
+  </si>
+  <si>
+    <t>00:44:59</t>
+  </si>
+  <si>
+    <t>02:22:10</t>
+  </si>
+  <si>
+    <t>23:52:29</t>
+  </si>
+  <si>
+    <t>01:29:25</t>
+  </si>
+  <si>
+    <t>06:24:06</t>
+  </si>
+  <si>
+    <t>22:59:55</t>
+  </si>
+  <si>
+    <t>00:36:39</t>
+  </si>
+  <si>
+    <t>23:43:51</t>
+  </si>
+  <si>
+    <t>01:21:10</t>
+  </si>
+  <si>
+    <t>06:15:52</t>
+  </si>
+  <si>
+    <t>22:51:01</t>
+  </si>
+  <si>
+    <t>01:48:10</t>
+  </si>
+  <si>
+    <t>03:25:03</t>
+  </si>
+  <si>
+    <t>00:55:02</t>
+  </si>
+  <si>
+    <t>02:33:01</t>
+  </si>
+  <si>
+    <t>01:40:44</t>
+  </si>
+  <si>
+    <t>03:16:09</t>
+  </si>
+  <si>
+    <t>00:48:08</t>
+  </si>
+  <si>
+    <t>02:24:26</t>
+  </si>
+  <si>
+    <t>23:55:08</t>
+  </si>
+  <si>
+    <t>01:32:16</t>
+  </si>
+  <si>
+    <t>06:24:48</t>
+  </si>
+  <si>
+    <t>23:01:14</t>
+  </si>
+  <si>
+    <t>00:39:49</t>
+  </si>
+  <si>
+    <t>23:47:05</t>
+  </si>
+  <si>
+    <t>01:22:49</t>
+  </si>
+  <si>
+    <t>06:18:25</t>
+  </si>
+  <si>
+    <t>22:54:02</t>
+  </si>
+  <si>
+    <t>01:50:25</t>
+  </si>
+  <si>
+    <t>03:27:25</t>
+  </si>
+  <si>
+    <t>00:57:45</t>
+  </si>
+  <si>
+    <t>02:35:12</t>
+  </si>
+  <si>
+    <t>01:42:50</t>
+  </si>
+  <si>
+    <t>03:19:24</t>
+  </si>
+  <si>
+    <t>00:50:16</t>
+  </si>
+  <si>
+    <t>02:27:02</t>
+  </si>
+  <si>
+    <t>23:57:28</t>
+  </si>
+  <si>
+    <t>01:34:34</t>
+  </si>
+  <si>
+    <t>06:28:29</t>
+  </si>
+  <si>
+    <t>23:04:21</t>
+  </si>
+  <si>
+    <t>00:41:57</t>
+  </si>
+  <si>
+    <t>23:49:11</t>
+  </si>
+  <si>
+    <t>01:25:47</t>
+  </si>
+  <si>
+    <t>06:20:51</t>
+  </si>
+  <si>
+    <t>22:56:13</t>
   </si>
   <si>
     <t>0°</t>
@@ -415,10 +436,13 @@
     <t>1°</t>
   </si>
   <si>
-    <t>04:19:23</t>
-  </si>
-  <si>
-    <t>06:20:31</t>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>06:20:03</t>
+  </si>
+  <si>
+    <t>06:12:22</t>
   </si>
   <si>
     <t>B</t>
@@ -431,6 +455,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -464,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,7 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -497,7 +554,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,61 +572,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +584,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -673,15 +682,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1085,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1163,55 +1163,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-63.5</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O2" s="6">
+        <v>85</v>
+      </c>
+      <c r="P2" s="7">
         <v>83</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-55.8</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O2" s="6">
-        <v>100</v>
-      </c>
-      <c r="P2" s="7">
-        <v>29</v>
-      </c>
       <c r="Q2" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R2" s="9">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1219,55 +1219,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="L3" s="4">
-        <v>-36.7</v>
+        <v>-47.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="O3" s="6">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P3" s="10">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="8">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R3" s="11">
-        <v>87</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1275,55 +1275,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L4" s="4">
-        <v>-63.5</v>
+        <v>-66.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O4" s="6">
-        <v>64</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
-        <v>42</v>
+        <v>145</v>
+      </c>
+      <c r="O4" s="12">
+        <v>9</v>
+      </c>
+      <c r="P4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>9</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1331,55 +1331,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" s="4">
-        <v>-47.7</v>
+        <v>-57.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O5" s="6">
-        <v>80</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>21</v>
-      </c>
-      <c r="R5" s="14">
-        <v>51</v>
+        <v>145</v>
+      </c>
+      <c r="O5" s="15">
+        <v>34</v>
+      </c>
+      <c r="P5" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>34</v>
+      </c>
+      <c r="R5" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1387,55 +1387,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L6" s="4">
-        <v>-66.7</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O6" s="15">
-        <v>5</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>5</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="O6" s="6">
+        <v>88</v>
+      </c>
+      <c r="P6" s="16">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>12</v>
+      </c>
+      <c r="R6" s="14">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1443,54 +1443,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L7" s="4">
-        <v>-57.5</v>
+        <v>-49.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O7" s="15">
-        <v>5</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>5</v>
-      </c>
-      <c r="R7" s="8">
+        <v>146</v>
+      </c>
+      <c r="O7" s="6">
+        <v>66</v>
+      </c>
+      <c r="P7" s="17">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>14</v>
+      </c>
+      <c r="R7" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1499,54 +1499,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L8" s="4">
-        <v>-64.90000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="O8" s="6">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="P8" s="17">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
+        <v>64</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1555,54 +1555,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L9" s="4">
-        <v>-49.5</v>
+        <v>-59.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="O9" s="6">
-        <v>67</v>
-      </c>
-      <c r="P9" s="18">
-        <v>65</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+        <v>98</v>
+      </c>
+      <c r="P9" s="19">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1611,54 +1611,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L10" s="4">
-        <v>-67.40000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O10" s="6">
-        <v>94</v>
-      </c>
-      <c r="P10" s="19">
-        <v>57</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+        <v>145</v>
+      </c>
+      <c r="O10" s="12">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1667,54 +1667,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L11" s="4">
-        <v>-59.2</v>
+        <v>-66.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O11" s="6">
-        <v>88</v>
-      </c>
-      <c r="P11" s="14">
-        <v>52</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+        <v>145</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1723,54 +1723,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="L12" s="4">
-        <v>-63.6</v>
+        <v>-9.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O12" s="20">
-        <v>37</v>
-      </c>
-      <c r="P12" s="10">
-        <v>37</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
+        <v>146</v>
+      </c>
+      <c r="O12" s="15">
+        <v>15</v>
+      </c>
+      <c r="P12" s="18">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1779,54 +1779,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L13" s="4">
-        <v>-66.3</v>
+        <v>-55.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O13" s="20">
-        <v>15</v>
-      </c>
-      <c r="P13" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
+        <v>146</v>
+      </c>
+      <c r="O13" s="6">
+        <v>51</v>
+      </c>
+      <c r="P13" s="19">
+        <v>51</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1835,54 +1835,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="L14" s="4">
-        <v>-9.5</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O14" s="20">
-        <v>19</v>
-      </c>
-      <c r="P14" s="13">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
+        <v>145</v>
+      </c>
+      <c r="O14" s="15">
+        <v>17</v>
+      </c>
+      <c r="P14" s="18">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1891,54 +1891,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L15" s="4">
-        <v>-55.6</v>
+        <v>-63.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O15" s="6">
-        <v>53</v>
-      </c>
-      <c r="P15" s="19">
-        <v>53</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
+        <v>145</v>
+      </c>
+      <c r="O15" s="15">
+        <v>8</v>
+      </c>
+      <c r="P15" s="14">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1947,54 +1947,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L16" s="4">
-        <v>-67.90000000000001</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O16" s="6">
-        <v>47</v>
-      </c>
-      <c r="P16" s="22">
-        <v>47</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
+        <v>146</v>
+      </c>
+      <c r="O16" s="15">
+        <v>3</v>
+      </c>
+      <c r="P16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2003,114 +2003,170 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="L17" s="4">
-        <v>-63.2</v>
+        <v>-11.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N17" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O17" s="6">
+        <v>68</v>
+      </c>
+      <c r="P17" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="O17" s="20">
-        <v>5</v>
-      </c>
-      <c r="P17" s="16">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
+      <c r="J18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-54.4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" s="6">
+        <v>52</v>
+      </c>
+      <c r="P18" s="19">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2129,12 +2185,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2151,22 +2207,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="166">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261005--01</t>
-  </si>
-  <si>
-    <t>20261005--02</t>
-  </si>
-  <si>
     <t>20261006--01</t>
   </si>
   <si>
@@ -121,22 +115,28 @@
     <t>20261011--03</t>
   </si>
   <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>05:26</t>
+    <t>20261012--01</t>
+  </si>
+  <si>
+    <t>20261012--02</t>
+  </si>
+  <si>
+    <t>20261012--03</t>
+  </si>
+  <si>
+    <t>20261012--04</t>
   </si>
   <si>
     <t>03:52</t>
   </si>
   <si>
-    <t>06:12</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>02:29</t>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>02:28</t>
   </si>
   <si>
     <t>06:16</t>
@@ -151,85 +151,100 @@
     <t>05:41</t>
   </si>
   <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>02:37</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>03:16</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>06:00</t>
+    <t>01:27</t>
+  </si>
+  <si>
+    <t>02:38</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>06:28</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>03:26</t>
+  </si>
+  <si>
+    <t>04:39</t>
+  </si>
+  <si>
+    <t>05:56</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:40:12</t>
-  </si>
-  <si>
-    <t>03:17:17</t>
-  </si>
-  <si>
-    <t>00:48:27</t>
-  </si>
-  <si>
-    <t>02:24:40</t>
-  </si>
-  <si>
-    <t>01:32:09</t>
-  </si>
-  <si>
-    <t>03:10:26</t>
-  </si>
-  <si>
-    <t>00:39:45</t>
-  </si>
-  <si>
-    <t>02:17:21</t>
-  </si>
-  <si>
-    <t>23:47:31</t>
-  </si>
-  <si>
-    <t>01:24:19</t>
-  </si>
-  <si>
-    <t>06:19:42</t>
-  </si>
-  <si>
-    <t>22:55:31</t>
-  </si>
-  <si>
-    <t>00:31:23</t>
-  </si>
-  <si>
-    <t>23:38:33</t>
-  </si>
-  <si>
-    <t>01:16:36</t>
-  </si>
-  <si>
-    <t>06:10:53</t>
-  </si>
-  <si>
-    <t>22:45:52</t>
-  </si>
-  <si>
-    <t>01:42:26</t>
-  </si>
-  <si>
-    <t>03:19:37</t>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>00:48:28</t>
+  </si>
+  <si>
+    <t>02:24:41</t>
+  </si>
+  <si>
+    <t>01:32:11</t>
+  </si>
+  <si>
+    <t>03:10:28</t>
+  </si>
+  <si>
+    <t>00:39:49</t>
+  </si>
+  <si>
+    <t>02:17:25</t>
+  </si>
+  <si>
+    <t>23:47:37</t>
+  </si>
+  <si>
+    <t>01:24:26</t>
+  </si>
+  <si>
+    <t>06:19:49</t>
+  </si>
+  <si>
+    <t>22:55:40</t>
+  </si>
+  <si>
+    <t>00:31:33</t>
+  </si>
+  <si>
+    <t>23:38:47</t>
+  </si>
+  <si>
+    <t>01:16:50</t>
+  </si>
+  <si>
+    <t>06:11:08</t>
+  </si>
+  <si>
+    <t>22:46:10</t>
+  </si>
+  <si>
+    <t>00:23:29</t>
+  </si>
+  <si>
+    <t>05:18:28</t>
+  </si>
+  <si>
+    <t>21:53:45</t>
+  </si>
+  <si>
+    <t>23:30:14</t>
   </si>
   <si>
     <t>00:51:10</t>
@@ -238,196 +253,226 @@
     <t>02:26:49</t>
   </si>
   <si>
-    <t>01:34:13</t>
-  </si>
-  <si>
-    <t>03:13:40</t>
-  </si>
-  <si>
-    <t>00:41:52</t>
-  </si>
-  <si>
-    <t>02:19:55</t>
-  </si>
-  <si>
-    <t>23:49:50</t>
-  </si>
-  <si>
-    <t>01:26:35</t>
-  </si>
-  <si>
-    <t>06:23:23</t>
-  </si>
-  <si>
-    <t>22:58:37</t>
-  </si>
-  <si>
-    <t>00:33:30</t>
-  </si>
-  <si>
-    <t>23:40:38</t>
-  </si>
-  <si>
-    <t>01:19:33</t>
-  </si>
-  <si>
-    <t>06:13:20</t>
-  </si>
-  <si>
-    <t>22:48:02</t>
-  </si>
-  <si>
-    <t>01:45:17</t>
-  </si>
-  <si>
-    <t>03:22:20</t>
-  </si>
-  <si>
-    <t>00:53:05</t>
-  </si>
-  <si>
-    <t>02:29:54</t>
-  </si>
-  <si>
-    <t>01:37:27</t>
-  </si>
-  <si>
-    <t>03:14:54</t>
-  </si>
-  <si>
-    <t>00:44:59</t>
-  </si>
-  <si>
-    <t>02:22:10</t>
-  </si>
-  <si>
-    <t>23:52:29</t>
-  </si>
-  <si>
-    <t>01:29:25</t>
-  </si>
-  <si>
-    <t>06:24:06</t>
-  </si>
-  <si>
-    <t>22:59:55</t>
-  </si>
-  <si>
-    <t>00:36:39</t>
-  </si>
-  <si>
-    <t>23:43:51</t>
-  </si>
-  <si>
-    <t>01:21:10</t>
-  </si>
-  <si>
-    <t>06:15:52</t>
-  </si>
-  <si>
-    <t>22:51:01</t>
-  </si>
-  <si>
-    <t>01:48:10</t>
-  </si>
-  <si>
-    <t>03:25:03</t>
+    <t>01:34:15</t>
+  </si>
+  <si>
+    <t>03:13:42</t>
+  </si>
+  <si>
+    <t>00:41:55</t>
+  </si>
+  <si>
+    <t>02:19:59</t>
+  </si>
+  <si>
+    <t>23:49:56</t>
+  </si>
+  <si>
+    <t>01:26:41</t>
+  </si>
+  <si>
+    <t>06:23:29</t>
+  </si>
+  <si>
+    <t>22:58:46</t>
+  </si>
+  <si>
+    <t>00:33:39</t>
+  </si>
+  <si>
+    <t>23:40:51</t>
+  </si>
+  <si>
+    <t>01:19:47</t>
+  </si>
+  <si>
+    <t>06:13:34</t>
+  </si>
+  <si>
+    <t>22:48:19</t>
+  </si>
+  <si>
+    <t>00:25:56</t>
+  </si>
+  <si>
+    <t>05:21:23</t>
+  </si>
+  <si>
+    <t>21:56:13</t>
+  </si>
+  <si>
+    <t>23:32:26</t>
+  </si>
+  <si>
+    <t>00:53:06</t>
+  </si>
+  <si>
+    <t>02:29:55</t>
+  </si>
+  <si>
+    <t>01:37:29</t>
+  </si>
+  <si>
+    <t>03:14:56</t>
+  </si>
+  <si>
+    <t>00:45:03</t>
+  </si>
+  <si>
+    <t>02:22:14</t>
+  </si>
+  <si>
+    <t>23:52:35</t>
+  </si>
+  <si>
+    <t>01:29:31</t>
+  </si>
+  <si>
+    <t>06:24:13</t>
+  </si>
+  <si>
+    <t>23:00:05</t>
+  </si>
+  <si>
+    <t>00:36:48</t>
+  </si>
+  <si>
+    <t>23:44:04</t>
+  </si>
+  <si>
+    <t>01:21:24</t>
+  </si>
+  <si>
+    <t>06:16:07</t>
+  </si>
+  <si>
+    <t>22:51:19</t>
+  </si>
+  <si>
+    <t>00:28:24</t>
+  </si>
+  <si>
+    <t>05:23:06</t>
+  </si>
+  <si>
+    <t>21:58:32</t>
+  </si>
+  <si>
+    <t>23:35:23</t>
   </si>
   <si>
     <t>00:55:02</t>
   </si>
   <si>
-    <t>02:33:01</t>
-  </si>
-  <si>
-    <t>01:40:44</t>
-  </si>
-  <si>
-    <t>03:16:09</t>
-  </si>
-  <si>
-    <t>00:48:08</t>
-  </si>
-  <si>
-    <t>02:24:26</t>
-  </si>
-  <si>
-    <t>23:55:08</t>
-  </si>
-  <si>
-    <t>01:32:16</t>
-  </si>
-  <si>
-    <t>06:24:48</t>
-  </si>
-  <si>
-    <t>23:01:14</t>
-  </si>
-  <si>
-    <t>00:39:49</t>
-  </si>
-  <si>
-    <t>23:47:05</t>
-  </si>
-  <si>
-    <t>01:22:49</t>
-  </si>
-  <si>
-    <t>06:18:25</t>
-  </si>
-  <si>
-    <t>22:54:02</t>
-  </si>
-  <si>
-    <t>01:50:25</t>
-  </si>
-  <si>
-    <t>03:27:25</t>
-  </si>
-  <si>
-    <t>00:57:45</t>
-  </si>
-  <si>
-    <t>02:35:12</t>
-  </si>
-  <si>
-    <t>01:42:50</t>
-  </si>
-  <si>
-    <t>03:19:24</t>
-  </si>
-  <si>
-    <t>00:50:16</t>
-  </si>
-  <si>
-    <t>02:27:02</t>
-  </si>
-  <si>
-    <t>23:57:28</t>
-  </si>
-  <si>
-    <t>01:34:34</t>
-  </si>
-  <si>
-    <t>06:28:29</t>
-  </si>
-  <si>
-    <t>23:04:21</t>
-  </si>
-  <si>
-    <t>00:41:57</t>
-  </si>
-  <si>
-    <t>23:49:11</t>
-  </si>
-  <si>
-    <t>01:25:47</t>
-  </si>
-  <si>
-    <t>06:20:51</t>
-  </si>
-  <si>
-    <t>22:56:13</t>
+    <t>02:33:02</t>
+  </si>
+  <si>
+    <t>01:40:45</t>
+  </si>
+  <si>
+    <t>03:16:10</t>
+  </si>
+  <si>
+    <t>00:48:11</t>
+  </si>
+  <si>
+    <t>02:24:30</t>
+  </si>
+  <si>
+    <t>23:55:14</t>
+  </si>
+  <si>
+    <t>01:32:22</t>
+  </si>
+  <si>
+    <t>06:24:56</t>
+  </si>
+  <si>
+    <t>23:01:24</t>
+  </si>
+  <si>
+    <t>00:39:59</t>
+  </si>
+  <si>
+    <t>23:47:19</t>
+  </si>
+  <si>
+    <t>01:23:02</t>
+  </si>
+  <si>
+    <t>06:18:40</t>
+  </si>
+  <si>
+    <t>22:54:20</t>
+  </si>
+  <si>
+    <t>00:30:53</t>
+  </si>
+  <si>
+    <t>05:24:49</t>
+  </si>
+  <si>
+    <t>22:00:52</t>
+  </si>
+  <si>
+    <t>23:38:22</t>
+  </si>
+  <si>
+    <t>00:57:46</t>
+  </si>
+  <si>
+    <t>02:35:13</t>
+  </si>
+  <si>
+    <t>01:42:51</t>
+  </si>
+  <si>
+    <t>03:19:26</t>
+  </si>
+  <si>
+    <t>00:50:19</t>
+  </si>
+  <si>
+    <t>02:27:06</t>
+  </si>
+  <si>
+    <t>23:57:34</t>
+  </si>
+  <si>
+    <t>01:34:40</t>
+  </si>
+  <si>
+    <t>06:28:36</t>
+  </si>
+  <si>
+    <t>23:04:30</t>
+  </si>
+  <si>
+    <t>00:42:07</t>
+  </si>
+  <si>
+    <t>23:49:24</t>
+  </si>
+  <si>
+    <t>01:26:00</t>
+  </si>
+  <si>
+    <t>06:21:06</t>
+  </si>
+  <si>
+    <t>22:56:30</t>
+  </si>
+  <si>
+    <t>00:33:21</t>
+  </si>
+  <si>
+    <t>05:27:44</t>
+  </si>
+  <si>
+    <t>22:03:22</t>
+  </si>
+  <si>
+    <t>23:40:35</t>
   </si>
   <si>
     <t>0°</t>
@@ -439,16 +484,25 @@
     <t>6°</t>
   </si>
   <si>
-    <t>06:20:03</t>
-  </si>
-  <si>
-    <t>06:12:22</t>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>06:20:10</t>
+  </si>
+  <si>
+    <t>06:12:36</t>
+  </si>
+  <si>
+    <t>05:22:30</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>3</t>
@@ -506,13 +560,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +578,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,31 +602,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,13 +620,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1085,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1163,55 +1217,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L2" s="4">
-        <v>-63.5</v>
+        <v>-66.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="O2" s="6">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="P2" s="7">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="8">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="R2" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1219,55 +1273,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L3" s="4">
-        <v>-47.8</v>
+        <v>-57.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O3" s="6">
-        <v>99</v>
-      </c>
-      <c r="P3" s="10">
-        <v>76</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>18</v>
-      </c>
-      <c r="R3" s="11">
-        <v>42</v>
+        <v>163</v>
+      </c>
+      <c r="O3" s="10">
+        <v>59</v>
+      </c>
+      <c r="P3" s="11">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>40</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1275,55 +1329,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4">
-        <v>-66.7</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O4" s="12">
-        <v>9</v>
+        <v>163</v>
+      </c>
+      <c r="O4" s="10">
+        <v>73</v>
       </c>
       <c r="P4" s="13">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="14">
-        <v>9</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1331,54 +1385,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L5" s="4">
-        <v>-57.5</v>
+        <v>-49.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O5" s="15">
-        <v>34</v>
+        <v>164</v>
+      </c>
+      <c r="O5" s="10">
+        <v>72</v>
       </c>
       <c r="P5" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="16">
-        <v>34</v>
-      </c>
-      <c r="R5" s="13">
+        <v>69</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>17</v>
+      </c>
+      <c r="R5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1387,55 +1441,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L6" s="4">
-        <v>-64.90000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O6" s="6">
-        <v>88</v>
-      </c>
-      <c r="P6" s="16">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>12</v>
-      </c>
-      <c r="R6" s="14">
-        <v>12</v>
+        <v>163</v>
+      </c>
+      <c r="O6" s="10">
+        <v>98</v>
+      </c>
+      <c r="P6" s="15">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1443,55 +1497,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L7" s="4">
-        <v>-49.6</v>
+        <v>-59.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O7" s="6">
-        <v>66</v>
-      </c>
-      <c r="P7" s="17">
-        <v>65</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>14</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O7" s="10">
+        <v>82</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1499,54 +1553,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L8" s="4">
-        <v>-67.40000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O8" s="6">
-        <v>98</v>
-      </c>
-      <c r="P8" s="17">
-        <v>64</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
+        <v>163</v>
+      </c>
+      <c r="O8" s="10">
+        <v>56</v>
+      </c>
+      <c r="P8" s="11">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1555,54 +1609,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L9" s="4">
-        <v>-59.3</v>
+        <v>-66.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O9" s="6">
-        <v>98</v>
-      </c>
-      <c r="P9" s="19">
-        <v>52</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>0</v>
-      </c>
-      <c r="R9" s="13">
+        <v>163</v>
+      </c>
+      <c r="O9" s="16">
+        <v>3</v>
+      </c>
+      <c r="P9" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1611,54 +1665,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="L10" s="4">
-        <v>-63.6</v>
+        <v>-9.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O10" s="12">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
+        <v>164</v>
+      </c>
+      <c r="O10" s="16">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1667,54 +1721,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L11" s="4">
-        <v>-66.3</v>
+        <v>-55.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O11" s="12">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
+        <v>164</v>
+      </c>
+      <c r="O11" s="6">
+        <v>6</v>
+      </c>
+      <c r="P11" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1723,54 +1777,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="L12" s="4">
-        <v>-9.6</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O12" s="15">
-        <v>15</v>
-      </c>
-      <c r="P12" s="18">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
+        <v>163</v>
+      </c>
+      <c r="O12" s="16">
+        <v>7</v>
+      </c>
+      <c r="P12" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1779,55 +1833,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L13" s="4">
-        <v>-55.5</v>
+        <v>-63.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O13" s="6">
-        <v>51</v>
-      </c>
-      <c r="P13" s="19">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O13" s="10">
+        <v>59</v>
+      </c>
+      <c r="P13" s="17">
+        <v>50</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1835,54 +1889,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L14" s="4">
-        <v>-67.90000000000001</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O14" s="15">
-        <v>17</v>
+        <v>164</v>
+      </c>
+      <c r="O14" s="10">
+        <v>31</v>
       </c>
       <c r="P14" s="18">
-        <v>16</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>0</v>
-      </c>
-      <c r="R14" s="13">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1891,55 +1945,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="L15" s="4">
-        <v>-63.1</v>
+        <v>-11.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O15" s="15">
-        <v>8</v>
-      </c>
-      <c r="P15" s="14">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O15" s="10">
+        <v>74</v>
+      </c>
+      <c r="P15" s="17">
+        <v>49</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="17">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1947,54 +2001,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L16" s="4">
-        <v>-67.59999999999999</v>
+        <v>-54.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O16" s="15">
-        <v>3</v>
-      </c>
-      <c r="P16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
+        <v>163</v>
+      </c>
+      <c r="O16" s="6">
+        <v>29</v>
+      </c>
+      <c r="P16" s="18">
+        <v>28</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2006,51 +2060,51 @@
         <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="L17" s="4">
-        <v>-11.6</v>
+        <v>-68.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O17" s="6">
-        <v>68</v>
-      </c>
-      <c r="P17" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>0</v>
-      </c>
-      <c r="R17" s="13">
+        <v>28</v>
+      </c>
+      <c r="P17" s="18">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2059,114 +2113,226 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-23.2</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="O18" s="10">
+        <v>49</v>
+      </c>
+      <c r="P18" s="17">
+        <v>49</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>0</v>
+      </c>
+      <c r="R18" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-44.1</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O19" s="6">
+        <v>27</v>
+      </c>
+      <c r="P19" s="7">
+        <v>22</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>0</v>
+      </c>
+      <c r="R19" s="19">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-54.4</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O18" s="6">
-        <v>52</v>
-      </c>
-      <c r="P18" s="19">
-        <v>50</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>0</v>
+      <c r="B20" s="2">
+        <v>33</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-62.5</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O20" s="6">
+        <v>24</v>
+      </c>
+      <c r="P20" s="7">
+        <v>18</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>0</v>
+      </c>
+      <c r="R20" s="19">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2185,12 +2351,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2207,22 +2373,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="168">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261006--01</t>
-  </si>
-  <si>
-    <t>20261006--02</t>
-  </si>
-  <si>
     <t>20261007--01</t>
   </si>
   <si>
@@ -127,40 +121,40 @@
     <t>20261012--04</t>
   </si>
   <si>
-    <t>03:52</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>02:28</t>
-  </si>
-  <si>
-    <t>06:16</t>
+    <t>20261013--01</t>
+  </si>
+  <si>
+    <t>20261013--02</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>02:29</t>
+  </si>
+  <si>
+    <t>06:15</t>
   </si>
   <si>
     <t>04:31</t>
   </si>
   <si>
-    <t>05:18</t>
+    <t>05:17</t>
   </si>
   <si>
     <t>05:41</t>
   </si>
   <si>
-    <t>01:27</t>
+    <t>01:29</t>
   </si>
   <si>
     <t>02:38</t>
   </si>
   <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>06:28</t>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:27</t>
   </si>
   <si>
     <t>03:15</t>
@@ -175,25 +169,25 @@
     <t>04:57</t>
   </si>
   <si>
-    <t>03:26</t>
-  </si>
-  <si>
-    <t>04:39</t>
+    <t>03:27</t>
+  </si>
+  <si>
+    <t>04:40</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
+    <t>06:24</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:19</t>
-  </si>
-  <si>
-    <t>00:48:28</t>
-  </si>
-  <si>
-    <t>02:24:41</t>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>05:38</t>
   </si>
   <si>
     <t>01:32:11</t>
@@ -202,55 +196,55 @@
     <t>03:10:28</t>
   </si>
   <si>
-    <t>00:39:49</t>
-  </si>
-  <si>
-    <t>02:17:25</t>
-  </si>
-  <si>
-    <t>23:47:37</t>
-  </si>
-  <si>
-    <t>01:24:26</t>
-  </si>
-  <si>
-    <t>06:19:49</t>
-  </si>
-  <si>
-    <t>22:55:40</t>
-  </si>
-  <si>
-    <t>00:31:33</t>
-  </si>
-  <si>
-    <t>23:38:47</t>
-  </si>
-  <si>
-    <t>01:16:50</t>
-  </si>
-  <si>
-    <t>06:11:08</t>
-  </si>
-  <si>
-    <t>22:46:10</t>
-  </si>
-  <si>
-    <t>00:23:29</t>
-  </si>
-  <si>
-    <t>05:18:28</t>
-  </si>
-  <si>
-    <t>21:53:45</t>
-  </si>
-  <si>
-    <t>23:30:14</t>
-  </si>
-  <si>
-    <t>00:51:10</t>
-  </si>
-  <si>
-    <t>02:26:49</t>
+    <t>00:39:50</t>
+  </si>
+  <si>
+    <t>02:17:26</t>
+  </si>
+  <si>
+    <t>23:47:39</t>
+  </si>
+  <si>
+    <t>01:24:28</t>
+  </si>
+  <si>
+    <t>06:19:51</t>
+  </si>
+  <si>
+    <t>22:55:44</t>
+  </si>
+  <si>
+    <t>00:31:36</t>
+  </si>
+  <si>
+    <t>23:38:52</t>
+  </si>
+  <si>
+    <t>01:16:56</t>
+  </si>
+  <si>
+    <t>06:11:14</t>
+  </si>
+  <si>
+    <t>22:46:18</t>
+  </si>
+  <si>
+    <t>00:23:38</t>
+  </si>
+  <si>
+    <t>05:18:36</t>
+  </si>
+  <si>
+    <t>21:53:55</t>
+  </si>
+  <si>
+    <t>23:30:25</t>
+  </si>
+  <si>
+    <t>06:02:21</t>
+  </si>
+  <si>
+    <t>22:37:19</t>
   </si>
   <si>
     <t>01:34:15</t>
@@ -259,55 +253,55 @@
     <t>03:13:42</t>
   </si>
   <si>
-    <t>00:41:55</t>
-  </si>
-  <si>
-    <t>02:19:59</t>
-  </si>
-  <si>
-    <t>23:49:56</t>
-  </si>
-  <si>
-    <t>01:26:41</t>
-  </si>
-  <si>
-    <t>06:23:29</t>
-  </si>
-  <si>
-    <t>22:58:46</t>
-  </si>
-  <si>
-    <t>00:33:39</t>
-  </si>
-  <si>
-    <t>23:40:51</t>
-  </si>
-  <si>
-    <t>01:19:47</t>
-  </si>
-  <si>
-    <t>06:13:34</t>
-  </si>
-  <si>
-    <t>22:48:19</t>
-  </si>
-  <si>
-    <t>00:25:56</t>
-  </si>
-  <si>
-    <t>05:21:23</t>
-  </si>
-  <si>
-    <t>21:56:13</t>
-  </si>
-  <si>
-    <t>23:32:26</t>
-  </si>
-  <si>
-    <t>00:53:06</t>
-  </si>
-  <si>
-    <t>02:29:55</t>
+    <t>00:41:57</t>
+  </si>
+  <si>
+    <t>02:20:00</t>
+  </si>
+  <si>
+    <t>23:49:59</t>
+  </si>
+  <si>
+    <t>01:26:44</t>
+  </si>
+  <si>
+    <t>06:23:31</t>
+  </si>
+  <si>
+    <t>22:58:49</t>
+  </si>
+  <si>
+    <t>00:33:43</t>
+  </si>
+  <si>
+    <t>23:40:57</t>
+  </si>
+  <si>
+    <t>01:19:53</t>
+  </si>
+  <si>
+    <t>06:13:40</t>
+  </si>
+  <si>
+    <t>22:48:27</t>
+  </si>
+  <si>
+    <t>00:26:04</t>
+  </si>
+  <si>
+    <t>05:21:31</t>
+  </si>
+  <si>
+    <t>21:56:23</t>
+  </si>
+  <si>
+    <t>23:32:36</t>
+  </si>
+  <si>
+    <t>06:04:29</t>
+  </si>
+  <si>
+    <t>22:39:24</t>
   </si>
   <si>
     <t>01:37:29</t>
@@ -316,163 +310,169 @@
     <t>03:14:56</t>
   </si>
   <si>
-    <t>00:45:03</t>
-  </si>
-  <si>
-    <t>02:22:14</t>
-  </si>
-  <si>
-    <t>23:52:35</t>
-  </si>
-  <si>
-    <t>01:29:31</t>
-  </si>
-  <si>
-    <t>06:24:13</t>
-  </si>
-  <si>
-    <t>23:00:05</t>
-  </si>
-  <si>
-    <t>00:36:48</t>
-  </si>
-  <si>
-    <t>23:44:04</t>
-  </si>
-  <si>
-    <t>01:21:24</t>
-  </si>
-  <si>
-    <t>06:16:07</t>
-  </si>
-  <si>
-    <t>22:51:19</t>
-  </si>
-  <si>
-    <t>00:28:24</t>
-  </si>
-  <si>
-    <t>05:23:06</t>
-  </si>
-  <si>
-    <t>21:58:32</t>
-  </si>
-  <si>
-    <t>23:35:23</t>
-  </si>
-  <si>
-    <t>00:55:02</t>
-  </si>
-  <si>
-    <t>02:33:02</t>
-  </si>
-  <si>
-    <t>01:40:45</t>
-  </si>
-  <si>
-    <t>03:16:10</t>
-  </si>
-  <si>
-    <t>00:48:11</t>
-  </si>
-  <si>
-    <t>02:24:30</t>
-  </si>
-  <si>
-    <t>23:55:14</t>
-  </si>
-  <si>
-    <t>01:32:22</t>
-  </si>
-  <si>
-    <t>06:24:56</t>
-  </si>
-  <si>
-    <t>23:01:24</t>
-  </si>
-  <si>
-    <t>00:39:59</t>
-  </si>
-  <si>
-    <t>23:47:19</t>
-  </si>
-  <si>
-    <t>01:23:02</t>
-  </si>
-  <si>
-    <t>06:18:40</t>
-  </si>
-  <si>
-    <t>22:54:20</t>
-  </si>
-  <si>
-    <t>00:30:53</t>
-  </si>
-  <si>
-    <t>05:24:49</t>
-  </si>
-  <si>
-    <t>22:00:52</t>
-  </si>
-  <si>
-    <t>23:38:22</t>
-  </si>
-  <si>
-    <t>00:57:46</t>
-  </si>
-  <si>
-    <t>02:35:13</t>
-  </si>
-  <si>
-    <t>01:42:51</t>
-  </si>
-  <si>
-    <t>03:19:26</t>
-  </si>
-  <si>
-    <t>00:50:19</t>
-  </si>
-  <si>
-    <t>02:27:06</t>
-  </si>
-  <si>
-    <t>23:57:34</t>
-  </si>
-  <si>
-    <t>01:34:40</t>
-  </si>
-  <si>
-    <t>06:28:36</t>
-  </si>
-  <si>
-    <t>23:04:30</t>
-  </si>
-  <si>
-    <t>00:42:07</t>
-  </si>
-  <si>
-    <t>23:49:24</t>
-  </si>
-  <si>
-    <t>01:26:00</t>
-  </si>
-  <si>
-    <t>06:21:06</t>
-  </si>
-  <si>
-    <t>22:56:30</t>
-  </si>
-  <si>
-    <t>00:33:21</t>
-  </si>
-  <si>
-    <t>05:27:44</t>
-  </si>
-  <si>
-    <t>22:03:22</t>
-  </si>
-  <si>
-    <t>23:40:35</t>
+    <t>00:45:04</t>
+  </si>
+  <si>
+    <t>02:22:15</t>
+  </si>
+  <si>
+    <t>23:52:37</t>
+  </si>
+  <si>
+    <t>01:29:34</t>
+  </si>
+  <si>
+    <t>06:24:15</t>
+  </si>
+  <si>
+    <t>23:00:08</t>
+  </si>
+  <si>
+    <t>00:36:52</t>
+  </si>
+  <si>
+    <t>23:44:10</t>
+  </si>
+  <si>
+    <t>01:21:30</t>
+  </si>
+  <si>
+    <t>06:16:13</t>
+  </si>
+  <si>
+    <t>22:51:27</t>
+  </si>
+  <si>
+    <t>00:28:32</t>
+  </si>
+  <si>
+    <t>05:23:15</t>
+  </si>
+  <si>
+    <t>21:58:43</t>
+  </si>
+  <si>
+    <t>23:35:34</t>
+  </si>
+  <si>
+    <t>06:07:41</t>
+  </si>
+  <si>
+    <t>22:42:35</t>
+  </si>
+  <si>
+    <t>01:40:46</t>
+  </si>
+  <si>
+    <t>03:16:11</t>
+  </si>
+  <si>
+    <t>00:48:12</t>
+  </si>
+  <si>
+    <t>02:24:31</t>
+  </si>
+  <si>
+    <t>23:55:16</t>
+  </si>
+  <si>
+    <t>01:32:25</t>
+  </si>
+  <si>
+    <t>06:25:00</t>
+  </si>
+  <si>
+    <t>23:01:27</t>
+  </si>
+  <si>
+    <t>00:40:02</t>
+  </si>
+  <si>
+    <t>23:47:24</t>
+  </si>
+  <si>
+    <t>01:23:08</t>
+  </si>
+  <si>
+    <t>06:18:46</t>
+  </si>
+  <si>
+    <t>22:54:28</t>
+  </si>
+  <si>
+    <t>00:31:01</t>
+  </si>
+  <si>
+    <t>05:24:58</t>
+  </si>
+  <si>
+    <t>22:01:03</t>
+  </si>
+  <si>
+    <t>23:38:32</t>
+  </si>
+  <si>
+    <t>06:10:53</t>
+  </si>
+  <si>
+    <t>22:45:48</t>
+  </si>
+  <si>
+    <t>01:42:52</t>
+  </si>
+  <si>
+    <t>03:19:27</t>
+  </si>
+  <si>
+    <t>00:50:21</t>
+  </si>
+  <si>
+    <t>02:27:07</t>
+  </si>
+  <si>
+    <t>23:57:36</t>
+  </si>
+  <si>
+    <t>01:34:42</t>
+  </si>
+  <si>
+    <t>06:28:39</t>
+  </si>
+  <si>
+    <t>23:04:34</t>
+  </si>
+  <si>
+    <t>00:42:10</t>
+  </si>
+  <si>
+    <t>23:49:30</t>
+  </si>
+  <si>
+    <t>01:26:06</t>
+  </si>
+  <si>
+    <t>06:21:13</t>
+  </si>
+  <si>
+    <t>22:56:38</t>
+  </si>
+  <si>
+    <t>00:33:29</t>
+  </si>
+  <si>
+    <t>05:27:53</t>
+  </si>
+  <si>
+    <t>22:03:32</t>
+  </si>
+  <si>
+    <t>23:40:45</t>
+  </si>
+  <si>
+    <t>06:13:00</t>
+  </si>
+  <si>
+    <t>22:47:55</t>
   </si>
   <si>
     <t>0°</t>
@@ -487,13 +487,19 @@
     <t>13°</t>
   </si>
   <si>
-    <t>06:20:10</t>
-  </si>
-  <si>
-    <t>06:12:36</t>
-  </si>
-  <si>
-    <t>05:22:30</t>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>06:20:12</t>
+  </si>
+  <si>
+    <t>06:12:42</t>
+  </si>
+  <si>
+    <t>05:22:38</t>
+  </si>
+  <si>
+    <t>06:05:15</t>
   </si>
   <si>
     <t>B</t>
@@ -545,7 +551,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -560,13 +566,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,13 +590,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,31 +620,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,7 +638,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -679,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -736,6 +754,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1217,13 +1241,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>58</v>
@@ -1247,25 +1271,25 @@
         <v>58</v>
       </c>
       <c r="L2" s="4">
-        <v>-66.7</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O2" s="6">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="P2" s="7">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1273,13 +1297,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>59</v>
@@ -1303,25 +1327,25 @@
         <v>59</v>
       </c>
       <c r="L3" s="4">
-        <v>-57.5</v>
+        <v>-49.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O3" s="10">
-        <v>59</v>
-      </c>
-      <c r="P3" s="11">
-        <v>53</v>
-      </c>
-      <c r="Q3" s="12">
-        <v>40</v>
+        <v>166</v>
+      </c>
+      <c r="O3" s="6">
+        <v>85</v>
+      </c>
+      <c r="P3" s="7">
+        <v>83</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>3</v>
       </c>
       <c r="R3" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1329,13 +1353,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>60</v>
@@ -1359,25 +1383,25 @@
         <v>60</v>
       </c>
       <c r="L4" s="4">
-        <v>-64.90000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O4" s="10">
-        <v>73</v>
-      </c>
-      <c r="P4" s="13">
-        <v>68</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>16</v>
-      </c>
-      <c r="R4" s="9">
-        <v>2</v>
+        <v>165</v>
+      </c>
+      <c r="O4" s="6">
+        <v>75</v>
+      </c>
+      <c r="P4" s="10">
+        <v>63</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1385,13 +1409,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>61</v>
@@ -1415,25 +1439,25 @@
         <v>61</v>
       </c>
       <c r="L5" s="4">
-        <v>-49.6</v>
+        <v>-59.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O5" s="10">
-        <v>72</v>
-      </c>
-      <c r="P5" s="13">
-        <v>69</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>17</v>
-      </c>
-      <c r="R5" s="9">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O5" s="6">
+        <v>86</v>
+      </c>
+      <c r="P5" s="12">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1441,13 +1465,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>62</v>
@@ -1471,25 +1495,25 @@
         <v>62</v>
       </c>
       <c r="L6" s="4">
-        <v>-67.40000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O6" s="10">
-        <v>98</v>
-      </c>
-      <c r="P6" s="15">
-        <v>63</v>
+        <v>165</v>
+      </c>
+      <c r="O6" s="6">
+        <v>39</v>
+      </c>
+      <c r="P6" s="14">
+        <v>39</v>
       </c>
       <c r="Q6" s="9">
         <v>0</v>
       </c>
-      <c r="R6" s="7">
-        <v>19</v>
+      <c r="R6" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1497,13 +1521,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>63</v>
@@ -1527,25 +1551,25 @@
         <v>63</v>
       </c>
       <c r="L7" s="4">
-        <v>-59.3</v>
+        <v>-66.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O7" s="10">
-        <v>82</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O7" s="15">
+        <v>4</v>
+      </c>
+      <c r="P7" s="8">
+        <v>4</v>
       </c>
       <c r="Q7" s="9">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
-        <v>19</v>
+      <c r="R7" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1553,13 +1577,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>64</v>
@@ -1577,25 +1601,25 @@
         <v>140</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="L8" s="4">
-        <v>-63.6</v>
+        <v>-9.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O8" s="10">
-        <v>56</v>
-      </c>
-      <c r="P8" s="11">
-        <v>56</v>
+        <v>166</v>
+      </c>
+      <c r="O8" s="15">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
       </c>
       <c r="Q8" s="9">
         <v>0</v>
@@ -1609,13 +1633,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>65</v>
@@ -1639,19 +1663,19 @@
         <v>65</v>
       </c>
       <c r="L9" s="4">
-        <v>-66.3</v>
+        <v>-55.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O9" s="16">
-        <v>3</v>
+        <v>166</v>
+      </c>
+      <c r="O9" s="15">
+        <v>8</v>
       </c>
       <c r="P9" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q9" s="9">
         <v>0</v>
@@ -1665,13 +1689,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>66</v>
@@ -1689,22 +1713,22 @@
         <v>142</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="L10" s="4">
-        <v>-9.5</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O10" s="16">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O10" s="15">
+        <v>2</v>
       </c>
       <c r="P10" s="9">
         <v>0</v>
@@ -1721,13 +1745,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>67</v>
@@ -1751,25 +1775,25 @@
         <v>67</v>
       </c>
       <c r="L11" s="4">
-        <v>-55.5</v>
+        <v>-63.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O11" s="6">
-        <v>6</v>
+        <v>165</v>
+      </c>
+      <c r="O11" s="16">
+        <v>5</v>
       </c>
       <c r="P11" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="9">
         <v>0</v>
       </c>
-      <c r="R11" s="9">
-        <v>0</v>
+      <c r="R11" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1777,13 +1801,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>68</v>
@@ -1807,19 +1831,19 @@
         <v>68</v>
       </c>
       <c r="L12" s="4">
-        <v>-67.90000000000001</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O12" s="16">
-        <v>7</v>
-      </c>
-      <c r="P12" s="8">
-        <v>3</v>
+        <v>166</v>
+      </c>
+      <c r="O12" s="6">
+        <v>66</v>
+      </c>
+      <c r="P12" s="11">
+        <v>15</v>
       </c>
       <c r="Q12" s="9">
         <v>0</v>
@@ -1833,13 +1857,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>69</v>
@@ -1857,31 +1881,31 @@
         <v>145</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="L13" s="4">
-        <v>-63.1</v>
+        <v>-11.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O13" s="10">
-        <v>59</v>
+        <v>167</v>
+      </c>
+      <c r="O13" s="16">
+        <v>32</v>
       </c>
       <c r="P13" s="17">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="9">
         <v>0</v>
       </c>
       <c r="R13" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1889,13 +1913,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>70</v>
@@ -1919,25 +1943,25 @@
         <v>70</v>
       </c>
       <c r="L14" s="4">
-        <v>-67.59999999999999</v>
+        <v>-54.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O14" s="10">
-        <v>31</v>
-      </c>
-      <c r="P14" s="18">
-        <v>30</v>
+        <v>165</v>
+      </c>
+      <c r="O14" s="6">
+        <v>95</v>
+      </c>
+      <c r="P14" s="12">
+        <v>61</v>
       </c>
       <c r="Q14" s="9">
         <v>0</v>
       </c>
-      <c r="R14" s="9">
-        <v>0</v>
+      <c r="R14" s="18">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1951,7 +1975,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>71</v>
@@ -1969,31 +1993,31 @@
         <v>147</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="L15" s="4">
-        <v>-11.5</v>
+        <v>-68.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="O15" s="10">
-        <v>74</v>
-      </c>
-      <c r="P15" s="17">
-        <v>49</v>
+      <c r="O15" s="6">
+        <v>95</v>
+      </c>
+      <c r="P15" s="12">
+        <v>61</v>
       </c>
       <c r="Q15" s="9">
         <v>0</v>
       </c>
-      <c r="R15" s="17">
-        <v>50</v>
+      <c r="R15" s="18">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2001,7 +2025,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>51</v>
@@ -2025,31 +2049,31 @@
         <v>148</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="L16" s="4">
-        <v>-54.5</v>
+        <v>-23.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O16" s="6">
-        <v>29</v>
-      </c>
-      <c r="P16" s="18">
-        <v>28</v>
+        <v>92</v>
+      </c>
+      <c r="P16" s="13">
+        <v>23</v>
       </c>
       <c r="Q16" s="9">
         <v>0</v>
       </c>
-      <c r="R16" s="9">
-        <v>0</v>
+      <c r="R16" s="19">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2057,13 +2081,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>73</v>
@@ -2087,25 +2111,25 @@
         <v>73</v>
       </c>
       <c r="L17" s="4">
-        <v>-68.2</v>
+        <v>-44.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O17" s="6">
-        <v>28</v>
-      </c>
-      <c r="P17" s="18">
-        <v>28</v>
+        <v>88</v>
+      </c>
+      <c r="P17" s="7">
+        <v>86</v>
       </c>
       <c r="Q17" s="9">
         <v>0</v>
       </c>
-      <c r="R17" s="9">
-        <v>0</v>
+      <c r="R17" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2113,13 +2137,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>74</v>
@@ -2137,31 +2161,31 @@
         <v>150</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="L18" s="4">
-        <v>-23.2</v>
+        <v>-62.5</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>162</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O18" s="10">
-        <v>49</v>
-      </c>
-      <c r="P18" s="17">
-        <v>49</v>
+        <v>165</v>
+      </c>
+      <c r="O18" s="6">
+        <v>95</v>
+      </c>
+      <c r="P18" s="20">
+        <v>94</v>
       </c>
       <c r="Q18" s="9">
         <v>0</v>
       </c>
-      <c r="R18" s="9">
-        <v>2</v>
+      <c r="R18" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2169,13 +2193,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>75</v>
@@ -2193,31 +2217,31 @@
         <v>151</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="L19" s="4">
-        <v>-44.1</v>
+        <v>-13.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O19" s="6">
-        <v>27</v>
-      </c>
-      <c r="P19" s="7">
-        <v>22</v>
+        <v>95</v>
+      </c>
+      <c r="P19" s="20">
+        <v>94</v>
       </c>
       <c r="Q19" s="9">
         <v>0</v>
       </c>
-      <c r="R19" s="19">
-        <v>27</v>
+      <c r="R19" s="20">
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2225,13 +2249,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>76</v>
@@ -2255,25 +2279,25 @@
         <v>76</v>
       </c>
       <c r="L20" s="4">
-        <v>-62.5</v>
+        <v>-53.4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O20" s="6">
-        <v>24</v>
-      </c>
-      <c r="P20" s="7">
-        <v>18</v>
+        <v>66</v>
+      </c>
+      <c r="P20" s="12">
+        <v>61</v>
       </c>
       <c r="Q20" s="9">
         <v>0</v>
       </c>
-      <c r="R20" s="19">
-        <v>24</v>
+      <c r="R20" s="21">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="185">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261007--01</t>
-  </si>
-  <si>
-    <t>20261007--02</t>
-  </si>
-  <si>
     <t>20261008--01</t>
   </si>
   <si>
@@ -127,13 +121,19 @@
     <t>20261013--02</t>
   </si>
   <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>02:29</t>
-  </si>
-  <si>
-    <t>06:15</t>
+    <t>20261014--01</t>
+  </si>
+  <si>
+    <t>20261014--02</t>
+  </si>
+  <si>
+    <t>20261014--03</t>
+  </si>
+  <si>
+    <t>20261014--04</t>
+  </si>
+  <si>
+    <t>06:16</t>
   </si>
   <si>
     <t>04:31</t>
@@ -145,334 +145,379 @@
     <t>05:41</t>
   </si>
   <si>
-    <t>01:29</t>
-  </si>
-  <si>
-    <t>02:38</t>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:39</t>
   </si>
   <si>
     <t>06:19</t>
   </si>
   <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>03:27</t>
-  </si>
-  <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>05:56</t>
+    <t>06:28</t>
+  </si>
+  <si>
+    <t>03:14</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>03:29</t>
+  </si>
+  <si>
+    <t>04:41</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>06:25</t>
   </si>
   <si>
     <t>06:24</t>
   </si>
   <si>
+    <t>00:17</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
+    <t>02:22</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
     <t>02:20</t>
   </si>
   <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>01:32:11</t>
-  </si>
-  <si>
-    <t>03:10:28</t>
-  </si>
-  <si>
-    <t>00:39:50</t>
-  </si>
-  <si>
-    <t>02:17:26</t>
-  </si>
-  <si>
-    <t>23:47:39</t>
-  </si>
-  <si>
-    <t>01:24:28</t>
-  </si>
-  <si>
-    <t>06:19:51</t>
-  </si>
-  <si>
-    <t>22:55:44</t>
-  </si>
-  <si>
-    <t>00:31:36</t>
-  </si>
-  <si>
-    <t>23:38:52</t>
-  </si>
-  <si>
-    <t>01:16:56</t>
-  </si>
-  <si>
-    <t>06:11:14</t>
-  </si>
-  <si>
-    <t>22:46:18</t>
-  </si>
-  <si>
-    <t>00:23:38</t>
-  </si>
-  <si>
-    <t>05:18:36</t>
-  </si>
-  <si>
-    <t>21:53:55</t>
-  </si>
-  <si>
-    <t>23:30:25</t>
-  </si>
-  <si>
-    <t>06:02:21</t>
-  </si>
-  <si>
-    <t>22:37:19</t>
-  </si>
-  <si>
-    <t>01:34:15</t>
-  </si>
-  <si>
-    <t>03:13:42</t>
+    <t>00:39:51</t>
+  </si>
+  <si>
+    <t>02:17:27</t>
+  </si>
+  <si>
+    <t>23:47:42</t>
+  </si>
+  <si>
+    <t>01:24:31</t>
+  </si>
+  <si>
+    <t>06:19:54</t>
+  </si>
+  <si>
+    <t>22:55:48</t>
+  </si>
+  <si>
+    <t>00:31:41</t>
+  </si>
+  <si>
+    <t>23:39:01</t>
+  </si>
+  <si>
+    <t>01:17:05</t>
+  </si>
+  <si>
+    <t>06:11:23</t>
+  </si>
+  <si>
+    <t>22:46:30</t>
+  </si>
+  <si>
+    <t>00:23:51</t>
+  </si>
+  <si>
+    <t>05:18:50</t>
+  </si>
+  <si>
+    <t>21:54:12</t>
+  </si>
+  <si>
+    <t>23:30:43</t>
+  </si>
+  <si>
+    <t>06:02:40</t>
+  </si>
+  <si>
+    <t>22:37:43</t>
+  </si>
+  <si>
+    <t>00:16:11</t>
+  </si>
+  <si>
+    <t>05:09:56</t>
+  </si>
+  <si>
+    <t>21:44:52</t>
+  </si>
+  <si>
+    <t>23:22:40</t>
   </si>
   <si>
     <t>00:41:57</t>
   </si>
   <si>
-    <t>02:20:00</t>
-  </si>
-  <si>
-    <t>23:49:59</t>
-  </si>
-  <si>
-    <t>01:26:44</t>
-  </si>
-  <si>
-    <t>06:23:31</t>
-  </si>
-  <si>
-    <t>22:58:49</t>
-  </si>
-  <si>
-    <t>00:33:43</t>
-  </si>
-  <si>
-    <t>23:40:57</t>
-  </si>
-  <si>
-    <t>01:19:53</t>
-  </si>
-  <si>
-    <t>06:13:40</t>
-  </si>
-  <si>
-    <t>22:48:27</t>
-  </si>
-  <si>
-    <t>00:26:04</t>
-  </si>
-  <si>
-    <t>05:21:31</t>
-  </si>
-  <si>
-    <t>21:56:23</t>
-  </si>
-  <si>
-    <t>23:32:36</t>
-  </si>
-  <si>
-    <t>06:04:29</t>
-  </si>
-  <si>
-    <t>22:39:24</t>
-  </si>
-  <si>
-    <t>01:37:29</t>
-  </si>
-  <si>
-    <t>03:14:56</t>
-  </si>
-  <si>
-    <t>00:45:04</t>
-  </si>
-  <si>
-    <t>02:22:15</t>
-  </si>
-  <si>
-    <t>23:52:37</t>
-  </si>
-  <si>
-    <t>01:29:34</t>
-  </si>
-  <si>
-    <t>06:24:15</t>
-  </si>
-  <si>
-    <t>23:00:08</t>
-  </si>
-  <si>
-    <t>00:36:52</t>
-  </si>
-  <si>
-    <t>23:44:10</t>
-  </si>
-  <si>
-    <t>01:21:30</t>
-  </si>
-  <si>
-    <t>06:16:13</t>
-  </si>
-  <si>
-    <t>22:51:27</t>
-  </si>
-  <si>
-    <t>00:28:32</t>
-  </si>
-  <si>
-    <t>05:23:15</t>
-  </si>
-  <si>
-    <t>21:58:43</t>
-  </si>
-  <si>
-    <t>23:35:34</t>
-  </si>
-  <si>
-    <t>06:07:41</t>
-  </si>
-  <si>
-    <t>22:42:35</t>
-  </si>
-  <si>
-    <t>01:40:46</t>
-  </si>
-  <si>
-    <t>03:16:11</t>
-  </si>
-  <si>
-    <t>00:48:12</t>
-  </si>
-  <si>
-    <t>02:24:31</t>
-  </si>
-  <si>
-    <t>23:55:16</t>
-  </si>
-  <si>
-    <t>01:32:25</t>
-  </si>
-  <si>
-    <t>06:25:00</t>
-  </si>
-  <si>
-    <t>23:01:27</t>
-  </si>
-  <si>
-    <t>00:40:02</t>
-  </si>
-  <si>
-    <t>23:47:24</t>
-  </si>
-  <si>
-    <t>01:23:08</t>
-  </si>
-  <si>
-    <t>06:18:46</t>
-  </si>
-  <si>
-    <t>22:54:28</t>
-  </si>
-  <si>
-    <t>00:31:01</t>
-  </si>
-  <si>
-    <t>05:24:58</t>
-  </si>
-  <si>
-    <t>22:01:03</t>
-  </si>
-  <si>
-    <t>23:38:32</t>
-  </si>
-  <si>
-    <t>06:10:53</t>
-  </si>
-  <si>
-    <t>22:45:48</t>
-  </si>
-  <si>
-    <t>01:42:52</t>
-  </si>
-  <si>
-    <t>03:19:27</t>
+    <t>02:20:01</t>
+  </si>
+  <si>
+    <t>23:50:01</t>
+  </si>
+  <si>
+    <t>01:26:46</t>
+  </si>
+  <si>
+    <t>06:23:33</t>
+  </si>
+  <si>
+    <t>22:58:54</t>
+  </si>
+  <si>
+    <t>00:33:48</t>
+  </si>
+  <si>
+    <t>23:41:05</t>
+  </si>
+  <si>
+    <t>01:20:02</t>
+  </si>
+  <si>
+    <t>06:13:49</t>
+  </si>
+  <si>
+    <t>22:48:39</t>
+  </si>
+  <si>
+    <t>00:26:17</t>
+  </si>
+  <si>
+    <t>05:21:44</t>
+  </si>
+  <si>
+    <t>21:56:40</t>
+  </si>
+  <si>
+    <t>23:32:55</t>
+  </si>
+  <si>
+    <t>06:04:48</t>
+  </si>
+  <si>
+    <t>22:39:48</t>
+  </si>
+  <si>
+    <t>00:20:29</t>
+  </si>
+  <si>
+    <t>05:12:13</t>
+  </si>
+  <si>
+    <t>21:46:57</t>
+  </si>
+  <si>
+    <t>23:25:24</t>
+  </si>
+  <si>
+    <t>00:45:05</t>
+  </si>
+  <si>
+    <t>02:22:16</t>
+  </si>
+  <si>
+    <t>23:52:39</t>
+  </si>
+  <si>
+    <t>01:29:36</t>
+  </si>
+  <si>
+    <t>06:24:18</t>
+  </si>
+  <si>
+    <t>23:00:13</t>
+  </si>
+  <si>
+    <t>00:36:57</t>
+  </si>
+  <si>
+    <t>23:44:18</t>
+  </si>
+  <si>
+    <t>01:21:39</t>
+  </si>
+  <si>
+    <t>06:16:23</t>
+  </si>
+  <si>
+    <t>22:51:39</t>
+  </si>
+  <si>
+    <t>00:28:45</t>
+  </si>
+  <si>
+    <t>05:23:29</t>
+  </si>
+  <si>
+    <t>21:59:00</t>
+  </si>
+  <si>
+    <t>23:35:52</t>
+  </si>
+  <si>
+    <t>06:08:00</t>
+  </si>
+  <si>
+    <t>22:42:59</t>
+  </si>
+  <si>
+    <t>05:15:06</t>
+  </si>
+  <si>
+    <t>21:50:07</t>
+  </si>
+  <si>
+    <t>23:27:21</t>
+  </si>
+  <si>
+    <t>00:48:13</t>
+  </si>
+  <si>
+    <t>02:24:32</t>
+  </si>
+  <si>
+    <t>23:55:18</t>
+  </si>
+  <si>
+    <t>01:32:27</t>
+  </si>
+  <si>
+    <t>06:25:03</t>
+  </si>
+  <si>
+    <t>23:01:33</t>
+  </si>
+  <si>
+    <t>00:40:07</t>
+  </si>
+  <si>
+    <t>23:47:33</t>
+  </si>
+  <si>
+    <t>01:23:16</t>
+  </si>
+  <si>
+    <t>06:18:56</t>
+  </si>
+  <si>
+    <t>22:54:41</t>
+  </si>
+  <si>
+    <t>00:31:13</t>
+  </si>
+  <si>
+    <t>05:25:13</t>
+  </si>
+  <si>
+    <t>22:01:21</t>
+  </si>
+  <si>
+    <t>23:38:50</t>
+  </si>
+  <si>
+    <t>06:11:13</t>
+  </si>
+  <si>
+    <t>22:46:12</t>
+  </si>
+  <si>
+    <t>00:20:46</t>
+  </si>
+  <si>
+    <t>05:17:59</t>
+  </si>
+  <si>
+    <t>21:53:19</t>
+  </si>
+  <si>
+    <t>23:29:19</t>
   </si>
   <si>
     <t>00:50:21</t>
   </si>
   <si>
-    <t>02:27:07</t>
-  </si>
-  <si>
-    <t>23:57:36</t>
-  </si>
-  <si>
-    <t>01:34:42</t>
-  </si>
-  <si>
-    <t>06:28:39</t>
-  </si>
-  <si>
-    <t>23:04:34</t>
-  </si>
-  <si>
-    <t>00:42:10</t>
-  </si>
-  <si>
-    <t>23:49:30</t>
-  </si>
-  <si>
-    <t>01:26:06</t>
-  </si>
-  <si>
-    <t>06:21:13</t>
-  </si>
-  <si>
-    <t>22:56:38</t>
-  </si>
-  <si>
-    <t>00:33:29</t>
-  </si>
-  <si>
-    <t>05:27:53</t>
-  </si>
-  <si>
-    <t>22:03:32</t>
-  </si>
-  <si>
-    <t>23:40:45</t>
-  </si>
-  <si>
-    <t>06:13:00</t>
-  </si>
-  <si>
-    <t>22:47:55</t>
+    <t>02:27:08</t>
+  </si>
+  <si>
+    <t>23:57:39</t>
+  </si>
+  <si>
+    <t>01:34:45</t>
+  </si>
+  <si>
+    <t>06:28:42</t>
+  </si>
+  <si>
+    <t>23:04:39</t>
+  </si>
+  <si>
+    <t>00:42:15</t>
+  </si>
+  <si>
+    <t>23:49:38</t>
+  </si>
+  <si>
+    <t>01:26:15</t>
+  </si>
+  <si>
+    <t>06:21:23</t>
+  </si>
+  <si>
+    <t>22:56:51</t>
+  </si>
+  <si>
+    <t>00:33:42</t>
+  </si>
+  <si>
+    <t>05:28:07</t>
+  </si>
+  <si>
+    <t>22:03:50</t>
+  </si>
+  <si>
+    <t>23:41:03</t>
+  </si>
+  <si>
+    <t>06:13:20</t>
+  </si>
+  <si>
+    <t>22:48:18</t>
+  </si>
+  <si>
+    <t>00:24:48</t>
+  </si>
+  <si>
+    <t>05:20:15</t>
+  </si>
+  <si>
+    <t>21:55:25</t>
+  </si>
+  <si>
+    <t>23:32:04</t>
   </si>
   <si>
     <t>0°</t>
@@ -490,16 +535,22 @@
     <t>16°</t>
   </si>
   <si>
-    <t>06:20:12</t>
-  </si>
-  <si>
-    <t>06:12:42</t>
-  </si>
-  <si>
-    <t>05:22:38</t>
-  </si>
-  <si>
-    <t>06:05:15</t>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>06:20:15</t>
+  </si>
+  <si>
+    <t>06:12:51</t>
+  </si>
+  <si>
+    <t>05:22:51</t>
+  </si>
+  <si>
+    <t>06:05:34</t>
+  </si>
+  <si>
+    <t>05:15:39</t>
   </si>
   <si>
     <t>B</t>
@@ -551,7 +602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,13 +617,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +635,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,13 +689,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,43 +713,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -760,6 +817,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1163,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1241,55 +1301,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="L2" s="4">
-        <v>-64.90000000000001</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="O2" s="6">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="P2" s="7">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="8">
-        <v>3</v>
-      </c>
-      <c r="R2" s="9">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1297,55 +1357,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L3" s="4">
-        <v>-49.6</v>
+        <v>-59.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="O3" s="6">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="P3" s="7">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="8">
-        <v>3</v>
-      </c>
-      <c r="R3" s="9">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1353,55 +1413,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L4" s="4">
-        <v>-67.40000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O4" s="6">
-        <v>75</v>
+        <v>182</v>
+      </c>
+      <c r="O4" s="9">
+        <v>23</v>
       </c>
       <c r="P4" s="10">
-        <v>63</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="11">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1409,55 +1469,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L5" s="4">
-        <v>-59.3</v>
+        <v>-66.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O5" s="6">
-        <v>86</v>
+        <v>182</v>
+      </c>
+      <c r="O5" s="11">
+        <v>47</v>
       </c>
       <c r="P5" s="12">
-        <v>62</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>26</v>
+        <v>47</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1465,54 +1525,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="L6" s="4">
-        <v>-63.6</v>
+        <v>-9.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O6" s="6">
-        <v>39</v>
-      </c>
-      <c r="P6" s="14">
-        <v>39</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9">
+        <v>183</v>
+      </c>
+      <c r="O6" s="11">
+        <v>43</v>
+      </c>
+      <c r="P6" s="12">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1521,54 +1581,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L7" s="4">
-        <v>-66.3</v>
+        <v>-55.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O7" s="15">
-        <v>4</v>
-      </c>
-      <c r="P7" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
+        <v>183</v>
+      </c>
+      <c r="O7" s="11">
+        <v>49</v>
+      </c>
+      <c r="P7" s="13">
+        <v>49</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1577,54 +1637,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="L8" s="4">
-        <v>-9.5</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O8" s="15">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
+        <v>182</v>
+      </c>
+      <c r="O8" s="11">
+        <v>48</v>
+      </c>
+      <c r="P8" s="13">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1633,54 +1693,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="L9" s="4">
-        <v>-55.5</v>
+        <v>-63.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O9" s="15">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="O9" s="9">
+        <v>36</v>
       </c>
       <c r="P9" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1689,54 +1749,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L10" s="4">
-        <v>-67.90000000000001</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O10" s="15">
-        <v>2</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
+        <v>183</v>
+      </c>
+      <c r="O10" s="11">
+        <v>50</v>
+      </c>
+      <c r="P10" s="12">
+        <v>47</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1745,55 +1805,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="L11" s="4">
-        <v>-63.2</v>
+        <v>-11.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O11" s="16">
-        <v>5</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9">
+        <v>184</v>
+      </c>
+      <c r="O11" s="11">
+        <v>52</v>
+      </c>
+      <c r="P11" s="13">
+        <v>49</v>
+      </c>
+      <c r="Q11" s="8">
         <v>0</v>
       </c>
       <c r="R11" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1801,54 +1861,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L12" s="4">
-        <v>-67.59999999999999</v>
+        <v>-54.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O12" s="6">
-        <v>66</v>
-      </c>
-      <c r="P12" s="11">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
+        <v>182</v>
+      </c>
+      <c r="O12" s="11">
+        <v>79</v>
+      </c>
+      <c r="P12" s="14">
+        <v>67</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1857,54 +1917,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="L13" s="4">
-        <v>-11.5</v>
+        <v>-68.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O13" s="16">
-        <v>32</v>
-      </c>
-      <c r="P13" s="17">
-        <v>32</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
+        <v>182</v>
+      </c>
+      <c r="O13" s="11">
+        <v>85</v>
+      </c>
+      <c r="P13" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1913,55 +1973,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="L14" s="4">
-        <v>-54.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O14" s="6">
-        <v>95</v>
-      </c>
-      <c r="P14" s="12">
-        <v>61</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="18">
-        <v>10</v>
+        <v>183</v>
+      </c>
+      <c r="O14" s="11">
+        <v>85</v>
+      </c>
+      <c r="P14" s="16">
+        <v>59</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1969,55 +2029,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="L15" s="4">
-        <v>-68.2</v>
+        <v>-44.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O15" s="6">
-        <v>95</v>
+        <v>182</v>
+      </c>
+      <c r="O15" s="11">
+        <v>72</v>
       </c>
       <c r="P15" s="12">
-        <v>61</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="18">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2025,55 +2085,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="L16" s="4">
-        <v>-23.2</v>
+        <v>-62.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O16" s="6">
-        <v>92</v>
-      </c>
-      <c r="P16" s="13">
-        <v>23</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>0</v>
-      </c>
-      <c r="R16" s="19">
-        <v>90</v>
+        <v>182</v>
+      </c>
+      <c r="O16" s="11">
+        <v>83</v>
+      </c>
+      <c r="P16" s="18">
+        <v>54</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="10">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2081,55 +2141,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="L17" s="4">
-        <v>-44.2</v>
+        <v>-13.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O17" s="6">
-        <v>88</v>
-      </c>
-      <c r="P17" s="7">
-        <v>86</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <v>4</v>
+        <v>184</v>
+      </c>
+      <c r="O17" s="11">
+        <v>80</v>
+      </c>
+      <c r="P17" s="19">
+        <v>29</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="20">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2137,55 +2197,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-53.4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O18" s="11">
         <v>55</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-62.5</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O18" s="6">
-        <v>95</v>
-      </c>
-      <c r="P18" s="20">
-        <v>94</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
-        <v>3</v>
+      <c r="P18" s="12">
+        <v>46</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="18">
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2193,55 +2253,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="L19" s="4">
-        <v>-13.6</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O19" s="6">
-        <v>95</v>
-      </c>
-      <c r="P19" s="20">
-        <v>94</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>0</v>
-      </c>
-      <c r="R19" s="20">
-        <v>95</v>
+        <v>183</v>
+      </c>
+      <c r="O19" s="11">
+        <v>39</v>
+      </c>
+      <c r="P19" s="19">
+        <v>28</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="21">
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2249,114 +2309,226 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="L20" s="4">
-        <v>-53.4</v>
+        <v>-25.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O20" s="6">
-        <v>66</v>
-      </c>
-      <c r="P20" s="12">
+        <v>184</v>
+      </c>
+      <c r="O20" s="11">
+        <v>57</v>
+      </c>
+      <c r="P20" s="10">
+        <v>24</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="18">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
         <v>61</v>
       </c>
-      <c r="Q20" s="9">
-        <v>0</v>
-      </c>
-      <c r="R20" s="21">
-        <v>33</v>
+      <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-42.9</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O21" s="6">
+        <v>10</v>
+      </c>
+      <c r="P21" s="7">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-61.9</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O22" s="6">
+        <v>8</v>
+      </c>
+      <c r="P22" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="22">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A22">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B22">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C22">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D22">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E22">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F22">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G22">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H22">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I22">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J22">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K22">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L22">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2375,12 +2547,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M22">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N22">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2397,22 +2569,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O22">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P22">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q22">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R22">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="194">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261008--01</t>
-  </si>
-  <si>
-    <t>20261008--02</t>
-  </si>
-  <si>
-    <t>20261008--03</t>
-  </si>
-  <si>
     <t>20261009--01</t>
   </si>
   <si>
@@ -133,13 +124,16 @@
     <t>20261014--04</t>
   </si>
   <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
-    <t>05:17</t>
+    <t>20261015--01</t>
+  </si>
+  <si>
+    <t>20261015--02</t>
+  </si>
+  <si>
+    <t>20261015--03</t>
+  </si>
+  <si>
+    <t>20261015--04</t>
   </si>
   <si>
     <t>05:41</t>
@@ -148,7 +142,7 @@
     <t>01:30</t>
   </si>
   <si>
-    <t>02:39</t>
+    <t>02:38</t>
   </si>
   <si>
     <t>06:19</t>
@@ -163,16 +157,16 @@
     <t>05:07</t>
   </si>
   <si>
-    <t>06:02</t>
+    <t>06:01</t>
   </si>
   <si>
     <t>04:56</t>
   </si>
   <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>04:41</t>
+    <t>03:28</t>
+  </si>
+  <si>
+    <t>04:40</t>
   </si>
   <si>
     <t>05:55</t>
@@ -181,19 +175,25 @@
     <t>06:25</t>
   </si>
   <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>00:17</t>
-  </si>
-  <si>
-    <t>05:46</t>
+    <t>00:19</t>
+  </si>
+  <si>
+    <t>05:45</t>
   </si>
   <si>
     <t>06:22</t>
   </si>
   <si>
-    <t>03:55</t>
+    <t>03:56</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>05:20</t>
   </si>
   <si>
     <t>00:00</t>
@@ -202,322 +202,337 @@
     <t>02:22</t>
   </si>
   <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>00:39:51</t>
-  </si>
-  <si>
-    <t>02:17:27</t>
-  </si>
-  <si>
-    <t>23:47:42</t>
-  </si>
-  <si>
-    <t>01:24:31</t>
-  </si>
-  <si>
-    <t>06:19:54</t>
-  </si>
-  <si>
-    <t>22:55:48</t>
-  </si>
-  <si>
-    <t>00:31:41</t>
-  </si>
-  <si>
-    <t>23:39:01</t>
-  </si>
-  <si>
-    <t>01:17:05</t>
-  </si>
-  <si>
-    <t>06:11:23</t>
-  </si>
-  <si>
-    <t>22:46:30</t>
-  </si>
-  <si>
-    <t>00:23:51</t>
-  </si>
-  <si>
-    <t>05:18:50</t>
-  </si>
-  <si>
-    <t>21:54:12</t>
-  </si>
-  <si>
-    <t>23:30:43</t>
-  </si>
-  <si>
-    <t>06:02:40</t>
-  </si>
-  <si>
-    <t>22:37:43</t>
-  </si>
-  <si>
-    <t>00:16:11</t>
-  </si>
-  <si>
-    <t>05:09:56</t>
-  </si>
-  <si>
-    <t>21:44:52</t>
-  </si>
-  <si>
-    <t>23:22:40</t>
-  </si>
-  <si>
-    <t>00:41:57</t>
-  </si>
-  <si>
-    <t>02:20:01</t>
-  </si>
-  <si>
-    <t>23:50:01</t>
+    <t>02:18</t>
+  </si>
+  <si>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>01:24:30</t>
+  </si>
+  <si>
+    <t>06:19:53</t>
+  </si>
+  <si>
+    <t>22:55:47</t>
+  </si>
+  <si>
+    <t>00:31:40</t>
+  </si>
+  <si>
+    <t>23:38:59</t>
+  </si>
+  <si>
+    <t>01:17:02</t>
+  </si>
+  <si>
+    <t>06:11:20</t>
+  </si>
+  <si>
+    <t>22:46:27</t>
+  </si>
+  <si>
+    <t>00:23:47</t>
+  </si>
+  <si>
+    <t>05:18:46</t>
+  </si>
+  <si>
+    <t>21:54:08</t>
+  </si>
+  <si>
+    <t>23:30:38</t>
+  </si>
+  <si>
+    <t>06:02:35</t>
+  </si>
+  <si>
+    <t>22:37:36</t>
+  </si>
+  <si>
+    <t>00:16:04</t>
+  </si>
+  <si>
+    <t>05:09:49</t>
+  </si>
+  <si>
+    <t>21:44:43</t>
+  </si>
+  <si>
+    <t>23:22:31</t>
+  </si>
+  <si>
+    <t>04:17:02</t>
+  </si>
+  <si>
+    <t>05:53:46</t>
+  </si>
+  <si>
+    <t>20:52:01</t>
+  </si>
+  <si>
+    <t>22:29:03</t>
   </si>
   <si>
     <t>01:26:46</t>
   </si>
   <si>
-    <t>06:23:33</t>
-  </si>
-  <si>
-    <t>22:58:54</t>
-  </si>
-  <si>
-    <t>00:33:48</t>
-  </si>
-  <si>
-    <t>23:41:05</t>
-  </si>
-  <si>
-    <t>01:20:02</t>
-  </si>
-  <si>
-    <t>06:13:49</t>
-  </si>
-  <si>
-    <t>22:48:39</t>
-  </si>
-  <si>
-    <t>00:26:17</t>
-  </si>
-  <si>
-    <t>05:21:44</t>
-  </si>
-  <si>
-    <t>21:56:40</t>
-  </si>
-  <si>
-    <t>23:32:55</t>
-  </si>
-  <si>
-    <t>06:04:48</t>
-  </si>
-  <si>
-    <t>22:39:48</t>
-  </si>
-  <si>
-    <t>00:20:29</t>
-  </si>
-  <si>
-    <t>05:12:13</t>
-  </si>
-  <si>
-    <t>21:46:57</t>
-  </si>
-  <si>
-    <t>23:25:24</t>
-  </si>
-  <si>
-    <t>00:45:05</t>
-  </si>
-  <si>
-    <t>02:22:16</t>
-  </si>
-  <si>
-    <t>23:52:39</t>
+    <t>06:23:32</t>
+  </si>
+  <si>
+    <t>22:58:53</t>
+  </si>
+  <si>
+    <t>00:33:47</t>
+  </si>
+  <si>
+    <t>23:41:03</t>
+  </si>
+  <si>
+    <t>01:20:00</t>
+  </si>
+  <si>
+    <t>06:13:47</t>
+  </si>
+  <si>
+    <t>22:48:36</t>
+  </si>
+  <si>
+    <t>00:26:14</t>
+  </si>
+  <si>
+    <t>05:21:41</t>
+  </si>
+  <si>
+    <t>21:56:36</t>
+  </si>
+  <si>
+    <t>23:32:50</t>
+  </si>
+  <si>
+    <t>06:04:43</t>
+  </si>
+  <si>
+    <t>22:39:41</t>
+  </si>
+  <si>
+    <t>00:20:22</t>
+  </si>
+  <si>
+    <t>05:12:06</t>
+  </si>
+  <si>
+    <t>21:46:48</t>
+  </si>
+  <si>
+    <t>23:25:15</t>
+  </si>
+  <si>
+    <t>04:19:37</t>
+  </si>
+  <si>
+    <t>05:55:53</t>
+  </si>
+  <si>
+    <t>20:54:15</t>
+  </si>
+  <si>
+    <t>22:31:24</t>
   </si>
   <si>
     <t>01:29:36</t>
   </si>
   <si>
-    <t>06:24:18</t>
-  </si>
-  <si>
-    <t>23:00:13</t>
-  </si>
-  <si>
-    <t>00:36:57</t>
-  </si>
-  <si>
-    <t>23:44:18</t>
-  </si>
-  <si>
-    <t>01:21:39</t>
-  </si>
-  <si>
-    <t>06:16:23</t>
-  </si>
-  <si>
-    <t>22:51:39</t>
-  </si>
-  <si>
-    <t>00:28:45</t>
-  </si>
-  <si>
-    <t>05:23:29</t>
-  </si>
-  <si>
-    <t>21:59:00</t>
-  </si>
-  <si>
-    <t>23:35:52</t>
-  </si>
-  <si>
-    <t>06:08:00</t>
-  </si>
-  <si>
-    <t>22:42:59</t>
-  </si>
-  <si>
-    <t>05:15:06</t>
-  </si>
-  <si>
-    <t>21:50:07</t>
-  </si>
-  <si>
-    <t>23:27:21</t>
-  </si>
-  <si>
-    <t>00:48:13</t>
-  </si>
-  <si>
-    <t>02:24:32</t>
-  </si>
-  <si>
-    <t>23:55:18</t>
+    <t>06:24:17</t>
+  </si>
+  <si>
+    <t>23:00:12</t>
+  </si>
+  <si>
+    <t>00:36:56</t>
+  </si>
+  <si>
+    <t>23:44:16</t>
+  </si>
+  <si>
+    <t>01:21:36</t>
+  </si>
+  <si>
+    <t>06:16:20</t>
+  </si>
+  <si>
+    <t>22:51:36</t>
+  </si>
+  <si>
+    <t>00:28:42</t>
+  </si>
+  <si>
+    <t>05:23:25</t>
+  </si>
+  <si>
+    <t>21:58:56</t>
+  </si>
+  <si>
+    <t>23:35:47</t>
+  </si>
+  <si>
+    <t>06:07:55</t>
+  </si>
+  <si>
+    <t>22:42:53</t>
+  </si>
+  <si>
+    <t>05:14:58</t>
+  </si>
+  <si>
+    <t>21:49:59</t>
+  </si>
+  <si>
+    <t>23:27:12</t>
+  </si>
+  <si>
+    <t>04:21:54</t>
+  </si>
+  <si>
+    <t>05:59:03</t>
+  </si>
+  <si>
+    <t>20:57:04</t>
+  </si>
+  <si>
+    <t>22:34:03</t>
   </si>
   <si>
     <t>01:32:27</t>
   </si>
   <si>
-    <t>06:25:03</t>
-  </si>
-  <si>
-    <t>23:01:33</t>
-  </si>
-  <si>
-    <t>00:40:07</t>
-  </si>
-  <si>
-    <t>23:47:33</t>
-  </si>
-  <si>
-    <t>01:23:16</t>
-  </si>
-  <si>
-    <t>06:18:56</t>
-  </si>
-  <si>
-    <t>22:54:41</t>
-  </si>
-  <si>
-    <t>00:31:13</t>
-  </si>
-  <si>
-    <t>05:25:13</t>
-  </si>
-  <si>
-    <t>22:01:21</t>
-  </si>
-  <si>
-    <t>23:38:50</t>
-  </si>
-  <si>
-    <t>06:11:13</t>
-  </si>
-  <si>
-    <t>22:46:12</t>
-  </si>
-  <si>
-    <t>00:20:46</t>
-  </si>
-  <si>
-    <t>05:17:59</t>
-  </si>
-  <si>
-    <t>21:53:19</t>
-  </si>
-  <si>
-    <t>23:29:19</t>
-  </si>
-  <si>
-    <t>00:50:21</t>
-  </si>
-  <si>
-    <t>02:27:08</t>
-  </si>
-  <si>
-    <t>23:57:39</t>
-  </si>
-  <si>
-    <t>01:34:45</t>
-  </si>
-  <si>
-    <t>06:28:42</t>
-  </si>
-  <si>
-    <t>23:04:39</t>
-  </si>
-  <si>
-    <t>00:42:15</t>
-  </si>
-  <si>
-    <t>23:49:38</t>
-  </si>
-  <si>
-    <t>01:26:15</t>
-  </si>
-  <si>
-    <t>06:21:23</t>
-  </si>
-  <si>
-    <t>22:56:51</t>
-  </si>
-  <si>
-    <t>00:33:42</t>
-  </si>
-  <si>
-    <t>05:28:07</t>
-  </si>
-  <si>
-    <t>22:03:50</t>
-  </si>
-  <si>
-    <t>23:41:03</t>
-  </si>
-  <si>
-    <t>06:13:20</t>
-  </si>
-  <si>
-    <t>22:48:18</t>
-  </si>
-  <si>
-    <t>00:24:48</t>
-  </si>
-  <si>
-    <t>05:20:15</t>
-  </si>
-  <si>
-    <t>21:55:25</t>
-  </si>
-  <si>
-    <t>23:32:04</t>
+    <t>06:25:02</t>
+  </si>
+  <si>
+    <t>23:01:31</t>
+  </si>
+  <si>
+    <t>00:40:06</t>
+  </si>
+  <si>
+    <t>23:47:31</t>
+  </si>
+  <si>
+    <t>01:23:14</t>
+  </si>
+  <si>
+    <t>06:18:54</t>
+  </si>
+  <si>
+    <t>22:54:37</t>
+  </si>
+  <si>
+    <t>00:31:10</t>
+  </si>
+  <si>
+    <t>05:25:09</t>
+  </si>
+  <si>
+    <t>22:01:16</t>
+  </si>
+  <si>
+    <t>23:38:45</t>
+  </si>
+  <si>
+    <t>06:11:08</t>
+  </si>
+  <si>
+    <t>22:46:06</t>
+  </si>
+  <si>
+    <t>00:20:41</t>
+  </si>
+  <si>
+    <t>05:17:51</t>
+  </si>
+  <si>
+    <t>21:53:10</t>
+  </si>
+  <si>
+    <t>23:29:11</t>
+  </si>
+  <si>
+    <t>04:24:11</t>
+  </si>
+  <si>
+    <t>06:02:12</t>
+  </si>
+  <si>
+    <t>20:59:54</t>
+  </si>
+  <si>
+    <t>22:36:44</t>
+  </si>
+  <si>
+    <t>01:34:44</t>
+  </si>
+  <si>
+    <t>06:28:41</t>
+  </si>
+  <si>
+    <t>23:04:38</t>
+  </si>
+  <si>
+    <t>00:42:14</t>
+  </si>
+  <si>
+    <t>23:49:36</t>
+  </si>
+  <si>
+    <t>01:26:13</t>
+  </si>
+  <si>
+    <t>06:21:20</t>
+  </si>
+  <si>
+    <t>22:56:48</t>
+  </si>
+  <si>
+    <t>00:33:38</t>
+  </si>
+  <si>
+    <t>05:28:04</t>
+  </si>
+  <si>
+    <t>22:03:45</t>
+  </si>
+  <si>
+    <t>23:40:59</t>
+  </si>
+  <si>
+    <t>06:13:15</t>
+  </si>
+  <si>
+    <t>22:48:12</t>
+  </si>
+  <si>
+    <t>00:24:41</t>
+  </si>
+  <si>
+    <t>05:20:08</t>
+  </si>
+  <si>
+    <t>21:55:16</t>
+  </si>
+  <si>
+    <t>23:31:55</t>
+  </si>
+  <si>
+    <t>04:26:45</t>
+  </si>
+  <si>
+    <t>06:04:20</t>
+  </si>
+  <si>
+    <t>21:02:09</t>
+  </si>
+  <si>
+    <t>22:39:05</t>
   </si>
   <si>
     <t>0°</t>
@@ -538,19 +553,31 @@
     <t>26°</t>
   </si>
   <si>
-    <t>06:20:15</t>
-  </si>
-  <si>
-    <t>06:12:51</t>
-  </si>
-  <si>
-    <t>05:22:51</t>
-  </si>
-  <si>
-    <t>06:05:34</t>
-  </si>
-  <si>
-    <t>05:15:39</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>38°</t>
+  </si>
+  <si>
+    <t>06:20:14</t>
+  </si>
+  <si>
+    <t>06:12:48</t>
+  </si>
+  <si>
+    <t>05:22:47</t>
+  </si>
+  <si>
+    <t>06:05:29</t>
+  </si>
+  <si>
+    <t>05:15:33</t>
+  </si>
+  <si>
+    <t>04:25:39</t>
+  </si>
+  <si>
+    <t>05:58:20</t>
   </si>
   <si>
     <t>B</t>
@@ -602,7 +629,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -635,13 +662,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,13 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,19 +698,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,13 +722,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -820,6 +859,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1223,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1301,10 +1346,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>60</v>
@@ -1313,34 +1358,34 @@
         <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L2" s="4">
-        <v>-67.40000000000001</v>
+        <v>-66.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="O2" s="6">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P2" s="7">
         <v>6</v>
@@ -1348,8 +1393,8 @@
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>5</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1357,55 +1402,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="L3" s="4">
-        <v>-59.3</v>
+        <v>-9.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="O3" s="6">
-        <v>9</v>
-      </c>
-      <c r="P3" s="7">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="P3" s="9">
+        <v>13</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1413,10 +1458,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>60</v>
@@ -1425,37 +1470,37 @@
         <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>66</v>
       </c>
       <c r="L4" s="4">
-        <v>-63.6</v>
+        <v>-55.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O4" s="9">
-        <v>23</v>
-      </c>
-      <c r="P4" s="10">
-        <v>23</v>
+        <v>192</v>
+      </c>
+      <c r="O4" s="10">
+        <v>46</v>
+      </c>
+      <c r="P4" s="11">
+        <v>46</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1469,10 +1514,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>60</v>
@@ -1481,36 +1526,36 @@
         <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>67</v>
       </c>
       <c r="L5" s="4">
-        <v>-66.3</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O5" s="11">
+        <v>191</v>
+      </c>
+      <c r="O5" s="10">
         <v>47</v>
       </c>
-      <c r="P5" s="12">
+      <c r="P5" s="11">
         <v>47</v>
       </c>
       <c r="Q5" s="8">
@@ -1525,55 +1570,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="L6" s="4">
-        <v>-9.5</v>
+        <v>-63.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O6" s="11">
-        <v>43</v>
+        <v>191</v>
+      </c>
+      <c r="O6" s="10">
+        <v>66</v>
       </c>
       <c r="P6" s="12">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="R6" s="13">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1581,10 +1626,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>60</v>
@@ -1593,43 +1638,43 @@
         <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L7" s="4">
-        <v>-55.6</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O7" s="11">
-        <v>49</v>
-      </c>
-      <c r="P7" s="13">
-        <v>49</v>
+        <v>192</v>
+      </c>
+      <c r="O7" s="10">
+        <v>86</v>
+      </c>
+      <c r="P7" s="14">
+        <v>86</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1637,49 +1682,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="L8" s="4">
-        <v>-67.90000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O8" s="11">
-        <v>48</v>
-      </c>
-      <c r="P8" s="13">
-        <v>48</v>
+        <v>193</v>
+      </c>
+      <c r="O8" s="10">
+        <v>81</v>
+      </c>
+      <c r="P8" s="15">
+        <v>81</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1693,10 +1738,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>60</v>
@@ -1705,37 +1750,37 @@
         <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L9" s="4">
-        <v>-63.2</v>
+        <v>-54.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O9" s="9">
-        <v>36</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="O9" s="10">
+        <v>93</v>
+      </c>
+      <c r="P9" s="16">
+        <v>52</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1749,10 +1794,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>60</v>
@@ -1761,37 +1806,37 @@
         <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L10" s="4">
-        <v>-67.59999999999999</v>
+        <v>-68.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O10" s="11">
-        <v>50</v>
-      </c>
-      <c r="P10" s="12">
-        <v>47</v>
+        <v>191</v>
+      </c>
+      <c r="O10" s="10">
+        <v>95</v>
+      </c>
+      <c r="P10" s="9">
+        <v>14</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1805,49 +1850,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L11" s="4">
-        <v>-11.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O11" s="11">
-        <v>52</v>
-      </c>
-      <c r="P11" s="13">
-        <v>49</v>
+        <v>192</v>
+      </c>
+      <c r="O11" s="10">
+        <v>95</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1861,10 +1906,10 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>60</v>
@@ -1873,37 +1918,37 @@
         <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>74</v>
       </c>
       <c r="L12" s="4">
-        <v>-54.6</v>
+        <v>-44.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O12" s="11">
-        <v>79</v>
-      </c>
-      <c r="P12" s="14">
-        <v>67</v>
+        <v>191</v>
+      </c>
+      <c r="O12" s="10">
+        <v>52</v>
+      </c>
+      <c r="P12" s="16">
+        <v>52</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1917,10 +1962,10 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>60</v>
@@ -1929,43 +1974,43 @@
         <v>75</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>75</v>
       </c>
       <c r="L13" s="4">
-        <v>-68.3</v>
+        <v>-62.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O13" s="11">
-        <v>85</v>
-      </c>
-      <c r="P13" s="15">
-        <v>85</v>
+        <v>191</v>
+      </c>
+      <c r="O13" s="17">
+        <v>34</v>
+      </c>
+      <c r="P13" s="18">
+        <v>28</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="R13" s="19">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1973,55 +2018,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="L14" s="4">
-        <v>-23.1</v>
+        <v>-13.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O14" s="11">
-        <v>85</v>
-      </c>
-      <c r="P14" s="16">
+        <v>193</v>
+      </c>
+      <c r="O14" s="10">
+        <v>89</v>
+      </c>
+      <c r="P14" s="20">
         <v>59</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
       </c>
-      <c r="R14" s="8">
-        <v>0</v>
+      <c r="R14" s="9">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2029,7 +2074,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>52</v>
@@ -2041,43 +2086,43 @@
         <v>77</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L15" s="4">
-        <v>-44.2</v>
+        <v>-53.4</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O15" s="11">
-        <v>72</v>
-      </c>
-      <c r="P15" s="12">
-        <v>45</v>
+        <v>191</v>
+      </c>
+      <c r="O15" s="10">
+        <v>93</v>
+      </c>
+      <c r="P15" s="21">
+        <v>88</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="17">
-        <v>14</v>
+      <c r="R15" s="21">
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2085,7 +2130,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2097,43 +2142,43 @@
         <v>78</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>78</v>
       </c>
       <c r="L16" s="4">
-        <v>-62.6</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O16" s="11">
-        <v>83</v>
-      </c>
-      <c r="P16" s="18">
-        <v>54</v>
+        <v>192</v>
+      </c>
+      <c r="O16" s="10">
+        <v>98</v>
+      </c>
+      <c r="P16" s="22">
+        <v>94</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
       </c>
-      <c r="R16" s="10">
-        <v>26</v>
+      <c r="R16" s="21">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2141,7 +2186,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>54</v>
@@ -2153,43 +2198,43 @@
         <v>79</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="L17" s="4">
-        <v>-13.5</v>
+        <v>-25.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O17" s="11">
-        <v>80</v>
-      </c>
-      <c r="P17" s="19">
-        <v>29</v>
+        <v>193</v>
+      </c>
+      <c r="O17" s="10">
+        <v>84</v>
+      </c>
+      <c r="P17" s="23">
+        <v>77</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
       </c>
-      <c r="R17" s="20">
-        <v>77</v>
+      <c r="R17" s="16">
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2197,7 +2242,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>55</v>
@@ -2209,43 +2254,43 @@
         <v>80</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L18" s="4">
-        <v>-53.4</v>
+        <v>-42.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O18" s="11">
-        <v>55</v>
-      </c>
-      <c r="P18" s="12">
-        <v>46</v>
+        <v>191</v>
+      </c>
+      <c r="O18" s="6">
+        <v>12</v>
+      </c>
+      <c r="P18" s="8">
+        <v>1</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
       </c>
-      <c r="R18" s="18">
-        <v>55</v>
+      <c r="R18" s="24">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2253,7 +2298,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>56</v>
@@ -2265,43 +2310,43 @@
         <v>81</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L19" s="4">
-        <v>-68.40000000000001</v>
+        <v>-61.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O19" s="11">
-        <v>39</v>
-      </c>
-      <c r="P19" s="19">
-        <v>28</v>
+        <v>191</v>
+      </c>
+      <c r="O19" s="6">
+        <v>8</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
       </c>
       <c r="Q19" s="8">
         <v>0</v>
       </c>
-      <c r="R19" s="21">
-        <v>39</v>
+      <c r="R19" s="24">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2309,55 +2354,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L20" s="4">
-        <v>-25.1</v>
+        <v>-36.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O20" s="11">
-        <v>57</v>
-      </c>
-      <c r="P20" s="10">
-        <v>24</v>
+        <v>191</v>
+      </c>
+      <c r="O20" s="6">
+        <v>3</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
       </c>
-      <c r="R20" s="18">
-        <v>57</v>
+      <c r="R20" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2365,55 +2410,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="L21" s="4">
-        <v>-42.9</v>
+        <v>-15.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="O21" s="6">
-        <v>10</v>
-      </c>
-      <c r="P21" s="7">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
       </c>
       <c r="Q21" s="8">
         <v>0</v>
       </c>
-      <c r="R21" s="22">
-        <v>10</v>
+      <c r="R21" s="7">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2421,10 +2466,10 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>60</v>
@@ -2433,102 +2478,158 @@
         <v>84</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L22" s="4">
-        <v>-61.9</v>
+        <v>-31.7</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O22" s="6">
-        <v>8</v>
-      </c>
-      <c r="P22" s="8">
-        <v>1</v>
+        <v>191</v>
+      </c>
+      <c r="O22" s="17">
+        <v>26</v>
+      </c>
+      <c r="P22" s="19">
+        <v>25</v>
       </c>
       <c r="Q22" s="8">
         <v>0</v>
       </c>
-      <c r="R22" s="22">
-        <v>8</v>
+      <c r="R22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>23</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-52.2</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="O23" s="17">
+        <v>29</v>
+      </c>
+      <c r="P23" s="18">
+        <v>29</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A22">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C22">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D22">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E22">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F22">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G22">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L22">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2547,12 +2648,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M22">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2569,22 +2670,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P22">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q22">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R22">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="206">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261009--01</t>
-  </si>
-  <si>
-    <t>20261009--02</t>
-  </si>
-  <si>
-    <t>20261009--03</t>
-  </si>
-  <si>
     <t>20261010--01</t>
   </si>
   <si>
@@ -136,13 +127,16 @@
     <t>20261015--04</t>
   </si>
   <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:38</t>
+    <t>20261016--01</t>
+  </si>
+  <si>
+    <t>20261016--02</t>
+  </si>
+  <si>
+    <t>20261016--03</t>
+  </si>
+  <si>
+    <t>20261016--04</t>
   </si>
   <si>
     <t>06:19</t>
@@ -154,7 +148,7 @@
     <t>03:14</t>
   </si>
   <si>
-    <t>05:07</t>
+    <t>05:06</t>
   </si>
   <si>
     <t>06:01</t>
@@ -166,16 +160,16 @@
     <t>03:28</t>
   </si>
   <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>00:19</t>
+    <t>04:39</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>00:21</t>
   </si>
   <si>
     <t>05:45</t>
@@ -187,13 +181,28 @@
     <t>03:56</t>
   </si>
   <si>
-    <t>04:34</t>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>06:18</t>
   </si>
   <si>
     <t>05:39</t>
   </si>
   <si>
-    <t>05:20</t>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>02:23</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>06:09</t>
   </si>
   <si>
     <t>00:00</t>
@@ -202,345 +211,363 @@
     <t>02:22</t>
   </si>
   <si>
+    <t>05:38</t>
+  </si>
+  <si>
     <t>02:18</t>
   </si>
   <si>
-    <t>03:52</t>
-  </si>
-  <si>
-    <t>01:24:30</t>
-  </si>
-  <si>
-    <t>06:19:53</t>
-  </si>
-  <si>
-    <t>22:55:47</t>
+    <t>03:51</t>
+  </si>
+  <si>
+    <t>00:51</t>
   </si>
   <si>
     <t>00:31:40</t>
   </si>
   <si>
-    <t>23:38:59</t>
-  </si>
-  <si>
-    <t>01:17:02</t>
-  </si>
-  <si>
-    <t>06:11:20</t>
-  </si>
-  <si>
-    <t>22:46:27</t>
-  </si>
-  <si>
-    <t>00:23:47</t>
-  </si>
-  <si>
-    <t>05:18:46</t>
-  </si>
-  <si>
-    <t>21:54:08</t>
-  </si>
-  <si>
-    <t>23:30:38</t>
-  </si>
-  <si>
-    <t>06:02:35</t>
-  </si>
-  <si>
-    <t>22:37:36</t>
-  </si>
-  <si>
-    <t>00:16:04</t>
-  </si>
-  <si>
-    <t>05:09:49</t>
-  </si>
-  <si>
-    <t>21:44:43</t>
-  </si>
-  <si>
-    <t>23:22:31</t>
-  </si>
-  <si>
-    <t>04:17:02</t>
-  </si>
-  <si>
-    <t>05:53:46</t>
-  </si>
-  <si>
-    <t>20:52:01</t>
-  </si>
-  <si>
-    <t>22:29:03</t>
-  </si>
-  <si>
-    <t>01:26:46</t>
-  </si>
-  <si>
-    <t>06:23:32</t>
-  </si>
-  <si>
-    <t>22:58:53</t>
-  </si>
-  <si>
-    <t>00:33:47</t>
-  </si>
-  <si>
-    <t>23:41:03</t>
-  </si>
-  <si>
-    <t>01:20:00</t>
-  </si>
-  <si>
-    <t>06:13:47</t>
-  </si>
-  <si>
-    <t>22:48:36</t>
-  </si>
-  <si>
-    <t>00:26:14</t>
-  </si>
-  <si>
-    <t>05:21:41</t>
-  </si>
-  <si>
-    <t>21:56:36</t>
-  </si>
-  <si>
-    <t>23:32:50</t>
-  </si>
-  <si>
-    <t>06:04:43</t>
-  </si>
-  <si>
-    <t>22:39:41</t>
-  </si>
-  <si>
-    <t>00:20:22</t>
-  </si>
-  <si>
-    <t>05:12:06</t>
-  </si>
-  <si>
-    <t>21:46:48</t>
-  </si>
-  <si>
-    <t>23:25:15</t>
-  </si>
-  <si>
-    <t>04:19:37</t>
-  </si>
-  <si>
-    <t>05:55:53</t>
-  </si>
-  <si>
-    <t>20:54:15</t>
-  </si>
-  <si>
-    <t>22:31:24</t>
-  </si>
-  <si>
-    <t>01:29:36</t>
-  </si>
-  <si>
-    <t>06:24:17</t>
-  </si>
-  <si>
-    <t>23:00:12</t>
-  </si>
-  <si>
-    <t>00:36:56</t>
-  </si>
-  <si>
-    <t>23:44:16</t>
-  </si>
-  <si>
-    <t>01:21:36</t>
-  </si>
-  <si>
-    <t>06:16:20</t>
-  </si>
-  <si>
-    <t>22:51:36</t>
-  </si>
-  <si>
-    <t>00:28:42</t>
-  </si>
-  <si>
-    <t>05:23:25</t>
-  </si>
-  <si>
-    <t>21:58:56</t>
-  </si>
-  <si>
-    <t>23:35:47</t>
-  </si>
-  <si>
-    <t>06:07:55</t>
-  </si>
-  <si>
-    <t>22:42:53</t>
-  </si>
-  <si>
-    <t>05:14:58</t>
-  </si>
-  <si>
-    <t>21:49:59</t>
-  </si>
-  <si>
-    <t>23:27:12</t>
-  </si>
-  <si>
-    <t>04:21:54</t>
-  </si>
-  <si>
-    <t>05:59:03</t>
-  </si>
-  <si>
-    <t>20:57:04</t>
-  </si>
-  <si>
-    <t>22:34:03</t>
-  </si>
-  <si>
-    <t>01:32:27</t>
-  </si>
-  <si>
-    <t>06:25:02</t>
-  </si>
-  <si>
-    <t>23:01:31</t>
-  </si>
-  <si>
-    <t>00:40:06</t>
-  </si>
-  <si>
-    <t>23:47:31</t>
-  </si>
-  <si>
-    <t>01:23:14</t>
-  </si>
-  <si>
-    <t>06:18:54</t>
-  </si>
-  <si>
-    <t>22:54:37</t>
-  </si>
-  <si>
-    <t>00:31:10</t>
-  </si>
-  <si>
-    <t>05:25:09</t>
-  </si>
-  <si>
-    <t>22:01:16</t>
-  </si>
-  <si>
-    <t>23:38:45</t>
-  </si>
-  <si>
-    <t>06:11:08</t>
-  </si>
-  <si>
-    <t>22:46:06</t>
-  </si>
-  <si>
-    <t>00:20:41</t>
-  </si>
-  <si>
-    <t>05:17:51</t>
-  </si>
-  <si>
-    <t>21:53:10</t>
-  </si>
-  <si>
-    <t>23:29:11</t>
-  </si>
-  <si>
-    <t>04:24:11</t>
-  </si>
-  <si>
-    <t>06:02:12</t>
-  </si>
-  <si>
-    <t>20:59:54</t>
-  </si>
-  <si>
-    <t>22:36:44</t>
-  </si>
-  <si>
-    <t>01:34:44</t>
-  </si>
-  <si>
-    <t>06:28:41</t>
-  </si>
-  <si>
-    <t>23:04:38</t>
-  </si>
-  <si>
-    <t>00:42:14</t>
-  </si>
-  <si>
-    <t>23:49:36</t>
-  </si>
-  <si>
-    <t>01:26:13</t>
-  </si>
-  <si>
-    <t>06:21:20</t>
-  </si>
-  <si>
-    <t>22:56:48</t>
-  </si>
-  <si>
-    <t>00:33:38</t>
-  </si>
-  <si>
-    <t>05:28:04</t>
-  </si>
-  <si>
-    <t>22:03:45</t>
-  </si>
-  <si>
-    <t>23:40:59</t>
-  </si>
-  <si>
-    <t>06:13:15</t>
-  </si>
-  <si>
-    <t>22:48:12</t>
-  </si>
-  <si>
-    <t>00:24:41</t>
-  </si>
-  <si>
-    <t>05:20:08</t>
-  </si>
-  <si>
-    <t>21:55:16</t>
-  </si>
-  <si>
-    <t>23:31:55</t>
-  </si>
-  <si>
-    <t>04:26:45</t>
-  </si>
-  <si>
-    <t>06:04:20</t>
-  </si>
-  <si>
-    <t>21:02:09</t>
-  </si>
-  <si>
-    <t>22:39:05</t>
+    <t>23:38:57</t>
+  </si>
+  <si>
+    <t>01:17:00</t>
+  </si>
+  <si>
+    <t>06:11:18</t>
+  </si>
+  <si>
+    <t>22:46:24</t>
+  </si>
+  <si>
+    <t>00:23:44</t>
+  </si>
+  <si>
+    <t>05:18:42</t>
+  </si>
+  <si>
+    <t>21:54:02</t>
+  </si>
+  <si>
+    <t>23:30:32</t>
+  </si>
+  <si>
+    <t>06:02:29</t>
+  </si>
+  <si>
+    <t>22:37:28</t>
+  </si>
+  <si>
+    <t>00:15:56</t>
+  </si>
+  <si>
+    <t>05:09:40</t>
+  </si>
+  <si>
+    <t>21:44:32</t>
+  </si>
+  <si>
+    <t>23:22:19</t>
+  </si>
+  <si>
+    <t>04:16:50</t>
+  </si>
+  <si>
+    <t>05:53:33</t>
+  </si>
+  <si>
+    <t>20:51:46</t>
+  </si>
+  <si>
+    <t>22:28:48</t>
+  </si>
+  <si>
+    <t>03:23:56</t>
+  </si>
+  <si>
+    <t>05:00:27</t>
+  </si>
+  <si>
+    <t>19:59:15</t>
+  </si>
+  <si>
+    <t>21:35:22</t>
+  </si>
+  <si>
+    <t>00:33:46</t>
+  </si>
+  <si>
+    <t>23:41:01</t>
+  </si>
+  <si>
+    <t>01:19:58</t>
+  </si>
+  <si>
+    <t>06:13:45</t>
+  </si>
+  <si>
+    <t>22:48:33</t>
+  </si>
+  <si>
+    <t>00:26:10</t>
+  </si>
+  <si>
+    <t>05:21:37</t>
+  </si>
+  <si>
+    <t>21:56:31</t>
+  </si>
+  <si>
+    <t>23:32:44</t>
+  </si>
+  <si>
+    <t>06:04:37</t>
+  </si>
+  <si>
+    <t>22:39:33</t>
+  </si>
+  <si>
+    <t>00:20:13</t>
+  </si>
+  <si>
+    <t>05:11:57</t>
+  </si>
+  <si>
+    <t>21:46:37</t>
+  </si>
+  <si>
+    <t>23:25:03</t>
+  </si>
+  <si>
+    <t>04:19:25</t>
+  </si>
+  <si>
+    <t>05:55:41</t>
+  </si>
+  <si>
+    <t>20:54:00</t>
+  </si>
+  <si>
+    <t>22:31:08</t>
+  </si>
+  <si>
+    <t>03:27:13</t>
+  </si>
+  <si>
+    <t>05:02:32</t>
+  </si>
+  <si>
+    <t>20:02:00</t>
+  </si>
+  <si>
+    <t>21:37:31</t>
+  </si>
+  <si>
+    <t>00:36:55</t>
+  </si>
+  <si>
+    <t>23:44:14</t>
+  </si>
+  <si>
+    <t>01:21:35</t>
+  </si>
+  <si>
+    <t>06:16:18</t>
+  </si>
+  <si>
+    <t>22:51:33</t>
+  </si>
+  <si>
+    <t>00:28:38</t>
+  </si>
+  <si>
+    <t>05:23:21</t>
+  </si>
+  <si>
+    <t>21:58:50</t>
+  </si>
+  <si>
+    <t>23:35:41</t>
+  </si>
+  <si>
+    <t>06:07:49</t>
+  </si>
+  <si>
+    <t>22:42:45</t>
+  </si>
+  <si>
+    <t>05:14:49</t>
+  </si>
+  <si>
+    <t>21:49:47</t>
+  </si>
+  <si>
+    <t>23:27:01</t>
+  </si>
+  <si>
+    <t>04:21:41</t>
+  </si>
+  <si>
+    <t>05:58:50</t>
+  </si>
+  <si>
+    <t>20:56:49</t>
+  </si>
+  <si>
+    <t>22:33:48</t>
+  </si>
+  <si>
+    <t>03:28:24</t>
+  </si>
+  <si>
+    <t>05:05:48</t>
+  </si>
+  <si>
+    <t>20:03:50</t>
+  </si>
+  <si>
+    <t>21:40:35</t>
+  </si>
+  <si>
+    <t>00:40:05</t>
+  </si>
+  <si>
+    <t>23:47:29</t>
+  </si>
+  <si>
+    <t>01:23:12</t>
+  </si>
+  <si>
+    <t>06:18:51</t>
+  </si>
+  <si>
+    <t>22:54:34</t>
+  </si>
+  <si>
+    <t>00:31:06</t>
+  </si>
+  <si>
+    <t>05:25:05</t>
+  </si>
+  <si>
+    <t>22:01:10</t>
+  </si>
+  <si>
+    <t>23:38:40</t>
+  </si>
+  <si>
+    <t>06:11:01</t>
+  </si>
+  <si>
+    <t>22:45:57</t>
+  </si>
+  <si>
+    <t>00:20:34</t>
+  </si>
+  <si>
+    <t>05:17:42</t>
+  </si>
+  <si>
+    <t>21:52:59</t>
+  </si>
+  <si>
+    <t>23:28:59</t>
+  </si>
+  <si>
+    <t>04:23:58</t>
+  </si>
+  <si>
+    <t>06:01:59</t>
+  </si>
+  <si>
+    <t>20:59:39</t>
+  </si>
+  <si>
+    <t>22:36:29</t>
+  </si>
+  <si>
+    <t>03:29:36</t>
+  </si>
+  <si>
+    <t>05:09:03</t>
+  </si>
+  <si>
+    <t>20:05:40</t>
+  </si>
+  <si>
+    <t>21:43:40</t>
+  </si>
+  <si>
+    <t>00:42:13</t>
+  </si>
+  <si>
+    <t>23:49:34</t>
+  </si>
+  <si>
+    <t>01:26:11</t>
+  </si>
+  <si>
+    <t>06:21:18</t>
+  </si>
+  <si>
+    <t>22:56:44</t>
+  </si>
+  <si>
+    <t>00:33:35</t>
+  </si>
+  <si>
+    <t>05:28:00</t>
+  </si>
+  <si>
+    <t>22:03:39</t>
+  </si>
+  <si>
+    <t>23:40:53</t>
+  </si>
+  <si>
+    <t>06:13:08</t>
+  </si>
+  <si>
+    <t>22:48:04</t>
+  </si>
+  <si>
+    <t>00:24:33</t>
+  </si>
+  <si>
+    <t>05:19:58</t>
+  </si>
+  <si>
+    <t>21:55:05</t>
+  </si>
+  <si>
+    <t>23:31:44</t>
+  </si>
+  <si>
+    <t>04:26:32</t>
+  </si>
+  <si>
+    <t>06:04:07</t>
+  </si>
+  <si>
+    <t>21:01:54</t>
+  </si>
+  <si>
+    <t>22:38:50</t>
+  </si>
+  <si>
+    <t>03:32:52</t>
+  </si>
+  <si>
+    <t>05:11:09</t>
+  </si>
+  <si>
+    <t>20:08:26</t>
+  </si>
+  <si>
+    <t>21:45:50</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>1°</t>
-  </si>
-  <si>
     <t>6°</t>
   </si>
   <si>
@@ -556,28 +583,37 @@
     <t>4°</t>
   </si>
   <si>
-    <t>38°</t>
-  </si>
-  <si>
-    <t>06:20:14</t>
-  </si>
-  <si>
-    <t>06:12:48</t>
-  </si>
-  <si>
-    <t>05:22:47</t>
-  </si>
-  <si>
-    <t>06:05:29</t>
-  </si>
-  <si>
-    <t>05:15:33</t>
-  </si>
-  <si>
-    <t>04:25:39</t>
-  </si>
-  <si>
-    <t>05:58:20</t>
+    <t>39°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>06:12:46</t>
+  </si>
+  <si>
+    <t>05:22:43</t>
+  </si>
+  <si>
+    <t>06:05:23</t>
+  </si>
+  <si>
+    <t>05:15:24</t>
+  </si>
+  <si>
+    <t>04:25:27</t>
+  </si>
+  <si>
+    <t>05:58:08</t>
+  </si>
+  <si>
+    <t>05:08:12</t>
+  </si>
+  <si>
+    <t>20:01:21</t>
   </si>
   <si>
     <t>B</t>
@@ -629,7 +665,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,13 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,67 +698,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,19 +722,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -793,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -862,9 +892,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1346,49 +1373,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-67.90000000000001</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O2" s="6">
         <v>40</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-66.3</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O2" s="6">
-        <v>8</v>
-      </c>
       <c r="P2" s="7">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1402,55 +1429,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="L3" s="4">
-        <v>-9.5</v>
+        <v>-63.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O3" s="6">
-        <v>14</v>
-      </c>
-      <c r="P3" s="9">
-        <v>13</v>
+        <v>203</v>
+      </c>
+      <c r="O3" s="9">
+        <v>90</v>
+      </c>
+      <c r="P3" s="10">
+        <v>83</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
-        <v>0</v>
+      <c r="R3" s="11">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1458,55 +1485,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-67.59999999999999</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O4" s="9">
+        <v>90</v>
+      </c>
+      <c r="P4" s="12">
+        <v>90</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11">
         <v>60</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-55.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O4" s="10">
-        <v>46</v>
-      </c>
-      <c r="P4" s="11">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1514,55 +1541,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="L5" s="4">
-        <v>-67.90000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O5" s="10">
-        <v>47</v>
-      </c>
-      <c r="P5" s="11">
-        <v>47</v>
+        <v>205</v>
+      </c>
+      <c r="O5" s="9">
+        <v>69</v>
+      </c>
+      <c r="P5" s="13">
+        <v>69</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
       <c r="R5" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1570,55 +1597,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L6" s="4">
-        <v>-63.2</v>
+        <v>-54.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O6" s="10">
-        <v>66</v>
-      </c>
-      <c r="P6" s="12">
-        <v>64</v>
+        <v>203</v>
+      </c>
+      <c r="O6" s="9">
+        <v>95</v>
+      </c>
+      <c r="P6" s="14">
+        <v>14</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="13">
-        <v>40</v>
+      <c r="R6" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1626,55 +1653,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L7" s="4">
-        <v>-67.59999999999999</v>
+        <v>-68.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O7" s="10">
-        <v>86</v>
-      </c>
-      <c r="P7" s="14">
-        <v>86</v>
+        <v>203</v>
+      </c>
+      <c r="O7" s="9">
+        <v>47</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>1</v>
+      <c r="R7" s="15">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1682,49 +1709,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L8" s="4">
-        <v>-11.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O8" s="10">
-        <v>81</v>
-      </c>
-      <c r="P8" s="15">
-        <v>81</v>
+        <v>204</v>
+      </c>
+      <c r="O8" s="9">
+        <v>48</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1738,49 +1765,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4">
-        <v>-54.5</v>
+        <v>-44.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O9" s="10">
-        <v>93</v>
+        <v>203</v>
+      </c>
+      <c r="O9" s="9">
+        <v>57</v>
       </c>
       <c r="P9" s="16">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1794,49 +1821,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L10" s="4">
-        <v>-68.3</v>
+        <v>-62.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O10" s="10">
-        <v>95</v>
-      </c>
-      <c r="P10" s="9">
-        <v>14</v>
+        <v>203</v>
+      </c>
+      <c r="O10" s="9">
+        <v>63</v>
+      </c>
+      <c r="P10" s="17">
+        <v>63</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1850,55 +1877,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="L11" s="4">
-        <v>-23.1</v>
+        <v>-13.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O11" s="10">
-        <v>95</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O11" s="9">
+        <v>54</v>
+      </c>
+      <c r="P11" s="18">
+        <v>51</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="8">
-        <v>0</v>
+      <c r="R11" s="14">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1906,49 +1933,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-44.2</v>
+        <v>-53.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O12" s="10">
-        <v>52</v>
-      </c>
-      <c r="P12" s="16">
-        <v>52</v>
+        <v>203</v>
+      </c>
+      <c r="O12" s="9">
+        <v>59</v>
+      </c>
+      <c r="P12" s="11">
+        <v>59</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1962,55 +1989,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-68.40000000000001</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O13" s="9">
         <v>75</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-62.6</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O13" s="17">
-        <v>34</v>
-      </c>
-      <c r="P13" s="18">
-        <v>28</v>
+      <c r="P13" s="13">
+        <v>71</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="19">
-        <v>25</v>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2018,55 +2045,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L14" s="4">
-        <v>-13.5</v>
+        <v>-25.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O14" s="10">
-        <v>89</v>
-      </c>
-      <c r="P14" s="20">
-        <v>59</v>
+        <v>205</v>
+      </c>
+      <c r="O14" s="9">
+        <v>90</v>
+      </c>
+      <c r="P14" s="17">
+        <v>63</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
       </c>
-      <c r="R14" s="9">
-        <v>17</v>
+      <c r="R14" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2074,55 +2101,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
+        <v>60</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L15" s="4">
-        <v>-53.4</v>
+        <v>-42.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O15" s="10">
+        <v>203</v>
+      </c>
+      <c r="O15" s="9">
+        <v>100</v>
+      </c>
+      <c r="P15" s="18">
+        <v>49</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="19">
         <v>93</v>
-      </c>
-      <c r="P15" s="21">
-        <v>88</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="21">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2130,55 +2157,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-61.8</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O16" s="9">
         <v>100</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-68.40000000000001</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O16" s="10">
-        <v>98</v>
-      </c>
-      <c r="P16" s="22">
+      <c r="P16" s="16">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="19">
         <v>94</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="21">
-        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2186,55 +2213,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="L17" s="4">
-        <v>-25.2</v>
+        <v>-36.8</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O17" s="10">
-        <v>84</v>
-      </c>
-      <c r="P17" s="23">
-        <v>77</v>
+        <v>203</v>
+      </c>
+      <c r="O17" s="9">
+        <v>86</v>
+      </c>
+      <c r="P17" s="15">
+        <v>4</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
       </c>
-      <c r="R17" s="16">
-        <v>50</v>
+      <c r="R17" s="10">
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2242,55 +2269,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="L18" s="4">
-        <v>-42.8</v>
+        <v>-15.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O18" s="6">
-        <v>12</v>
-      </c>
-      <c r="P18" s="8">
-        <v>1</v>
+        <v>205</v>
+      </c>
+      <c r="O18" s="9">
+        <v>72</v>
+      </c>
+      <c r="P18" s="15">
+        <v>3</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
       </c>
-      <c r="R18" s="24">
-        <v>12</v>
+      <c r="R18" s="13">
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2298,55 +2325,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L19" s="4">
-        <v>-61.8</v>
+        <v>-31.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O19" s="6">
-        <v>8</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="24">
-        <v>8</v>
+        <v>203</v>
+      </c>
+      <c r="O19" s="9">
+        <v>100</v>
+      </c>
+      <c r="P19" s="7">
+        <v>40</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>46</v>
+      </c>
+      <c r="R19" s="21">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2354,55 +2381,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>186</v>
+        <v>87</v>
       </c>
       <c r="L20" s="4">
-        <v>-36.8</v>
+        <v>-52.2</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O20" s="6">
-        <v>3</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
-        <v>3</v>
+        <v>203</v>
+      </c>
+      <c r="O20" s="9">
+        <v>100</v>
+      </c>
+      <c r="P20" s="22">
+        <v>36</v>
+      </c>
+      <c r="Q20" s="20">
+        <v>44</v>
+      </c>
+      <c r="R20" s="21">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2410,46 +2437,46 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>187</v>
+        <v>88</v>
       </c>
       <c r="L21" s="4">
-        <v>-15.7</v>
+        <v>-48.4</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O21" s="6">
-        <v>4</v>
+        <v>204</v>
+      </c>
+      <c r="O21" s="9">
+        <v>100</v>
       </c>
       <c r="P21" s="8">
         <v>0</v>
@@ -2457,8 +2484,8 @@
       <c r="Q21" s="8">
         <v>0</v>
       </c>
-      <c r="R21" s="7">
-        <v>4</v>
+      <c r="R21" s="21">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2466,55 +2493,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="L22" s="4">
-        <v>-31.7</v>
+        <v>-27.4</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O22" s="17">
-        <v>26</v>
-      </c>
-      <c r="P22" s="19">
-        <v>25</v>
+        <v>205</v>
+      </c>
+      <c r="O22" s="9">
+        <v>77</v>
+      </c>
+      <c r="P22" s="8">
+        <v>1</v>
       </c>
       <c r="Q22" s="8">
         <v>0</v>
       </c>
-      <c r="R22" s="8">
-        <v>0</v>
+      <c r="R22" s="23">
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2522,114 +2549,170 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-20.1</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O23" s="9">
+        <v>74</v>
+      </c>
+      <c r="P23" s="15">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="11">
         <v>60</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-52.2</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O23" s="17">
-        <v>29</v>
-      </c>
-      <c r="P23" s="18">
-        <v>29</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0</v>
-      </c>
       <c r="R23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2">
+        <v>41</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-41.3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O24" s="9">
+        <v>73</v>
+      </c>
+      <c r="P24" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>54</v>
+      </c>
+      <c r="R24" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A24">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B24">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C24">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D24">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F24">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G24">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H24">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I24">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J24">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K24">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2648,12 +2731,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M24">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N24">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2670,22 +2753,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O24">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P24">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q24">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R24">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="222">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261010--01</t>
-  </si>
-  <si>
-    <t>20261010--02</t>
-  </si>
-  <si>
     <t>20261011--01</t>
   </si>
   <si>
@@ -139,430 +133,475 @@
     <t>20261016--04</t>
   </si>
   <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:28</t>
+    <t>20261017--01</t>
+  </si>
+  <si>
+    <t>20261017--02</t>
+  </si>
+  <si>
+    <t>20261017--03</t>
+  </si>
+  <si>
+    <t>20261017--04</t>
   </si>
   <si>
     <t>03:14</t>
   </si>
   <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>06:01</t>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>06:00</t>
   </si>
   <si>
     <t>04:56</t>
   </si>
   <si>
-    <t>03:28</t>
+    <t>03:26</t>
   </si>
   <si>
     <t>04:39</t>
   </si>
   <si>
-    <t>05:56</t>
+    <t>05:55</t>
   </si>
   <si>
     <t>06:24</t>
   </si>
   <si>
-    <t>00:21</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>03:56</t>
-  </si>
-  <si>
-    <t>04:33</t>
+    <t>00:24</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>03:58</t>
+  </si>
+  <si>
+    <t>04:30</t>
   </si>
   <si>
     <t>06:18</t>
   </si>
   <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>02:23</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>06:09</t>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>02:16</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>04:08</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>02:39</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:22</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>02:18</t>
-  </si>
-  <si>
-    <t>03:51</t>
-  </si>
-  <si>
-    <t>00:51</t>
-  </si>
-  <si>
-    <t>00:31:40</t>
-  </si>
-  <si>
-    <t>23:38:57</t>
-  </si>
-  <si>
-    <t>01:17:00</t>
-  </si>
-  <si>
-    <t>06:11:18</t>
-  </si>
-  <si>
-    <t>22:46:24</t>
-  </si>
-  <si>
-    <t>00:23:44</t>
-  </si>
-  <si>
-    <t>05:18:42</t>
-  </si>
-  <si>
-    <t>21:54:02</t>
-  </si>
-  <si>
-    <t>23:30:32</t>
-  </si>
-  <si>
-    <t>06:02:29</t>
-  </si>
-  <si>
-    <t>22:37:28</t>
-  </si>
-  <si>
-    <t>00:15:56</t>
-  </si>
-  <si>
-    <t>05:09:40</t>
-  </si>
-  <si>
-    <t>21:44:32</t>
-  </si>
-  <si>
-    <t>23:22:19</t>
-  </si>
-  <si>
-    <t>04:16:50</t>
-  </si>
-  <si>
-    <t>05:53:33</t>
-  </si>
-  <si>
-    <t>20:51:46</t>
-  </si>
-  <si>
-    <t>22:28:48</t>
-  </si>
-  <si>
-    <t>03:23:56</t>
-  </si>
-  <si>
-    <t>05:00:27</t>
-  </si>
-  <si>
-    <t>19:59:15</t>
-  </si>
-  <si>
-    <t>21:35:22</t>
-  </si>
-  <si>
-    <t>00:33:46</t>
-  </si>
-  <si>
-    <t>23:41:01</t>
-  </si>
-  <si>
-    <t>01:19:58</t>
-  </si>
-  <si>
-    <t>06:13:45</t>
-  </si>
-  <si>
-    <t>22:48:33</t>
-  </si>
-  <si>
-    <t>00:26:10</t>
-  </si>
-  <si>
-    <t>05:21:37</t>
-  </si>
-  <si>
-    <t>21:56:31</t>
-  </si>
-  <si>
-    <t>23:32:44</t>
-  </si>
-  <si>
-    <t>06:04:37</t>
-  </si>
-  <si>
-    <t>22:39:33</t>
-  </si>
-  <si>
-    <t>00:20:13</t>
-  </si>
-  <si>
-    <t>05:11:57</t>
-  </si>
-  <si>
-    <t>21:46:37</t>
-  </si>
-  <si>
-    <t>23:25:03</t>
-  </si>
-  <si>
-    <t>04:19:25</t>
-  </si>
-  <si>
-    <t>05:55:41</t>
-  </si>
-  <si>
-    <t>20:54:00</t>
-  </si>
-  <si>
-    <t>22:31:08</t>
-  </si>
-  <si>
-    <t>03:27:13</t>
-  </si>
-  <si>
-    <t>05:02:32</t>
-  </si>
-  <si>
-    <t>20:02:00</t>
-  </si>
-  <si>
-    <t>21:37:31</t>
-  </si>
-  <si>
-    <t>00:36:55</t>
-  </si>
-  <si>
-    <t>23:44:14</t>
-  </si>
-  <si>
-    <t>01:21:35</t>
-  </si>
-  <si>
-    <t>06:16:18</t>
-  </si>
-  <si>
-    <t>22:51:33</t>
-  </si>
-  <si>
-    <t>00:28:38</t>
-  </si>
-  <si>
-    <t>05:23:21</t>
-  </si>
-  <si>
-    <t>21:58:50</t>
-  </si>
-  <si>
-    <t>23:35:41</t>
-  </si>
-  <si>
-    <t>06:07:49</t>
-  </si>
-  <si>
-    <t>22:42:45</t>
-  </si>
-  <si>
-    <t>05:14:49</t>
-  </si>
-  <si>
-    <t>21:49:47</t>
-  </si>
-  <si>
-    <t>23:27:01</t>
-  </si>
-  <si>
-    <t>04:21:41</t>
-  </si>
-  <si>
-    <t>05:58:50</t>
-  </si>
-  <si>
-    <t>20:56:49</t>
-  </si>
-  <si>
-    <t>22:33:48</t>
-  </si>
-  <si>
-    <t>03:28:24</t>
-  </si>
-  <si>
-    <t>05:05:48</t>
-  </si>
-  <si>
-    <t>20:03:50</t>
-  </si>
-  <si>
-    <t>21:40:35</t>
-  </si>
-  <si>
-    <t>00:40:05</t>
-  </si>
-  <si>
-    <t>23:47:29</t>
-  </si>
-  <si>
-    <t>01:23:12</t>
-  </si>
-  <si>
-    <t>06:18:51</t>
-  </si>
-  <si>
-    <t>22:54:34</t>
-  </si>
-  <si>
-    <t>00:31:06</t>
-  </si>
-  <si>
-    <t>05:25:05</t>
-  </si>
-  <si>
-    <t>22:01:10</t>
-  </si>
-  <si>
-    <t>23:38:40</t>
-  </si>
-  <si>
-    <t>06:11:01</t>
-  </si>
-  <si>
-    <t>22:45:57</t>
-  </si>
-  <si>
-    <t>00:20:34</t>
-  </si>
-  <si>
-    <t>05:17:42</t>
-  </si>
-  <si>
-    <t>21:52:59</t>
-  </si>
-  <si>
-    <t>23:28:59</t>
-  </si>
-  <si>
-    <t>04:23:58</t>
-  </si>
-  <si>
-    <t>06:01:59</t>
-  </si>
-  <si>
-    <t>20:59:39</t>
-  </si>
-  <si>
-    <t>22:36:29</t>
-  </si>
-  <si>
-    <t>03:29:36</t>
-  </si>
-  <si>
-    <t>05:09:03</t>
-  </si>
-  <si>
-    <t>20:05:40</t>
-  </si>
-  <si>
-    <t>21:43:40</t>
-  </si>
-  <si>
-    <t>00:42:13</t>
-  </si>
-  <si>
-    <t>23:49:34</t>
-  </si>
-  <si>
-    <t>01:26:11</t>
-  </si>
-  <si>
-    <t>06:21:18</t>
-  </si>
-  <si>
-    <t>22:56:44</t>
-  </si>
-  <si>
-    <t>00:33:35</t>
-  </si>
-  <si>
-    <t>05:28:00</t>
-  </si>
-  <si>
-    <t>22:03:39</t>
-  </si>
-  <si>
-    <t>23:40:53</t>
-  </si>
-  <si>
-    <t>06:13:08</t>
-  </si>
-  <si>
-    <t>22:48:04</t>
-  </si>
-  <si>
-    <t>00:24:33</t>
-  </si>
-  <si>
-    <t>05:19:58</t>
-  </si>
-  <si>
-    <t>21:55:05</t>
-  </si>
-  <si>
-    <t>23:31:44</t>
-  </si>
-  <si>
-    <t>04:26:32</t>
-  </si>
-  <si>
-    <t>06:04:07</t>
-  </si>
-  <si>
-    <t>21:01:54</t>
-  </si>
-  <si>
-    <t>22:38:50</t>
-  </si>
-  <si>
-    <t>03:32:52</t>
-  </si>
-  <si>
-    <t>05:11:09</t>
-  </si>
-  <si>
-    <t>20:08:26</t>
-  </si>
-  <si>
-    <t>21:45:50</t>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>03:49</t>
+  </si>
+  <si>
+    <t>00:48</t>
+  </si>
+  <si>
+    <t>00:27</t>
+  </si>
+  <si>
+    <t>01:16:59</t>
+  </si>
+  <si>
+    <t>06:11:17</t>
+  </si>
+  <si>
+    <t>22:46:20</t>
+  </si>
+  <si>
+    <t>00:23:39</t>
+  </si>
+  <si>
+    <t>05:18:37</t>
+  </si>
+  <si>
+    <t>21:53:53</t>
+  </si>
+  <si>
+    <t>23:30:22</t>
+  </si>
+  <si>
+    <t>06:02:16</t>
+  </si>
+  <si>
+    <t>22:37:09</t>
+  </si>
+  <si>
+    <t>00:15:35</t>
+  </si>
+  <si>
+    <t>05:09:18</t>
+  </si>
+  <si>
+    <t>21:44:02</t>
+  </si>
+  <si>
+    <t>23:21:48</t>
+  </si>
+  <si>
+    <t>04:16:16</t>
+  </si>
+  <si>
+    <t>05:52:58</t>
+  </si>
+  <si>
+    <t>20:51:03</t>
+  </si>
+  <si>
+    <t>22:28:02</t>
+  </si>
+  <si>
+    <t>03:23:08</t>
+  </si>
+  <si>
+    <t>04:59:37</t>
+  </si>
+  <si>
+    <t>19:58:16</t>
+  </si>
+  <si>
+    <t>21:34:20</t>
+  </si>
+  <si>
+    <t>04:06:16</t>
+  </si>
+  <si>
+    <t>05:43:34</t>
+  </si>
+  <si>
+    <t>20:40:44</t>
+  </si>
+  <si>
+    <t>22:18:52</t>
+  </si>
+  <si>
+    <t>01:19:57</t>
+  </si>
+  <si>
+    <t>06:13:43</t>
+  </si>
+  <si>
+    <t>22:48:29</t>
+  </si>
+  <si>
+    <t>00:26:06</t>
+  </si>
+  <si>
+    <t>05:21:32</t>
+  </si>
+  <si>
+    <t>21:56:21</t>
+  </si>
+  <si>
+    <t>23:32:34</t>
+  </si>
+  <si>
+    <t>06:04:24</t>
+  </si>
+  <si>
+    <t>22:39:14</t>
+  </si>
+  <si>
+    <t>00:19:53</t>
+  </si>
+  <si>
+    <t>05:11:35</t>
+  </si>
+  <si>
+    <t>21:46:07</t>
+  </si>
+  <si>
+    <t>23:24:30</t>
+  </si>
+  <si>
+    <t>04:18:52</t>
+  </si>
+  <si>
+    <t>05:55:06</t>
+  </si>
+  <si>
+    <t>20:53:17</t>
+  </si>
+  <si>
+    <t>22:30:22</t>
+  </si>
+  <si>
+    <t>03:26:27</t>
+  </si>
+  <si>
+    <t>05:01:43</t>
+  </si>
+  <si>
+    <t>20:01:03</t>
+  </si>
+  <si>
+    <t>21:36:28</t>
+  </si>
+  <si>
+    <t>04:08:26</t>
+  </si>
+  <si>
+    <t>05:46:12</t>
+  </si>
+  <si>
+    <t>20:42:48</t>
+  </si>
+  <si>
+    <t>22:22:01</t>
+  </si>
+  <si>
+    <t>01:21:33</t>
+  </si>
+  <si>
+    <t>06:16:17</t>
+  </si>
+  <si>
+    <t>22:51:29</t>
+  </si>
+  <si>
+    <t>00:28:33</t>
+  </si>
+  <si>
+    <t>05:23:15</t>
+  </si>
+  <si>
+    <t>21:58:40</t>
+  </si>
+  <si>
+    <t>23:35:31</t>
+  </si>
+  <si>
+    <t>06:07:36</t>
+  </si>
+  <si>
+    <t>22:42:25</t>
+  </si>
+  <si>
+    <t>05:14:27</t>
+  </si>
+  <si>
+    <t>21:49:17</t>
+  </si>
+  <si>
+    <t>23:26:29</t>
+  </si>
+  <si>
+    <t>04:21:07</t>
+  </si>
+  <si>
+    <t>05:58:15</t>
+  </si>
+  <si>
+    <t>20:56:05</t>
+  </si>
+  <si>
+    <t>22:33:02</t>
+  </si>
+  <si>
+    <t>03:27:35</t>
+  </si>
+  <si>
+    <t>05:04:58</t>
+  </si>
+  <si>
+    <t>20:02:49</t>
+  </si>
+  <si>
+    <t>21:39:33</t>
+  </si>
+  <si>
+    <t>04:11:30</t>
+  </si>
+  <si>
+    <t>05:48:16</t>
+  </si>
+  <si>
+    <t>20:46:01</t>
+  </si>
+  <si>
+    <t>22:23:20</t>
+  </si>
+  <si>
+    <t>01:23:11</t>
+  </si>
+  <si>
+    <t>06:18:50</t>
+  </si>
+  <si>
+    <t>22:54:29</t>
+  </si>
+  <si>
+    <t>00:31:02</t>
+  </si>
+  <si>
+    <t>05:24:58</t>
+  </si>
+  <si>
+    <t>22:01:00</t>
+  </si>
+  <si>
+    <t>23:38:29</t>
+  </si>
+  <si>
+    <t>06:10:48</t>
+  </si>
+  <si>
+    <t>22:45:38</t>
+  </si>
+  <si>
+    <t>00:20:17</t>
+  </si>
+  <si>
+    <t>05:17:19</t>
+  </si>
+  <si>
+    <t>21:52:28</t>
+  </si>
+  <si>
+    <t>23:28:28</t>
+  </si>
+  <si>
+    <t>04:23:22</t>
+  </si>
+  <si>
+    <t>06:01:24</t>
+  </si>
+  <si>
+    <t>20:58:53</t>
+  </si>
+  <si>
+    <t>22:35:44</t>
+  </si>
+  <si>
+    <t>03:28:43</t>
+  </si>
+  <si>
+    <t>05:08:13</t>
+  </si>
+  <si>
+    <t>20:04:36</t>
+  </si>
+  <si>
+    <t>21:42:38</t>
+  </si>
+  <si>
+    <t>04:14:34</t>
+  </si>
+  <si>
+    <t>05:50:20</t>
+  </si>
+  <si>
+    <t>20:49:14</t>
+  </si>
+  <si>
+    <t>22:24:40</t>
+  </si>
+  <si>
+    <t>01:26:09</t>
+  </si>
+  <si>
+    <t>06:21:16</t>
+  </si>
+  <si>
+    <t>22:56:40</t>
+  </si>
+  <si>
+    <t>00:33:30</t>
+  </si>
+  <si>
+    <t>05:27:54</t>
+  </si>
+  <si>
+    <t>22:03:29</t>
+  </si>
+  <si>
+    <t>23:40:42</t>
+  </si>
+  <si>
+    <t>06:12:55</t>
+  </si>
+  <si>
+    <t>22:47:44</t>
+  </si>
+  <si>
+    <t>00:24:13</t>
+  </si>
+  <si>
+    <t>05:19:35</t>
+  </si>
+  <si>
+    <t>21:54:34</t>
+  </si>
+  <si>
+    <t>23:31:12</t>
+  </si>
+  <si>
+    <t>04:25:57</t>
+  </si>
+  <si>
+    <t>06:03:32</t>
+  </si>
+  <si>
+    <t>21:01:09</t>
+  </si>
+  <si>
+    <t>22:38:05</t>
+  </si>
+  <si>
+    <t>03:32:02</t>
+  </si>
+  <si>
+    <t>05:10:18</t>
+  </si>
+  <si>
+    <t>20:07:24</t>
+  </si>
+  <si>
+    <t>21:44:48</t>
+  </si>
+  <si>
+    <t>04:16:44</t>
+  </si>
+  <si>
+    <t>20:51:20</t>
+  </si>
+  <si>
+    <t>22:27:49</t>
   </si>
   <si>
     <t>0°</t>
@@ -583,37 +622,46 @@
     <t>4°</t>
   </si>
   <si>
-    <t>39°</t>
-  </si>
-  <si>
-    <t>17°</t>
+    <t>40°</t>
   </si>
   <si>
     <t>8°</t>
   </si>
   <si>
-    <t>06:12:46</t>
-  </si>
-  <si>
-    <t>05:22:43</t>
-  </si>
-  <si>
-    <t>06:05:23</t>
-  </si>
-  <si>
-    <t>05:15:24</t>
-  </si>
-  <si>
-    <t>04:25:27</t>
-  </si>
-  <si>
-    <t>05:58:08</t>
-  </si>
-  <si>
-    <t>05:08:12</t>
-  </si>
-  <si>
-    <t>20:01:21</t>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>06:12:45</t>
+  </si>
+  <si>
+    <t>05:22:38</t>
+  </si>
+  <si>
+    <t>06:05:11</t>
+  </si>
+  <si>
+    <t>05:15:03</t>
+  </si>
+  <si>
+    <t>04:24:55</t>
+  </si>
+  <si>
+    <t>05:57:35</t>
+  </si>
+  <si>
+    <t>05:07:25</t>
+  </si>
+  <si>
+    <t>20:00:23</t>
+  </si>
+  <si>
+    <t>05:49:53</t>
+  </si>
+  <si>
+    <t>20:42:42</t>
   </si>
   <si>
     <t>B</t>
@@ -625,13 +673,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -665,7 +713,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,13 +728,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,7 +746,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,61 +818,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,13 +842,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -823,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -892,6 +952,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1295,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1373,55 +1439,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L2" s="4">
-        <v>-67.90000000000001</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="O2" s="6">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="P2" s="7">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1429,55 +1495,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>206</v>
       </c>
       <c r="L3" s="4">
-        <v>-63.2</v>
+        <v>-11.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="O3" s="9">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="P3" s="10">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="11">
-        <v>60</v>
+      <c r="R3" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1485,55 +1551,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-54.5</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="O4" s="9">
         <v>43</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-67.59999999999999</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O4" s="9">
-        <v>90</v>
-      </c>
-      <c r="P4" s="12">
-        <v>90</v>
+      <c r="P4" s="11">
+        <v>3</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="11">
-        <v>60</v>
+      <c r="R4" s="10">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1541,55 +1607,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="L5" s="4">
-        <v>-11.5</v>
+        <v>-68.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O5" s="9">
-        <v>69</v>
-      </c>
-      <c r="P5" s="13">
-        <v>69</v>
+        <v>221</v>
+      </c>
+      <c r="O5" s="6">
+        <v>52</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>2</v>
+      <c r="R5" s="12">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1597,55 +1663,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="L6" s="4">
-        <v>-54.5</v>
+        <v>-23.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O6" s="9">
-        <v>95</v>
-      </c>
-      <c r="P6" s="14">
-        <v>14</v>
+        <v>219</v>
+      </c>
+      <c r="O6" s="6">
+        <v>83</v>
+      </c>
+      <c r="P6" s="13">
+        <v>51</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
       </c>
       <c r="R6" s="14">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1653,55 +1719,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4">
-        <v>-68.3</v>
+        <v>-44.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O7" s="9">
-        <v>47</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
+        <v>221</v>
+      </c>
+      <c r="O7" s="6">
+        <v>59</v>
+      </c>
+      <c r="P7" s="15">
+        <v>59</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="15">
-        <v>7</v>
+      <c r="R7" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1709,55 +1775,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="L8" s="4">
-        <v>-23.1</v>
+        <v>-62.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O8" s="9">
-        <v>48</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
+        <v>221</v>
+      </c>
+      <c r="O8" s="6">
+        <v>44</v>
+      </c>
+      <c r="P8" s="16">
+        <v>43</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
       </c>
       <c r="R8" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1765,55 +1831,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="L9" s="4">
-        <v>-44.2</v>
+        <v>-13.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O9" s="9">
-        <v>57</v>
-      </c>
-      <c r="P9" s="16">
-        <v>54</v>
+        <v>220</v>
+      </c>
+      <c r="O9" s="6">
+        <v>96</v>
+      </c>
+      <c r="P9" s="17">
+        <v>92</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="8">
-        <v>0</v>
+      <c r="R9" s="18">
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1821,55 +1887,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L10" s="4">
-        <v>-62.6</v>
+        <v>-53.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O10" s="9">
-        <v>63</v>
-      </c>
-      <c r="P10" s="17">
-        <v>63</v>
+        <v>221</v>
+      </c>
+      <c r="O10" s="6">
+        <v>91</v>
+      </c>
+      <c r="P10" s="18">
+        <v>79</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="8">
-        <v>0</v>
+      <c r="R10" s="17">
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1877,55 +1943,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="L11" s="4">
-        <v>-13.6</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O11" s="9">
-        <v>54</v>
-      </c>
-      <c r="P11" s="18">
-        <v>51</v>
+        <v>219</v>
+      </c>
+      <c r="O11" s="6">
+        <v>83</v>
+      </c>
+      <c r="P11" s="19">
+        <v>71</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="14">
-        <v>13</v>
+      <c r="R11" s="20">
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1933,55 +1999,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="L12" s="4">
-        <v>-53.4</v>
+        <v>-25.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O12" s="9">
-        <v>59</v>
-      </c>
-      <c r="P12" s="11">
-        <v>59</v>
+        <v>220</v>
+      </c>
+      <c r="O12" s="6">
+        <v>92</v>
+      </c>
+      <c r="P12" s="21">
+        <v>12</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="8">
-        <v>0</v>
+      <c r="R12" s="22">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1989,55 +2055,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L13" s="4">
-        <v>-68.40000000000001</v>
+        <v>-42.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" s="9">
-        <v>75</v>
-      </c>
-      <c r="P13" s="13">
-        <v>71</v>
+        <v>221</v>
+      </c>
+      <c r="O13" s="6">
+        <v>92</v>
+      </c>
+      <c r="P13" s="8">
+        <v>1</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="R13" s="17">
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2045,55 +2111,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="L14" s="4">
-        <v>-25.2</v>
+        <v>-61.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="O14" s="9">
-        <v>90</v>
-      </c>
-      <c r="P14" s="17">
-        <v>63</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="15">
-        <v>3</v>
+        <v>48</v>
+      </c>
+      <c r="P14" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>4</v>
+      </c>
+      <c r="R14" s="12">
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2101,55 +2167,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="L15" s="4">
-        <v>-42.8</v>
+        <v>-36.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O15" s="9">
-        <v>100</v>
-      </c>
-      <c r="P15" s="18">
-        <v>49</v>
+        <v>221</v>
+      </c>
+      <c r="O15" s="6">
+        <v>90</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="19">
-        <v>93</v>
+      <c r="R15" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2157,55 +2223,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="L16" s="4">
-        <v>-61.8</v>
+        <v>-15.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O16" s="9">
-        <v>100</v>
-      </c>
-      <c r="P16" s="16">
-        <v>55</v>
+        <v>220</v>
+      </c>
+      <c r="O16" s="6">
+        <v>90</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
       </c>
-      <c r="R16" s="19">
-        <v>94</v>
+      <c r="R16" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2213,55 +2279,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="L17" s="4">
-        <v>-36.8</v>
+        <v>-31.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O17" s="9">
-        <v>86</v>
-      </c>
-      <c r="P17" s="15">
-        <v>4</v>
+        <v>221</v>
+      </c>
+      <c r="O17" s="6">
+        <v>100</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
       </c>
-      <c r="R17" s="10">
-        <v>85</v>
+      <c r="R17" s="17">
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2269,55 +2335,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="L18" s="4">
-        <v>-15.7</v>
+        <v>-52</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O18" s="9">
-        <v>72</v>
-      </c>
-      <c r="P18" s="15">
-        <v>3</v>
+        <v>221</v>
+      </c>
+      <c r="O18" s="6">
+        <v>75</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
       </c>
-      <c r="R18" s="13">
-        <v>71</v>
+      <c r="R18" s="23">
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2325,54 +2391,54 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L19" s="4">
-        <v>-31.6</v>
+        <v>-48.5</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O19" s="9">
+        <v>219</v>
+      </c>
+      <c r="O19" s="6">
         <v>100</v>
       </c>
-      <c r="P19" s="7">
-        <v>40</v>
-      </c>
-      <c r="Q19" s="20">
-        <v>46</v>
-      </c>
-      <c r="R19" s="21">
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="24">
         <v>100</v>
       </c>
     </row>
@@ -2381,55 +2447,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>87</v>
+        <v>212</v>
       </c>
       <c r="L20" s="4">
-        <v>-52.2</v>
+        <v>-27.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O20" s="9">
-        <v>100</v>
-      </c>
-      <c r="P20" s="22">
-        <v>36</v>
-      </c>
-      <c r="Q20" s="20">
-        <v>44</v>
-      </c>
-      <c r="R20" s="21">
-        <v>100</v>
+        <v>220</v>
+      </c>
+      <c r="O20" s="6">
+        <v>96</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7">
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2437,55 +2503,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="L21" s="4">
-        <v>-48.4</v>
+        <v>-19.8</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O21" s="9">
-        <v>100</v>
-      </c>
-      <c r="P21" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="21">
-        <v>100</v>
+        <v>219</v>
+      </c>
+      <c r="O21" s="6">
+        <v>91</v>
+      </c>
+      <c r="P21" s="25">
+        <v>20</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>90</v>
+      </c>
+      <c r="R21" s="22">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2493,55 +2559,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>198</v>
+        <v>93</v>
       </c>
       <c r="L22" s="4">
-        <v>-27.4</v>
+        <v>-41.1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O22" s="9">
-        <v>77</v>
-      </c>
-      <c r="P22" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
-      </c>
-      <c r="R22" s="23">
-        <v>77</v>
+        <v>221</v>
+      </c>
+      <c r="O22" s="6">
+        <v>95</v>
+      </c>
+      <c r="P22" s="10">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>95</v>
+      </c>
+      <c r="R22" s="22">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2549,55 +2615,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>199</v>
+        <v>94</v>
       </c>
       <c r="L23" s="4">
-        <v>-20.1</v>
+        <v>-39.4</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O23" s="9">
+        <v>221</v>
+      </c>
+      <c r="O23" s="6">
+        <v>75</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="23">
         <v>74</v>
       </c>
-      <c r="P23" s="15">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="11">
-        <v>60</v>
-      </c>
-      <c r="R23" s="8">
-        <v>0</v>
+      <c r="R23" s="15">
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2605,114 +2671,226 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
+        <v>16</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-18.2</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O24" s="6">
+        <v>72</v>
+      </c>
+      <c r="P24" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>70</v>
+      </c>
+      <c r="R24" s="22">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-41.3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O24" s="9">
-        <v>73</v>
-      </c>
-      <c r="P24" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="16">
-        <v>54</v>
-      </c>
-      <c r="R24" s="8">
+      <c r="B25" s="2">
+        <v>88</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-29.6</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="O25" s="6">
+        <v>93</v>
+      </c>
+      <c r="P25" s="10">
+        <v>27</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>93</v>
+      </c>
+      <c r="R25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-50.5</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O26" s="6">
+        <v>87</v>
+      </c>
+      <c r="P26" s="22">
+        <v>28</v>
+      </c>
+      <c r="Q26" s="20">
+        <v>87</v>
+      </c>
+      <c r="R26" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A24">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B24">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C24">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D24">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F24">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G24">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H24">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I24">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J24">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K24">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L24">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2731,12 +2909,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M24">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N24">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2753,22 +2931,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O24">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q24">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R24">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="234">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261011--01</t>
-  </si>
-  <si>
-    <t>20261011--02</t>
-  </si>
-  <si>
-    <t>20261011--03</t>
-  </si>
-  <si>
     <t>20261012--01</t>
   </si>
   <si>
@@ -145,22 +136,25 @@
     <t>20261017--04</t>
   </si>
   <si>
-    <t>03:14</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>04:56</t>
+    <t>20261018--01</t>
+  </si>
+  <si>
+    <t>20261018--02</t>
+  </si>
+  <si>
+    <t>20261018--03</t>
+  </si>
+  <si>
+    <t>20261018--04</t>
+  </si>
+  <si>
+    <t>04:55</t>
   </si>
   <si>
     <t>03:26</t>
   </si>
   <si>
-    <t>04:39</t>
+    <t>04:38</t>
   </si>
   <si>
     <t>05:55</t>
@@ -169,7 +163,7 @@
     <t>06:24</t>
   </si>
   <si>
-    <t>00:24</t>
+    <t>00:22</t>
   </si>
   <si>
     <t>05:44</t>
@@ -178,145 +172,154 @@
     <t>06:21</t>
   </si>
   <si>
-    <t>03:58</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>06:18</t>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>06:19</t>
   </si>
   <si>
     <t>05:36</t>
   </si>
   <si>
-    <t>05:22</t>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>03:34</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>05:38</t>
   </si>
   <si>
     <t>02:16</t>
   </si>
   <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>03:33</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>04:08</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>02:39</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>03:49</t>
-  </si>
-  <si>
-    <t>00:48</t>
-  </si>
-  <si>
-    <t>00:27</t>
-  </si>
-  <si>
-    <t>01:16:59</t>
-  </si>
-  <si>
-    <t>06:11:17</t>
-  </si>
-  <si>
-    <t>22:46:20</t>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>00:49</t>
+  </si>
+  <si>
+    <t>00:28</t>
+  </si>
+  <si>
+    <t>02:47</t>
   </si>
   <si>
     <t>00:23:39</t>
   </si>
   <si>
-    <t>05:18:37</t>
-  </si>
-  <si>
-    <t>21:53:53</t>
-  </si>
-  <si>
-    <t>23:30:22</t>
-  </si>
-  <si>
-    <t>06:02:16</t>
-  </si>
-  <si>
-    <t>22:37:09</t>
-  </si>
-  <si>
-    <t>00:15:35</t>
-  </si>
-  <si>
-    <t>05:09:18</t>
-  </si>
-  <si>
-    <t>21:44:02</t>
-  </si>
-  <si>
-    <t>23:21:48</t>
-  </si>
-  <si>
-    <t>04:16:16</t>
-  </si>
-  <si>
-    <t>05:52:58</t>
-  </si>
-  <si>
-    <t>20:51:03</t>
-  </si>
-  <si>
-    <t>22:28:02</t>
-  </si>
-  <si>
-    <t>03:23:08</t>
-  </si>
-  <si>
-    <t>04:59:37</t>
-  </si>
-  <si>
-    <t>19:58:16</t>
-  </si>
-  <si>
-    <t>21:34:20</t>
-  </si>
-  <si>
-    <t>04:06:16</t>
-  </si>
-  <si>
-    <t>05:43:34</t>
-  </si>
-  <si>
-    <t>20:40:44</t>
-  </si>
-  <si>
-    <t>22:18:52</t>
-  </si>
-  <si>
-    <t>01:19:57</t>
-  </si>
-  <si>
-    <t>06:13:43</t>
-  </si>
-  <si>
-    <t>22:48:29</t>
+    <t>05:18:36</t>
+  </si>
+  <si>
+    <t>21:53:54</t>
+  </si>
+  <si>
+    <t>23:30:23</t>
+  </si>
+  <si>
+    <t>06:02:18</t>
+  </si>
+  <si>
+    <t>22:37:13</t>
+  </si>
+  <si>
+    <t>00:15:40</t>
+  </si>
+  <si>
+    <t>05:09:23</t>
+  </si>
+  <si>
+    <t>21:44:11</t>
+  </si>
+  <si>
+    <t>23:21:57</t>
+  </si>
+  <si>
+    <t>04:16:27</t>
+  </si>
+  <si>
+    <t>05:53:09</t>
+  </si>
+  <si>
+    <t>20:51:18</t>
+  </si>
+  <si>
+    <t>22:28:18</t>
+  </si>
+  <si>
+    <t>03:23:25</t>
+  </si>
+  <si>
+    <t>04:59:55</t>
+  </si>
+  <si>
+    <t>19:58:39</t>
+  </si>
+  <si>
+    <t>21:34:44</t>
+  </si>
+  <si>
+    <t>04:06:42</t>
+  </si>
+  <si>
+    <t>05:44:01</t>
+  </si>
+  <si>
+    <t>20:41:18</t>
+  </si>
+  <si>
+    <t>22:19:28</t>
+  </si>
+  <si>
+    <t>03:13:28</t>
+  </si>
+  <si>
+    <t>04:50:19</t>
+  </si>
+  <si>
+    <t>19:48:00</t>
+  </si>
+  <si>
+    <t>21:25:27</t>
   </si>
   <si>
     <t>00:26:06</t>
@@ -325,73 +328,76 @@
     <t>05:21:32</t>
   </si>
   <si>
-    <t>21:56:21</t>
-  </si>
-  <si>
-    <t>23:32:34</t>
-  </si>
-  <si>
-    <t>06:04:24</t>
-  </si>
-  <si>
-    <t>22:39:14</t>
-  </si>
-  <si>
-    <t>00:19:53</t>
-  </si>
-  <si>
-    <t>05:11:35</t>
-  </si>
-  <si>
-    <t>21:46:07</t>
-  </si>
-  <si>
-    <t>23:24:30</t>
-  </si>
-  <si>
-    <t>04:18:52</t>
-  </si>
-  <si>
-    <t>05:55:06</t>
-  </si>
-  <si>
-    <t>20:53:17</t>
-  </si>
-  <si>
-    <t>22:30:22</t>
-  </si>
-  <si>
-    <t>03:26:27</t>
-  </si>
-  <si>
-    <t>05:01:43</t>
-  </si>
-  <si>
-    <t>20:01:03</t>
-  </si>
-  <si>
-    <t>21:36:28</t>
-  </si>
-  <si>
-    <t>04:08:26</t>
-  </si>
-  <si>
-    <t>05:46:12</t>
-  </si>
-  <si>
-    <t>20:42:48</t>
-  </si>
-  <si>
-    <t>22:22:01</t>
-  </si>
-  <si>
-    <t>01:21:33</t>
-  </si>
-  <si>
-    <t>06:16:17</t>
-  </si>
-  <si>
-    <t>22:51:29</t>
+    <t>21:56:22</t>
+  </si>
+  <si>
+    <t>23:32:35</t>
+  </si>
+  <si>
+    <t>06:04:26</t>
+  </si>
+  <si>
+    <t>22:39:18</t>
+  </si>
+  <si>
+    <t>00:19:58</t>
+  </si>
+  <si>
+    <t>05:11:40</t>
+  </si>
+  <si>
+    <t>21:46:16</t>
+  </si>
+  <si>
+    <t>23:24:40</t>
+  </si>
+  <si>
+    <t>04:19:02</t>
+  </si>
+  <si>
+    <t>05:55:16</t>
+  </si>
+  <si>
+    <t>20:53:33</t>
+  </si>
+  <si>
+    <t>22:30:38</t>
+  </si>
+  <si>
+    <t>03:26:43</t>
+  </si>
+  <si>
+    <t>05:02:00</t>
+  </si>
+  <si>
+    <t>20:01:26</t>
+  </si>
+  <si>
+    <t>21:36:53</t>
+  </si>
+  <si>
+    <t>04:08:52</t>
+  </si>
+  <si>
+    <t>05:46:40</t>
+  </si>
+  <si>
+    <t>20:43:22</t>
+  </si>
+  <si>
+    <t>22:22:38</t>
+  </si>
+  <si>
+    <t>03:15:50</t>
+  </si>
+  <si>
+    <t>04:52:33</t>
+  </si>
+  <si>
+    <t>19:50:08</t>
+  </si>
+  <si>
+    <t>21:27:58</t>
   </si>
   <si>
     <t>00:28:33</t>
@@ -400,73 +406,76 @@
     <t>05:23:15</t>
   </si>
   <si>
-    <t>21:58:40</t>
+    <t>21:58:41</t>
   </si>
   <si>
     <t>23:35:31</t>
   </si>
   <si>
-    <t>06:07:36</t>
-  </si>
-  <si>
-    <t>22:42:25</t>
-  </si>
-  <si>
-    <t>05:14:27</t>
-  </si>
-  <si>
-    <t>21:49:17</t>
-  </si>
-  <si>
-    <t>23:26:29</t>
-  </si>
-  <si>
-    <t>04:21:07</t>
-  </si>
-  <si>
-    <t>05:58:15</t>
-  </si>
-  <si>
-    <t>20:56:05</t>
-  </si>
-  <si>
-    <t>22:33:02</t>
-  </si>
-  <si>
-    <t>03:27:35</t>
-  </si>
-  <si>
-    <t>05:04:58</t>
-  </si>
-  <si>
-    <t>20:02:49</t>
-  </si>
-  <si>
-    <t>21:39:33</t>
-  </si>
-  <si>
-    <t>04:11:30</t>
-  </si>
-  <si>
-    <t>05:48:16</t>
-  </si>
-  <si>
-    <t>20:46:01</t>
-  </si>
-  <si>
-    <t>22:23:20</t>
-  </si>
-  <si>
-    <t>01:23:11</t>
-  </si>
-  <si>
-    <t>06:18:50</t>
-  </si>
-  <si>
-    <t>22:54:29</t>
-  </si>
-  <si>
-    <t>00:31:02</t>
+    <t>06:07:38</t>
+  </si>
+  <si>
+    <t>22:42:29</t>
+  </si>
+  <si>
+    <t>05:14:32</t>
+  </si>
+  <si>
+    <t>21:49:26</t>
+  </si>
+  <si>
+    <t>23:26:38</t>
+  </si>
+  <si>
+    <t>04:21:17</t>
+  </si>
+  <si>
+    <t>05:58:26</t>
+  </si>
+  <si>
+    <t>20:56:20</t>
+  </si>
+  <si>
+    <t>22:33:18</t>
+  </si>
+  <si>
+    <t>03:27:53</t>
+  </si>
+  <si>
+    <t>05:05:16</t>
+  </si>
+  <si>
+    <t>20:03:13</t>
+  </si>
+  <si>
+    <t>21:39:57</t>
+  </si>
+  <si>
+    <t>04:11:57</t>
+  </si>
+  <si>
+    <t>05:48:43</t>
+  </si>
+  <si>
+    <t>20:46:35</t>
+  </si>
+  <si>
+    <t>22:23:55</t>
+  </si>
+  <si>
+    <t>03:18:28</t>
+  </si>
+  <si>
+    <t>04:55:27</t>
+  </si>
+  <si>
+    <t>19:53:11</t>
+  </si>
+  <si>
+    <t>21:30:16</t>
+  </si>
+  <si>
+    <t>00:31:01</t>
   </si>
   <si>
     <t>05:24:58</t>
@@ -475,141 +484,156 @@
     <t>22:01:00</t>
   </si>
   <si>
-    <t>23:38:29</t>
-  </si>
-  <si>
-    <t>06:10:48</t>
-  </si>
-  <si>
-    <t>22:45:38</t>
-  </si>
-  <si>
-    <t>00:20:17</t>
-  </si>
-  <si>
-    <t>05:17:19</t>
-  </si>
-  <si>
-    <t>21:52:28</t>
-  </si>
-  <si>
-    <t>23:28:28</t>
-  </si>
-  <si>
-    <t>04:23:22</t>
-  </si>
-  <si>
-    <t>06:01:24</t>
-  </si>
-  <si>
-    <t>20:58:53</t>
-  </si>
-  <si>
-    <t>22:35:44</t>
-  </si>
-  <si>
-    <t>03:28:43</t>
-  </si>
-  <si>
-    <t>05:08:13</t>
-  </si>
-  <si>
-    <t>20:04:36</t>
-  </si>
-  <si>
-    <t>21:42:38</t>
-  </si>
-  <si>
-    <t>04:14:34</t>
-  </si>
-  <si>
-    <t>05:50:20</t>
-  </si>
-  <si>
-    <t>20:49:14</t>
-  </si>
-  <si>
-    <t>22:24:40</t>
-  </si>
-  <si>
-    <t>01:26:09</t>
-  </si>
-  <si>
-    <t>06:21:16</t>
-  </si>
-  <si>
-    <t>22:56:40</t>
-  </si>
-  <si>
-    <t>00:33:30</t>
-  </si>
-  <si>
-    <t>05:27:54</t>
-  </si>
-  <si>
-    <t>22:03:29</t>
-  </si>
-  <si>
-    <t>23:40:42</t>
-  </si>
-  <si>
-    <t>06:12:55</t>
-  </si>
-  <si>
-    <t>22:47:44</t>
-  </si>
-  <si>
-    <t>00:24:13</t>
-  </si>
-  <si>
-    <t>05:19:35</t>
-  </si>
-  <si>
-    <t>21:54:34</t>
-  </si>
-  <si>
-    <t>23:31:12</t>
-  </si>
-  <si>
-    <t>04:25:57</t>
-  </si>
-  <si>
-    <t>06:03:32</t>
-  </si>
-  <si>
-    <t>21:01:09</t>
-  </si>
-  <si>
-    <t>22:38:05</t>
-  </si>
-  <si>
-    <t>03:32:02</t>
-  </si>
-  <si>
-    <t>05:10:18</t>
-  </si>
-  <si>
-    <t>20:07:24</t>
-  </si>
-  <si>
-    <t>21:44:48</t>
-  </si>
-  <si>
-    <t>04:16:44</t>
-  </si>
-  <si>
-    <t>20:51:20</t>
-  </si>
-  <si>
-    <t>22:27:49</t>
+    <t>23:38:30</t>
+  </si>
+  <si>
+    <t>06:10:50</t>
+  </si>
+  <si>
+    <t>22:45:42</t>
+  </si>
+  <si>
+    <t>00:20:20</t>
+  </si>
+  <si>
+    <t>05:17:24</t>
+  </si>
+  <si>
+    <t>21:52:37</t>
+  </si>
+  <si>
+    <t>23:28:37</t>
+  </si>
+  <si>
+    <t>04:23:33</t>
+  </si>
+  <si>
+    <t>06:01:35</t>
+  </si>
+  <si>
+    <t>20:59:09</t>
+  </si>
+  <si>
+    <t>22:35:59</t>
+  </si>
+  <si>
+    <t>03:29:02</t>
+  </si>
+  <si>
+    <t>05:08:31</t>
+  </si>
+  <si>
+    <t>20:05:00</t>
+  </si>
+  <si>
+    <t>21:43:02</t>
+  </si>
+  <si>
+    <t>04:15:01</t>
+  </si>
+  <si>
+    <t>05:50:46</t>
+  </si>
+  <si>
+    <t>20:49:49</t>
+  </si>
+  <si>
+    <t>22:25:13</t>
+  </si>
+  <si>
+    <t>03:21:06</t>
+  </si>
+  <si>
+    <t>04:58:22</t>
+  </si>
+  <si>
+    <t>19:56:16</t>
+  </si>
+  <si>
+    <t>21:32:35</t>
+  </si>
+  <si>
+    <t>00:33:29</t>
+  </si>
+  <si>
+    <t>05:27:53</t>
+  </si>
+  <si>
+    <t>22:03:30</t>
+  </si>
+  <si>
+    <t>23:40:43</t>
+  </si>
+  <si>
+    <t>06:12:57</t>
+  </si>
+  <si>
+    <t>22:47:48</t>
+  </si>
+  <si>
+    <t>00:24:17</t>
+  </si>
+  <si>
+    <t>05:19:41</t>
+  </si>
+  <si>
+    <t>21:54:43</t>
+  </si>
+  <si>
+    <t>23:31:21</t>
+  </si>
+  <si>
+    <t>04:26:08</t>
+  </si>
+  <si>
+    <t>06:03:43</t>
+  </si>
+  <si>
+    <t>21:01:24</t>
+  </si>
+  <si>
+    <t>22:38:20</t>
+  </si>
+  <si>
+    <t>03:32:20</t>
+  </si>
+  <si>
+    <t>05:10:37</t>
+  </si>
+  <si>
+    <t>20:07:47</t>
+  </si>
+  <si>
+    <t>21:45:12</t>
+  </si>
+  <si>
+    <t>04:17:11</t>
+  </si>
+  <si>
+    <t>05:53:25</t>
+  </si>
+  <si>
+    <t>20:51:54</t>
+  </si>
+  <si>
+    <t>22:28:24</t>
+  </si>
+  <si>
+    <t>03:23:29</t>
+  </si>
+  <si>
+    <t>05:00:35</t>
+  </si>
+  <si>
+    <t>19:58:24</t>
+  </si>
+  <si>
+    <t>21:35:07</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>6°</t>
-  </si>
-  <si>
     <t>13°</t>
   </si>
   <si>
@@ -622,10 +646,13 @@
     <t>4°</t>
   </si>
   <si>
-    <t>40°</t>
-  </si>
-  <si>
-    <t>8°</t>
+    <t>39°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>7°</t>
   </si>
   <si>
     <t>12°</t>
@@ -634,52 +661,61 @@
     <t>9°</t>
   </si>
   <si>
-    <t>06:12:45</t>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>41°</t>
   </si>
   <si>
     <t>05:22:38</t>
   </si>
   <si>
-    <t>06:05:11</t>
-  </si>
-  <si>
-    <t>05:15:03</t>
-  </si>
-  <si>
-    <t>04:24:55</t>
-  </si>
-  <si>
-    <t>05:57:35</t>
-  </si>
-  <si>
-    <t>05:07:25</t>
-  </si>
-  <si>
-    <t>20:00:23</t>
-  </si>
-  <si>
-    <t>05:49:53</t>
-  </si>
-  <si>
-    <t>20:42:42</t>
+    <t>06:05:12</t>
+  </si>
+  <si>
+    <t>05:15:08</t>
+  </si>
+  <si>
+    <t>04:25:05</t>
+  </si>
+  <si>
+    <t>05:57:45</t>
+  </si>
+  <si>
+    <t>05:07:42</t>
+  </si>
+  <si>
+    <t>20:00:45</t>
+  </si>
+  <si>
+    <t>05:50:18</t>
+  </si>
+  <si>
+    <t>20:43:15</t>
+  </si>
+  <si>
+    <t>05:00:11</t>
+  </si>
+  <si>
+    <t>19:52:55</t>
+  </si>
+  <si>
+    <t>21:25:33</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -713,7 +749,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -728,7 +764,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,7 +818,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,19 +854,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,73 +866,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,7 +907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,12 +976,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1361,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1439,55 +1457,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L2" s="4">
-        <v>-67.59999999999999</v>
+        <v>-68.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="O2" s="6">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="P2" s="7">
-        <v>94</v>
-      </c>
-      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1495,55 +1513,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-23.2</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="O3" s="9">
+        <v>95</v>
+      </c>
+      <c r="P3" s="10">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
         <v>44</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-11.5</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O3" s="9">
-        <v>29</v>
-      </c>
-      <c r="P3" s="10">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1551,55 +1569,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L4" s="4">
-        <v>-54.5</v>
+        <v>-44.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="O4" s="9">
-        <v>43</v>
-      </c>
-      <c r="P4" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="10">
-        <v>27</v>
+        <v>44</v>
+      </c>
+      <c r="P4" s="12">
+        <v>42</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1607,55 +1625,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L5" s="4">
-        <v>-68.2</v>
+        <v>-62.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O5" s="6">
-        <v>52</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
-        <v>33</v>
+        <v>231</v>
+      </c>
+      <c r="O5" s="9">
+        <v>56</v>
+      </c>
+      <c r="P5" s="13">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1663,55 +1681,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="L6" s="4">
-        <v>-23.2</v>
+        <v>-13.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O6" s="6">
-        <v>83</v>
-      </c>
-      <c r="P6" s="13">
-        <v>51</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="14">
-        <v>55</v>
+        <v>233</v>
+      </c>
+      <c r="O6" s="9">
+        <v>96</v>
+      </c>
+      <c r="P6" s="14">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="15">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1719,55 +1737,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L7" s="4">
-        <v>-44.2</v>
+        <v>-53.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O7" s="6">
-        <v>59</v>
-      </c>
-      <c r="P7" s="15">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>1</v>
+        <v>231</v>
+      </c>
+      <c r="O7" s="9">
+        <v>100</v>
+      </c>
+      <c r="P7" s="16">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1775,55 +1793,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L8" s="4">
-        <v>-62.5</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O8" s="6">
-        <v>44</v>
+        <v>232</v>
+      </c>
+      <c r="O8" s="9">
+        <v>100</v>
       </c>
       <c r="P8" s="16">
-        <v>43</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1831,55 +1849,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="L9" s="4">
-        <v>-13.6</v>
+        <v>-25.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O9" s="6">
-        <v>96</v>
-      </c>
-      <c r="P9" s="17">
-        <v>92</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="18">
-        <v>78</v>
+        <v>233</v>
+      </c>
+      <c r="O9" s="9">
+        <v>100</v>
+      </c>
+      <c r="P9" s="18">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1887,55 +1905,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L10" s="4">
-        <v>-53.3</v>
+        <v>-42.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O10" s="6">
-        <v>91</v>
-      </c>
-      <c r="P10" s="18">
-        <v>79</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="17">
-        <v>91</v>
+        <v>231</v>
+      </c>
+      <c r="O10" s="9">
+        <v>96</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="19">
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1943,55 +1961,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L11" s="4">
-        <v>-68.40000000000001</v>
+        <v>-61.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O11" s="6">
-        <v>83</v>
-      </c>
-      <c r="P11" s="19">
-        <v>71</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="20">
-        <v>83</v>
+        <v>231</v>
+      </c>
+      <c r="O11" s="9">
+        <v>96</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="19">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1999,55 +2017,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L12" s="4">
-        <v>-25.3</v>
+        <v>-36.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O12" s="6">
-        <v>92</v>
-      </c>
-      <c r="P12" s="21">
-        <v>12</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="22">
-        <v>30</v>
+        <v>231</v>
+      </c>
+      <c r="O12" s="9">
+        <v>95</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2055,55 +2073,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="L13" s="4">
-        <v>-42.7</v>
+        <v>-15.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O13" s="6">
-        <v>92</v>
-      </c>
-      <c r="P13" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="17">
-        <v>92</v>
+        <v>233</v>
+      </c>
+      <c r="O13" s="9">
+        <v>95</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2111,55 +2129,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L14" s="4">
-        <v>-61.7</v>
+        <v>-31.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="O14" s="9">
-        <v>48</v>
-      </c>
-      <c r="P14" s="11">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>4</v>
-      </c>
-      <c r="R14" s="12">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="P14" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>1</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2167,55 +2185,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L15" s="4">
-        <v>-36.9</v>
+        <v>-52.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O15" s="6">
-        <v>90</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
-        <v>1</v>
+        <v>231</v>
+      </c>
+      <c r="O15" s="9">
+        <v>85</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2223,55 +2241,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>211</v>
+        <v>90</v>
       </c>
       <c r="L16" s="4">
-        <v>-15.8</v>
+        <v>-48.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O16" s="6">
+        <v>232</v>
+      </c>
+      <c r="O16" s="9">
         <v>90</v>
       </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>2</v>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>10</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2279,55 +2297,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="L17" s="4">
-        <v>-31.4</v>
+        <v>-27.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O17" s="6">
-        <v>100</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="17">
-        <v>89</v>
+        <v>233</v>
+      </c>
+      <c r="O17" s="9">
+        <v>90</v>
+      </c>
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>2</v>
+      </c>
+      <c r="R17" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2335,55 +2353,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="L18" s="4">
-        <v>-52</v>
+        <v>-19.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O18" s="6">
-        <v>75</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="23">
-        <v>75</v>
+        <v>232</v>
+      </c>
+      <c r="O18" s="9">
+        <v>95</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2391,55 +2409,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L19" s="4">
-        <v>-48.5</v>
+        <v>-41.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O19" s="6">
-        <v>100</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="24">
-        <v>100</v>
+        <v>231</v>
+      </c>
+      <c r="O19" s="9">
+        <v>95</v>
+      </c>
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="18">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2447,55 +2465,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="L20" s="4">
-        <v>-27.5</v>
+        <v>-39.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O20" s="6">
-        <v>96</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
-        <v>96</v>
+        <v>231</v>
+      </c>
+      <c r="O20" s="20">
+        <v>19</v>
+      </c>
+      <c r="P20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="19">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2503,55 +2521,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="L21" s="4">
-        <v>-19.8</v>
+        <v>-18.1</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O21" s="6">
-        <v>91</v>
-      </c>
-      <c r="P21" s="25">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>90</v>
-      </c>
-      <c r="R21" s="22">
-        <v>30</v>
+        <v>233</v>
+      </c>
+      <c r="O21" s="20">
+        <v>32</v>
+      </c>
+      <c r="P21" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2559,54 +2577,54 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="L22" s="4">
-        <v>-41.1</v>
+        <v>-29.7</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O22" s="6">
-        <v>95</v>
-      </c>
-      <c r="P22" s="10">
-        <v>25</v>
+        <v>231</v>
+      </c>
+      <c r="O22" s="9">
+        <v>91</v>
+      </c>
+      <c r="P22" s="19">
+        <v>18</v>
       </c>
       <c r="Q22" s="7">
-        <v>95</v>
-      </c>
-      <c r="R22" s="22">
+        <v>0</v>
+      </c>
+      <c r="R22" s="15">
         <v>30</v>
       </c>
     </row>
@@ -2615,55 +2633,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-50.6</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="O23" s="9">
         <v>94</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-39.4</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O23" s="6">
-        <v>75</v>
-      </c>
-      <c r="P23" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="23">
-        <v>74</v>
-      </c>
-      <c r="R23" s="15">
-        <v>62</v>
+      <c r="P23" s="21">
+        <v>15</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>0</v>
+      </c>
+      <c r="R23" s="21">
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2671,55 +2689,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>214</v>
+        <v>98</v>
       </c>
       <c r="L24" s="4">
-        <v>-18.2</v>
+        <v>-50.7</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O24" s="6">
-        <v>72</v>
-      </c>
-      <c r="P24" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="19">
-        <v>70</v>
-      </c>
-      <c r="R24" s="22">
-        <v>31</v>
+        <v>231</v>
+      </c>
+      <c r="O24" s="9">
+        <v>59</v>
+      </c>
+      <c r="P24" s="13">
+        <v>53</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2727,54 +2745,54 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="L25" s="4">
-        <v>-29.6</v>
+        <v>-29.8</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O25" s="6">
-        <v>93</v>
-      </c>
-      <c r="P25" s="10">
-        <v>27</v>
+        <v>231</v>
+      </c>
+      <c r="O25" s="9">
+        <v>68</v>
+      </c>
+      <c r="P25" s="22">
+        <v>52</v>
       </c>
       <c r="Q25" s="7">
-        <v>93</v>
-      </c>
-      <c r="R25" s="8">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2783,114 +2801,170 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-18.2</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="O26" s="9">
+        <v>81</v>
+      </c>
+      <c r="P26" s="23">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-50.5</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O26" s="6">
-        <v>87</v>
-      </c>
-      <c r="P26" s="22">
-        <v>28</v>
-      </c>
-      <c r="Q26" s="20">
-        <v>87</v>
-      </c>
-      <c r="R26" s="8">
+      <c r="D27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-39.4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="O27" s="9">
+        <v>79</v>
+      </c>
+      <c r="P27" s="23">
+        <v>79</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D27">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J27">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K27">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2909,12 +2983,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M27">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2931,22 +3005,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O27">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P27">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q27">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R27">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="228">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261012--01</t>
-  </si>
-  <si>
-    <t>20261012--02</t>
-  </si>
-  <si>
-    <t>20261012--03</t>
-  </si>
-  <si>
-    <t>20261012--04</t>
-  </si>
-  <si>
     <t>20261013--01</t>
   </si>
   <si>
@@ -148,19 +136,19 @@
     <t>20261018--04</t>
   </si>
   <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>03:26</t>
-  </si>
-  <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>06:24</t>
+    <t>20261019--01</t>
+  </si>
+  <si>
+    <t>20261019--02</t>
+  </si>
+  <si>
+    <t>20261019--03</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>06:23</t>
   </si>
   <si>
     <t>00:22</t>
@@ -175,7 +163,7 @@
     <t>03:57</t>
   </si>
   <si>
-    <t>04:31</t>
+    <t>04:32</t>
   </si>
   <si>
     <t>06:19</t>
@@ -193,19 +181,22 @@
     <t>06:31</t>
   </si>
   <si>
-    <t>03:34</t>
+    <t>03:35</t>
   </si>
   <si>
     <t>06:09</t>
   </si>
   <si>
-    <t>04:06</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>02:35</t>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>02:33</t>
   </si>
   <si>
     <t>05:16</t>
@@ -217,22 +208,25 @@
     <t>06:08</t>
   </si>
   <si>
-    <t>04:37</t>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>05:38</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
     <t>02:16</t>
   </si>
   <si>
-    <t>03:50</t>
+    <t>03:51</t>
   </si>
   <si>
     <t>00:49</t>
@@ -241,405 +235,390 @@
     <t>00:28</t>
   </si>
   <si>
-    <t>02:47</t>
-  </si>
-  <si>
-    <t>00:23:39</t>
-  </si>
-  <si>
-    <t>05:18:36</t>
-  </si>
-  <si>
-    <t>21:53:54</t>
-  </si>
-  <si>
-    <t>23:30:23</t>
+    <t>02:46</t>
+  </si>
+  <si>
+    <t>01:16</t>
   </si>
   <si>
     <t>06:02:18</t>
   </si>
   <si>
-    <t>22:37:13</t>
-  </si>
-  <si>
-    <t>00:15:40</t>
-  </si>
-  <si>
-    <t>05:09:23</t>
-  </si>
-  <si>
-    <t>21:44:11</t>
-  </si>
-  <si>
-    <t>23:21:57</t>
-  </si>
-  <si>
-    <t>04:16:27</t>
-  </si>
-  <si>
-    <t>05:53:09</t>
-  </si>
-  <si>
-    <t>20:51:18</t>
-  </si>
-  <si>
-    <t>22:28:18</t>
-  </si>
-  <si>
-    <t>03:23:25</t>
-  </si>
-  <si>
-    <t>04:59:55</t>
+    <t>22:37:14</t>
+  </si>
+  <si>
+    <t>00:15:41</t>
+  </si>
+  <si>
+    <t>05:09:24</t>
+  </si>
+  <si>
+    <t>21:44:13</t>
+  </si>
+  <si>
+    <t>23:21:59</t>
+  </si>
+  <si>
+    <t>04:16:29</t>
+  </si>
+  <si>
+    <t>05:53:11</t>
+  </si>
+  <si>
+    <t>20:51:22</t>
+  </si>
+  <si>
+    <t>22:28:22</t>
+  </si>
+  <si>
+    <t>03:23:30</t>
+  </si>
+  <si>
+    <t>05:00:00</t>
+  </si>
+  <si>
+    <t>19:58:46</t>
+  </si>
+  <si>
+    <t>21:34:52</t>
+  </si>
+  <si>
+    <t>04:06:50</t>
+  </si>
+  <si>
+    <t>05:44:09</t>
+  </si>
+  <si>
+    <t>20:41:29</t>
+  </si>
+  <si>
+    <t>22:19:39</t>
+  </si>
+  <si>
+    <t>03:13:39</t>
+  </si>
+  <si>
+    <t>04:50:32</t>
+  </si>
+  <si>
+    <t>19:48:15</t>
+  </si>
+  <si>
+    <t>21:25:42</t>
+  </si>
+  <si>
+    <t>02:20:26</t>
+  </si>
+  <si>
+    <t>03:57:01</t>
+  </si>
+  <si>
+    <t>20:31:50</t>
+  </si>
+  <si>
+    <t>06:04:25</t>
+  </si>
+  <si>
+    <t>22:39:19</t>
+  </si>
+  <si>
+    <t>00:19:58</t>
+  </si>
+  <si>
+    <t>05:11:41</t>
+  </si>
+  <si>
+    <t>21:46:18</t>
+  </si>
+  <si>
+    <t>23:24:42</t>
+  </si>
+  <si>
+    <t>04:19:04</t>
+  </si>
+  <si>
+    <t>05:55:19</t>
+  </si>
+  <si>
+    <t>20:53:37</t>
+  </si>
+  <si>
+    <t>22:30:42</t>
+  </si>
+  <si>
+    <t>03:26:48</t>
+  </si>
+  <si>
+    <t>05:02:05</t>
+  </si>
+  <si>
+    <t>20:01:32</t>
+  </si>
+  <si>
+    <t>21:37:00</t>
+  </si>
+  <si>
+    <t>04:09:00</t>
+  </si>
+  <si>
+    <t>05:46:49</t>
+  </si>
+  <si>
+    <t>20:43:33</t>
+  </si>
+  <si>
+    <t>22:22:50</t>
+  </si>
+  <si>
+    <t>03:16:02</t>
+  </si>
+  <si>
+    <t>04:52:45</t>
+  </si>
+  <si>
+    <t>19:50:23</t>
+  </si>
+  <si>
+    <t>21:28:14</t>
+  </si>
+  <si>
+    <t>02:23:14</t>
+  </si>
+  <si>
+    <t>03:59:07</t>
+  </si>
+  <si>
+    <t>20:34:04</t>
+  </si>
+  <si>
+    <t>06:07:38</t>
+  </si>
+  <si>
+    <t>22:42:30</t>
+  </si>
+  <si>
+    <t>05:14:33</t>
+  </si>
+  <si>
+    <t>21:49:28</t>
+  </si>
+  <si>
+    <t>23:26:40</t>
+  </si>
+  <si>
+    <t>04:21:20</t>
+  </si>
+  <si>
+    <t>05:58:29</t>
+  </si>
+  <si>
+    <t>20:56:24</t>
+  </si>
+  <si>
+    <t>22:33:22</t>
+  </si>
+  <si>
+    <t>03:27:57</t>
+  </si>
+  <si>
+    <t>05:05:21</t>
+  </si>
+  <si>
+    <t>20:03:20</t>
+  </si>
+  <si>
+    <t>21:40:04</t>
+  </si>
+  <si>
+    <t>04:12:05</t>
+  </si>
+  <si>
+    <t>05:48:51</t>
+  </si>
+  <si>
+    <t>20:46:46</t>
+  </si>
+  <si>
+    <t>22:24:06</t>
+  </si>
+  <si>
+    <t>03:18:40</t>
+  </si>
+  <si>
+    <t>04:55:39</t>
+  </si>
+  <si>
+    <t>19:53:26</t>
+  </si>
+  <si>
+    <t>21:30:32</t>
+  </si>
+  <si>
+    <t>02:25:06</t>
+  </si>
+  <si>
+    <t>04:02:20</t>
+  </si>
+  <si>
+    <t>20:36:57</t>
+  </si>
+  <si>
+    <t>06:10:50</t>
+  </si>
+  <si>
+    <t>22:45:42</t>
+  </si>
+  <si>
+    <t>00:20:20</t>
+  </si>
+  <si>
+    <t>05:17:25</t>
+  </si>
+  <si>
+    <t>21:52:39</t>
+  </si>
+  <si>
+    <t>23:28:39</t>
+  </si>
+  <si>
+    <t>04:23:36</t>
+  </si>
+  <si>
+    <t>06:01:38</t>
+  </si>
+  <si>
+    <t>20:59:13</t>
+  </si>
+  <si>
+    <t>22:36:03</t>
+  </si>
+  <si>
+    <t>03:29:07</t>
+  </si>
+  <si>
+    <t>05:08:36</t>
+  </si>
+  <si>
+    <t>20:05:07</t>
+  </si>
+  <si>
+    <t>21:43:09</t>
+  </si>
+  <si>
+    <t>04:15:10</t>
+  </si>
+  <si>
+    <t>05:50:54</t>
+  </si>
+  <si>
+    <t>20:49:59</t>
+  </si>
+  <si>
+    <t>22:25:23</t>
+  </si>
+  <si>
+    <t>03:21:18</t>
+  </si>
+  <si>
+    <t>04:58:34</t>
+  </si>
+  <si>
+    <t>19:56:31</t>
+  </si>
+  <si>
+    <t>21:32:50</t>
+  </si>
+  <si>
+    <t>02:26:59</t>
+  </si>
+  <si>
+    <t>04:05:33</t>
+  </si>
+  <si>
+    <t>20:39:50</t>
+  </si>
+  <si>
+    <t>06:12:57</t>
+  </si>
+  <si>
+    <t>22:47:49</t>
+  </si>
+  <si>
+    <t>00:24:18</t>
+  </si>
+  <si>
+    <t>05:19:42</t>
+  </si>
+  <si>
+    <t>21:54:45</t>
+  </si>
+  <si>
+    <t>23:31:23</t>
+  </si>
+  <si>
+    <t>04:26:11</t>
+  </si>
+  <si>
+    <t>06:03:46</t>
+  </si>
+  <si>
+    <t>21:01:28</t>
+  </si>
+  <si>
+    <t>22:38:24</t>
+  </si>
+  <si>
+    <t>03:32:25</t>
+  </si>
+  <si>
+    <t>05:10:42</t>
+  </si>
+  <si>
+    <t>20:07:54</t>
+  </si>
+  <si>
+    <t>21:45:19</t>
+  </si>
+  <si>
+    <t>04:17:20</t>
+  </si>
+  <si>
+    <t>05:53:33</t>
+  </si>
+  <si>
+    <t>20:52:04</t>
+  </si>
+  <si>
+    <t>22:28:35</t>
+  </si>
+  <si>
+    <t>03:23:41</t>
+  </si>
+  <si>
+    <t>05:00:47</t>
   </si>
   <si>
     <t>19:58:39</t>
   </si>
   <si>
-    <t>21:34:44</t>
-  </si>
-  <si>
-    <t>04:06:42</t>
-  </si>
-  <si>
-    <t>05:44:01</t>
-  </si>
-  <si>
-    <t>20:41:18</t>
-  </si>
-  <si>
-    <t>22:19:28</t>
-  </si>
-  <si>
-    <t>03:13:28</t>
-  </si>
-  <si>
-    <t>04:50:19</t>
-  </si>
-  <si>
-    <t>19:48:00</t>
-  </si>
-  <si>
-    <t>21:25:27</t>
-  </si>
-  <si>
-    <t>00:26:06</t>
-  </si>
-  <si>
-    <t>05:21:32</t>
-  </si>
-  <si>
-    <t>21:56:22</t>
-  </si>
-  <si>
-    <t>23:32:35</t>
-  </si>
-  <si>
-    <t>06:04:26</t>
-  </si>
-  <si>
-    <t>22:39:18</t>
-  </si>
-  <si>
-    <t>00:19:58</t>
-  </si>
-  <si>
-    <t>05:11:40</t>
-  </si>
-  <si>
-    <t>21:46:16</t>
-  </si>
-  <si>
-    <t>23:24:40</t>
-  </si>
-  <si>
-    <t>04:19:02</t>
-  </si>
-  <si>
-    <t>05:55:16</t>
-  </si>
-  <si>
-    <t>20:53:33</t>
-  </si>
-  <si>
-    <t>22:30:38</t>
-  </si>
-  <si>
-    <t>03:26:43</t>
-  </si>
-  <si>
-    <t>05:02:00</t>
-  </si>
-  <si>
-    <t>20:01:26</t>
-  </si>
-  <si>
-    <t>21:36:53</t>
-  </si>
-  <si>
-    <t>04:08:52</t>
-  </si>
-  <si>
-    <t>05:46:40</t>
-  </si>
-  <si>
-    <t>20:43:22</t>
-  </si>
-  <si>
-    <t>22:22:38</t>
-  </si>
-  <si>
-    <t>03:15:50</t>
-  </si>
-  <si>
-    <t>04:52:33</t>
-  </si>
-  <si>
-    <t>19:50:08</t>
-  </si>
-  <si>
-    <t>21:27:58</t>
-  </si>
-  <si>
-    <t>00:28:33</t>
-  </si>
-  <si>
-    <t>05:23:15</t>
-  </si>
-  <si>
-    <t>21:58:41</t>
-  </si>
-  <si>
-    <t>23:35:31</t>
-  </si>
-  <si>
-    <t>06:07:38</t>
-  </si>
-  <si>
-    <t>22:42:29</t>
-  </si>
-  <si>
-    <t>05:14:32</t>
-  </si>
-  <si>
-    <t>21:49:26</t>
-  </si>
-  <si>
-    <t>23:26:38</t>
-  </si>
-  <si>
-    <t>04:21:17</t>
-  </si>
-  <si>
-    <t>05:58:26</t>
-  </si>
-  <si>
-    <t>20:56:20</t>
-  </si>
-  <si>
-    <t>22:33:18</t>
-  </si>
-  <si>
-    <t>03:27:53</t>
-  </si>
-  <si>
-    <t>05:05:16</t>
-  </si>
-  <si>
-    <t>20:03:13</t>
-  </si>
-  <si>
-    <t>21:39:57</t>
-  </si>
-  <si>
-    <t>04:11:57</t>
-  </si>
-  <si>
-    <t>05:48:43</t>
-  </si>
-  <si>
-    <t>20:46:35</t>
-  </si>
-  <si>
-    <t>22:23:55</t>
-  </si>
-  <si>
-    <t>03:18:28</t>
-  </si>
-  <si>
-    <t>04:55:27</t>
-  </si>
-  <si>
-    <t>19:53:11</t>
-  </si>
-  <si>
-    <t>21:30:16</t>
-  </si>
-  <si>
-    <t>00:31:01</t>
-  </si>
-  <si>
-    <t>05:24:58</t>
-  </si>
-  <si>
-    <t>22:01:00</t>
-  </si>
-  <si>
-    <t>23:38:30</t>
-  </si>
-  <si>
-    <t>06:10:50</t>
-  </si>
-  <si>
-    <t>22:45:42</t>
-  </si>
-  <si>
-    <t>00:20:20</t>
-  </si>
-  <si>
-    <t>05:17:24</t>
-  </si>
-  <si>
-    <t>21:52:37</t>
-  </si>
-  <si>
-    <t>23:28:37</t>
-  </si>
-  <si>
-    <t>04:23:33</t>
-  </si>
-  <si>
-    <t>06:01:35</t>
-  </si>
-  <si>
-    <t>20:59:09</t>
-  </si>
-  <si>
-    <t>22:35:59</t>
-  </si>
-  <si>
-    <t>03:29:02</t>
-  </si>
-  <si>
-    <t>05:08:31</t>
-  </si>
-  <si>
-    <t>20:05:00</t>
-  </si>
-  <si>
-    <t>21:43:02</t>
-  </si>
-  <si>
-    <t>04:15:01</t>
-  </si>
-  <si>
-    <t>05:50:46</t>
-  </si>
-  <si>
-    <t>20:49:49</t>
-  </si>
-  <si>
-    <t>22:25:13</t>
-  </si>
-  <si>
-    <t>03:21:06</t>
-  </si>
-  <si>
-    <t>04:58:22</t>
-  </si>
-  <si>
-    <t>19:56:16</t>
-  </si>
-  <si>
-    <t>21:32:35</t>
-  </si>
-  <si>
-    <t>00:33:29</t>
-  </si>
-  <si>
-    <t>05:27:53</t>
-  </si>
-  <si>
-    <t>22:03:30</t>
-  </si>
-  <si>
-    <t>23:40:43</t>
-  </si>
-  <si>
-    <t>06:12:57</t>
-  </si>
-  <si>
-    <t>22:47:48</t>
-  </si>
-  <si>
-    <t>00:24:17</t>
-  </si>
-  <si>
-    <t>05:19:41</t>
-  </si>
-  <si>
-    <t>21:54:43</t>
-  </si>
-  <si>
-    <t>23:31:21</t>
-  </si>
-  <si>
-    <t>04:26:08</t>
-  </si>
-  <si>
-    <t>06:03:43</t>
-  </si>
-  <si>
-    <t>21:01:24</t>
-  </si>
-  <si>
-    <t>22:38:20</t>
-  </si>
-  <si>
-    <t>03:32:20</t>
-  </si>
-  <si>
-    <t>05:10:37</t>
-  </si>
-  <si>
-    <t>20:07:47</t>
-  </si>
-  <si>
-    <t>21:45:12</t>
-  </si>
-  <si>
-    <t>04:17:11</t>
-  </si>
-  <si>
-    <t>05:53:25</t>
-  </si>
-  <si>
-    <t>20:51:54</t>
-  </si>
-  <si>
-    <t>22:28:24</t>
-  </si>
-  <si>
-    <t>03:23:29</t>
-  </si>
-  <si>
-    <t>05:00:35</t>
-  </si>
-  <si>
-    <t>19:58:24</t>
-  </si>
-  <si>
-    <t>21:35:07</t>
+    <t>21:35:23</t>
+  </si>
+  <si>
+    <t>02:29:47</t>
+  </si>
+  <si>
+    <t>04:07:39</t>
+  </si>
+  <si>
+    <t>20:42:05</t>
+  </si>
+  <si>
+    <t>16°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>26°</t>
   </si>
   <si>
@@ -661,61 +640,64 @@
     <t>9°</t>
   </si>
   <si>
-    <t>1°</t>
+    <t>2°</t>
   </si>
   <si>
     <t>41°</t>
   </si>
   <si>
-    <t>05:22:38</t>
+    <t>19°</t>
   </si>
   <si>
     <t>06:05:12</t>
   </si>
   <si>
-    <t>05:15:08</t>
-  </si>
-  <si>
-    <t>04:25:05</t>
-  </si>
-  <si>
-    <t>05:57:45</t>
-  </si>
-  <si>
-    <t>05:07:42</t>
-  </si>
-  <si>
-    <t>20:00:45</t>
-  </si>
-  <si>
-    <t>05:50:18</t>
-  </si>
-  <si>
-    <t>20:43:15</t>
-  </si>
-  <si>
-    <t>05:00:11</t>
-  </si>
-  <si>
-    <t>19:52:55</t>
-  </si>
-  <si>
-    <t>21:25:33</t>
+    <t>05:15:09</t>
+  </si>
+  <si>
+    <t>04:25:07</t>
+  </si>
+  <si>
+    <t>05:57:47</t>
+  </si>
+  <si>
+    <t>05:07:47</t>
+  </si>
+  <si>
+    <t>20:00:52</t>
+  </si>
+  <si>
+    <t>05:50:26</t>
+  </si>
+  <si>
+    <t>20:43:25</t>
+  </si>
+  <si>
+    <t>05:00:23</t>
+  </si>
+  <si>
+    <t>19:53:09</t>
+  </si>
+  <si>
+    <t>21:25:47</t>
+  </si>
+  <si>
+    <t>20:35:20</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>2</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -749,7 +731,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -764,7 +746,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,31 +764,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,61 +836,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -907,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -973,9 +949,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1379,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1457,55 +1430,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="L2" s="4">
-        <v>-68.2</v>
+        <v>-13.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="O2" s="6">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>7</v>
+        <v>83</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1513,55 +1486,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>217</v>
+        <v>76</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.2</v>
+        <v>-53.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O3" s="9">
-        <v>95</v>
+        <v>226</v>
+      </c>
+      <c r="O3" s="6">
+        <v>90</v>
       </c>
       <c r="P3" s="10">
-        <v>76</v>
-      </c>
-      <c r="Q3" s="7">
+        <v>66</v>
+      </c>
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
       <c r="R3" s="11">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1569,55 +1542,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L4" s="4">
-        <v>-44.2</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O4" s="9">
-        <v>44</v>
-      </c>
-      <c r="P4" s="12">
-        <v>42</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>4</v>
+        <v>227</v>
+      </c>
+      <c r="O4" s="6">
+        <v>93</v>
+      </c>
+      <c r="P4" s="10">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1625,55 +1598,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="L5" s="4">
-        <v>-62.5</v>
+        <v>-25.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O5" s="9">
-        <v>56</v>
+        <v>225</v>
+      </c>
+      <c r="O5" s="6">
+        <v>98</v>
       </c>
       <c r="P5" s="13">
-        <v>56</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="14">
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1681,55 +1654,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="L6" s="4">
-        <v>-13.6</v>
+        <v>-42.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O6" s="9">
-        <v>96</v>
-      </c>
-      <c r="P6" s="14">
-        <v>93</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="15">
-        <v>31</v>
+        <v>226</v>
+      </c>
+      <c r="O6" s="6">
+        <v>69</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1737,7 +1710,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
@@ -1746,45 +1719,45 @@
         <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L7" s="4">
-        <v>-53.3</v>
+        <v>-61.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O7" s="9">
+        <v>226</v>
+      </c>
+      <c r="O7" s="6">
         <v>100</v>
       </c>
-      <c r="P7" s="16">
-        <v>68</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="17">
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="15">
         <v>100</v>
       </c>
     </row>
@@ -1793,7 +1766,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
@@ -1802,46 +1775,46 @@
         <v>68</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="L8" s="4">
-        <v>-68.40000000000001</v>
+        <v>-36.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O8" s="9">
+        <v>226</v>
+      </c>
+      <c r="O8" s="6">
         <v>100</v>
       </c>
-      <c r="P8" s="16">
-        <v>71</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="17">
-        <v>100</v>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="14">
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1849,54 +1822,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L9" s="4">
-        <v>-25.3</v>
+        <v>-15.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O9" s="9">
+        <v>225</v>
+      </c>
+      <c r="O9" s="6">
         <v>100</v>
       </c>
-      <c r="P9" s="18">
-        <v>12</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="17">
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="15">
         <v>100</v>
       </c>
     </row>
@@ -1905,7 +1878,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
@@ -1914,46 +1887,46 @@
         <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L10" s="4">
-        <v>-42.7</v>
+        <v>-31.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O10" s="9">
-        <v>96</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="19">
-        <v>18</v>
+        <v>226</v>
+      </c>
+      <c r="O10" s="6">
+        <v>100</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>14</v>
+      </c>
+      <c r="R10" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1961,7 +1934,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>52</v>
@@ -1970,46 +1943,46 @@
         <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L11" s="4">
-        <v>-61.7</v>
+        <v>-52.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O11" s="9">
-        <v>96</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="19">
-        <v>19</v>
+        <v>226</v>
+      </c>
+      <c r="O11" s="6">
+        <v>100</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>9</v>
+      </c>
+      <c r="R11" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2017,7 +1990,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>53</v>
@@ -2026,46 +1999,46 @@
         <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="L12" s="4">
-        <v>-36.9</v>
+        <v>-48.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O12" s="9">
-        <v>95</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
-        <v>0</v>
+        <v>227</v>
+      </c>
+      <c r="O12" s="6">
+        <v>100</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>34</v>
+      </c>
+      <c r="R12" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2073,55 +2046,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="L13" s="4">
-        <v>-15.8</v>
+        <v>-27.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O13" s="9">
-        <v>95</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
-        <v>0</v>
+        <v>225</v>
+      </c>
+      <c r="O13" s="6">
+        <v>99</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>37</v>
+      </c>
+      <c r="R13" s="17">
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2129,7 +2102,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>55</v>
@@ -2138,46 +2111,46 @@
         <v>68</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>216</v>
       </c>
       <c r="L14" s="4">
-        <v>-31.5</v>
+        <v>-20</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O14" s="9">
-        <v>78</v>
+        <v>227</v>
+      </c>
+      <c r="O14" s="6">
+        <v>79</v>
       </c>
       <c r="P14" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>1</v>
-      </c>
-      <c r="R14" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>5</v>
+      </c>
+      <c r="R14" s="16">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2185,7 +2158,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>56</v>
@@ -2194,45 +2167,45 @@
         <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L15" s="4">
-        <v>-52.1</v>
+        <v>-41.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O15" s="9">
-        <v>85</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7">
+        <v>226</v>
+      </c>
+      <c r="O15" s="6">
+        <v>80</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2241,7 +2214,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>57</v>
@@ -2250,45 +2223,45 @@
         <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L16" s="4">
-        <v>-48.5</v>
+        <v>-39.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O16" s="9">
-        <v>90</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>10</v>
-      </c>
-      <c r="R16" s="7">
+        <v>226</v>
+      </c>
+      <c r="O16" s="6">
+        <v>69</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>11</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2297,54 +2270,54 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="L17" s="4">
-        <v>-27.5</v>
+        <v>-18.1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O17" s="9">
-        <v>90</v>
-      </c>
-      <c r="P17" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>2</v>
-      </c>
-      <c r="R17" s="7">
+        <v>225</v>
+      </c>
+      <c r="O17" s="19">
+        <v>27</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>4</v>
+      </c>
+      <c r="R17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2353,7 +2326,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>59</v>
@@ -2362,45 +2335,45 @@
         <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L18" s="4">
-        <v>-19.9</v>
+        <v>-29.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O18" s="9">
-        <v>95</v>
-      </c>
-      <c r="P18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7">
+        <v>226</v>
+      </c>
+      <c r="O18" s="6">
+        <v>57</v>
+      </c>
+      <c r="P18" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="20">
+        <v>57</v>
+      </c>
+      <c r="R18" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2409,7 +2382,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>60</v>
@@ -2418,46 +2391,46 @@
         <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L19" s="4">
-        <v>-41.2</v>
+        <v>-50.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O19" s="9">
-        <v>95</v>
-      </c>
-      <c r="P19" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
+        <v>227</v>
+      </c>
+      <c r="O19" s="6">
+        <v>68</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>1</v>
       </c>
       <c r="R19" s="18">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2465,55 +2438,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L20" s="4">
-        <v>-39.3</v>
+        <v>-50.7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O20" s="20">
-        <v>19</v>
-      </c>
-      <c r="P20" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="19">
-        <v>19</v>
+        <v>226</v>
+      </c>
+      <c r="O20" s="6">
+        <v>55</v>
+      </c>
+      <c r="P20" s="21">
+        <v>52</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="18">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2521,55 +2494,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-29.8</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="L21" s="4">
-        <v>-18.1</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="N21" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O21" s="20">
-        <v>32</v>
-      </c>
-      <c r="P21" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>0</v>
-      </c>
-      <c r="R21" s="15">
-        <v>32</v>
+        <v>226</v>
+      </c>
+      <c r="O21" s="6">
+        <v>54</v>
+      </c>
+      <c r="P21" s="21">
+        <v>52</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2577,55 +2550,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-18.3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L22" s="4">
-        <v>-29.7</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O22" s="9">
-        <v>91</v>
-      </c>
-      <c r="P22" s="19">
-        <v>18</v>
-      </c>
-      <c r="Q22" s="7">
-        <v>0</v>
-      </c>
-      <c r="R22" s="15">
-        <v>30</v>
+      <c r="O22" s="6">
+        <v>45</v>
+      </c>
+      <c r="P22" s="22">
+        <v>45</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2633,55 +2606,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K23" s="1" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="L23" s="4">
-        <v>-50.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O23" s="9">
-        <v>94</v>
-      </c>
-      <c r="P23" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>0</v>
-      </c>
-      <c r="R23" s="21">
-        <v>15</v>
+        <v>226</v>
+      </c>
+      <c r="O23" s="19">
+        <v>17</v>
+      </c>
+      <c r="P23" s="16">
+        <v>17</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2689,54 +2662,54 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L24" s="4">
-        <v>-50.7</v>
+        <v>-61.3</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O24" s="9">
-        <v>59</v>
-      </c>
-      <c r="P24" s="13">
-        <v>53</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7">
+        <v>227</v>
+      </c>
+      <c r="O24" s="6">
+        <v>60</v>
+      </c>
+      <c r="P24" s="22">
+        <v>45</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>0</v>
+      </c>
+      <c r="R24" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2745,54 +2718,54 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-41.6</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="L25" s="4">
-        <v>-29.8</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O25" s="9">
-        <v>68</v>
-      </c>
-      <c r="P25" s="22">
-        <v>52</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7">
+      <c r="O25" s="6">
+        <v>86</v>
+      </c>
+      <c r="P25" s="11">
+        <v>71</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>0</v>
+      </c>
+      <c r="R25" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2801,170 +2774,114 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L26" s="4">
-        <v>-18.2</v>
+        <v>-28</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O26" s="9">
-        <v>81</v>
-      </c>
-      <c r="P26" s="23">
-        <v>81</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>0</v>
-      </c>
-      <c r="R26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2">
-        <v>18</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-39.4</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O27" s="9">
-        <v>79</v>
-      </c>
-      <c r="P27" s="23">
-        <v>79</v>
-      </c>
-      <c r="Q27" s="7">
-        <v>0</v>
-      </c>
-      <c r="R27" s="7">
-        <v>0</v>
+        <v>225</v>
+      </c>
+      <c r="O26" s="6">
+        <v>82</v>
+      </c>
+      <c r="P26" s="12">
+        <v>82</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>0</v>
+      </c>
+      <c r="R26" s="18">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A27">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B27">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2983,12 +2900,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -3005,22 +2922,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="234">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261013--01</t>
-  </si>
-  <si>
-    <t>20261013--02</t>
-  </si>
-  <si>
     <t>20261014--01</t>
   </si>
   <si>
@@ -145,79 +139,85 @@
     <t>20261019--03</t>
   </si>
   <si>
-    <t>06:25</t>
+    <t>20261020--01</t>
+  </si>
+  <si>
+    <t>20261020--02</t>
+  </si>
+  <si>
+    <t>20261020--03</t>
+  </si>
+  <si>
+    <t>00:21</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>03:56</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>03:34</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>04:38</t>
+  </si>
+  <si>
+    <t>03:43</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>05:45</t>
   </si>
   <si>
     <t>06:23</t>
   </si>
   <si>
-    <t>00:22</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>03:57</t>
-  </si>
-  <si>
-    <t>04:32</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>02:19</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>02:33</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>05:38</t>
+    <t>01:21</t>
   </si>
   <si>
     <t>00:00</t>
@@ -235,387 +235,402 @@
     <t>00:28</t>
   </si>
   <si>
-    <t>02:46</t>
+    <t>02:47</t>
   </si>
   <si>
     <t>01:16</t>
   </si>
   <si>
-    <t>06:02:18</t>
-  </si>
-  <si>
-    <t>22:37:14</t>
-  </si>
-  <si>
-    <t>00:15:41</t>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>00:15:40</t>
   </si>
   <si>
     <t>05:09:24</t>
   </si>
   <si>
-    <t>21:44:13</t>
-  </si>
-  <si>
-    <t>23:21:59</t>
-  </si>
-  <si>
-    <t>04:16:29</t>
-  </si>
-  <si>
-    <t>05:53:11</t>
-  </si>
-  <si>
-    <t>20:51:22</t>
-  </si>
-  <si>
-    <t>22:28:22</t>
+    <t>21:44:11</t>
+  </si>
+  <si>
+    <t>23:21:58</t>
+  </si>
+  <si>
+    <t>04:16:27</t>
+  </si>
+  <si>
+    <t>05:53:09</t>
+  </si>
+  <si>
+    <t>20:51:19</t>
+  </si>
+  <si>
+    <t>22:28:19</t>
+  </si>
+  <si>
+    <t>03:23:26</t>
+  </si>
+  <si>
+    <t>04:59:56</t>
+  </si>
+  <si>
+    <t>19:58:40</t>
+  </si>
+  <si>
+    <t>21:34:45</t>
+  </si>
+  <si>
+    <t>04:06:43</t>
+  </si>
+  <si>
+    <t>05:44:02</t>
+  </si>
+  <si>
+    <t>20:41:19</t>
+  </si>
+  <si>
+    <t>22:19:29</t>
+  </si>
+  <si>
+    <t>03:13:29</t>
+  </si>
+  <si>
+    <t>04:50:21</t>
+  </si>
+  <si>
+    <t>19:48:02</t>
+  </si>
+  <si>
+    <t>21:25:28</t>
+  </si>
+  <si>
+    <t>02:20:12</t>
+  </si>
+  <si>
+    <t>03:56:46</t>
+  </si>
+  <si>
+    <t>20:31:32</t>
+  </si>
+  <si>
+    <t>03:03:14</t>
+  </si>
+  <si>
+    <t>04:40:54</t>
+  </si>
+  <si>
+    <t>19:37:42</t>
+  </si>
+  <si>
+    <t>00:19:58</t>
+  </si>
+  <si>
+    <t>05:11:40</t>
+  </si>
+  <si>
+    <t>21:46:16</t>
+  </si>
+  <si>
+    <t>23:24:41</t>
+  </si>
+  <si>
+    <t>04:19:02</t>
+  </si>
+  <si>
+    <t>05:55:17</t>
+  </si>
+  <si>
+    <t>20:53:33</t>
+  </si>
+  <si>
+    <t>22:30:39</t>
+  </si>
+  <si>
+    <t>03:26:44</t>
+  </si>
+  <si>
+    <t>05:02:01</t>
+  </si>
+  <si>
+    <t>20:01:27</t>
+  </si>
+  <si>
+    <t>21:36:54</t>
+  </si>
+  <si>
+    <t>04:08:53</t>
+  </si>
+  <si>
+    <t>05:46:41</t>
+  </si>
+  <si>
+    <t>20:43:23</t>
+  </si>
+  <si>
+    <t>22:22:39</t>
+  </si>
+  <si>
+    <t>03:15:52</t>
+  </si>
+  <si>
+    <t>04:52:34</t>
+  </si>
+  <si>
+    <t>19:50:09</t>
+  </si>
+  <si>
+    <t>21:27:59</t>
+  </si>
+  <si>
+    <t>02:23:00</t>
+  </si>
+  <si>
+    <t>03:58:52</t>
+  </si>
+  <si>
+    <t>20:33:46</t>
+  </si>
+  <si>
+    <t>03:05:21</t>
+  </si>
+  <si>
+    <t>04:44:30</t>
+  </si>
+  <si>
+    <t>19:39:48</t>
+  </si>
+  <si>
+    <t>05:14:32</t>
+  </si>
+  <si>
+    <t>21:49:26</t>
+  </si>
+  <si>
+    <t>23:26:39</t>
+  </si>
+  <si>
+    <t>04:21:17</t>
+  </si>
+  <si>
+    <t>05:58:26</t>
+  </si>
+  <si>
+    <t>20:56:21</t>
+  </si>
+  <si>
+    <t>22:33:19</t>
+  </si>
+  <si>
+    <t>03:27:53</t>
+  </si>
+  <si>
+    <t>05:05:17</t>
+  </si>
+  <si>
+    <t>20:03:14</t>
+  </si>
+  <si>
+    <t>21:39:58</t>
+  </si>
+  <si>
+    <t>04:11:58</t>
+  </si>
+  <si>
+    <t>05:48:44</t>
+  </si>
+  <si>
+    <t>20:46:36</t>
+  </si>
+  <si>
+    <t>22:23:57</t>
+  </si>
+  <si>
+    <t>03:18:30</t>
+  </si>
+  <si>
+    <t>04:55:29</t>
+  </si>
+  <si>
+    <t>19:53:13</t>
+  </si>
+  <si>
+    <t>21:30:18</t>
+  </si>
+  <si>
+    <t>02:24:52</t>
+  </si>
+  <si>
+    <t>04:02:05</t>
+  </si>
+  <si>
+    <t>20:36:38</t>
+  </si>
+  <si>
+    <t>03:08:32</t>
+  </si>
+  <si>
+    <t>04:45:11</t>
+  </si>
+  <si>
+    <t>19:42:58</t>
+  </si>
+  <si>
+    <t>00:20:19</t>
+  </si>
+  <si>
+    <t>05:17:24</t>
+  </si>
+  <si>
+    <t>21:52:37</t>
+  </si>
+  <si>
+    <t>23:28:37</t>
+  </si>
+  <si>
+    <t>04:23:33</t>
+  </si>
+  <si>
+    <t>06:01:36</t>
+  </si>
+  <si>
+    <t>20:59:09</t>
+  </si>
+  <si>
+    <t>22:36:00</t>
+  </si>
+  <si>
+    <t>03:29:03</t>
+  </si>
+  <si>
+    <t>05:08:32</t>
+  </si>
+  <si>
+    <t>20:05:01</t>
+  </si>
+  <si>
+    <t>21:43:03</t>
+  </si>
+  <si>
+    <t>04:15:02</t>
+  </si>
+  <si>
+    <t>05:50:47</t>
+  </si>
+  <si>
+    <t>20:49:50</t>
+  </si>
+  <si>
+    <t>22:25:14</t>
+  </si>
+  <si>
+    <t>03:21:08</t>
+  </si>
+  <si>
+    <t>04:58:24</t>
+  </si>
+  <si>
+    <t>19:56:17</t>
+  </si>
+  <si>
+    <t>21:32:37</t>
+  </si>
+  <si>
+    <t>02:26:43</t>
+  </si>
+  <si>
+    <t>04:05:18</t>
+  </si>
+  <si>
+    <t>20:39:31</t>
+  </si>
+  <si>
+    <t>03:11:44</t>
+  </si>
+  <si>
+    <t>04:45:51</t>
+  </si>
+  <si>
+    <t>19:46:09</t>
+  </si>
+  <si>
+    <t>00:24:17</t>
+  </si>
+  <si>
+    <t>05:19:41</t>
+  </si>
+  <si>
+    <t>21:54:43</t>
+  </si>
+  <si>
+    <t>23:31:22</t>
+  </si>
+  <si>
+    <t>04:26:08</t>
+  </si>
+  <si>
+    <t>06:03:43</t>
+  </si>
+  <si>
+    <t>21:01:25</t>
+  </si>
+  <si>
+    <t>22:38:21</t>
+  </si>
+  <si>
+    <t>03:32:21</t>
+  </si>
+  <si>
+    <t>05:10:37</t>
+  </si>
+  <si>
+    <t>20:07:48</t>
+  </si>
+  <si>
+    <t>21:45:12</t>
+  </si>
+  <si>
+    <t>04:17:12</t>
+  </si>
+  <si>
+    <t>05:53:26</t>
+  </si>
+  <si>
+    <t>20:51:55</t>
+  </si>
+  <si>
+    <t>22:28:25</t>
   </si>
   <si>
     <t>03:23:30</t>
   </si>
   <si>
-    <t>05:00:00</t>
-  </si>
-  <si>
-    <t>19:58:46</t>
-  </si>
-  <si>
-    <t>21:34:52</t>
-  </si>
-  <si>
-    <t>04:06:50</t>
-  </si>
-  <si>
-    <t>05:44:09</t>
-  </si>
-  <si>
-    <t>20:41:29</t>
-  </si>
-  <si>
-    <t>22:19:39</t>
-  </si>
-  <si>
-    <t>03:13:39</t>
-  </si>
-  <si>
-    <t>04:50:32</t>
+    <t>05:00:37</t>
+  </si>
+  <si>
+    <t>19:58:25</t>
+  </si>
+  <si>
+    <t>21:35:09</t>
+  </si>
+  <si>
+    <t>02:29:31</t>
+  </si>
+  <si>
+    <t>04:07:23</t>
+  </si>
+  <si>
+    <t>20:41:46</t>
+  </si>
+  <si>
+    <t>03:13:50</t>
+  </si>
+  <si>
+    <t>04:49:28</t>
   </si>
   <si>
     <t>19:48:15</t>
   </si>
   <si>
-    <t>21:25:42</t>
-  </si>
-  <si>
-    <t>02:20:26</t>
-  </si>
-  <si>
-    <t>03:57:01</t>
-  </si>
-  <si>
-    <t>20:31:50</t>
-  </si>
-  <si>
-    <t>06:04:25</t>
-  </si>
-  <si>
-    <t>22:39:19</t>
-  </si>
-  <si>
-    <t>00:19:58</t>
-  </si>
-  <si>
-    <t>05:11:41</t>
-  </si>
-  <si>
-    <t>21:46:18</t>
-  </si>
-  <si>
-    <t>23:24:42</t>
-  </si>
-  <si>
-    <t>04:19:04</t>
-  </si>
-  <si>
-    <t>05:55:19</t>
-  </si>
-  <si>
-    <t>20:53:37</t>
-  </si>
-  <si>
-    <t>22:30:42</t>
-  </si>
-  <si>
-    <t>03:26:48</t>
-  </si>
-  <si>
-    <t>05:02:05</t>
-  </si>
-  <si>
-    <t>20:01:32</t>
-  </si>
-  <si>
-    <t>21:37:00</t>
-  </si>
-  <si>
-    <t>04:09:00</t>
-  </si>
-  <si>
-    <t>05:46:49</t>
-  </si>
-  <si>
-    <t>20:43:33</t>
-  </si>
-  <si>
-    <t>22:22:50</t>
-  </si>
-  <si>
-    <t>03:16:02</t>
-  </si>
-  <si>
-    <t>04:52:45</t>
-  </si>
-  <si>
-    <t>19:50:23</t>
-  </si>
-  <si>
-    <t>21:28:14</t>
-  </si>
-  <si>
-    <t>02:23:14</t>
-  </si>
-  <si>
-    <t>03:59:07</t>
-  </si>
-  <si>
-    <t>20:34:04</t>
-  </si>
-  <si>
-    <t>06:07:38</t>
-  </si>
-  <si>
-    <t>22:42:30</t>
-  </si>
-  <si>
-    <t>05:14:33</t>
-  </si>
-  <si>
-    <t>21:49:28</t>
-  </si>
-  <si>
-    <t>23:26:40</t>
-  </si>
-  <si>
-    <t>04:21:20</t>
-  </si>
-  <si>
-    <t>05:58:29</t>
-  </si>
-  <si>
-    <t>20:56:24</t>
-  </si>
-  <si>
-    <t>22:33:22</t>
-  </si>
-  <si>
-    <t>03:27:57</t>
-  </si>
-  <si>
-    <t>05:05:21</t>
-  </si>
-  <si>
-    <t>20:03:20</t>
-  </si>
-  <si>
-    <t>21:40:04</t>
-  </si>
-  <si>
-    <t>04:12:05</t>
-  </si>
-  <si>
-    <t>05:48:51</t>
-  </si>
-  <si>
-    <t>20:46:46</t>
-  </si>
-  <si>
-    <t>22:24:06</t>
-  </si>
-  <si>
-    <t>03:18:40</t>
-  </si>
-  <si>
-    <t>04:55:39</t>
-  </si>
-  <si>
-    <t>19:53:26</t>
-  </si>
-  <si>
-    <t>21:30:32</t>
-  </si>
-  <si>
-    <t>02:25:06</t>
-  </si>
-  <si>
-    <t>04:02:20</t>
-  </si>
-  <si>
-    <t>20:36:57</t>
-  </si>
-  <si>
-    <t>06:10:50</t>
-  </si>
-  <si>
-    <t>22:45:42</t>
-  </si>
-  <si>
-    <t>00:20:20</t>
-  </si>
-  <si>
-    <t>05:17:25</t>
-  </si>
-  <si>
-    <t>21:52:39</t>
-  </si>
-  <si>
-    <t>23:28:39</t>
-  </si>
-  <si>
-    <t>04:23:36</t>
-  </si>
-  <si>
-    <t>06:01:38</t>
-  </si>
-  <si>
-    <t>20:59:13</t>
-  </si>
-  <si>
-    <t>22:36:03</t>
-  </si>
-  <si>
-    <t>03:29:07</t>
-  </si>
-  <si>
-    <t>05:08:36</t>
-  </si>
-  <si>
-    <t>20:05:07</t>
-  </si>
-  <si>
-    <t>21:43:09</t>
-  </si>
-  <si>
-    <t>04:15:10</t>
-  </si>
-  <si>
-    <t>05:50:54</t>
-  </si>
-  <si>
-    <t>20:49:59</t>
-  </si>
-  <si>
-    <t>22:25:23</t>
-  </si>
-  <si>
-    <t>03:21:18</t>
-  </si>
-  <si>
-    <t>04:58:34</t>
-  </si>
-  <si>
-    <t>19:56:31</t>
-  </si>
-  <si>
-    <t>21:32:50</t>
-  </si>
-  <si>
-    <t>02:26:59</t>
-  </si>
-  <si>
-    <t>04:05:33</t>
-  </si>
-  <si>
-    <t>20:39:50</t>
-  </si>
-  <si>
-    <t>06:12:57</t>
-  </si>
-  <si>
-    <t>22:47:49</t>
-  </si>
-  <si>
-    <t>00:24:18</t>
-  </si>
-  <si>
-    <t>05:19:42</t>
-  </si>
-  <si>
-    <t>21:54:45</t>
-  </si>
-  <si>
-    <t>23:31:23</t>
-  </si>
-  <si>
-    <t>04:26:11</t>
-  </si>
-  <si>
-    <t>06:03:46</t>
-  </si>
-  <si>
-    <t>21:01:28</t>
-  </si>
-  <si>
-    <t>22:38:24</t>
-  </si>
-  <si>
-    <t>03:32:25</t>
-  </si>
-  <si>
-    <t>05:10:42</t>
-  </si>
-  <si>
-    <t>20:07:54</t>
-  </si>
-  <si>
-    <t>21:45:19</t>
-  </si>
-  <si>
-    <t>04:17:20</t>
-  </si>
-  <si>
-    <t>05:53:33</t>
-  </si>
-  <si>
-    <t>20:52:04</t>
-  </si>
-  <si>
-    <t>22:28:35</t>
-  </si>
-  <si>
-    <t>03:23:41</t>
-  </si>
-  <si>
-    <t>05:00:47</t>
-  </si>
-  <si>
-    <t>19:58:39</t>
-  </si>
-  <si>
-    <t>21:35:23</t>
-  </si>
-  <si>
-    <t>02:29:47</t>
-  </si>
-  <si>
-    <t>04:07:39</t>
-  </si>
-  <si>
-    <t>20:42:05</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>0°</t>
   </si>
   <si>
@@ -640,7 +655,7 @@
     <t>9°</t>
   </si>
   <si>
-    <t>2°</t>
+    <t>1°</t>
   </si>
   <si>
     <t>41°</t>
@@ -649,55 +664,58 @@
     <t>19°</t>
   </si>
   <si>
-    <t>06:05:12</t>
-  </si>
-  <si>
-    <t>05:15:09</t>
-  </si>
-  <si>
-    <t>04:25:07</t>
-  </si>
-  <si>
-    <t>05:57:47</t>
-  </si>
-  <si>
-    <t>05:07:47</t>
-  </si>
-  <si>
-    <t>20:00:52</t>
-  </si>
-  <si>
-    <t>05:50:26</t>
-  </si>
-  <si>
-    <t>20:43:25</t>
-  </si>
-  <si>
-    <t>05:00:23</t>
-  </si>
-  <si>
-    <t>19:53:09</t>
-  </si>
-  <si>
-    <t>21:25:47</t>
-  </si>
-  <si>
-    <t>20:35:20</t>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>05:15:08</t>
+  </si>
+  <si>
+    <t>04:25:05</t>
+  </si>
+  <si>
+    <t>05:57:45</t>
+  </si>
+  <si>
+    <t>05:07:43</t>
+  </si>
+  <si>
+    <t>20:00:46</t>
+  </si>
+  <si>
+    <t>05:50:19</t>
+  </si>
+  <si>
+    <t>20:43:16</t>
+  </si>
+  <si>
+    <t>05:00:13</t>
+  </si>
+  <si>
+    <t>19:52:56</t>
+  </si>
+  <si>
+    <t>21:25:34</t>
+  </si>
+  <si>
+    <t>20:35:02</t>
+  </si>
+  <si>
+    <t>19:44:18</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -746,13 +764,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,7 +782,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,73 +848,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1352,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1430,55 +1448,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="L2" s="4">
-        <v>-13.6</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="O2" s="6">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="P2" s="7">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
       <c r="R2" s="9">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1486,55 +1504,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="L3" s="4">
-        <v>-53.4</v>
+        <v>-25.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O3" s="6">
-        <v>90</v>
-      </c>
-      <c r="P3" s="10">
-        <v>66</v>
+        <v>232</v>
+      </c>
+      <c r="O3" s="10">
+        <v>52</v>
+      </c>
+      <c r="P3" s="11">
+        <v>35</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="11">
-        <v>68</v>
+      <c r="R3" s="12">
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1542,55 +1560,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L4" s="4">
-        <v>-68.40000000000001</v>
+        <v>-42.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O4" s="6">
-        <v>93</v>
-      </c>
-      <c r="P4" s="10">
-        <v>64</v>
+        <v>233</v>
+      </c>
+      <c r="O4" s="10">
+        <v>90</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="12">
-        <v>79</v>
+      <c r="R4" s="13">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1598,55 +1616,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="L5" s="4">
-        <v>-25.3</v>
+        <v>-61.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O5" s="6">
-        <v>98</v>
-      </c>
-      <c r="P5" s="13">
-        <v>9</v>
+        <v>233</v>
+      </c>
+      <c r="O5" s="10">
+        <v>99</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
       <c r="R5" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1654,46 +1672,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="L6" s="4">
-        <v>-42.7</v>
+        <v>-36.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O6" s="6">
-        <v>69</v>
+        <v>233</v>
+      </c>
+      <c r="O6" s="10">
+        <v>100</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1701,8 +1719,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="11">
-        <v>69</v>
+      <c r="R6" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1710,54 +1728,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="L7" s="4">
-        <v>-61.8</v>
+        <v>-15.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O7" s="6">
+        <v>232</v>
+      </c>
+      <c r="O7" s="10">
         <v>100</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="15">
+      <c r="Q7" s="15">
+        <v>21</v>
+      </c>
+      <c r="R7" s="14">
         <v>100</v>
       </c>
     </row>
@@ -1766,45 +1784,45 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="L8" s="4">
-        <v>-36.9</v>
+        <v>-31.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O8" s="6">
+        <v>233</v>
+      </c>
+      <c r="O8" s="10">
         <v>100</v>
       </c>
       <c r="P8" s="8">
@@ -1814,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="14">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1822,45 +1840,45 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="L9" s="4">
-        <v>-15.8</v>
+        <v>-52.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O9" s="6">
+        <v>233</v>
+      </c>
+      <c r="O9" s="10">
         <v>100</v>
       </c>
       <c r="P9" s="8">
@@ -1869,7 +1887,7 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="15">
+      <c r="R9" s="14">
         <v>100</v>
       </c>
     </row>
@@ -1878,54 +1896,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L10" s="4">
-        <v>-31.5</v>
+        <v>-48.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O10" s="6">
+        <v>231</v>
+      </c>
+      <c r="O10" s="10">
         <v>100</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="16">
-        <v>14</v>
-      </c>
-      <c r="R10" s="15">
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="14">
         <v>100</v>
       </c>
     </row>
@@ -1934,54 +1952,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="L11" s="4">
-        <v>-52.1</v>
+        <v>-27.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O11" s="6">
+        <v>232</v>
+      </c>
+      <c r="O11" s="10">
         <v>100</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="13">
-        <v>9</v>
-      </c>
-      <c r="R11" s="15">
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="14">
         <v>100</v>
       </c>
     </row>
@@ -1990,55 +2008,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>85</v>
+        <v>221</v>
       </c>
       <c r="L12" s="4">
-        <v>-48.5</v>
+        <v>-19.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O12" s="6">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
       <c r="Q12" s="9">
-        <v>34</v>
-      </c>
-      <c r="R12" s="15">
-        <v>100</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2046,55 +2064,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>215</v>
+        <v>87</v>
       </c>
       <c r="L13" s="4">
-        <v>-27.5</v>
+        <v>-41.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="O13" s="6">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="9">
-        <v>37</v>
-      </c>
-      <c r="R13" s="17">
-        <v>91</v>
+      <c r="Q13" s="7">
+        <v>10</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2102,7 +2120,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>55</v>
@@ -2111,46 +2129,46 @@
         <v>68</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>216</v>
+        <v>88</v>
       </c>
       <c r="L14" s="4">
-        <v>-20</v>
+        <v>-39.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O14" s="6">
-        <v>79</v>
+        <v>233</v>
+      </c>
+      <c r="O14" s="16">
+        <v>0</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="18">
-        <v>5</v>
-      </c>
-      <c r="R14" s="16">
-        <v>17</v>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2158,46 +2176,46 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="L15" s="4">
-        <v>-41.2</v>
+        <v>-18.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O15" s="6">
-        <v>80</v>
+        <v>232</v>
+      </c>
+      <c r="O15" s="16">
+        <v>1</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -2214,7 +2232,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>57</v>
@@ -2223,43 +2241,43 @@
         <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="L16" s="4">
-        <v>-39.3</v>
+        <v>-29.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O16" s="6">
-        <v>69</v>
+        <v>233</v>
+      </c>
+      <c r="O16" s="16">
+        <v>0</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="13">
-        <v>11</v>
+      <c r="Q16" s="8">
+        <v>0</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>
@@ -2270,52 +2288,52 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>217</v>
+        <v>91</v>
       </c>
       <c r="L17" s="4">
-        <v>-18.1</v>
+        <v>-50.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O17" s="19">
-        <v>27</v>
+        <v>231</v>
+      </c>
+      <c r="O17" s="16">
+        <v>0</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="18">
-        <v>4</v>
+      <c r="Q17" s="8">
+        <v>0</v>
       </c>
       <c r="R17" s="8">
         <v>0</v>
@@ -2326,7 +2344,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>59</v>
@@ -2335,43 +2353,43 @@
         <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="L18" s="4">
-        <v>-29.7</v>
+        <v>-50.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O18" s="6">
-        <v>57</v>
-      </c>
-      <c r="P18" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="20">
-        <v>57</v>
+        <v>233</v>
+      </c>
+      <c r="O18" s="10">
+        <v>50</v>
+      </c>
+      <c r="P18" s="17">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -2382,7 +2400,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>60</v>
@@ -2391,46 +2409,46 @@
         <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>92</v>
+        <v>224</v>
       </c>
       <c r="L19" s="4">
-        <v>-50.7</v>
+        <v>-29.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O19" s="6">
-        <v>68</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
+        <v>233</v>
+      </c>
+      <c r="O19" s="10">
+        <v>49</v>
+      </c>
+      <c r="P19" s="17">
+        <v>49</v>
       </c>
       <c r="Q19" s="8">
-        <v>1</v>
-      </c>
-      <c r="R19" s="18">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2438,55 +2456,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="L20" s="4">
-        <v>-50.7</v>
+        <v>-18.2</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O20" s="6">
-        <v>55</v>
-      </c>
-      <c r="P20" s="21">
-        <v>52</v>
+        <v>232</v>
+      </c>
+      <c r="O20" s="10">
+        <v>74</v>
+      </c>
+      <c r="P20" s="18">
+        <v>74</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
       </c>
-      <c r="R20" s="18">
-        <v>3</v>
+      <c r="R20" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2494,7 +2512,7 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>62</v>
@@ -2503,46 +2521,46 @@
         <v>68</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="L21" s="4">
-        <v>-29.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O21" s="6">
-        <v>54</v>
-      </c>
-      <c r="P21" s="21">
-        <v>52</v>
+        <v>233</v>
+      </c>
+      <c r="O21" s="10">
+        <v>68</v>
+      </c>
+      <c r="P21" s="19">
+        <v>65</v>
       </c>
       <c r="Q21" s="8">
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2550,55 +2568,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>220</v>
+        <v>96</v>
       </c>
       <c r="L22" s="4">
-        <v>-18.3</v>
+        <v>-61.3</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O22" s="6">
-        <v>45</v>
-      </c>
-      <c r="P22" s="22">
-        <v>45</v>
+        <v>231</v>
+      </c>
+      <c r="O22" s="10">
+        <v>77</v>
+      </c>
+      <c r="P22" s="18">
+        <v>75</v>
       </c>
       <c r="Q22" s="8">
         <v>0</v>
       </c>
       <c r="R22" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2606,7 +2624,7 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>64</v>
@@ -2615,46 +2633,46 @@
         <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="L23" s="4">
-        <v>-39.4</v>
+        <v>-41.7</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O23" s="19">
-        <v>17</v>
-      </c>
-      <c r="P23" s="16">
-        <v>17</v>
+        <v>233</v>
+      </c>
+      <c r="O23" s="10">
+        <v>82</v>
+      </c>
+      <c r="P23" s="12">
+        <v>72</v>
       </c>
       <c r="Q23" s="8">
         <v>0</v>
       </c>
-      <c r="R23" s="8">
-        <v>0</v>
+      <c r="R23" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2662,55 +2680,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-27.9</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="O24" s="10">
         <v>97</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-61.3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O24" s="6">
-        <v>60</v>
-      </c>
-      <c r="P24" s="22">
-        <v>45</v>
+      <c r="P24" s="21">
+        <v>47</v>
       </c>
       <c r="Q24" s="8">
-        <v>0</v>
-      </c>
-      <c r="R24" s="8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R24" s="11">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2718,49 +2736,49 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
+        <v>57</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L25" s="4">
-        <v>-41.6</v>
+        <v>-53.1</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O25" s="6">
-        <v>86</v>
-      </c>
-      <c r="P25" s="11">
-        <v>71</v>
+        <v>233</v>
+      </c>
+      <c r="O25" s="16">
+        <v>1</v>
+      </c>
+      <c r="P25" s="8">
+        <v>1</v>
       </c>
       <c r="Q25" s="8">
         <v>0</v>
@@ -2774,114 +2792,170 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="L26" s="4">
-        <v>-28</v>
+        <v>-32.5</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O26" s="6">
-        <v>82</v>
-      </c>
-      <c r="P26" s="12">
-        <v>82</v>
+        <v>231</v>
+      </c>
+      <c r="O26" s="16">
+        <v>4</v>
+      </c>
+      <c r="P26" s="20">
+        <v>3</v>
       </c>
       <c r="Q26" s="8">
         <v>0</v>
       </c>
-      <c r="R26" s="18">
-        <v>4</v>
+      <c r="R26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2">
+        <v>57</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-16.4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="O27" s="10">
+        <v>84</v>
+      </c>
+      <c r="P27" s="22">
+        <v>84</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D27">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J27">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K27">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2900,12 +2974,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M27">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2922,22 +2996,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O27">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P27">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q27">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R27">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="225">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261014--01</t>
-  </si>
-  <si>
-    <t>20261014--02</t>
-  </si>
-  <si>
-    <t>20261014--03</t>
-  </si>
-  <si>
-    <t>20261014--04</t>
-  </si>
-  <si>
     <t>20261015--01</t>
   </si>
   <si>
@@ -148,84 +136,84 @@
     <t>20261020--03</t>
   </si>
   <si>
-    <t>00:21</t>
-  </si>
-  <si>
-    <t>05:44</t>
+    <t>20261021--01</t>
+  </si>
+  <si>
+    <t>20261021--02</t>
+  </si>
+  <si>
+    <t>20261021--03</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>02:18</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>03:34</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>03:42</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>01:25</t>
   </si>
   <si>
     <t>06:21</t>
   </si>
   <si>
-    <t>03:56</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>02:19</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>03:34</t>
-  </si>
-  <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>04:06</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>03:43</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>01:21</t>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:02</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:16</t>
-  </si>
-  <si>
     <t>03:51</t>
   </si>
   <si>
@@ -238,411 +226,393 @@
     <t>02:47</t>
   </si>
   <si>
-    <t>01:16</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>00:15:40</t>
-  </si>
-  <si>
-    <t>05:09:24</t>
-  </si>
-  <si>
-    <t>21:44:11</t>
-  </si>
-  <si>
-    <t>23:21:58</t>
-  </si>
-  <si>
-    <t>04:16:27</t>
-  </si>
-  <si>
-    <t>05:53:09</t>
-  </si>
-  <si>
-    <t>20:51:19</t>
-  </si>
-  <si>
-    <t>22:28:19</t>
-  </si>
-  <si>
-    <t>03:23:26</t>
-  </si>
-  <si>
-    <t>04:59:56</t>
-  </si>
-  <si>
-    <t>19:58:40</t>
-  </si>
-  <si>
-    <t>21:34:45</t>
-  </si>
-  <si>
-    <t>04:06:43</t>
-  </si>
-  <si>
-    <t>05:44:02</t>
-  </si>
-  <si>
-    <t>20:41:19</t>
-  </si>
-  <si>
-    <t>22:19:29</t>
-  </si>
-  <si>
-    <t>03:13:29</t>
-  </si>
-  <si>
-    <t>04:50:21</t>
+    <t>01:17</t>
+  </si>
+  <si>
+    <t>01:22</t>
+  </si>
+  <si>
+    <t>04:16:26</t>
+  </si>
+  <si>
+    <t>05:53:08</t>
+  </si>
+  <si>
+    <t>20:51:18</t>
+  </si>
+  <si>
+    <t>22:28:17</t>
+  </si>
+  <si>
+    <t>03:23:25</t>
+  </si>
+  <si>
+    <t>04:59:54</t>
+  </si>
+  <si>
+    <t>19:58:38</t>
+  </si>
+  <si>
+    <t>21:34:43</t>
+  </si>
+  <si>
+    <t>04:06:40</t>
+  </si>
+  <si>
+    <t>05:43:58</t>
+  </si>
+  <si>
+    <t>20:41:15</t>
+  </si>
+  <si>
+    <t>22:19:24</t>
+  </si>
+  <si>
+    <t>03:13:24</t>
+  </si>
+  <si>
+    <t>04:50:15</t>
+  </si>
+  <si>
+    <t>19:47:55</t>
+  </si>
+  <si>
+    <t>21:25:21</t>
+  </si>
+  <si>
+    <t>02:20:04</t>
+  </si>
+  <si>
+    <t>03:56:38</t>
+  </si>
+  <si>
+    <t>20:31:22</t>
+  </si>
+  <si>
+    <t>03:03:03</t>
+  </si>
+  <si>
+    <t>04:40:42</t>
+  </si>
+  <si>
+    <t>19:37:29</t>
+  </si>
+  <si>
+    <t>02:09:28</t>
+  </si>
+  <si>
+    <t>03:46:31</t>
+  </si>
+  <si>
+    <t>20:21:32</t>
+  </si>
+  <si>
+    <t>04:19:01</t>
+  </si>
+  <si>
+    <t>05:55:16</t>
+  </si>
+  <si>
+    <t>20:53:32</t>
+  </si>
+  <si>
+    <t>22:30:37</t>
+  </si>
+  <si>
+    <t>03:26:43</t>
+  </si>
+  <si>
+    <t>05:01:59</t>
+  </si>
+  <si>
+    <t>20:01:24</t>
+  </si>
+  <si>
+    <t>21:36:51</t>
+  </si>
+  <si>
+    <t>04:08:50</t>
+  </si>
+  <si>
+    <t>05:46:38</t>
+  </si>
+  <si>
+    <t>20:43:19</t>
+  </si>
+  <si>
+    <t>22:22:34</t>
+  </si>
+  <si>
+    <t>03:15:46</t>
+  </si>
+  <si>
+    <t>04:52:28</t>
+  </si>
+  <si>
+    <t>19:50:02</t>
+  </si>
+  <si>
+    <t>21:27:52</t>
+  </si>
+  <si>
+    <t>02:22:53</t>
+  </si>
+  <si>
+    <t>03:58:44</t>
+  </si>
+  <si>
+    <t>20:33:35</t>
+  </si>
+  <si>
+    <t>03:05:10</t>
+  </si>
+  <si>
+    <t>04:44:17</t>
+  </si>
+  <si>
+    <t>19:39:34</t>
+  </si>
+  <si>
+    <t>02:11:42</t>
+  </si>
+  <si>
+    <t>03:48:55</t>
+  </si>
+  <si>
+    <t>20:24:20</t>
+  </si>
+  <si>
+    <t>04:21:17</t>
+  </si>
+  <si>
+    <t>05:58:26</t>
+  </si>
+  <si>
+    <t>20:56:20</t>
+  </si>
+  <si>
+    <t>22:33:17</t>
+  </si>
+  <si>
+    <t>03:27:52</t>
+  </si>
+  <si>
+    <t>05:05:15</t>
+  </si>
+  <si>
+    <t>20:03:11</t>
+  </si>
+  <si>
+    <t>21:39:55</t>
+  </si>
+  <si>
+    <t>04:11:54</t>
+  </si>
+  <si>
+    <t>05:48:40</t>
+  </si>
+  <si>
+    <t>20:46:32</t>
+  </si>
+  <si>
+    <t>22:23:52</t>
+  </si>
+  <si>
+    <t>03:18:24</t>
+  </si>
+  <si>
+    <t>04:55:23</t>
+  </si>
+  <si>
+    <t>19:53:06</t>
+  </si>
+  <si>
+    <t>21:30:11</t>
+  </si>
+  <si>
+    <t>02:24:44</t>
+  </si>
+  <si>
+    <t>04:01:57</t>
+  </si>
+  <si>
+    <t>20:36:28</t>
+  </si>
+  <si>
+    <t>03:08:21</t>
+  </si>
+  <si>
+    <t>04:45:00</t>
+  </si>
+  <si>
+    <t>19:42:44</t>
+  </si>
+  <si>
+    <t>02:14:36</t>
+  </si>
+  <si>
+    <t>03:51:26</t>
+  </si>
+  <si>
+    <t>20:26:10</t>
+  </si>
+  <si>
+    <t>04:23:32</t>
+  </si>
+  <si>
+    <t>06:01:35</t>
+  </si>
+  <si>
+    <t>20:59:08</t>
+  </si>
+  <si>
+    <t>22:35:58</t>
+  </si>
+  <si>
+    <t>03:29:01</t>
+  </si>
+  <si>
+    <t>05:08:30</t>
+  </si>
+  <si>
+    <t>20:04:58</t>
+  </si>
+  <si>
+    <t>21:43:00</t>
+  </si>
+  <si>
+    <t>04:14:59</t>
+  </si>
+  <si>
+    <t>05:50:44</t>
+  </si>
+  <si>
+    <t>20:49:45</t>
+  </si>
+  <si>
+    <t>22:25:09</t>
+  </si>
+  <si>
+    <t>03:21:02</t>
+  </si>
+  <si>
+    <t>04:58:18</t>
+  </si>
+  <si>
+    <t>19:56:10</t>
+  </si>
+  <si>
+    <t>21:32:29</t>
+  </si>
+  <si>
+    <t>02:26:35</t>
+  </si>
+  <si>
+    <t>04:05:10</t>
+  </si>
+  <si>
+    <t>20:39:21</t>
+  </si>
+  <si>
+    <t>03:11:33</t>
+  </si>
+  <si>
+    <t>04:45:42</t>
+  </si>
+  <si>
+    <t>19:45:55</t>
+  </si>
+  <si>
+    <t>02:17:29</t>
+  </si>
+  <si>
+    <t>03:53:57</t>
+  </si>
+  <si>
+    <t>20:28:02</t>
+  </si>
+  <si>
+    <t>04:26:08</t>
+  </si>
+  <si>
+    <t>06:03:43</t>
+  </si>
+  <si>
+    <t>21:01:23</t>
+  </si>
+  <si>
+    <t>22:38:19</t>
+  </si>
+  <si>
+    <t>03:32:19</t>
+  </si>
+  <si>
+    <t>05:10:35</t>
+  </si>
+  <si>
+    <t>20:07:45</t>
+  </si>
+  <si>
+    <t>21:45:10</t>
+  </si>
+  <si>
+    <t>04:17:09</t>
+  </si>
+  <si>
+    <t>05:53:23</t>
+  </si>
+  <si>
+    <t>20:51:50</t>
+  </si>
+  <si>
+    <t>22:28:20</t>
+  </si>
+  <si>
+    <t>05:00:31</t>
+  </si>
+  <si>
+    <t>19:58:18</t>
+  </si>
+  <si>
+    <t>21:35:02</t>
+  </si>
+  <si>
+    <t>02:29:23</t>
+  </si>
+  <si>
+    <t>04:07:15</t>
+  </si>
+  <si>
+    <t>20:41:36</t>
+  </si>
+  <si>
+    <t>03:13:39</t>
+  </si>
+  <si>
+    <t>04:49:17</t>
   </si>
   <si>
     <t>19:48:02</t>
   </si>
   <si>
-    <t>21:25:28</t>
-  </si>
-  <si>
-    <t>02:20:12</t>
-  </si>
-  <si>
-    <t>03:56:46</t>
-  </si>
-  <si>
-    <t>20:31:32</t>
-  </si>
-  <si>
-    <t>03:03:14</t>
-  </si>
-  <si>
-    <t>04:40:54</t>
-  </si>
-  <si>
-    <t>19:37:42</t>
-  </si>
-  <si>
-    <t>00:19:58</t>
-  </si>
-  <si>
-    <t>05:11:40</t>
-  </si>
-  <si>
-    <t>21:46:16</t>
-  </si>
-  <si>
-    <t>23:24:41</t>
-  </si>
-  <si>
-    <t>04:19:02</t>
-  </si>
-  <si>
-    <t>05:55:17</t>
-  </si>
-  <si>
-    <t>20:53:33</t>
-  </si>
-  <si>
-    <t>22:30:39</t>
-  </si>
-  <si>
-    <t>03:26:44</t>
-  </si>
-  <si>
-    <t>05:02:01</t>
-  </si>
-  <si>
-    <t>20:01:27</t>
-  </si>
-  <si>
-    <t>21:36:54</t>
-  </si>
-  <si>
-    <t>04:08:53</t>
-  </si>
-  <si>
-    <t>05:46:41</t>
-  </si>
-  <si>
-    <t>20:43:23</t>
-  </si>
-  <si>
-    <t>22:22:39</t>
-  </si>
-  <si>
-    <t>03:15:52</t>
-  </si>
-  <si>
-    <t>04:52:34</t>
-  </si>
-  <si>
-    <t>19:50:09</t>
-  </si>
-  <si>
-    <t>21:27:59</t>
-  </si>
-  <si>
-    <t>02:23:00</t>
-  </si>
-  <si>
-    <t>03:58:52</t>
-  </si>
-  <si>
-    <t>20:33:46</t>
-  </si>
-  <si>
-    <t>03:05:21</t>
-  </si>
-  <si>
-    <t>04:44:30</t>
-  </si>
-  <si>
-    <t>19:39:48</t>
-  </si>
-  <si>
-    <t>05:14:32</t>
-  </si>
-  <si>
-    <t>21:49:26</t>
-  </si>
-  <si>
-    <t>23:26:39</t>
-  </si>
-  <si>
-    <t>04:21:17</t>
-  </si>
-  <si>
-    <t>05:58:26</t>
-  </si>
-  <si>
-    <t>20:56:21</t>
-  </si>
-  <si>
-    <t>22:33:19</t>
-  </si>
-  <si>
-    <t>03:27:53</t>
-  </si>
-  <si>
-    <t>05:05:17</t>
-  </si>
-  <si>
-    <t>20:03:14</t>
-  </si>
-  <si>
-    <t>21:39:58</t>
-  </si>
-  <si>
-    <t>04:11:58</t>
-  </si>
-  <si>
-    <t>05:48:44</t>
-  </si>
-  <si>
-    <t>20:46:36</t>
-  </si>
-  <si>
-    <t>22:23:57</t>
-  </si>
-  <si>
-    <t>03:18:30</t>
-  </si>
-  <si>
-    <t>04:55:29</t>
-  </si>
-  <si>
-    <t>19:53:13</t>
-  </si>
-  <si>
-    <t>21:30:18</t>
-  </si>
-  <si>
-    <t>02:24:52</t>
-  </si>
-  <si>
-    <t>04:02:05</t>
-  </si>
-  <si>
-    <t>20:36:38</t>
-  </si>
-  <si>
-    <t>03:08:32</t>
-  </si>
-  <si>
-    <t>04:45:11</t>
-  </si>
-  <si>
-    <t>19:42:58</t>
-  </si>
-  <si>
-    <t>00:20:19</t>
-  </si>
-  <si>
-    <t>05:17:24</t>
-  </si>
-  <si>
-    <t>21:52:37</t>
-  </si>
-  <si>
-    <t>23:28:37</t>
-  </si>
-  <si>
-    <t>04:23:33</t>
-  </si>
-  <si>
-    <t>06:01:36</t>
-  </si>
-  <si>
-    <t>20:59:09</t>
-  </si>
-  <si>
-    <t>22:36:00</t>
-  </si>
-  <si>
-    <t>03:29:03</t>
-  </si>
-  <si>
-    <t>05:08:32</t>
-  </si>
-  <si>
-    <t>20:05:01</t>
-  </si>
-  <si>
-    <t>21:43:03</t>
-  </si>
-  <si>
-    <t>04:15:02</t>
-  </si>
-  <si>
-    <t>05:50:47</t>
-  </si>
-  <si>
-    <t>20:49:50</t>
-  </si>
-  <si>
-    <t>22:25:14</t>
-  </si>
-  <si>
-    <t>03:21:08</t>
-  </si>
-  <si>
-    <t>04:58:24</t>
-  </si>
-  <si>
-    <t>19:56:17</t>
-  </si>
-  <si>
-    <t>21:32:37</t>
-  </si>
-  <si>
-    <t>02:26:43</t>
-  </si>
-  <si>
-    <t>04:05:18</t>
-  </si>
-  <si>
-    <t>20:39:31</t>
-  </si>
-  <si>
-    <t>03:11:44</t>
-  </si>
-  <si>
-    <t>04:45:51</t>
-  </si>
-  <si>
-    <t>19:46:09</t>
-  </si>
-  <si>
-    <t>00:24:17</t>
-  </si>
-  <si>
-    <t>05:19:41</t>
-  </si>
-  <si>
-    <t>21:54:43</t>
-  </si>
-  <si>
-    <t>23:31:22</t>
-  </si>
-  <si>
-    <t>04:26:08</t>
-  </si>
-  <si>
-    <t>06:03:43</t>
-  </si>
-  <si>
-    <t>21:01:25</t>
-  </si>
-  <si>
-    <t>22:38:21</t>
-  </si>
-  <si>
-    <t>03:32:21</t>
-  </si>
-  <si>
-    <t>05:10:37</t>
-  </si>
-  <si>
-    <t>20:07:48</t>
-  </si>
-  <si>
-    <t>21:45:12</t>
-  </si>
-  <si>
-    <t>04:17:12</t>
-  </si>
-  <si>
-    <t>05:53:26</t>
-  </si>
-  <si>
-    <t>20:51:55</t>
-  </si>
-  <si>
-    <t>22:28:25</t>
-  </si>
-  <si>
-    <t>03:23:30</t>
-  </si>
-  <si>
-    <t>05:00:37</t>
-  </si>
-  <si>
-    <t>19:58:25</t>
-  </si>
-  <si>
-    <t>21:35:09</t>
-  </si>
-  <si>
-    <t>02:29:31</t>
-  </si>
-  <si>
-    <t>04:07:23</t>
-  </si>
-  <si>
-    <t>20:41:46</t>
-  </si>
-  <si>
-    <t>03:13:50</t>
-  </si>
-  <si>
-    <t>04:49:28</t>
-  </si>
-  <si>
-    <t>19:48:15</t>
+    <t>02:19:43</t>
+  </si>
+  <si>
+    <t>03:56:21</t>
+  </si>
+  <si>
+    <t>20:30:50</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>39°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>39°</t>
-  </si>
-  <si>
     <t>17°</t>
   </si>
   <si>
@@ -667,40 +637,43 @@
     <t>30°</t>
   </si>
   <si>
-    <t>05:15:08</t>
-  </si>
-  <si>
-    <t>04:25:05</t>
-  </si>
-  <si>
-    <t>05:57:45</t>
-  </si>
-  <si>
-    <t>05:07:43</t>
-  </si>
-  <si>
-    <t>20:00:46</t>
-  </si>
-  <si>
-    <t>05:50:19</t>
-  </si>
-  <si>
-    <t>20:43:16</t>
-  </si>
-  <si>
-    <t>05:00:13</t>
-  </si>
-  <si>
-    <t>19:52:56</t>
-  </si>
-  <si>
-    <t>21:25:34</t>
-  </si>
-  <si>
-    <t>20:35:02</t>
-  </si>
-  <si>
-    <t>19:44:18</t>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>04:25:04</t>
+  </si>
+  <si>
+    <t>05:57:44</t>
+  </si>
+  <si>
+    <t>05:07:41</t>
+  </si>
+  <si>
+    <t>20:00:43</t>
+  </si>
+  <si>
+    <t>05:50:16</t>
+  </si>
+  <si>
+    <t>20:43:11</t>
+  </si>
+  <si>
+    <t>05:00:07</t>
+  </si>
+  <si>
+    <t>19:52:49</t>
+  </si>
+  <si>
+    <t>21:25:27</t>
+  </si>
+  <si>
+    <t>20:34:52</t>
+  </si>
+  <si>
+    <t>19:44:05</t>
+  </si>
+  <si>
+    <t>20:25:42</t>
   </si>
   <si>
     <t>B</t>
@@ -709,13 +682,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -764,7 +737,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,31 +773,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,55 +815,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1370,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1448,55 +1421,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="L2" s="4">
-        <v>-68.40000000000001</v>
+        <v>-36.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="O2" s="6">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="P2" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
       <c r="R2" s="9">
-        <v>17</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1504,55 +1477,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L3" s="4">
-        <v>-25.3</v>
+        <v>-15.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O3" s="10">
-        <v>52</v>
-      </c>
-      <c r="P3" s="11">
-        <v>35</v>
+        <v>223</v>
+      </c>
+      <c r="O3" s="6">
+        <v>96</v>
+      </c>
+      <c r="P3" s="10">
+        <v>15</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="12">
-        <v>70</v>
+      <c r="R3" s="9">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1560,55 +1533,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L4" s="4">
-        <v>-42.7</v>
+        <v>-31.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O4" s="10">
-        <v>90</v>
+        <v>222</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="13">
-        <v>62</v>
+      <c r="Q4" s="11">
+        <v>8</v>
+      </c>
+      <c r="R4" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1616,55 +1589,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L5" s="4">
-        <v>-61.7</v>
+        <v>-52.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O5" s="10">
-        <v>99</v>
+        <v>222</v>
+      </c>
+      <c r="O5" s="6">
+        <v>100</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="14">
-        <v>99</v>
+      <c r="Q5" s="7">
+        <v>20</v>
+      </c>
+      <c r="R5" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1672,54 +1645,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="L6" s="4">
-        <v>-36.9</v>
+        <v>-48.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O6" s="10">
+        <v>224</v>
+      </c>
+      <c r="O6" s="6">
         <v>100</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="14">
+      <c r="Q6" s="12">
+        <v>71</v>
+      </c>
+      <c r="R6" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1728,54 +1701,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>79</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L7" s="4">
-        <v>-15.8</v>
+        <v>-27.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O7" s="10">
+        <v>223</v>
+      </c>
+      <c r="O7" s="6">
         <v>100</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="15">
-        <v>21</v>
-      </c>
-      <c r="R7" s="14">
+      <c r="Q7" s="12">
+        <v>69</v>
+      </c>
+      <c r="R7" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1784,55 +1757,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="L8" s="4">
-        <v>-31.5</v>
+        <v>-19.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O8" s="10">
-        <v>100</v>
+        <v>224</v>
+      </c>
+      <c r="O8" s="13">
+        <v>5</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="14">
-        <v>100</v>
+      <c r="Q8" s="14">
+        <v>4</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1840,46 +1813,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L9" s="4">
-        <v>-52.1</v>
+        <v>-41.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O9" s="10">
-        <v>100</v>
+        <v>222</v>
+      </c>
+      <c r="O9" s="13">
+        <v>1</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1887,8 +1860,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="14">
-        <v>100</v>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1896,46 +1869,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L10" s="4">
-        <v>-48.5</v>
+        <v>-39.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O10" s="10">
-        <v>100</v>
+        <v>222</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1943,8 +1916,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="14">
-        <v>100</v>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1952,46 +1925,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="L11" s="4">
-        <v>-27.5</v>
+        <v>-18.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O11" s="10">
-        <v>100</v>
+        <v>223</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1999,8 +1972,8 @@
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="14">
-        <v>100</v>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2008,52 +1981,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L12" s="4">
-        <v>-19.9</v>
+        <v>-29.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O12" s="6">
-        <v>41</v>
+        <v>222</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="9">
-        <v>17</v>
+      <c r="Q12" s="8">
+        <v>0</v>
       </c>
       <c r="R12" s="8">
         <v>0</v>
@@ -2064,52 +2037,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L13" s="4">
-        <v>-41.2</v>
+        <v>-50.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O13" s="6">
-        <v>28</v>
+        <v>224</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="7">
-        <v>10</v>
+      <c r="Q13" s="8">
+        <v>0</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -2120,49 +2093,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L14" s="4">
-        <v>-39.3</v>
+        <v>-50.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O14" s="16">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
+        <v>222</v>
+      </c>
+      <c r="O14" s="6">
+        <v>51</v>
+      </c>
+      <c r="P14" s="15">
+        <v>51</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -2176,49 +2149,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-29.8</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="L15" s="4">
-        <v>-18.1</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O15" s="16">
-        <v>1</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
+      <c r="O15" s="6">
+        <v>41</v>
+      </c>
+      <c r="P15" s="16">
+        <v>41</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -2232,55 +2205,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-18.2</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="O16" s="6">
         <v>68</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-29.7</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O16" s="16">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
+      <c r="P16" s="17">
+        <v>67</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
       </c>
-      <c r="R16" s="8">
-        <v>0</v>
+      <c r="R16" s="7">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2288,55 +2261,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-39.3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="O17" s="6">
+        <v>63</v>
+      </c>
+      <c r="P17" s="18">
         <v>58</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-50.7</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O17" s="16">
-        <v>0</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
       <c r="Q17" s="8">
         <v>0</v>
       </c>
-      <c r="R17" s="8">
-        <v>0</v>
+      <c r="R17" s="18">
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2344,55 +2317,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L18" s="4">
-        <v>-50.7</v>
+        <v>-61.4</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O18" s="10">
-        <v>50</v>
-      </c>
-      <c r="P18" s="17">
-        <v>50</v>
+        <v>224</v>
+      </c>
+      <c r="O18" s="6">
+        <v>70</v>
+      </c>
+      <c r="P18" s="15">
+        <v>52</v>
       </c>
       <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="R18" s="12">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2400,55 +2373,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>224</v>
+        <v>89</v>
       </c>
       <c r="L19" s="4">
-        <v>-29.8</v>
+        <v>-41.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O19" s="10">
-        <v>49</v>
-      </c>
-      <c r="P19" s="17">
-        <v>49</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8">
-        <v>0</v>
+        <v>222</v>
+      </c>
+      <c r="O19" s="6">
+        <v>53</v>
+      </c>
+      <c r="P19" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>12</v>
+      </c>
+      <c r="R19" s="19">
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2456,55 +2429,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L20" s="4">
-        <v>-18.2</v>
+        <v>-27.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O20" s="10">
-        <v>74</v>
-      </c>
-      <c r="P20" s="18">
-        <v>74</v>
+        <v>223</v>
+      </c>
+      <c r="O20" s="6">
+        <v>99</v>
+      </c>
+      <c r="P20" s="20">
+        <v>93</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
       </c>
-      <c r="R20" s="8">
-        <v>0</v>
+      <c r="R20" s="15">
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2512,55 +2485,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>226</v>
+        <v>91</v>
       </c>
       <c r="L21" s="4">
-        <v>-39.4</v>
+        <v>-53.1</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O21" s="10">
-        <v>68</v>
-      </c>
-      <c r="P21" s="19">
-        <v>65</v>
+        <v>222</v>
+      </c>
+      <c r="O21" s="13">
+        <v>2</v>
+      </c>
+      <c r="P21" s="8">
+        <v>2</v>
       </c>
       <c r="Q21" s="8">
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2568,55 +2541,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L22" s="4">
-        <v>-61.3</v>
+        <v>-32.5</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O22" s="10">
-        <v>77</v>
-      </c>
-      <c r="P22" s="18">
-        <v>75</v>
+        <v>224</v>
+      </c>
+      <c r="O22" s="21">
+        <v>3</v>
+      </c>
+      <c r="P22" s="8">
+        <v>2</v>
       </c>
       <c r="Q22" s="8">
         <v>0</v>
       </c>
-      <c r="R22" s="8">
-        <v>1</v>
+      <c r="R22" s="14">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2624,55 +2597,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
+        <v>58</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-16.4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="O23" s="6">
+        <v>70</v>
+      </c>
+      <c r="P23" s="17">
         <v>67</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-41.7</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O23" s="10">
-        <v>82</v>
-      </c>
-      <c r="P23" s="12">
-        <v>72</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0</v>
-      </c>
-      <c r="R23" s="20">
-        <v>4</v>
+      <c r="Q23" s="11">
+        <v>8</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2680,55 +2653,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>227</v>
+        <v>94</v>
       </c>
       <c r="L24" s="4">
-        <v>-27.9</v>
+        <v>-63.6</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O24" s="10">
-        <v>97</v>
-      </c>
-      <c r="P24" s="21">
-        <v>47</v>
+        <v>222</v>
+      </c>
+      <c r="O24" s="6">
+        <v>50</v>
+      </c>
+      <c r="P24" s="15">
+        <v>49</v>
       </c>
       <c r="Q24" s="8">
-        <v>1</v>
-      </c>
-      <c r="R24" s="11">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="R24" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2736,49 +2709,49 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L25" s="4">
-        <v>-53.1</v>
+        <v>-44.3</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O25" s="16">
-        <v>1</v>
-      </c>
-      <c r="P25" s="8">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="O25" s="6">
+        <v>47</v>
+      </c>
+      <c r="P25" s="22">
+        <v>47</v>
       </c>
       <c r="Q25" s="8">
         <v>0</v>
@@ -2792,170 +2765,114 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-26.1</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O26" s="6">
         <v>67</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-32.5</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O26" s="16">
-        <v>4</v>
-      </c>
-      <c r="P26" s="20">
-        <v>3</v>
+      <c r="P26" s="17">
+        <v>67</v>
       </c>
       <c r="Q26" s="8">
         <v>0</v>
       </c>
       <c r="R26" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2">
-        <v>57</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O27" s="10">
-        <v>84</v>
-      </c>
-      <c r="P27" s="22">
-        <v>84</v>
-      </c>
-      <c r="Q27" s="8">
-        <v>0</v>
-      </c>
-      <c r="R27" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A27">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B27">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2974,12 +2891,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2996,22 +2913,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="219">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261015--01</t>
-  </si>
-  <si>
-    <t>20261015--02</t>
-  </si>
-  <si>
-    <t>20261015--03</t>
-  </si>
-  <si>
-    <t>20261015--04</t>
-  </si>
-  <si>
     <t>20261016--01</t>
   </si>
   <si>
@@ -145,16 +133,13 @@
     <t>20261021--03</t>
   </si>
   <si>
-    <t>04:31</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>05:21</t>
+    <t>20261022--01</t>
+  </si>
+  <si>
+    <t>20261022--02</t>
+  </si>
+  <si>
+    <t>20261022--03</t>
   </si>
   <si>
     <t>02:18</t>
@@ -175,16 +160,16 @@
     <t>06:26</t>
   </si>
   <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>05:16</t>
+    <t>02:34</t>
+  </si>
+  <si>
+    <t>05:15</t>
   </si>
   <si>
     <t>05:50</t>
   </si>
   <si>
-    <t>06:08</t>
+    <t>06:07</t>
   </si>
   <si>
     <t>04:37</t>
@@ -199,10 +184,10 @@
     <t>06:23</t>
   </si>
   <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>06:21</t>
+    <t>01:23</t>
+  </si>
+  <si>
+    <t>06:20</t>
   </si>
   <si>
     <t>05:47</t>
@@ -211,403 +196,400 @@
     <t>05:02</t>
   </si>
   <si>
+    <t>03:41</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:51</t>
-  </si>
-  <si>
     <t>00:49</t>
   </si>
   <si>
     <t>00:28</t>
   </si>
   <si>
-    <t>02:47</t>
-  </si>
-  <si>
-    <t>01:17</t>
-  </si>
-  <si>
-    <t>01:22</t>
-  </si>
-  <si>
-    <t>04:16:26</t>
-  </si>
-  <si>
-    <t>05:53:08</t>
-  </si>
-  <si>
-    <t>20:51:18</t>
-  </si>
-  <si>
-    <t>22:28:17</t>
-  </si>
-  <si>
-    <t>03:23:25</t>
-  </si>
-  <si>
-    <t>04:59:54</t>
-  </si>
-  <si>
-    <t>19:58:38</t>
-  </si>
-  <si>
-    <t>21:34:43</t>
-  </si>
-  <si>
-    <t>04:06:40</t>
-  </si>
-  <si>
-    <t>05:43:58</t>
-  </si>
-  <si>
-    <t>20:41:15</t>
-  </si>
-  <si>
-    <t>22:19:24</t>
-  </si>
-  <si>
-    <t>03:13:24</t>
-  </si>
-  <si>
-    <t>04:50:15</t>
-  </si>
-  <si>
-    <t>19:47:55</t>
-  </si>
-  <si>
-    <t>21:25:21</t>
-  </si>
-  <si>
-    <t>02:20:04</t>
-  </si>
-  <si>
-    <t>03:56:38</t>
-  </si>
-  <si>
-    <t>20:31:22</t>
-  </si>
-  <si>
-    <t>03:03:03</t>
-  </si>
-  <si>
-    <t>04:40:42</t>
-  </si>
-  <si>
-    <t>19:37:29</t>
-  </si>
-  <si>
-    <t>02:09:28</t>
-  </si>
-  <si>
-    <t>03:46:31</t>
-  </si>
-  <si>
-    <t>20:21:32</t>
-  </si>
-  <si>
-    <t>04:19:01</t>
-  </si>
-  <si>
-    <t>05:55:16</t>
-  </si>
-  <si>
-    <t>20:53:32</t>
-  </si>
-  <si>
-    <t>22:30:37</t>
-  </si>
-  <si>
-    <t>03:26:43</t>
-  </si>
-  <si>
-    <t>05:01:59</t>
-  </si>
-  <si>
-    <t>20:01:24</t>
-  </si>
-  <si>
-    <t>21:36:51</t>
-  </si>
-  <si>
-    <t>04:08:50</t>
-  </si>
-  <si>
-    <t>05:46:38</t>
-  </si>
-  <si>
-    <t>20:43:19</t>
-  </si>
-  <si>
-    <t>22:22:34</t>
-  </si>
-  <si>
-    <t>03:15:46</t>
-  </si>
-  <si>
-    <t>04:52:28</t>
-  </si>
-  <si>
-    <t>19:50:02</t>
-  </si>
-  <si>
-    <t>21:27:52</t>
-  </si>
-  <si>
-    <t>02:22:53</t>
-  </si>
-  <si>
-    <t>03:58:44</t>
-  </si>
-  <si>
-    <t>20:33:35</t>
-  </si>
-  <si>
-    <t>03:05:10</t>
-  </si>
-  <si>
-    <t>04:44:17</t>
-  </si>
-  <si>
-    <t>19:39:34</t>
-  </si>
-  <si>
-    <t>02:11:42</t>
-  </si>
-  <si>
-    <t>03:48:55</t>
-  </si>
-  <si>
-    <t>20:24:20</t>
-  </si>
-  <si>
-    <t>04:21:17</t>
-  </si>
-  <si>
-    <t>05:58:26</t>
-  </si>
-  <si>
-    <t>20:56:20</t>
-  </si>
-  <si>
-    <t>22:33:17</t>
-  </si>
-  <si>
-    <t>03:27:52</t>
-  </si>
-  <si>
-    <t>05:05:15</t>
-  </si>
-  <si>
-    <t>20:03:11</t>
-  </si>
-  <si>
-    <t>21:39:55</t>
-  </si>
-  <si>
-    <t>04:11:54</t>
-  </si>
-  <si>
-    <t>05:48:40</t>
-  </si>
-  <si>
-    <t>20:46:32</t>
-  </si>
-  <si>
-    <t>22:23:52</t>
-  </si>
-  <si>
-    <t>03:18:24</t>
-  </si>
-  <si>
-    <t>04:55:23</t>
-  </si>
-  <si>
-    <t>19:53:06</t>
-  </si>
-  <si>
-    <t>21:30:11</t>
-  </si>
-  <si>
-    <t>02:24:44</t>
-  </si>
-  <si>
-    <t>04:01:57</t>
-  </si>
-  <si>
-    <t>20:36:28</t>
-  </si>
-  <si>
-    <t>03:08:21</t>
-  </si>
-  <si>
-    <t>04:45:00</t>
-  </si>
-  <si>
-    <t>19:42:44</t>
-  </si>
-  <si>
-    <t>02:14:36</t>
-  </si>
-  <si>
-    <t>03:51:26</t>
-  </si>
-  <si>
-    <t>20:26:10</t>
-  </si>
-  <si>
-    <t>04:23:32</t>
-  </si>
-  <si>
-    <t>06:01:35</t>
-  </si>
-  <si>
-    <t>20:59:08</t>
-  </si>
-  <si>
-    <t>22:35:58</t>
-  </si>
-  <si>
-    <t>03:29:01</t>
-  </si>
-  <si>
-    <t>05:08:30</t>
-  </si>
-  <si>
-    <t>20:04:58</t>
-  </si>
-  <si>
-    <t>21:43:00</t>
-  </si>
-  <si>
-    <t>04:14:59</t>
-  </si>
-  <si>
-    <t>05:50:44</t>
-  </si>
-  <si>
-    <t>20:49:45</t>
-  </si>
-  <si>
-    <t>22:25:09</t>
-  </si>
-  <si>
-    <t>03:21:02</t>
-  </si>
-  <si>
-    <t>04:58:18</t>
-  </si>
-  <si>
-    <t>19:56:10</t>
-  </si>
-  <si>
-    <t>21:32:29</t>
-  </si>
-  <si>
-    <t>02:26:35</t>
-  </si>
-  <si>
-    <t>04:05:10</t>
-  </si>
-  <si>
-    <t>20:39:21</t>
-  </si>
-  <si>
-    <t>03:11:33</t>
-  </si>
-  <si>
-    <t>04:45:42</t>
-  </si>
-  <si>
-    <t>19:45:55</t>
-  </si>
-  <si>
-    <t>02:17:29</t>
-  </si>
-  <si>
-    <t>03:53:57</t>
-  </si>
-  <si>
-    <t>20:28:02</t>
-  </si>
-  <si>
-    <t>04:26:08</t>
-  </si>
-  <si>
-    <t>06:03:43</t>
-  </si>
-  <si>
-    <t>21:01:23</t>
-  </si>
-  <si>
-    <t>22:38:19</t>
-  </si>
-  <si>
-    <t>03:32:19</t>
-  </si>
-  <si>
-    <t>05:10:35</t>
-  </si>
-  <si>
-    <t>20:07:45</t>
-  </si>
-  <si>
-    <t>21:45:10</t>
-  </si>
-  <si>
-    <t>04:17:09</t>
-  </si>
-  <si>
-    <t>05:53:23</t>
-  </si>
-  <si>
-    <t>20:51:50</t>
-  </si>
-  <si>
-    <t>22:28:20</t>
-  </si>
-  <si>
-    <t>05:00:31</t>
-  </si>
-  <si>
-    <t>19:58:18</t>
-  </si>
-  <si>
-    <t>21:35:02</t>
-  </si>
-  <si>
-    <t>02:29:23</t>
-  </si>
-  <si>
-    <t>04:07:15</t>
-  </si>
-  <si>
-    <t>20:41:36</t>
-  </si>
-  <si>
-    <t>03:13:39</t>
-  </si>
-  <si>
-    <t>04:49:17</t>
-  </si>
-  <si>
-    <t>19:48:02</t>
-  </si>
-  <si>
-    <t>02:19:43</t>
-  </si>
-  <si>
-    <t>03:56:21</t>
-  </si>
-  <si>
-    <t>20:30:50</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>39°</t>
+    <t>02:46</t>
+  </si>
+  <si>
+    <t>01:16</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>01:21</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>03:23:26</t>
+  </si>
+  <si>
+    <t>04:59:55</t>
+  </si>
+  <si>
+    <t>19:58:40</t>
+  </si>
+  <si>
+    <t>21:34:45</t>
+  </si>
+  <si>
+    <t>04:06:42</t>
+  </si>
+  <si>
+    <t>05:44:01</t>
+  </si>
+  <si>
+    <t>20:41:18</t>
+  </si>
+  <si>
+    <t>22:19:28</t>
+  </si>
+  <si>
+    <t>03:13:27</t>
+  </si>
+  <si>
+    <t>04:50:19</t>
+  </si>
+  <si>
+    <t>19:47:59</t>
+  </si>
+  <si>
+    <t>21:25:26</t>
+  </si>
+  <si>
+    <t>02:20:09</t>
+  </si>
+  <si>
+    <t>03:56:43</t>
+  </si>
+  <si>
+    <t>20:31:28</t>
+  </si>
+  <si>
+    <t>03:03:10</t>
+  </si>
+  <si>
+    <t>04:40:49</t>
+  </si>
+  <si>
+    <t>19:37:37</t>
+  </si>
+  <si>
+    <t>02:09:36</t>
+  </si>
+  <si>
+    <t>03:46:40</t>
+  </si>
+  <si>
+    <t>20:21:43</t>
+  </si>
+  <si>
+    <t>01:16:00</t>
+  </si>
+  <si>
+    <t>02:52:42</t>
+  </si>
+  <si>
+    <t>19:27:22</t>
+  </si>
+  <si>
+    <t>03:26:44</t>
+  </si>
+  <si>
+    <t>05:02:00</t>
+  </si>
+  <si>
+    <t>20:01:26</t>
+  </si>
+  <si>
+    <t>21:36:53</t>
+  </si>
+  <si>
+    <t>04:08:52</t>
+  </si>
+  <si>
+    <t>05:46:40</t>
+  </si>
+  <si>
+    <t>20:43:22</t>
+  </si>
+  <si>
+    <t>22:22:38</t>
+  </si>
+  <si>
+    <t>03:15:50</t>
+  </si>
+  <si>
+    <t>04:52:32</t>
+  </si>
+  <si>
+    <t>19:50:07</t>
+  </si>
+  <si>
+    <t>21:27:57</t>
+  </si>
+  <si>
+    <t>02:22:58</t>
+  </si>
+  <si>
+    <t>03:58:49</t>
+  </si>
+  <si>
+    <t>20:33:42</t>
+  </si>
+  <si>
+    <t>03:05:16</t>
+  </si>
+  <si>
+    <t>04:44:25</t>
+  </si>
+  <si>
+    <t>19:39:43</t>
+  </si>
+  <si>
+    <t>02:11:51</t>
+  </si>
+  <si>
+    <t>03:49:04</t>
+  </si>
+  <si>
+    <t>20:24:31</t>
+  </si>
+  <si>
+    <t>01:18:33</t>
+  </si>
+  <si>
+    <t>02:54:50</t>
+  </si>
+  <si>
+    <t>19:29:44</t>
+  </si>
+  <si>
+    <t>03:27:53</t>
+  </si>
+  <si>
+    <t>05:05:16</t>
+  </si>
+  <si>
+    <t>20:03:13</t>
+  </si>
+  <si>
+    <t>21:39:57</t>
+  </si>
+  <si>
+    <t>04:11:57</t>
+  </si>
+  <si>
+    <t>05:48:43</t>
+  </si>
+  <si>
+    <t>20:46:35</t>
+  </si>
+  <si>
+    <t>22:23:55</t>
+  </si>
+  <si>
+    <t>03:18:28</t>
+  </si>
+  <si>
+    <t>04:55:26</t>
+  </si>
+  <si>
+    <t>19:53:10</t>
+  </si>
+  <si>
+    <t>21:30:15</t>
+  </si>
+  <si>
+    <t>02:24:49</t>
+  </si>
+  <si>
+    <t>04:02:02</t>
+  </si>
+  <si>
+    <t>20:36:35</t>
+  </si>
+  <si>
+    <t>03:08:28</t>
+  </si>
+  <si>
+    <t>04:45:06</t>
+  </si>
+  <si>
+    <t>19:42:53</t>
+  </si>
+  <si>
+    <t>02:14:44</t>
+  </si>
+  <si>
+    <t>03:51:35</t>
+  </si>
+  <si>
+    <t>20:26:21</t>
+  </si>
+  <si>
+    <t>01:20:51</t>
+  </si>
+  <si>
+    <t>02:57:55</t>
+  </si>
+  <si>
+    <t>19:32:21</t>
+  </si>
+  <si>
+    <t>03:29:02</t>
+  </si>
+  <si>
+    <t>05:08:31</t>
+  </si>
+  <si>
+    <t>20:05:00</t>
+  </si>
+  <si>
+    <t>21:43:02</t>
+  </si>
+  <si>
+    <t>04:15:01</t>
+  </si>
+  <si>
+    <t>05:50:46</t>
+  </si>
+  <si>
+    <t>20:49:48</t>
+  </si>
+  <si>
+    <t>22:25:12</t>
+  </si>
+  <si>
+    <t>03:21:05</t>
+  </si>
+  <si>
+    <t>04:58:22</t>
+  </si>
+  <si>
+    <t>19:56:14</t>
+  </si>
+  <si>
+    <t>21:32:34</t>
+  </si>
+  <si>
+    <t>02:26:40</t>
+  </si>
+  <si>
+    <t>04:05:15</t>
+  </si>
+  <si>
+    <t>20:39:28</t>
+  </si>
+  <si>
+    <t>03:11:39</t>
+  </si>
+  <si>
+    <t>04:45:48</t>
+  </si>
+  <si>
+    <t>19:46:03</t>
+  </si>
+  <si>
+    <t>02:17:38</t>
+  </si>
+  <si>
+    <t>03:54:06</t>
+  </si>
+  <si>
+    <t>20:28:12</t>
+  </si>
+  <si>
+    <t>01:23:09</t>
+  </si>
+  <si>
+    <t>03:01:00</t>
+  </si>
+  <si>
+    <t>19:34:58</t>
+  </si>
+  <si>
+    <t>03:32:20</t>
+  </si>
+  <si>
+    <t>05:10:37</t>
+  </si>
+  <si>
+    <t>20:07:47</t>
+  </si>
+  <si>
+    <t>21:45:11</t>
+  </si>
+  <si>
+    <t>04:17:11</t>
+  </si>
+  <si>
+    <t>05:53:25</t>
+  </si>
+  <si>
+    <t>20:51:53</t>
+  </si>
+  <si>
+    <t>22:28:23</t>
+  </si>
+  <si>
+    <t>03:23:28</t>
+  </si>
+  <si>
+    <t>05:00:35</t>
+  </si>
+  <si>
+    <t>19:58:23</t>
+  </si>
+  <si>
+    <t>21:35:06</t>
+  </si>
+  <si>
+    <t>02:29:28</t>
+  </si>
+  <si>
+    <t>04:07:20</t>
+  </si>
+  <si>
+    <t>20:41:42</t>
+  </si>
+  <si>
+    <t>03:13:46</t>
+  </si>
+  <si>
+    <t>04:49:23</t>
+  </si>
+  <si>
+    <t>19:48:10</t>
+  </si>
+  <si>
+    <t>02:19:52</t>
+  </si>
+  <si>
+    <t>03:56:29</t>
+  </si>
+  <si>
+    <t>20:31:00</t>
+  </si>
+  <si>
+    <t>01:25:41</t>
+  </si>
+  <si>
+    <t>03:03:08</t>
+  </si>
+  <si>
+    <t>19:37:20</t>
   </si>
   <si>
     <t>0°</t>
@@ -640,40 +622,40 @@
     <t>14°</t>
   </si>
   <si>
-    <t>04:25:04</t>
-  </si>
-  <si>
-    <t>05:57:44</t>
-  </si>
-  <si>
-    <t>05:07:41</t>
-  </si>
-  <si>
-    <t>20:00:43</t>
-  </si>
-  <si>
-    <t>05:50:16</t>
-  </si>
-  <si>
-    <t>20:43:11</t>
-  </si>
-  <si>
-    <t>05:00:07</t>
-  </si>
-  <si>
-    <t>19:52:49</t>
-  </si>
-  <si>
-    <t>21:25:27</t>
-  </si>
-  <si>
-    <t>20:34:52</t>
-  </si>
-  <si>
-    <t>19:44:05</t>
-  </si>
-  <si>
-    <t>20:25:42</t>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>05:07:42</t>
+  </si>
+  <si>
+    <t>20:00:45</t>
+  </si>
+  <si>
+    <t>05:50:18</t>
+  </si>
+  <si>
+    <t>20:43:14</t>
+  </si>
+  <si>
+    <t>05:00:11</t>
+  </si>
+  <si>
+    <t>19:52:53</t>
+  </si>
+  <si>
+    <t>21:25:32</t>
+  </si>
+  <si>
+    <t>20:34:58</t>
+  </si>
+  <si>
+    <t>19:44:13</t>
+  </si>
+  <si>
+    <t>20:25:52</t>
+  </si>
+  <si>
+    <t>19:34:42</t>
   </si>
   <si>
     <t>B</t>
@@ -682,13 +664,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -722,7 +704,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -743,7 +725,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,13 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,19 +761,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -797,43 +809,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,7 +862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -940,6 +928,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1343,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1421,55 +1412,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>208</v>
+        <v>72</v>
       </c>
       <c r="L2" s="4">
-        <v>-36.9</v>
+        <v>-48.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="O2" s="6">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R2" s="9">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1477,55 +1468,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="L3" s="4">
-        <v>-15.8</v>
+        <v>-27.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="O3" s="6">
-        <v>96</v>
-      </c>
-      <c r="P3" s="10">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="8">
+        <v>100</v>
+      </c>
+      <c r="P3" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="10">
         <v>0</v>
       </c>
       <c r="R3" s="9">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1533,55 +1524,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
       </c>
       <c r="L4" s="4">
-        <v>-31.5</v>
+        <v>-19.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>8</v>
-      </c>
-      <c r="R4" s="9">
-        <v>100</v>
+        <v>216</v>
+      </c>
+      <c r="O4" s="11">
+        <v>16</v>
+      </c>
+      <c r="P4" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>7</v>
+      </c>
+      <c r="R4" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1589,55 +1580,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>75</v>
       </c>
       <c r="L5" s="4">
-        <v>-52.1</v>
+        <v>-41.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>20</v>
-      </c>
-      <c r="R5" s="9">
-        <v>100</v>
+        <v>218</v>
+      </c>
+      <c r="O5" s="11">
+        <v>15</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>11</v>
+      </c>
+      <c r="R5" s="7">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1645,55 +1636,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>76</v>
       </c>
       <c r="L6" s="4">
-        <v>-48.5</v>
+        <v>-39.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>71</v>
-      </c>
-      <c r="R6" s="9">
-        <v>100</v>
+        <v>218</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1701,55 +1692,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="L7" s="4">
-        <v>-27.5</v>
+        <v>-18.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>69</v>
-      </c>
-      <c r="R7" s="9">
-        <v>100</v>
+        <v>217</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1757,54 +1748,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L8" s="4">
-        <v>-19.9</v>
+        <v>-29.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O8" s="13">
-        <v>5</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>4</v>
-      </c>
-      <c r="R8" s="8">
+        <v>218</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1813,54 +1804,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>79</v>
       </c>
       <c r="L9" s="4">
-        <v>-41.2</v>
+        <v>-50.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O9" s="13">
-        <v>1</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+        <v>216</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1869,54 +1860,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L10" s="4">
-        <v>-39.3</v>
+        <v>-50.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+        <v>218</v>
+      </c>
+      <c r="O10" s="6">
+        <v>58</v>
+      </c>
+      <c r="P10" s="13">
+        <v>58</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1925,54 +1916,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="L11" s="4">
-        <v>-18.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+        <v>218</v>
+      </c>
+      <c r="O11" s="6">
+        <v>59</v>
+      </c>
+      <c r="P11" s="13">
+        <v>59</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1981,55 +1972,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="L12" s="4">
-        <v>-29.7</v>
+        <v>-18.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O12" s="13">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O12" s="6">
+        <v>72</v>
+      </c>
+      <c r="P12" s="14">
+        <v>69</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2037,55 +2028,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="L13" s="4">
-        <v>-50.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O13" s="13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
+        <v>218</v>
+      </c>
+      <c r="O13" s="6">
+        <v>89</v>
+      </c>
+      <c r="P13" s="15">
+        <v>88</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
+      <c r="R13" s="16">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2093,55 +2084,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L14" s="4">
-        <v>-50.7</v>
+        <v>-61.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="O14" s="6">
-        <v>51</v>
-      </c>
-      <c r="P14" s="15">
-        <v>51</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="P14" s="16">
+        <v>38</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>0</v>
+      </c>
+      <c r="R14" s="17">
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2149,55 +2140,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-41.7</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="L15" s="4">
-        <v>-29.8</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="N15" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O15" s="6">
-        <v>41</v>
-      </c>
-      <c r="P15" s="16">
-        <v>41</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="P15" s="18">
+        <v>63</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>0</v>
+      </c>
+      <c r="R15" s="15">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2205,55 +2196,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-27.9</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="L16" s="4">
-        <v>-18.2</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="O16" s="6">
-        <v>68</v>
-      </c>
-      <c r="P16" s="17">
-        <v>67</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7">
-        <v>19</v>
+        <v>100</v>
+      </c>
+      <c r="P16" s="19">
+        <v>97</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>8</v>
+      </c>
+      <c r="R16" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2261,55 +2252,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>216</v>
+        <v>87</v>
       </c>
       <c r="L17" s="4">
-        <v>-39.3</v>
+        <v>-53.1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O17" s="6">
-        <v>63</v>
-      </c>
-      <c r="P17" s="18">
-        <v>58</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="18">
-        <v>58</v>
+        <v>100</v>
+      </c>
+      <c r="P17" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2317,55 +2308,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L18" s="4">
-        <v>-61.4</v>
+        <v>-32.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="O18" s="6">
-        <v>70</v>
-      </c>
-      <c r="P18" s="15">
-        <v>52</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>2</v>
-      </c>
-      <c r="R18" s="12">
-        <v>70</v>
+        <v>100</v>
+      </c>
+      <c r="P18" s="7">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>5</v>
+      </c>
+      <c r="R18" s="17">
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2373,55 +2364,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>89</v>
+        <v>211</v>
       </c>
       <c r="L19" s="4">
-        <v>-41.7</v>
+        <v>-16.4</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="O19" s="6">
-        <v>53</v>
-      </c>
-      <c r="P19" s="11">
-        <v>12</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>12</v>
-      </c>
-      <c r="R19" s="19">
-        <v>53</v>
+        <v>97</v>
+      </c>
+      <c r="P19" s="15">
+        <v>92</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>83</v>
+      </c>
+      <c r="R19" s="14">
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2429,55 +2420,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="L20" s="4">
-        <v>-27.9</v>
+        <v>-63.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="O20" s="6">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="P20" s="20">
-        <v>93</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="15">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>0</v>
+      </c>
+      <c r="R20" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2485,54 +2476,54 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>91</v>
       </c>
       <c r="L21" s="4">
-        <v>-53.1</v>
+        <v>-44.2</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O21" s="13">
-        <v>2</v>
-      </c>
-      <c r="P21" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8">
+        <v>218</v>
+      </c>
+      <c r="O21" s="21">
+        <v>40</v>
+      </c>
+      <c r="P21" s="16">
+        <v>40</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>0</v>
+      </c>
+      <c r="R21" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2541,55 +2532,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="L22" s="4">
-        <v>-32.5</v>
+        <v>-26.1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O22" s="21">
-        <v>3</v>
-      </c>
-      <c r="P22" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
-      </c>
-      <c r="R22" s="14">
-        <v>3</v>
+        <v>216</v>
+      </c>
+      <c r="O22" s="6">
+        <v>62</v>
+      </c>
+      <c r="P22" s="13">
+        <v>61</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>0</v>
+      </c>
+      <c r="R22" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2597,54 +2588,54 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="K23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-71.3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="L23" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="O23" s="6">
-        <v>70</v>
-      </c>
-      <c r="P23" s="17">
-        <v>67</v>
-      </c>
-      <c r="Q23" s="11">
-        <v>8</v>
-      </c>
-      <c r="R23" s="8">
+        <v>34</v>
+      </c>
+      <c r="P23" s="22">
+        <v>34</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>0</v>
+      </c>
+      <c r="R23" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2653,54 +2644,54 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>94</v>
       </c>
       <c r="L24" s="4">
-        <v>-63.6</v>
+        <v>-55.6</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O24" s="6">
-        <v>50</v>
-      </c>
-      <c r="P24" s="15">
         <v>49</v>
       </c>
-      <c r="Q24" s="8">
-        <v>0</v>
-      </c>
-      <c r="R24" s="8">
+      <c r="P24" s="20">
+        <v>49</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>0</v>
+      </c>
+      <c r="R24" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2709,170 +2700,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>95</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="L25" s="4">
-        <v>-44.3</v>
+        <v>-14.5</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="O25" s="6">
-        <v>47</v>
-      </c>
-      <c r="P25" s="22">
-        <v>47</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>0</v>
-      </c>
-      <c r="R25" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>14</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-26.1</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O26" s="6">
-        <v>67</v>
-      </c>
-      <c r="P26" s="17">
-        <v>67</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>0</v>
-      </c>
-      <c r="R26" s="8">
+        <v>61</v>
+      </c>
+      <c r="P25" s="23">
+        <v>55</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>0</v>
+      </c>
+      <c r="R25" s="10">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2891,12 +2826,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2913,22 +2848,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="199">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261016--01</t>
-  </si>
-  <si>
-    <t>20261016--02</t>
-  </si>
-  <si>
-    <t>20261016--03</t>
-  </si>
-  <si>
-    <t>20261016--04</t>
-  </si>
-  <si>
     <t>20261017--01</t>
   </si>
   <si>
@@ -142,13 +130,10 @@
     <t>20261022--03</t>
   </si>
   <si>
-    <t>02:18</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>03:34</t>
+    <t>20261023--01</t>
+  </si>
+  <si>
+    <t>20261023--02</t>
   </si>
   <si>
     <t>06:09</t>
@@ -166,7 +151,7 @@
     <t>05:15</t>
   </si>
   <si>
-    <t>05:50</t>
+    <t>05:49</t>
   </si>
   <si>
     <t>06:07</t>
@@ -178,6 +163,9 @@
     <t>03:42</t>
   </si>
   <si>
+    <t>06:27</t>
+  </si>
+  <si>
     <t>05:46</t>
   </si>
   <si>
@@ -190,10 +178,7 @@
     <t>06:20</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:02</t>
+    <t>05:03</t>
   </si>
   <si>
     <t>03:41</t>
@@ -205,22 +190,19 @@
     <t>06:10</t>
   </si>
   <si>
-    <t>05:14</t>
+    <t>02:27</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:49</t>
-  </si>
-  <si>
     <t>00:28</t>
   </si>
   <si>
     <t>02:46</t>
   </si>
   <si>
-    <t>01:16</t>
+    <t>01:17</t>
   </si>
   <si>
     <t>04:30</t>
@@ -229,19 +211,7 @@
     <t>01:21</t>
   </si>
   <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>03:23:26</t>
-  </si>
-  <si>
-    <t>04:59:55</t>
-  </si>
-  <si>
-    <t>19:58:40</t>
-  </si>
-  <si>
-    <t>21:34:45</t>
+    <t>04:59</t>
   </si>
   <si>
     <t>04:06:42</t>
@@ -265,7 +235,7 @@
     <t>19:47:59</t>
   </si>
   <si>
-    <t>21:25:26</t>
+    <t>21:25:25</t>
   </si>
   <si>
     <t>02:20:09</t>
@@ -277,43 +247,37 @@
     <t>20:31:28</t>
   </si>
   <si>
-    <t>03:03:10</t>
-  </si>
-  <si>
-    <t>04:40:49</t>
-  </si>
-  <si>
-    <t>19:37:37</t>
-  </si>
-  <si>
-    <t>02:09:36</t>
-  </si>
-  <si>
-    <t>03:46:40</t>
-  </si>
-  <si>
-    <t>20:21:43</t>
-  </si>
-  <si>
-    <t>01:16:00</t>
-  </si>
-  <si>
-    <t>02:52:42</t>
-  </si>
-  <si>
-    <t>19:27:22</t>
-  </si>
-  <si>
-    <t>03:26:44</t>
-  </si>
-  <si>
-    <t>05:02:00</t>
-  </si>
-  <si>
-    <t>20:01:26</t>
-  </si>
-  <si>
-    <t>21:36:53</t>
+    <t>03:03:09</t>
+  </si>
+  <si>
+    <t>04:40:48</t>
+  </si>
+  <si>
+    <t>19:37:36</t>
+  </si>
+  <si>
+    <t>02:09:35</t>
+  </si>
+  <si>
+    <t>03:46:39</t>
+  </si>
+  <si>
+    <t>20:21:41</t>
+  </si>
+  <si>
+    <t>01:15:58</t>
+  </si>
+  <si>
+    <t>02:52:40</t>
+  </si>
+  <si>
+    <t>19:27:20</t>
+  </si>
+  <si>
+    <t>00:22:17</t>
+  </si>
+  <si>
+    <t>01:58:45</t>
   </si>
   <si>
     <t>04:08:52</t>
@@ -340,55 +304,49 @@
     <t>21:27:57</t>
   </si>
   <si>
-    <t>02:22:58</t>
-  </si>
-  <si>
-    <t>03:58:49</t>
-  </si>
-  <si>
-    <t>20:33:42</t>
+    <t>02:22:57</t>
+  </si>
+  <si>
+    <t>03:58:48</t>
+  </si>
+  <si>
+    <t>20:33:41</t>
   </si>
   <si>
     <t>03:05:16</t>
   </si>
   <si>
-    <t>04:44:25</t>
-  </si>
-  <si>
-    <t>19:39:43</t>
-  </si>
-  <si>
-    <t>02:11:51</t>
-  </si>
-  <si>
-    <t>03:49:04</t>
-  </si>
-  <si>
-    <t>20:24:31</t>
-  </si>
-  <si>
-    <t>01:18:33</t>
-  </si>
-  <si>
-    <t>02:54:50</t>
-  </si>
-  <si>
-    <t>19:29:44</t>
-  </si>
-  <si>
-    <t>03:27:53</t>
-  </si>
-  <si>
-    <t>05:05:16</t>
-  </si>
-  <si>
-    <t>20:03:13</t>
-  </si>
-  <si>
-    <t>21:39:57</t>
-  </si>
-  <si>
-    <t>04:11:57</t>
+    <t>04:44:24</t>
+  </si>
+  <si>
+    <t>19:39:42</t>
+  </si>
+  <si>
+    <t>02:11:50</t>
+  </si>
+  <si>
+    <t>03:49:02</t>
+  </si>
+  <si>
+    <t>20:24:29</t>
+  </si>
+  <si>
+    <t>01:18:31</t>
+  </si>
+  <si>
+    <t>02:54:48</t>
+  </si>
+  <si>
+    <t>19:29:41</t>
+  </si>
+  <si>
+    <t>00:25:31</t>
+  </si>
+  <si>
+    <t>02:00:50</t>
+  </si>
+  <si>
+    <t>04:11:56</t>
   </si>
   <si>
     <t>05:48:43</t>
@@ -412,52 +370,46 @@
     <t>21:30:15</t>
   </si>
   <si>
-    <t>02:24:49</t>
+    <t>02:24:48</t>
   </si>
   <si>
     <t>04:02:02</t>
   </si>
   <si>
-    <t>20:36:35</t>
-  </si>
-  <si>
-    <t>03:08:28</t>
-  </si>
-  <si>
-    <t>04:45:06</t>
-  </si>
-  <si>
-    <t>19:42:53</t>
-  </si>
-  <si>
-    <t>02:14:44</t>
-  </si>
-  <si>
-    <t>03:51:35</t>
-  </si>
-  <si>
-    <t>20:26:21</t>
-  </si>
-  <si>
-    <t>01:20:51</t>
-  </si>
-  <si>
-    <t>02:57:55</t>
-  </si>
-  <si>
-    <t>19:32:21</t>
-  </si>
-  <si>
-    <t>03:29:02</t>
-  </si>
-  <si>
-    <t>05:08:31</t>
-  </si>
-  <si>
-    <t>20:05:00</t>
-  </si>
-  <si>
-    <t>21:43:02</t>
+    <t>20:36:34</t>
+  </si>
+  <si>
+    <t>03:08:27</t>
+  </si>
+  <si>
+    <t>04:45:05</t>
+  </si>
+  <si>
+    <t>19:42:51</t>
+  </si>
+  <si>
+    <t>02:14:43</t>
+  </si>
+  <si>
+    <t>03:51:33</t>
+  </si>
+  <si>
+    <t>20:26:19</t>
+  </si>
+  <si>
+    <t>01:20:49</t>
+  </si>
+  <si>
+    <t>02:57:53</t>
+  </si>
+  <si>
+    <t>19:32:18</t>
+  </si>
+  <si>
+    <t>00:26:44</t>
+  </si>
+  <si>
+    <t>02:04:03</t>
   </si>
   <si>
     <t>04:15:01</t>
@@ -475,7 +427,7 @@
     <t>03:21:05</t>
   </si>
   <si>
-    <t>04:58:22</t>
+    <t>04:58:21</t>
   </si>
   <si>
     <t>19:56:14</t>
@@ -484,52 +436,46 @@
     <t>21:32:34</t>
   </si>
   <si>
-    <t>02:26:40</t>
+    <t>02:26:39</t>
   </si>
   <si>
     <t>04:05:15</t>
   </si>
   <si>
-    <t>20:39:28</t>
+    <t>20:39:27</t>
   </si>
   <si>
     <t>03:11:39</t>
   </si>
   <si>
-    <t>04:45:48</t>
-  </si>
-  <si>
-    <t>19:46:03</t>
-  </si>
-  <si>
-    <t>02:17:38</t>
-  </si>
-  <si>
-    <t>03:54:06</t>
-  </si>
-  <si>
-    <t>20:28:12</t>
-  </si>
-  <si>
-    <t>01:23:09</t>
-  </si>
-  <si>
-    <t>03:01:00</t>
-  </si>
-  <si>
-    <t>19:34:58</t>
-  </si>
-  <si>
-    <t>03:32:20</t>
-  </si>
-  <si>
-    <t>05:10:37</t>
-  </si>
-  <si>
-    <t>20:07:47</t>
-  </si>
-  <si>
-    <t>21:45:11</t>
+    <t>04:45:47</t>
+  </si>
+  <si>
+    <t>19:46:02</t>
+  </si>
+  <si>
+    <t>02:17:36</t>
+  </si>
+  <si>
+    <t>03:54:05</t>
+  </si>
+  <si>
+    <t>20:28:10</t>
+  </si>
+  <si>
+    <t>01:23:07</t>
+  </si>
+  <si>
+    <t>03:00:58</t>
+  </si>
+  <si>
+    <t>19:34:56</t>
+  </si>
+  <si>
+    <t>00:27:58</t>
+  </si>
+  <si>
+    <t>02:07:17</t>
   </si>
   <si>
     <t>04:17:11</t>
@@ -547,10 +493,10 @@
     <t>03:23:28</t>
   </si>
   <si>
-    <t>05:00:35</t>
-  </si>
-  <si>
-    <t>19:58:23</t>
+    <t>05:00:34</t>
+  </si>
+  <si>
+    <t>19:58:22</t>
   </si>
   <si>
     <t>21:35:06</t>
@@ -562,45 +508,45 @@
     <t>04:07:20</t>
   </si>
   <si>
-    <t>20:41:42</t>
-  </si>
-  <si>
-    <t>03:13:46</t>
+    <t>20:41:41</t>
+  </si>
+  <si>
+    <t>03:13:45</t>
   </si>
   <si>
     <t>04:49:23</t>
   </si>
   <si>
-    <t>19:48:10</t>
-  </si>
-  <si>
-    <t>02:19:52</t>
-  </si>
-  <si>
-    <t>03:56:29</t>
-  </si>
-  <si>
-    <t>20:31:00</t>
-  </si>
-  <si>
-    <t>01:25:41</t>
-  </si>
-  <si>
-    <t>03:03:08</t>
-  </si>
-  <si>
-    <t>19:37:20</t>
+    <t>19:48:08</t>
+  </si>
+  <si>
+    <t>02:19:51</t>
+  </si>
+  <si>
+    <t>03:56:28</t>
+  </si>
+  <si>
+    <t>20:30:58</t>
+  </si>
+  <si>
+    <t>01:25:39</t>
+  </si>
+  <si>
+    <t>03:03:06</t>
+  </si>
+  <si>
+    <t>19:37:18</t>
+  </si>
+  <si>
+    <t>00:31:11</t>
+  </si>
+  <si>
+    <t>02:09:22</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
@@ -625,37 +571,31 @@
     <t>11°</t>
   </si>
   <si>
-    <t>05:07:42</t>
-  </si>
-  <si>
-    <t>20:00:45</t>
-  </si>
-  <si>
     <t>05:50:18</t>
   </si>
   <si>
     <t>20:43:14</t>
   </si>
   <si>
-    <t>05:00:11</t>
+    <t>05:00:10</t>
   </si>
   <si>
     <t>19:52:53</t>
   </si>
   <si>
-    <t>21:25:32</t>
+    <t>21:25:31</t>
   </si>
   <si>
     <t>20:34:58</t>
   </si>
   <si>
-    <t>19:44:13</t>
-  </si>
-  <si>
-    <t>20:25:52</t>
-  </si>
-  <si>
-    <t>19:34:42</t>
+    <t>19:44:12</t>
+  </si>
+  <si>
+    <t>20:25:50</t>
+  </si>
+  <si>
+    <t>19:34:40</t>
   </si>
   <si>
     <t>B</t>
@@ -664,13 +604,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -704,7 +644,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -719,7 +659,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,7 +713,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,25 +731,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,55 +761,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -862,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -931,6 +877,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1334,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1412,55 +1361,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L2" s="4">
-        <v>-48.5</v>
+        <v>-39.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="P2" s="7">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="8">
-        <v>28</v>
-      </c>
-      <c r="R2" s="9">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1468,55 +1417,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="L3" s="4">
-        <v>-27.5</v>
+        <v>-18.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>100</v>
+        <v>197</v>
+      </c>
+      <c r="O3" s="9">
+        <v>29</v>
+      </c>
+      <c r="P3" s="10">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1524,55 +1473,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-29.7</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-19.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O4" s="11">
-        <v>16</v>
-      </c>
-      <c r="P4" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>7</v>
-      </c>
-      <c r="R4" s="7">
-        <v>3</v>
+        <v>196</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1580,55 +1529,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L5" s="4">
-        <v>-41.2</v>
+        <v>-50.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O5" s="11">
-        <v>15</v>
-      </c>
-      <c r="P5" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>11</v>
-      </c>
-      <c r="R5" s="7">
-        <v>4</v>
+        <v>198</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1636,54 +1585,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L6" s="4">
-        <v>-39.3</v>
+        <v>-50.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="O6" s="11">
-        <v>0</v>
-      </c>
-      <c r="P6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>0</v>
-      </c>
-      <c r="R6" s="10">
+        <v>50</v>
+      </c>
+      <c r="P6" s="12">
+        <v>50</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1692,54 +1641,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="L7" s="4">
-        <v>-18.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="O7" s="11">
-        <v>0</v>
-      </c>
-      <c r="P7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>0</v>
-      </c>
-      <c r="R7" s="10">
+        <v>51</v>
+      </c>
+      <c r="P7" s="12">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1748,55 +1697,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="L8" s="4">
-        <v>-29.7</v>
+        <v>-18.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="O8" s="11">
-        <v>0</v>
-      </c>
-      <c r="P8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="P8" s="13">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1804,55 +1753,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="L9" s="4">
-        <v>-50.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="O9" s="11">
-        <v>0</v>
-      </c>
-      <c r="P9" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>0</v>
-      </c>
-      <c r="R9" s="10">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="P9" s="12">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1860,55 +1809,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L10" s="4">
-        <v>-50.7</v>
+        <v>-61.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O10" s="6">
-        <v>58</v>
-      </c>
-      <c r="P10" s="13">
-        <v>58</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>0</v>
-      </c>
-      <c r="R10" s="10">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="O10" s="11">
+        <v>67</v>
+      </c>
+      <c r="P10" s="7">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>6</v>
+      </c>
+      <c r="R10" s="15">
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1916,54 +1865,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>207</v>
+        <v>75</v>
       </c>
       <c r="L11" s="4">
-        <v>-29.8</v>
+        <v>-41.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O11" s="6">
-        <v>59</v>
-      </c>
-      <c r="P11" s="13">
-        <v>59</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>0</v>
-      </c>
-      <c r="R11" s="10">
+        <v>196</v>
+      </c>
+      <c r="O11" s="11">
+        <v>91</v>
+      </c>
+      <c r="P11" s="16">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1972,55 +1921,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="L12" s="4">
-        <v>-18.2</v>
+        <v>-27.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O12" s="6">
-        <v>72</v>
-      </c>
-      <c r="P12" s="14">
-        <v>69</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>0</v>
-      </c>
-      <c r="R12" s="10">
+        <v>197</v>
+      </c>
+      <c r="O12" s="11">
+        <v>99</v>
+      </c>
+      <c r="P12" s="17">
+        <v>99</v>
+      </c>
+      <c r="Q12" s="8">
         <v>2</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2028,55 +1977,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="L13" s="4">
-        <v>-39.4</v>
+        <v>-53.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O13" s="6">
-        <v>89</v>
-      </c>
-      <c r="P13" s="15">
-        <v>88</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>0</v>
-      </c>
-      <c r="R13" s="16">
-        <v>41</v>
+        <v>196</v>
+      </c>
+      <c r="O13" s="11">
+        <v>85</v>
+      </c>
+      <c r="P13" s="18">
+        <v>85</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2084,55 +2033,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L14" s="4">
-        <v>-61.4</v>
+        <v>-32.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O14" s="6">
-        <v>89</v>
-      </c>
-      <c r="P14" s="16">
-        <v>38</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>0</v>
-      </c>
-      <c r="R14" s="17">
-        <v>86</v>
+        <v>198</v>
+      </c>
+      <c r="O14" s="11">
+        <v>80</v>
+      </c>
+      <c r="P14" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>1</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2140,55 +2089,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="L15" s="4">
-        <v>-41.7</v>
+        <v>-16.4</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O15" s="6">
-        <v>88</v>
-      </c>
-      <c r="P15" s="18">
-        <v>63</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>0</v>
-      </c>
-      <c r="R15" s="15">
-        <v>88</v>
+        <v>197</v>
+      </c>
+      <c r="O15" s="11">
+        <v>94</v>
+      </c>
+      <c r="P15" s="20">
+        <v>94</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>3</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2196,55 +2145,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="L16" s="4">
-        <v>-27.9</v>
+        <v>-63.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O16" s="6">
-        <v>100</v>
-      </c>
-      <c r="P16" s="19">
-        <v>97</v>
-      </c>
-      <c r="Q16" s="12">
-        <v>8</v>
-      </c>
-      <c r="R16" s="9">
-        <v>100</v>
+        <v>196</v>
+      </c>
+      <c r="O16" s="11">
+        <v>53</v>
+      </c>
+      <c r="P16" s="12">
+        <v>50</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2252,55 +2201,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L17" s="4">
-        <v>-53.1</v>
+        <v>-44.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O17" s="6">
-        <v>100</v>
+        <v>196</v>
+      </c>
+      <c r="O17" s="9">
+        <v>29</v>
       </c>
       <c r="P17" s="7">
-        <v>7</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9">
-        <v>100</v>
+        <v>21</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2308,55 +2257,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L18" s="4">
-        <v>-32.5</v>
+        <v>-26.1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O18" s="6">
-        <v>100</v>
-      </c>
-      <c r="P18" s="7">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>5</v>
-      </c>
-      <c r="R18" s="17">
-        <v>84</v>
+        <v>198</v>
+      </c>
+      <c r="O18" s="9">
+        <v>30</v>
+      </c>
+      <c r="P18" s="10">
+        <v>30</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2364,55 +2313,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="L19" s="4">
-        <v>-16.4</v>
+        <v>-71.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O19" s="6">
-        <v>97</v>
-      </c>
-      <c r="P19" s="15">
-        <v>92</v>
-      </c>
-      <c r="Q19" s="17">
-        <v>83</v>
-      </c>
-      <c r="R19" s="14">
-        <v>72</v>
+        <v>196</v>
+      </c>
+      <c r="O19" s="11">
+        <v>78</v>
+      </c>
+      <c r="P19" s="21">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2420,54 +2369,54 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L20" s="4">
-        <v>-63.6</v>
+        <v>-55.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O20" s="6">
-        <v>49</v>
-      </c>
-      <c r="P20" s="20">
-        <v>48</v>
-      </c>
-      <c r="Q20" s="10">
-        <v>0</v>
-      </c>
-      <c r="R20" s="10">
+        <v>196</v>
+      </c>
+      <c r="O20" s="11">
+        <v>87</v>
+      </c>
+      <c r="P20" s="18">
+        <v>86</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2476,54 +2425,54 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="L21" s="4">
-        <v>-44.2</v>
+        <v>-14.5</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O21" s="21">
-        <v>40</v>
-      </c>
-      <c r="P21" s="16">
-        <v>40</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>0</v>
-      </c>
-      <c r="R21" s="10">
+        <v>197</v>
+      </c>
+      <c r="O21" s="11">
+        <v>70</v>
+      </c>
+      <c r="P21" s="22">
+        <v>70</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2532,54 +2481,54 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>212</v>
+        <v>86</v>
       </c>
       <c r="L22" s="4">
-        <v>-26.1</v>
+        <v>-72.2</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O22" s="6">
-        <v>62</v>
-      </c>
-      <c r="P22" s="13">
-        <v>61</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>0</v>
-      </c>
-      <c r="R22" s="10">
+        <v>198</v>
+      </c>
+      <c r="O22" s="11">
+        <v>51</v>
+      </c>
+      <c r="P22" s="23">
+        <v>44</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2588,226 +2537,114 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="L23" s="4">
-        <v>-71.3</v>
+        <v>-65.8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O23" s="6">
-        <v>34</v>
-      </c>
-      <c r="P23" s="22">
-        <v>34</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>0</v>
-      </c>
-      <c r="R23" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="2">
-        <v>43</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-55.6</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O24" s="6">
-        <v>49</v>
-      </c>
-      <c r="P24" s="20">
-        <v>49</v>
-      </c>
-      <c r="Q24" s="10">
-        <v>0</v>
-      </c>
-      <c r="R24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2">
-        <v>22</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-14.5</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O25" s="6">
-        <v>61</v>
-      </c>
-      <c r="P25" s="23">
-        <v>55</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>0</v>
-      </c>
-      <c r="R25" s="10">
+        <v>196</v>
+      </c>
+      <c r="O23" s="9">
+        <v>37</v>
+      </c>
+      <c r="P23" s="24">
+        <v>24</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2826,12 +2663,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2848,22 +2685,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261017--01</t>
-  </si>
-  <si>
-    <t>20261017--02</t>
-  </si>
-  <si>
-    <t>20261017--03</t>
-  </si>
-  <si>
-    <t>20261017--04</t>
-  </si>
-  <si>
     <t>20261018--01</t>
   </si>
   <si>
@@ -100,9 +88,6 @@
     <t>20261019--02</t>
   </si>
   <si>
-    <t>20261019--03</t>
-  </si>
-  <si>
     <t>20261020--01</t>
   </si>
   <si>
@@ -118,9 +103,6 @@
     <t>20261021--02</t>
   </si>
   <si>
-    <t>20261021--03</t>
-  </si>
-  <si>
     <t>20261022--01</t>
   </si>
   <si>
@@ -136,76 +118,76 @@
     <t>20261023--02</t>
   </si>
   <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>04:06</t>
+    <t>20261024--01</t>
+  </si>
+  <si>
+    <t>20261024--02</t>
+  </si>
+  <si>
+    <t>20261024--03</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>03:42</t>
   </si>
   <si>
     <t>06:26</t>
   </si>
   <si>
-    <t>02:34</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>06:07</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>03:42</t>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>01:24</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>05:02</t>
+  </si>
+  <si>
+    <t>03:41</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>02:26</t>
   </si>
   <si>
     <t>06:27</t>
   </si>
   <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>01:23</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>05:03</t>
-  </si>
-  <si>
-    <t>03:41</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>02:27</t>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>03:49</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:28</t>
-  </si>
-  <si>
     <t>02:46</t>
   </si>
   <si>
-    <t>01:17</t>
-  </si>
-  <si>
-    <t>04:30</t>
+    <t>04:31</t>
   </si>
   <si>
     <t>01:21</t>
@@ -214,18 +196,6 @@
     <t>04:59</t>
   </si>
   <si>
-    <t>04:06:42</t>
-  </si>
-  <si>
-    <t>05:44:01</t>
-  </si>
-  <si>
-    <t>20:41:18</t>
-  </si>
-  <si>
-    <t>22:19:28</t>
-  </si>
-  <si>
     <t>03:13:27</t>
   </si>
   <si>
@@ -238,58 +208,49 @@
     <t>21:25:25</t>
   </si>
   <si>
-    <t>02:20:09</t>
-  </si>
-  <si>
-    <t>03:56:43</t>
-  </si>
-  <si>
-    <t>20:31:28</t>
-  </si>
-  <si>
-    <t>03:03:09</t>
-  </si>
-  <si>
-    <t>04:40:48</t>
-  </si>
-  <si>
-    <t>19:37:36</t>
-  </si>
-  <si>
-    <t>02:09:35</t>
-  </si>
-  <si>
-    <t>03:46:39</t>
-  </si>
-  <si>
-    <t>20:21:41</t>
-  </si>
-  <si>
-    <t>01:15:58</t>
-  </si>
-  <si>
-    <t>02:52:40</t>
-  </si>
-  <si>
-    <t>19:27:20</t>
-  </si>
-  <si>
-    <t>00:22:17</t>
-  </si>
-  <si>
-    <t>01:58:45</t>
-  </si>
-  <si>
-    <t>04:08:52</t>
-  </si>
-  <si>
-    <t>05:46:40</t>
-  </si>
-  <si>
-    <t>20:43:22</t>
-  </si>
-  <si>
-    <t>22:22:38</t>
+    <t>02:20:08</t>
+  </si>
+  <si>
+    <t>03:56:42</t>
+  </si>
+  <si>
+    <t>03:03:08</t>
+  </si>
+  <si>
+    <t>04:40:47</t>
+  </si>
+  <si>
+    <t>19:37:34</t>
+  </si>
+  <si>
+    <t>03:46:36</t>
+  </si>
+  <si>
+    <t>20:21:38</t>
+  </si>
+  <si>
+    <t>01:15:54</t>
+  </si>
+  <si>
+    <t>02:52:35</t>
+  </si>
+  <si>
+    <t>19:27:14</t>
+  </si>
+  <si>
+    <t>00:22:12</t>
+  </si>
+  <si>
+    <t>01:58:39</t>
+  </si>
+  <si>
+    <t>01:04:43</t>
+  </si>
+  <si>
+    <t>02:42:01</t>
+  </si>
+  <si>
+    <t>19:16:55</t>
   </si>
   <si>
     <t>03:15:50</t>
@@ -301,7 +262,7 @@
     <t>19:50:07</t>
   </si>
   <si>
-    <t>21:27:57</t>
+    <t>21:27:56</t>
   </si>
   <si>
     <t>02:22:57</t>
@@ -310,55 +271,46 @@
     <t>03:58:48</t>
   </si>
   <si>
-    <t>20:33:41</t>
-  </si>
-  <si>
-    <t>03:05:16</t>
-  </si>
-  <si>
-    <t>04:44:24</t>
-  </si>
-  <si>
-    <t>19:39:42</t>
-  </si>
-  <si>
-    <t>02:11:50</t>
-  </si>
-  <si>
-    <t>03:49:02</t>
-  </si>
-  <si>
-    <t>20:24:29</t>
-  </si>
-  <si>
-    <t>01:18:31</t>
-  </si>
-  <si>
-    <t>02:54:48</t>
-  </si>
-  <si>
-    <t>19:29:41</t>
-  </si>
-  <si>
-    <t>00:25:31</t>
-  </si>
-  <si>
-    <t>02:00:50</t>
-  </si>
-  <si>
-    <t>04:11:56</t>
-  </si>
-  <si>
-    <t>05:48:43</t>
-  </si>
-  <si>
-    <t>20:46:35</t>
-  </si>
-  <si>
-    <t>22:23:55</t>
-  </si>
-  <si>
-    <t>03:18:28</t>
+    <t>03:05:14</t>
+  </si>
+  <si>
+    <t>04:44:22</t>
+  </si>
+  <si>
+    <t>19:39:39</t>
+  </si>
+  <si>
+    <t>03:49:00</t>
+  </si>
+  <si>
+    <t>20:24:25</t>
+  </si>
+  <si>
+    <t>01:18:27</t>
+  </si>
+  <si>
+    <t>02:54:44</t>
+  </si>
+  <si>
+    <t>19:29:36</t>
+  </si>
+  <si>
+    <t>00:25:26</t>
+  </si>
+  <si>
+    <t>02:00:44</t>
+  </si>
+  <si>
+    <t>01:06:52</t>
+  </si>
+  <si>
+    <t>02:44:44</t>
+  </si>
+  <si>
+    <t>19:20:08</t>
+  </si>
+  <si>
+    <t>03:18:27</t>
   </si>
   <si>
     <t>04:55:26</t>
@@ -373,55 +325,46 @@
     <t>02:24:48</t>
   </si>
   <si>
-    <t>04:02:02</t>
-  </si>
-  <si>
-    <t>20:36:34</t>
-  </si>
-  <si>
-    <t>03:08:27</t>
-  </si>
-  <si>
-    <t>04:45:05</t>
-  </si>
-  <si>
-    <t>19:42:51</t>
-  </si>
-  <si>
-    <t>02:14:43</t>
-  </si>
-  <si>
-    <t>03:51:33</t>
-  </si>
-  <si>
-    <t>20:26:19</t>
-  </si>
-  <si>
-    <t>01:20:49</t>
-  </si>
-  <si>
-    <t>02:57:53</t>
-  </si>
-  <si>
-    <t>19:32:18</t>
-  </si>
-  <si>
-    <t>00:26:44</t>
-  </si>
-  <si>
-    <t>02:04:03</t>
-  </si>
-  <si>
-    <t>04:15:01</t>
-  </si>
-  <si>
-    <t>05:50:46</t>
-  </si>
-  <si>
-    <t>20:49:48</t>
-  </si>
-  <si>
-    <t>22:25:12</t>
+    <t>04:02:01</t>
+  </si>
+  <si>
+    <t>03:08:26</t>
+  </si>
+  <si>
+    <t>04:45:04</t>
+  </si>
+  <si>
+    <t>19:42:49</t>
+  </si>
+  <si>
+    <t>03:51:31</t>
+  </si>
+  <si>
+    <t>20:26:15</t>
+  </si>
+  <si>
+    <t>01:20:45</t>
+  </si>
+  <si>
+    <t>02:57:49</t>
+  </si>
+  <si>
+    <t>19:32:13</t>
+  </si>
+  <si>
+    <t>00:26:39</t>
+  </si>
+  <si>
+    <t>02:03:57</t>
+  </si>
+  <si>
+    <t>01:09:56</t>
+  </si>
+  <si>
+    <t>02:46:38</t>
+  </si>
+  <si>
+    <t>19:21:21</t>
   </si>
   <si>
     <t>03:21:05</t>
@@ -433,61 +376,52 @@
     <t>19:56:14</t>
   </si>
   <si>
-    <t>21:32:34</t>
+    <t>21:32:33</t>
   </si>
   <si>
     <t>02:26:39</t>
   </si>
   <si>
-    <t>04:05:15</t>
-  </si>
-  <si>
-    <t>20:39:27</t>
-  </si>
-  <si>
-    <t>03:11:39</t>
-  </si>
-  <si>
-    <t>04:45:47</t>
-  </si>
-  <si>
-    <t>19:46:02</t>
-  </si>
-  <si>
-    <t>02:17:36</t>
-  </si>
-  <si>
-    <t>03:54:05</t>
-  </si>
-  <si>
-    <t>20:28:10</t>
-  </si>
-  <si>
-    <t>01:23:07</t>
-  </si>
-  <si>
-    <t>03:00:58</t>
-  </si>
-  <si>
-    <t>19:34:56</t>
-  </si>
-  <si>
-    <t>00:27:58</t>
-  </si>
-  <si>
-    <t>02:07:17</t>
-  </si>
-  <si>
-    <t>04:17:11</t>
-  </si>
-  <si>
-    <t>05:53:25</t>
-  </si>
-  <si>
-    <t>20:51:53</t>
-  </si>
-  <si>
-    <t>22:28:23</t>
+    <t>04:05:14</t>
+  </si>
+  <si>
+    <t>03:11:37</t>
+  </si>
+  <si>
+    <t>04:45:46</t>
+  </si>
+  <si>
+    <t>19:46:00</t>
+  </si>
+  <si>
+    <t>03:54:02</t>
+  </si>
+  <si>
+    <t>20:28:06</t>
+  </si>
+  <si>
+    <t>01:23:03</t>
+  </si>
+  <si>
+    <t>03:00:54</t>
+  </si>
+  <si>
+    <t>19:34:50</t>
+  </si>
+  <si>
+    <t>00:27:52</t>
+  </si>
+  <si>
+    <t>02:07:11</t>
+  </si>
+  <si>
+    <t>01:13:00</t>
+  </si>
+  <si>
+    <t>02:48:33</t>
+  </si>
+  <si>
+    <t>19:22:34</t>
   </si>
   <si>
     <t>03:23:28</t>
@@ -499,69 +433,63 @@
     <t>19:58:22</t>
   </si>
   <si>
-    <t>21:35:06</t>
-  </si>
-  <si>
-    <t>02:29:28</t>
-  </si>
-  <si>
-    <t>04:07:20</t>
-  </si>
-  <si>
-    <t>20:41:41</t>
-  </si>
-  <si>
-    <t>03:13:45</t>
-  </si>
-  <si>
-    <t>04:49:23</t>
-  </si>
-  <si>
-    <t>19:48:08</t>
-  </si>
-  <si>
-    <t>02:19:51</t>
-  </si>
-  <si>
-    <t>03:56:28</t>
-  </si>
-  <si>
-    <t>20:30:58</t>
-  </si>
-  <si>
-    <t>01:25:39</t>
-  </si>
-  <si>
-    <t>03:03:06</t>
-  </si>
-  <si>
-    <t>19:37:18</t>
-  </si>
-  <si>
-    <t>00:31:11</t>
-  </si>
-  <si>
-    <t>02:09:22</t>
+    <t>21:35:05</t>
+  </si>
+  <si>
+    <t>02:29:27</t>
+  </si>
+  <si>
+    <t>04:07:19</t>
+  </si>
+  <si>
+    <t>03:13:43</t>
+  </si>
+  <si>
+    <t>04:49:21</t>
+  </si>
+  <si>
+    <t>19:48:06</t>
+  </si>
+  <si>
+    <t>03:56:25</t>
+  </si>
+  <si>
+    <t>20:30:55</t>
+  </si>
+  <si>
+    <t>01:25:35</t>
+  </si>
+  <si>
+    <t>03:03:02</t>
+  </si>
+  <si>
+    <t>19:37:12</t>
+  </si>
+  <si>
+    <t>00:31:05</t>
+  </si>
+  <si>
+    <t>02:09:16</t>
+  </si>
+  <si>
+    <t>01:15:09</t>
+  </si>
+  <si>
+    <t>02:51:16</t>
+  </si>
+  <si>
+    <t>19:25:48</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
     <t>1°</t>
   </si>
   <si>
     <t>41°</t>
   </si>
   <si>
-    <t>19°</t>
-  </si>
-  <si>
     <t>30°</t>
   </si>
   <si>
@@ -571,10 +499,7 @@
     <t>11°</t>
   </si>
   <si>
-    <t>05:50:18</t>
-  </si>
-  <si>
-    <t>20:43:14</t>
+    <t>5°</t>
   </si>
   <si>
     <t>05:00:10</t>
@@ -586,22 +511,25 @@
     <t>21:25:31</t>
   </si>
   <si>
-    <t>20:34:58</t>
-  </si>
-  <si>
-    <t>19:44:12</t>
-  </si>
-  <si>
-    <t>20:25:50</t>
-  </si>
-  <si>
-    <t>19:34:40</t>
+    <t>19:44:10</t>
+  </si>
+  <si>
+    <t>20:25:46</t>
+  </si>
+  <si>
+    <t>19:34:35</t>
+  </si>
+  <si>
+    <t>19:24:13</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>3</t>
@@ -644,7 +572,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -659,7 +587,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,7 +611,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,7 +647,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,37 +665,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,31 +701,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -808,7 +742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -880,6 +814,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1283,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1361,55 +1298,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L2" s="4">
-        <v>-39.3</v>
+        <v>-50.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="O2" s="6">
         <v>20</v>
       </c>
       <c r="P2" s="7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="R2" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1417,54 +1354,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="L3" s="4">
-        <v>-18.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O3" s="9">
-        <v>29</v>
+        <v>172</v>
+      </c>
+      <c r="O3" s="6">
+        <v>39</v>
       </c>
       <c r="P3" s="10">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="8">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="9">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1473,55 +1410,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-18.2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O4" s="11">
         <v>87</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-29.7</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O4" s="6">
+      <c r="P4" s="12">
+        <v>87</v>
+      </c>
+      <c r="Q4" s="9">
         <v>0</v>
       </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
+      <c r="R4" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1529,55 +1466,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="L5" s="4">
-        <v>-50.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="O5" s="11">
+        <v>60</v>
+      </c>
+      <c r="P5" s="14">
+        <v>37</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>2</v>
+      </c>
+      <c r="R5" s="15">
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1585,55 +1522,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-61.4</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="O6" s="11">
+        <v>92</v>
+      </c>
+      <c r="P6" s="16">
+        <v>92</v>
+      </c>
+      <c r="Q6" s="8">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-50.7</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O6" s="11">
-        <v>50</v>
-      </c>
-      <c r="P6" s="12">
-        <v>50</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="R6" s="7">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1641,55 +1578,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>187</v>
+        <v>65</v>
       </c>
       <c r="L7" s="4">
-        <v>-29.8</v>
+        <v>-41.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="O7" s="11">
-        <v>51</v>
-      </c>
-      <c r="P7" s="12">
-        <v>51</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="P7" s="16">
+        <v>89</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>9</v>
       </c>
       <c r="R7" s="8">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1697,55 +1634,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="L8" s="4">
-        <v>-18.2</v>
+        <v>-53.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="O8" s="11">
-        <v>46</v>
-      </c>
-      <c r="P8" s="13">
-        <v>39</v>
-      </c>
-      <c r="Q8" s="8">
+        <v>100</v>
+      </c>
+      <c r="P8" s="18">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="9">
         <v>0</v>
       </c>
-      <c r="R8" s="8">
-        <v>1</v>
+      <c r="R8" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1753,55 +1690,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="L9" s="4">
-        <v>-39.4</v>
+        <v>-32.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="O9" s="11">
-        <v>57</v>
-      </c>
-      <c r="P9" s="12">
-        <v>52</v>
-      </c>
-      <c r="Q9" s="8">
+        <v>100</v>
+      </c>
+      <c r="P9" s="18">
+        <v>49</v>
+      </c>
+      <c r="Q9" s="9">
         <v>0</v>
       </c>
-      <c r="R9" s="8">
-        <v>1</v>
+      <c r="R9" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1809,55 +1746,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-16.4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O10" s="11">
+        <v>100</v>
+      </c>
+      <c r="P10" s="20">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="21">
         <v>59</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-61.4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O10" s="11">
-        <v>67</v>
-      </c>
-      <c r="P10" s="7">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="14">
-        <v>6</v>
-      </c>
-      <c r="R10" s="15">
-        <v>67</v>
+      <c r="R10" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1865,55 +1802,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L11" s="4">
-        <v>-41.7</v>
+        <v>-44.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="O11" s="11">
-        <v>91</v>
-      </c>
-      <c r="P11" s="16">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="P11" s="14">
+        <v>37</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>50</v>
       </c>
       <c r="R11" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1921,54 +1858,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-26.1</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="O12" s="11">
         <v>62</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-27.9</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O12" s="11">
-        <v>99</v>
-      </c>
-      <c r="P12" s="17">
-        <v>99</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>2</v>
-      </c>
-      <c r="R12" s="8">
+      <c r="P12" s="21">
+        <v>62</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1977,54 +1914,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-71.3</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="O13" s="11">
         <v>57</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-53.1</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O13" s="11">
-        <v>85</v>
-      </c>
-      <c r="P13" s="18">
-        <v>85</v>
-      </c>
-      <c r="Q13" s="8">
+      <c r="P13" s="22">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="9">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2033,54 +1970,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L14" s="4">
-        <v>-32.5</v>
+        <v>-55.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O14" s="11">
-        <v>80</v>
-      </c>
-      <c r="P14" s="19">
-        <v>80</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>1</v>
-      </c>
-      <c r="R14" s="8">
+        <v>172</v>
+      </c>
+      <c r="O14" s="6">
+        <v>40</v>
+      </c>
+      <c r="P14" s="14">
+        <v>37</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>3</v>
+      </c>
+      <c r="R14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2089,54 +2026,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-14.5</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O15" s="11">
         <v>79</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O15" s="11">
-        <v>94</v>
-      </c>
-      <c r="P15" s="20">
-        <v>94</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>3</v>
-      </c>
-      <c r="R15" s="8">
+      <c r="P15" s="23">
+        <v>77</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>2</v>
+      </c>
+      <c r="R15" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2145,55 +2082,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L16" s="4">
-        <v>-63.6</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="O16" s="11">
-        <v>53</v>
-      </c>
-      <c r="P16" s="12">
-        <v>50</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="P16" s="24">
+        <v>81</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1</v>
+      </c>
+      <c r="R16" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2201,55 +2138,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-65.90000000000001</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-44.2</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="N17" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O17" s="9">
-        <v>29</v>
-      </c>
-      <c r="P17" s="7">
-        <v>21</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="O17" s="11">
+        <v>94</v>
+      </c>
+      <c r="P17" s="12">
+        <v>84</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>1</v>
+      </c>
+      <c r="R17" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2257,54 +2194,54 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="L18" s="4">
-        <v>-26.1</v>
+        <v>-72.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O18" s="9">
-        <v>30</v>
-      </c>
-      <c r="P18" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
+        <v>172</v>
+      </c>
+      <c r="O18" s="11">
+        <v>95</v>
+      </c>
+      <c r="P18" s="24">
+        <v>81</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>87</v>
+      </c>
+      <c r="R18" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2313,54 +2250,54 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L19" s="4">
-        <v>-71.3</v>
+        <v>-58.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="O19" s="11">
-        <v>78</v>
-      </c>
-      <c r="P19" s="21">
+        <v>94</v>
+      </c>
+      <c r="P19" s="25">
+        <v>64</v>
+      </c>
+      <c r="Q19" s="23">
         <v>74</v>
       </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8">
+      <c r="R19" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2369,282 +2306,114 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="L20" s="4">
-        <v>-55.6</v>
+        <v>-12.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="O20" s="11">
-        <v>87</v>
-      </c>
-      <c r="P20" s="18">
-        <v>86</v>
-      </c>
-      <c r="Q20" s="8">
+        <v>95</v>
+      </c>
+      <c r="P20" s="20">
+        <v>95</v>
+      </c>
+      <c r="Q20" s="9">
         <v>0</v>
       </c>
-      <c r="R20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2">
-        <v>22</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-14.5</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O21" s="11">
-        <v>70</v>
-      </c>
-      <c r="P21" s="22">
-        <v>70</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="2">
-        <v>12</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-72.2</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O22" s="11">
-        <v>51</v>
-      </c>
-      <c r="P22" s="23">
-        <v>44</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
-      </c>
-      <c r="R22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="2">
-        <v>85</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-65.8</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O23" s="9">
-        <v>37</v>
-      </c>
-      <c r="P23" s="24">
-        <v>24</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0</v>
-      </c>
-      <c r="R23" s="8">
+      <c r="R20" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2663,12 +2432,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2685,22 +2454,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
   <si>
     <t>Datum</t>
   </si>
@@ -70,24 +70,15 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261018--01</t>
-  </si>
-  <si>
-    <t>20261018--02</t>
-  </si>
-  <si>
-    <t>20261018--03</t>
-  </si>
-  <si>
-    <t>20261018--04</t>
-  </si>
-  <si>
     <t>20261019--01</t>
   </si>
   <si>
     <t>20261019--02</t>
   </si>
   <si>
+    <t>20261019--03</t>
+  </si>
+  <si>
     <t>20261020--01</t>
   </si>
   <si>
@@ -103,6 +94,9 @@
     <t>20261021--02</t>
   </si>
   <si>
+    <t>20261021--03</t>
+  </si>
+  <si>
     <t>20261022--01</t>
   </si>
   <si>
@@ -127,67 +121,79 @@
     <t>20261024--03</t>
   </si>
   <si>
+    <t>20261025--01</t>
+  </si>
+  <si>
+    <t>20261025--02</t>
+  </si>
+  <si>
+    <t>20261025--03</t>
+  </si>
+  <si>
+    <t>03:42</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>01:24</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:03</t>
+  </si>
+  <si>
+    <t>03:41</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
     <t>05:15</t>
   </si>
   <si>
-    <t>05:49</t>
+    <t>02:26</t>
+  </si>
+  <si>
+    <t>06:27</t>
   </si>
   <si>
     <t>06:07</t>
   </si>
   <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>03:42</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>01:24</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>05:02</t>
-  </si>
-  <si>
-    <t>03:41</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>06:10</t>
+    <t>03:50</t>
   </si>
   <si>
     <t>05:14</t>
   </si>
   <si>
-    <t>02:26</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>03:49</t>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>03:38</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:46</t>
-  </si>
-  <si>
-    <t>04:31</t>
+    <t>01:16</t>
+  </si>
+  <si>
+    <t>04:30</t>
   </si>
   <si>
     <t>01:21</t>
@@ -196,22 +202,13 @@
     <t>04:59</t>
   </si>
   <si>
-    <t>03:13:27</t>
-  </si>
-  <si>
-    <t>04:50:19</t>
-  </si>
-  <si>
-    <t>19:47:59</t>
-  </si>
-  <si>
-    <t>21:25:25</t>
-  </si>
-  <si>
     <t>02:20:08</t>
   </si>
   <si>
-    <t>03:56:42</t>
+    <t>03:56:43</t>
+  </si>
+  <si>
+    <t>20:31:27</t>
   </si>
   <si>
     <t>03:03:08</t>
@@ -223,10 +220,13 @@
     <t>19:37:34</t>
   </si>
   <si>
+    <t>02:09:33</t>
+  </si>
+  <si>
     <t>03:46:36</t>
   </si>
   <si>
-    <t>20:21:38</t>
+    <t>20:21:37</t>
   </si>
   <si>
     <t>01:15:54</t>
@@ -238,31 +238,28 @@
     <t>19:27:14</t>
   </si>
   <si>
-    <t>00:22:12</t>
-  </si>
-  <si>
-    <t>01:58:39</t>
-  </si>
-  <si>
-    <t>01:04:43</t>
-  </si>
-  <si>
-    <t>02:42:01</t>
-  </si>
-  <si>
-    <t>19:16:55</t>
-  </si>
-  <si>
-    <t>03:15:50</t>
-  </si>
-  <si>
-    <t>04:52:32</t>
-  </si>
-  <si>
-    <t>19:50:07</t>
-  </si>
-  <si>
-    <t>21:27:56</t>
+    <t>00:22:11</t>
+  </si>
+  <si>
+    <t>01:58:38</t>
+  </si>
+  <si>
+    <t>01:04:41</t>
+  </si>
+  <si>
+    <t>02:42:00</t>
+  </si>
+  <si>
+    <t>19:16:53</t>
+  </si>
+  <si>
+    <t>00:10:43</t>
+  </si>
+  <si>
+    <t>01:47:32</t>
+  </si>
+  <si>
+    <t>23:16:41</t>
   </si>
   <si>
     <t>02:22:57</t>
@@ -271,16 +268,22 @@
     <t>03:58:48</t>
   </si>
   <si>
+    <t>20:33:41</t>
+  </si>
+  <si>
     <t>03:05:14</t>
   </si>
   <si>
     <t>04:44:22</t>
   </si>
   <si>
-    <t>19:39:39</t>
-  </si>
-  <si>
-    <t>03:49:00</t>
+    <t>19:39:40</t>
+  </si>
+  <si>
+    <t>02:11:47</t>
+  </si>
+  <si>
+    <t>03:48:59</t>
   </si>
   <si>
     <t>20:24:25</t>
@@ -289,37 +292,34 @@
     <t>01:18:27</t>
   </si>
   <si>
-    <t>02:54:44</t>
-  </si>
-  <si>
-    <t>19:29:36</t>
-  </si>
-  <si>
-    <t>00:25:26</t>
-  </si>
-  <si>
-    <t>02:00:44</t>
-  </si>
-  <si>
-    <t>01:06:52</t>
-  </si>
-  <si>
-    <t>02:44:44</t>
-  </si>
-  <si>
-    <t>19:20:08</t>
-  </si>
-  <si>
-    <t>03:18:27</t>
-  </si>
-  <si>
-    <t>04:55:26</t>
-  </si>
-  <si>
-    <t>19:53:10</t>
-  </si>
-  <si>
-    <t>21:30:15</t>
+    <t>02:54:43</t>
+  </si>
+  <si>
+    <t>19:29:35</t>
+  </si>
+  <si>
+    <t>00:25:25</t>
+  </si>
+  <si>
+    <t>02:00:43</t>
+  </si>
+  <si>
+    <t>01:06:51</t>
+  </si>
+  <si>
+    <t>02:44:42</t>
+  </si>
+  <si>
+    <t>19:20:06</t>
+  </si>
+  <si>
+    <t>00:13:05</t>
+  </si>
+  <si>
+    <t>01:49:46</t>
+  </si>
+  <si>
+    <t>23:19:30</t>
   </si>
   <si>
     <t>02:24:48</t>
@@ -328,6 +328,9 @@
     <t>04:02:01</t>
   </si>
   <si>
+    <t>20:36:33</t>
+  </si>
+  <si>
     <t>03:08:26</t>
   </si>
   <si>
@@ -337,46 +340,46 @@
     <t>19:42:49</t>
   </si>
   <si>
+    <t>02:14:40</t>
+  </si>
+  <si>
     <t>03:51:31</t>
   </si>
   <si>
     <t>20:26:15</t>
   </si>
   <si>
-    <t>01:20:45</t>
-  </si>
-  <si>
-    <t>02:57:49</t>
-  </si>
-  <si>
-    <t>19:32:13</t>
-  </si>
-  <si>
-    <t>00:26:39</t>
-  </si>
-  <si>
-    <t>02:03:57</t>
-  </si>
-  <si>
-    <t>01:09:56</t>
-  </si>
-  <si>
-    <t>02:46:38</t>
-  </si>
-  <si>
-    <t>19:21:21</t>
-  </si>
-  <si>
-    <t>03:21:05</t>
-  </si>
-  <si>
-    <t>04:58:21</t>
-  </si>
-  <si>
-    <t>19:56:14</t>
-  </si>
-  <si>
-    <t>21:32:33</t>
+    <t>01:20:44</t>
+  </si>
+  <si>
+    <t>02:57:48</t>
+  </si>
+  <si>
+    <t>19:32:12</t>
+  </si>
+  <si>
+    <t>00:26:38</t>
+  </si>
+  <si>
+    <t>02:03:56</t>
+  </si>
+  <si>
+    <t>01:09:54</t>
+  </si>
+  <si>
+    <t>02:46:37</t>
+  </si>
+  <si>
+    <t>19:21:19</t>
+  </si>
+  <si>
+    <t>00:15:42</t>
+  </si>
+  <si>
+    <t>01:52:38</t>
+  </si>
+  <si>
+    <t>23:21:19</t>
   </si>
   <si>
     <t>02:26:39</t>
@@ -385,6 +388,9 @@
     <t>04:05:14</t>
   </si>
   <si>
+    <t>20:39:26</t>
+  </si>
+  <si>
     <t>03:11:37</t>
   </si>
   <si>
@@ -394,13 +400,16 @@
     <t>19:46:00</t>
   </si>
   <si>
+    <t>02:17:34</t>
+  </si>
+  <si>
     <t>03:54:02</t>
   </si>
   <si>
     <t>20:28:06</t>
   </si>
   <si>
-    <t>01:23:03</t>
+    <t>01:23:02</t>
   </si>
   <si>
     <t>03:00:54</t>
@@ -409,31 +418,28 @@
     <t>19:34:50</t>
   </si>
   <si>
-    <t>00:27:52</t>
-  </si>
-  <si>
-    <t>02:07:11</t>
-  </si>
-  <si>
-    <t>01:13:00</t>
-  </si>
-  <si>
-    <t>02:48:33</t>
-  </si>
-  <si>
-    <t>19:22:34</t>
-  </si>
-  <si>
-    <t>03:23:28</t>
-  </si>
-  <si>
-    <t>05:00:34</t>
-  </si>
-  <si>
-    <t>19:58:22</t>
-  </si>
-  <si>
-    <t>21:35:05</t>
+    <t>00:27:51</t>
+  </si>
+  <si>
+    <t>02:07:10</t>
+  </si>
+  <si>
+    <t>01:12:58</t>
+  </si>
+  <si>
+    <t>02:48:32</t>
+  </si>
+  <si>
+    <t>19:22:32</t>
+  </si>
+  <si>
+    <t>00:18:19</t>
+  </si>
+  <si>
+    <t>01:55:29</t>
+  </si>
+  <si>
+    <t>23:23:08</t>
   </si>
   <si>
     <t>02:29:27</t>
@@ -442,6 +448,9 @@
     <t>04:07:19</t>
   </si>
   <si>
+    <t>20:41:40</t>
+  </si>
+  <si>
     <t>03:13:43</t>
   </si>
   <si>
@@ -451,16 +460,19 @@
     <t>19:48:06</t>
   </si>
   <si>
+    <t>02:19:48</t>
+  </si>
+  <si>
     <t>03:56:25</t>
   </si>
   <si>
-    <t>20:30:55</t>
+    <t>20:30:54</t>
   </si>
   <si>
     <t>01:25:35</t>
   </si>
   <si>
-    <t>03:03:02</t>
+    <t>03:03:01</t>
   </si>
   <si>
     <t>19:37:12</t>
@@ -469,25 +481,31 @@
     <t>00:31:05</t>
   </si>
   <si>
-    <t>02:09:16</t>
-  </si>
-  <si>
-    <t>01:15:09</t>
-  </si>
-  <si>
-    <t>02:51:16</t>
-  </si>
-  <si>
-    <t>19:25:48</t>
+    <t>02:09:15</t>
+  </si>
+  <si>
+    <t>01:15:07</t>
+  </si>
+  <si>
+    <t>02:51:14</t>
+  </si>
+  <si>
+    <t>19:25:46</t>
+  </si>
+  <si>
+    <t>00:20:41</t>
+  </si>
+  <si>
+    <t>01:57:42</t>
+  </si>
+  <si>
+    <t>23:25:57</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>41°</t>
+    <t>19°</t>
   </si>
   <si>
     <t>30°</t>
@@ -502,13 +520,7 @@
     <t>5°</t>
   </si>
   <si>
-    <t>05:00:10</t>
-  </si>
-  <si>
-    <t>19:52:53</t>
-  </si>
-  <si>
-    <t>21:25:31</t>
+    <t>20:34:57</t>
   </si>
   <si>
     <t>19:44:10</t>
@@ -517,10 +529,10 @@
     <t>20:25:46</t>
   </si>
   <si>
-    <t>19:34:35</t>
-  </si>
-  <si>
-    <t>19:24:13</t>
+    <t>19:34:34</t>
+  </si>
+  <si>
+    <t>19:24:11</t>
   </si>
   <si>
     <t>B</t>
@@ -532,13 +544,13 @@
     <t>A</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -572,7 +584,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -587,7 +599,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,7 +623,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,91 +695,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,7 +742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,12 +811,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1220,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1298,55 +1292,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L2" s="4">
-        <v>-50.7</v>
+        <v>-61.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O2" s="6">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="P2" s="7">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="Q2" s="8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R2" s="9">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1354,55 +1348,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="L3" s="4">
-        <v>-29.8</v>
+        <v>-41.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="O3" s="6">
-        <v>39</v>
-      </c>
-      <c r="P3" s="10">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="P3" s="7">
+        <v>95</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>10</v>
+      </c>
+      <c r="R3" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1410,55 +1404,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="L4" s="4">
-        <v>-18.2</v>
+        <v>-27.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O4" s="11">
-        <v>87</v>
+        <v>178</v>
+      </c>
+      <c r="O4" s="6">
+        <v>97</v>
       </c>
       <c r="P4" s="12">
-        <v>87</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>6</v>
       </c>
       <c r="R4" s="13">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1466,55 +1460,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>164</v>
+        <v>65</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.4</v>
+        <v>-53.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O5" s="11">
-        <v>60</v>
+        <v>177</v>
+      </c>
+      <c r="O5" s="6">
+        <v>97</v>
       </c>
       <c r="P5" s="14">
-        <v>37</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>2</v>
-      </c>
-      <c r="R5" s="15">
-        <v>32</v>
+        <v>49</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>1</v>
+      </c>
+      <c r="R5" s="7">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1522,55 +1516,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L6" s="4">
-        <v>-61.4</v>
+        <v>-32.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O6" s="11">
-        <v>92</v>
+        <v>176</v>
+      </c>
+      <c r="O6" s="6">
+        <v>100</v>
       </c>
       <c r="P6" s="16">
-        <v>92</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>22</v>
-      </c>
-      <c r="R6" s="7">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>1</v>
+      </c>
+      <c r="R6" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1578,55 +1572,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="L7" s="4">
-        <v>-41.7</v>
+        <v>-16.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O7" s="11">
-        <v>89</v>
-      </c>
-      <c r="P7" s="16">
-        <v>89</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>9</v>
-      </c>
-      <c r="R7" s="8">
-        <v>19</v>
+        <v>178</v>
+      </c>
+      <c r="O7" s="6">
+        <v>100</v>
+      </c>
+      <c r="P7" s="13">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>23</v>
+      </c>
+      <c r="R7" s="17">
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1634,55 +1628,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L8" s="4">
-        <v>-53.1</v>
+        <v>-63.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O8" s="11">
-        <v>100</v>
-      </c>
-      <c r="P8" s="18">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="9">
+        <v>177</v>
+      </c>
+      <c r="O8" s="6">
+        <v>99</v>
+      </c>
+      <c r="P8" s="15">
         <v>0</v>
       </c>
-      <c r="R8" s="19">
-        <v>100</v>
+      <c r="Q8" s="19">
+        <v>64</v>
+      </c>
+      <c r="R8" s="14">
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1690,54 +1684,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L9" s="4">
-        <v>-32.5</v>
+        <v>-44.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O9" s="11">
+        <v>177</v>
+      </c>
+      <c r="O9" s="6">
         <v>100</v>
       </c>
-      <c r="P9" s="18">
-        <v>49</v>
-      </c>
-      <c r="Q9" s="9">
+      <c r="P9" s="15">
         <v>0</v>
       </c>
-      <c r="R9" s="19">
+      <c r="Q9" s="20">
+        <v>92</v>
+      </c>
+      <c r="R9" s="17">
         <v>100</v>
       </c>
     </row>
@@ -1746,55 +1740,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L10" s="4">
-        <v>-16.4</v>
+        <v>-26.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O10" s="11">
-        <v>100</v>
-      </c>
-      <c r="P10" s="20">
-        <v>94</v>
+        <v>176</v>
+      </c>
+      <c r="O10" s="6">
+        <v>95</v>
+      </c>
+      <c r="P10" s="8">
+        <v>13</v>
       </c>
       <c r="Q10" s="21">
-        <v>59</v>
-      </c>
-      <c r="R10" s="19">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="R10" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1802,55 +1796,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L11" s="4">
-        <v>-44.2</v>
+        <v>-71.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O11" s="11">
-        <v>88</v>
-      </c>
-      <c r="P11" s="14">
-        <v>37</v>
+        <v>177</v>
+      </c>
+      <c r="O11" s="6">
+        <v>81</v>
+      </c>
+      <c r="P11" s="12">
+        <v>81</v>
       </c>
       <c r="Q11" s="18">
-        <v>50</v>
-      </c>
-      <c r="R11" s="8">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1858,54 +1852,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="L12" s="4">
-        <v>-26.1</v>
+        <v>-55.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O12" s="11">
-        <v>62</v>
-      </c>
-      <c r="P12" s="21">
-        <v>62</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
+        <v>177</v>
+      </c>
+      <c r="O12" s="6">
+        <v>68</v>
+      </c>
+      <c r="P12" s="13">
+        <v>68</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>17</v>
+      </c>
+      <c r="R12" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1914,54 +1908,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="L13" s="4">
-        <v>-71.3</v>
+        <v>-14.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O13" s="11">
-        <v>57</v>
-      </c>
-      <c r="P13" s="22">
-        <v>56</v>
-      </c>
-      <c r="Q13" s="9">
+        <v>178</v>
+      </c>
+      <c r="O13" s="6">
+        <v>65</v>
+      </c>
+      <c r="P13" s="19">
+        <v>65</v>
+      </c>
+      <c r="Q13" s="15">
         <v>0</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1970,54 +1964,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L14" s="4">
-        <v>-55.6</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O14" s="6">
-        <v>40</v>
-      </c>
-      <c r="P14" s="14">
-        <v>37</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>3</v>
-      </c>
-      <c r="R14" s="9">
+        <v>58</v>
+      </c>
+      <c r="P14" s="22">
+        <v>58</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>0</v>
+      </c>
+      <c r="R14" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2026,54 +2020,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="L15" s="4">
-        <v>-14.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O15" s="11">
-        <v>79</v>
-      </c>
-      <c r="P15" s="23">
-        <v>77</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>2</v>
-      </c>
-      <c r="R15" s="9">
+        <v>177</v>
+      </c>
+      <c r="O15" s="23">
+        <v>12</v>
+      </c>
+      <c r="P15" s="10">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="15">
+        <v>0</v>
+      </c>
+      <c r="R15" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2082,55 +2076,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L16" s="4">
-        <v>-72.09999999999999</v>
+        <v>-72.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O16" s="11">
-        <v>86</v>
-      </c>
-      <c r="P16" s="24">
-        <v>81</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>1</v>
-      </c>
-      <c r="R16" s="17">
-        <v>8</v>
+        <v>177</v>
+      </c>
+      <c r="O16" s="6">
+        <v>97</v>
+      </c>
+      <c r="P16" s="7">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>0</v>
+      </c>
+      <c r="R16" s="22">
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2138,55 +2132,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L17" s="4">
-        <v>-65.90000000000001</v>
+        <v>-58.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O17" s="11">
-        <v>94</v>
-      </c>
-      <c r="P17" s="12">
-        <v>84</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>1</v>
-      </c>
-      <c r="R17" s="17">
-        <v>8</v>
+        <v>177</v>
+      </c>
+      <c r="O17" s="6">
+        <v>98</v>
+      </c>
+      <c r="P17" s="7">
+        <v>97</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16">
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2194,55 +2188,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="L18" s="4">
-        <v>-72.8</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O18" s="11">
-        <v>95</v>
-      </c>
-      <c r="P18" s="24">
-        <v>81</v>
-      </c>
-      <c r="Q18" s="12">
-        <v>87</v>
-      </c>
-      <c r="R18" s="9">
+        <v>176</v>
+      </c>
+      <c r="O18" s="6">
+        <v>80</v>
+      </c>
+      <c r="P18" s="12">
+        <v>79</v>
+      </c>
+      <c r="Q18" s="15">
         <v>0</v>
+      </c>
+      <c r="R18" s="14">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2250,55 +2244,43 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L19" s="4">
-        <v>-58.2</v>
+        <v>-71.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O19" s="11">
-        <v>94</v>
-      </c>
-      <c r="P19" s="25">
-        <v>64</v>
-      </c>
-      <c r="Q19" s="23">
-        <v>74</v>
-      </c>
-      <c r="R19" s="9">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2306,114 +2288,146 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-68.2</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
+        <v>14</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-12.5</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O20" s="11">
-        <v>95</v>
-      </c>
-      <c r="P20" s="20">
-        <v>95</v>
-      </c>
-      <c r="Q20" s="9">
-        <v>0</v>
-      </c>
-      <c r="R20" s="9">
-        <v>0</v>
+      <c r="J21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-63.9</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2432,12 +2446,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2454,22 +2468,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="162">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261019--01</t>
-  </si>
-  <si>
-    <t>20261019--02</t>
-  </si>
-  <si>
-    <t>20261019--03</t>
-  </si>
-  <si>
     <t>20261020--01</t>
   </si>
   <si>
@@ -130,384 +121,345 @@
     <t>20261025--03</t>
   </si>
   <si>
-    <t>03:42</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>05:45</t>
+    <t>20261026--01</t>
   </si>
   <si>
     <t>06:23</t>
   </si>
   <si>
-    <t>01:24</t>
+    <t>01:22</t>
   </si>
   <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:03</t>
-  </si>
-  <si>
-    <t>03:41</t>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>05:02</t>
+  </si>
+  <si>
+    <t>03:40</t>
   </si>
   <si>
     <t>04:35</t>
   </si>
   <si>
-    <t>06:11</t>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>02:27</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>03:48</t>
+  </si>
+  <si>
+    <t>02:23</t>
   </si>
   <si>
     <t>05:15</t>
   </si>
   <si>
-    <t>02:26</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>06:07</t>
-  </si>
-  <si>
-    <t>03:50</t>
-  </si>
-  <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>03:38</t>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>06:22</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:16</t>
-  </si>
-  <si>
     <t>04:30</t>
   </si>
   <si>
-    <t>01:21</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>02:20:08</t>
-  </si>
-  <si>
-    <t>03:56:43</t>
-  </si>
-  <si>
-    <t>20:31:27</t>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>03:03:10</t>
+  </si>
+  <si>
+    <t>04:40:49</t>
+  </si>
+  <si>
+    <t>19:37:37</t>
+  </si>
+  <si>
+    <t>02:09:37</t>
+  </si>
+  <si>
+    <t>03:46:40</t>
+  </si>
+  <si>
+    <t>20:21:44</t>
+  </si>
+  <si>
+    <t>01:16:01</t>
+  </si>
+  <si>
+    <t>02:52:42</t>
+  </si>
+  <si>
+    <t>19:27:24</t>
+  </si>
+  <si>
+    <t>00:22:21</t>
+  </si>
+  <si>
+    <t>01:58:49</t>
+  </si>
+  <si>
+    <t>01:04:57</t>
+  </si>
+  <si>
+    <t>02:42:15</t>
+  </si>
+  <si>
+    <t>19:17:12</t>
+  </si>
+  <si>
+    <t>00:11:03</t>
+  </si>
+  <si>
+    <t>01:47:53</t>
+  </si>
+  <si>
+    <t>23:17:06</t>
+  </si>
+  <si>
+    <t>00:53:38</t>
+  </si>
+  <si>
+    <t>03:05:16</t>
+  </si>
+  <si>
+    <t>04:44:25</t>
+  </si>
+  <si>
+    <t>19:39:43</t>
+  </si>
+  <si>
+    <t>02:11:51</t>
+  </si>
+  <si>
+    <t>03:49:04</t>
+  </si>
+  <si>
+    <t>20:24:32</t>
+  </si>
+  <si>
+    <t>01:18:34</t>
+  </si>
+  <si>
+    <t>02:54:50</t>
+  </si>
+  <si>
+    <t>19:29:45</t>
+  </si>
+  <si>
+    <t>00:25:35</t>
+  </si>
+  <si>
+    <t>02:00:54</t>
+  </si>
+  <si>
+    <t>01:07:06</t>
+  </si>
+  <si>
+    <t>02:44:58</t>
+  </si>
+  <si>
+    <t>19:20:27</t>
+  </si>
+  <si>
+    <t>00:13:25</t>
+  </si>
+  <si>
+    <t>01:50:07</t>
+  </si>
+  <si>
+    <t>23:19:55</t>
+  </si>
+  <si>
+    <t>00:55:44</t>
+  </si>
+  <si>
+    <t>03:08:28</t>
+  </si>
+  <si>
+    <t>04:45:06</t>
+  </si>
+  <si>
+    <t>19:42:53</t>
+  </si>
+  <si>
+    <t>02:14:44</t>
+  </si>
+  <si>
+    <t>03:51:35</t>
+  </si>
+  <si>
+    <t>20:26:21</t>
+  </si>
+  <si>
+    <t>01:20:51</t>
+  </si>
+  <si>
+    <t>02:57:55</t>
+  </si>
+  <si>
+    <t>19:32:22</t>
+  </si>
+  <si>
+    <t>00:26:48</t>
+  </si>
+  <si>
+    <t>02:04:07</t>
+  </si>
+  <si>
+    <t>01:10:09</t>
+  </si>
+  <si>
+    <t>02:46:52</t>
+  </si>
+  <si>
+    <t>19:21:38</t>
+  </si>
+  <si>
+    <t>00:16:03</t>
+  </si>
+  <si>
+    <t>01:52:58</t>
+  </si>
+  <si>
+    <t>23:21:45</t>
+  </si>
+  <si>
+    <t>00:58:55</t>
+  </si>
+  <si>
+    <t>03:11:39</t>
+  </si>
+  <si>
+    <t>04:45:47</t>
+  </si>
+  <si>
+    <t>19:46:03</t>
+  </si>
+  <si>
+    <t>02:17:37</t>
+  </si>
+  <si>
+    <t>03:54:06</t>
+  </si>
+  <si>
+    <t>20:28:12</t>
+  </si>
+  <si>
+    <t>01:23:09</t>
+  </si>
+  <si>
+    <t>03:01:00</t>
+  </si>
+  <si>
+    <t>19:34:59</t>
+  </si>
+  <si>
+    <t>00:28:02</t>
+  </si>
+  <si>
+    <t>02:07:21</t>
+  </si>
+  <si>
+    <t>01:13:13</t>
+  </si>
+  <si>
+    <t>02:48:46</t>
+  </si>
+  <si>
+    <t>19:22:50</t>
+  </si>
+  <si>
+    <t>00:18:40</t>
+  </si>
+  <si>
+    <t>01:55:49</t>
+  </si>
+  <si>
+    <t>23:23:35</t>
+  </si>
+  <si>
+    <t>01:02:06</t>
+  </si>
+  <si>
+    <t>03:13:45</t>
+  </si>
+  <si>
+    <t>04:49:23</t>
+  </si>
+  <si>
+    <t>19:48:09</t>
+  </si>
+  <si>
+    <t>02:19:52</t>
+  </si>
+  <si>
+    <t>03:56:29</t>
+  </si>
+  <si>
+    <t>20:31:00</t>
+  </si>
+  <si>
+    <t>01:25:41</t>
   </si>
   <si>
     <t>03:03:08</t>
   </si>
   <si>
-    <t>04:40:47</t>
-  </si>
-  <si>
-    <t>19:37:34</t>
-  </si>
-  <si>
-    <t>02:09:33</t>
-  </si>
-  <si>
-    <t>03:46:36</t>
-  </si>
-  <si>
-    <t>20:21:37</t>
-  </si>
-  <si>
-    <t>01:15:54</t>
-  </si>
-  <si>
-    <t>02:52:35</t>
-  </si>
-  <si>
-    <t>19:27:14</t>
-  </si>
-  <si>
-    <t>00:22:11</t>
-  </si>
-  <si>
-    <t>01:58:38</t>
-  </si>
-  <si>
-    <t>01:04:41</t>
-  </si>
-  <si>
-    <t>02:42:00</t>
-  </si>
-  <si>
-    <t>19:16:53</t>
-  </si>
-  <si>
-    <t>00:10:43</t>
-  </si>
-  <si>
-    <t>01:47:32</t>
-  </si>
-  <si>
-    <t>23:16:41</t>
-  </si>
-  <si>
-    <t>02:22:57</t>
-  </si>
-  <si>
-    <t>03:58:48</t>
-  </si>
-  <si>
-    <t>20:33:41</t>
-  </si>
-  <si>
-    <t>03:05:14</t>
-  </si>
-  <si>
-    <t>04:44:22</t>
-  </si>
-  <si>
-    <t>19:39:40</t>
-  </si>
-  <si>
-    <t>02:11:47</t>
-  </si>
-  <si>
-    <t>03:48:59</t>
-  </si>
-  <si>
-    <t>20:24:25</t>
-  </si>
-  <si>
-    <t>01:18:27</t>
-  </si>
-  <si>
-    <t>02:54:43</t>
-  </si>
-  <si>
-    <t>19:29:35</t>
-  </si>
-  <si>
-    <t>00:25:25</t>
-  </si>
-  <si>
-    <t>02:00:43</t>
-  </si>
-  <si>
-    <t>01:06:51</t>
-  </si>
-  <si>
-    <t>02:44:42</t>
-  </si>
-  <si>
-    <t>19:20:06</t>
-  </si>
-  <si>
-    <t>00:13:05</t>
-  </si>
-  <si>
-    <t>01:49:46</t>
-  </si>
-  <si>
-    <t>23:19:30</t>
-  </si>
-  <si>
-    <t>02:24:48</t>
-  </si>
-  <si>
-    <t>04:02:01</t>
-  </si>
-  <si>
-    <t>20:36:33</t>
-  </si>
-  <si>
-    <t>03:08:26</t>
-  </si>
-  <si>
-    <t>04:45:04</t>
-  </si>
-  <si>
-    <t>19:42:49</t>
-  </si>
-  <si>
-    <t>02:14:40</t>
-  </si>
-  <si>
-    <t>03:51:31</t>
-  </si>
-  <si>
-    <t>20:26:15</t>
-  </si>
-  <si>
-    <t>01:20:44</t>
-  </si>
-  <si>
-    <t>02:57:48</t>
-  </si>
-  <si>
-    <t>19:32:12</t>
-  </si>
-  <si>
-    <t>00:26:38</t>
-  </si>
-  <si>
-    <t>02:03:56</t>
-  </si>
-  <si>
-    <t>01:09:54</t>
-  </si>
-  <si>
-    <t>02:46:37</t>
-  </si>
-  <si>
-    <t>19:21:19</t>
-  </si>
-  <si>
-    <t>00:15:42</t>
-  </si>
-  <si>
-    <t>01:52:38</t>
-  </si>
-  <si>
-    <t>23:21:19</t>
-  </si>
-  <si>
-    <t>02:26:39</t>
-  </si>
-  <si>
-    <t>04:05:14</t>
-  </si>
-  <si>
-    <t>20:39:26</t>
-  </si>
-  <si>
-    <t>03:11:37</t>
-  </si>
-  <si>
-    <t>04:45:46</t>
-  </si>
-  <si>
-    <t>19:46:00</t>
-  </si>
-  <si>
-    <t>02:17:34</t>
-  </si>
-  <si>
-    <t>03:54:02</t>
-  </si>
-  <si>
-    <t>20:28:06</t>
-  </si>
-  <si>
-    <t>01:23:02</t>
-  </si>
-  <si>
-    <t>03:00:54</t>
-  </si>
-  <si>
-    <t>19:34:50</t>
-  </si>
-  <si>
-    <t>00:27:51</t>
-  </si>
-  <si>
-    <t>02:07:10</t>
-  </si>
-  <si>
-    <t>01:12:58</t>
-  </si>
-  <si>
-    <t>02:48:32</t>
-  </si>
-  <si>
-    <t>19:22:32</t>
-  </si>
-  <si>
-    <t>00:18:19</t>
-  </si>
-  <si>
-    <t>01:55:29</t>
-  </si>
-  <si>
-    <t>23:23:08</t>
-  </si>
-  <si>
-    <t>02:29:27</t>
-  </si>
-  <si>
-    <t>04:07:19</t>
-  </si>
-  <si>
-    <t>20:41:40</t>
-  </si>
-  <si>
-    <t>03:13:43</t>
-  </si>
-  <si>
-    <t>04:49:21</t>
-  </si>
-  <si>
-    <t>19:48:06</t>
-  </si>
-  <si>
-    <t>02:19:48</t>
-  </si>
-  <si>
-    <t>03:56:25</t>
-  </si>
-  <si>
-    <t>20:30:54</t>
-  </si>
-  <si>
-    <t>01:25:35</t>
-  </si>
-  <si>
-    <t>03:03:01</t>
-  </si>
-  <si>
-    <t>19:37:12</t>
-  </si>
-  <si>
-    <t>00:31:05</t>
-  </si>
-  <si>
-    <t>02:09:15</t>
-  </si>
-  <si>
-    <t>01:15:07</t>
-  </si>
-  <si>
-    <t>02:51:14</t>
-  </si>
-  <si>
-    <t>19:25:46</t>
-  </si>
-  <si>
-    <t>00:20:41</t>
-  </si>
-  <si>
-    <t>01:57:42</t>
-  </si>
-  <si>
-    <t>23:25:57</t>
+    <t>19:37:21</t>
+  </si>
+  <si>
+    <t>00:31:15</t>
+  </si>
+  <si>
+    <t>02:09:25</t>
+  </si>
+  <si>
+    <t>01:15:22</t>
+  </si>
+  <si>
+    <t>02:51:29</t>
+  </si>
+  <si>
+    <t>19:26:05</t>
+  </si>
+  <si>
+    <t>00:21:01</t>
+  </si>
+  <si>
+    <t>01:58:02</t>
+  </si>
+  <si>
+    <t>23:26:23</t>
+  </si>
+  <si>
+    <t>01:04:11</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>19°</t>
-  </si>
-  <si>
     <t>30°</t>
   </si>
   <si>
@@ -520,19 +472,16 @@
     <t>5°</t>
   </si>
   <si>
-    <t>20:34:57</t>
-  </si>
-  <si>
-    <t>19:44:10</t>
-  </si>
-  <si>
-    <t>20:25:46</t>
-  </si>
-  <si>
-    <t>19:34:34</t>
-  </si>
-  <si>
-    <t>19:24:11</t>
+    <t>19:44:13</t>
+  </si>
+  <si>
+    <t>20:25:52</t>
+  </si>
+  <si>
+    <t>19:34:43</t>
+  </si>
+  <si>
+    <t>19:24:29</t>
   </si>
   <si>
     <t>B</t>
@@ -544,10 +493,10 @@
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>2</t>
@@ -584,7 +533,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -605,7 +554,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,85 +632,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -808,9 +751,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1214,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1292,55 +1232,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L2" s="4">
-        <v>-61.4</v>
+        <v>-53.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="O2" s="6">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="Q2" s="8">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="R2" s="9">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1348,55 +1288,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L3" s="4">
-        <v>-41.7</v>
+        <v>-32.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="O3" s="6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P3" s="7">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="Q3" s="10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R3" s="11">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1404,55 +1344,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="L4" s="4">
-        <v>-27.9</v>
+        <v>-16.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="O4" s="6">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P4" s="12">
-        <v>82</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>6</v>
-      </c>
-      <c r="R4" s="13">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>44</v>
+      </c>
+      <c r="R4" s="14">
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1460,55 +1400,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L5" s="4">
-        <v>-53.1</v>
+        <v>-63.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="O5" s="6">
-        <v>97</v>
-      </c>
-      <c r="P5" s="14">
-        <v>49</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>1</v>
-      </c>
-      <c r="R5" s="7">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="P5" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>25</v>
+      </c>
+      <c r="R5" s="11">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1516,54 +1456,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L6" s="4">
-        <v>-32.5</v>
+        <v>-44.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="O6" s="6">
         <v>100</v>
       </c>
       <c r="P6" s="16">
-        <v>32</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>1</v>
-      </c>
-      <c r="R6" s="17">
+        <v>8</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>56</v>
+      </c>
+      <c r="R6" s="11">
         <v>100</v>
       </c>
     </row>
@@ -1572,55 +1512,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="L7" s="4">
-        <v>-16.4</v>
+        <v>-26.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="13">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>23</v>
-      </c>
-      <c r="R7" s="17">
-        <v>99</v>
+        <v>96</v>
+      </c>
+      <c r="P7" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>0</v>
+      </c>
+      <c r="R7" s="16">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1628,55 +1568,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L8" s="4">
-        <v>-63.6</v>
+        <v>-71.3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="O8" s="6">
-        <v>99</v>
-      </c>
-      <c r="P8" s="15">
+        <v>85</v>
+      </c>
+      <c r="P8" s="18">
+        <v>61</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>11</v>
+      </c>
+      <c r="R8" s="15">
         <v>0</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>64</v>
-      </c>
-      <c r="R8" s="14">
-        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1684,55 +1624,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-55.6</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O9" s="6">
+        <v>72</v>
+      </c>
+      <c r="P9" s="13">
         <v>45</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-44.2</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O9" s="6">
-        <v>100</v>
-      </c>
-      <c r="P9" s="15">
+      <c r="Q9" s="19">
+        <v>13</v>
+      </c>
+      <c r="R9" s="15">
         <v>0</v>
-      </c>
-      <c r="Q9" s="20">
-        <v>92</v>
-      </c>
-      <c r="R9" s="17">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1740,52 +1680,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="L10" s="4">
-        <v>-26.1</v>
+        <v>-14.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="O10" s="6">
-        <v>95</v>
-      </c>
-      <c r="P10" s="8">
-        <v>13</v>
-      </c>
-      <c r="Q10" s="21">
-        <v>40</v>
+        <v>72</v>
+      </c>
+      <c r="P10" s="7">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>1</v>
       </c>
       <c r="R10" s="15">
         <v>0</v>
@@ -1796,52 +1736,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L11" s="4">
-        <v>-71.3</v>
+        <v>-72.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="O11" s="6">
-        <v>81</v>
-      </c>
-      <c r="P11" s="12">
-        <v>81</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>23</v>
+        <v>70</v>
+      </c>
+      <c r="P11" s="7">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>0</v>
       </c>
       <c r="R11" s="15">
         <v>0</v>
@@ -1852,52 +1792,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L12" s="4">
-        <v>-55.6</v>
+        <v>-65.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="O12" s="6">
-        <v>68</v>
-      </c>
-      <c r="P12" s="13">
-        <v>68</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>17</v>
+        <v>65</v>
+      </c>
+      <c r="P12" s="14">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>0</v>
       </c>
       <c r="R12" s="15">
         <v>0</v>
@@ -1908,49 +1848,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="L13" s="4">
-        <v>-14.5</v>
+        <v>-72.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="O13" s="6">
-        <v>65</v>
-      </c>
-      <c r="P13" s="19">
-        <v>65</v>
+        <v>95</v>
+      </c>
+      <c r="P13" s="20">
+        <v>95</v>
       </c>
       <c r="Q13" s="15">
         <v>0</v>
@@ -1964,49 +1904,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L14" s="4">
-        <v>-72.09999999999999</v>
+        <v>-58.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="O14" s="6">
-        <v>58</v>
-      </c>
-      <c r="P14" s="22">
-        <v>58</v>
+        <v>95</v>
+      </c>
+      <c r="P14" s="20">
+        <v>95</v>
       </c>
       <c r="Q14" s="15">
         <v>0</v>
@@ -2020,49 +1960,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="L15" s="4">
-        <v>-65.90000000000001</v>
+        <v>-12.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O15" s="23">
-        <v>12</v>
-      </c>
-      <c r="P15" s="10">
-        <v>12</v>
+        <v>160</v>
+      </c>
+      <c r="O15" s="6">
+        <v>67</v>
+      </c>
+      <c r="P15" s="14">
+        <v>67</v>
       </c>
       <c r="Q15" s="15">
         <v>0</v>
@@ -2076,55 +2016,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G16